--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
   <si>
     <t>League</t>
   </si>
@@ -254,6 +254,24 @@
   </si>
   <si>
     <t>SnapshotTS</t>
+  </si>
+  <si>
+    <t>Colombian Primera B</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>01:10:00</t>
+  </si>
+  <si>
+    <t>Real Cartagena</t>
+  </si>
+  <si>
+    <t>Independiente Yumbo</t>
+  </si>
+  <si>
+    <t>2026-08-05 01:57:35</t>
   </si>
 </sst>
 </file>
@@ -585,7 +603,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB1"/>
+  <dimension ref="A1:CB2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -830,6 +848,248 @@
         <v>79</v>
       </c>
     </row>
+    <row r="2" spans="1:80">
+      <c r="A2" t="s">
+        <v>80</v>
+      </c>
+      <c r="B2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F2">
+        <v>1.6</v>
+      </c>
+      <c r="G2">
+        <v>1.73</v>
+      </c>
+      <c r="H2">
+        <v>5.9</v>
+      </c>
+      <c r="I2">
+        <v>7.6</v>
+      </c>
+      <c r="J2">
+        <v>3.4</v>
+      </c>
+      <c r="K2">
+        <v>4.2</v>
+      </c>
+      <c r="L2">
+        <v>1.01</v>
+      </c>
+      <c r="M2">
+        <v>1.08</v>
+      </c>
+      <c r="N2">
+        <v>2.9</v>
+      </c>
+      <c r="O2">
+        <v>1.37</v>
+      </c>
+      <c r="P2">
+        <v>1.71</v>
+      </c>
+      <c r="Q2">
+        <v>2.1</v>
+      </c>
+      <c r="R2">
+        <v>1.27</v>
+      </c>
+      <c r="S2">
+        <v>3.4</v>
+      </c>
+      <c r="T2">
+        <v>2.08</v>
+      </c>
+      <c r="U2">
+        <v>1.75</v>
+      </c>
+      <c r="V2">
+        <v>1.15</v>
+      </c>
+      <c r="W2">
+        <v>2.36</v>
+      </c>
+      <c r="X2">
+        <v>14.5</v>
+      </c>
+      <c r="Y2">
+        <v>23</v>
+      </c>
+      <c r="Z2">
+        <v>70</v>
+      </c>
+      <c r="AA2">
+        <v>280</v>
+      </c>
+      <c r="AB2">
+        <v>7.2</v>
+      </c>
+      <c r="AC2">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD2">
+        <v>28</v>
+      </c>
+      <c r="AE2">
+        <v>150</v>
+      </c>
+      <c r="AF2">
+        <v>9.4</v>
+      </c>
+      <c r="AG2">
+        <v>12.5</v>
+      </c>
+      <c r="AH2">
+        <v>27</v>
+      </c>
+      <c r="AI2">
+        <v>150</v>
+      </c>
+      <c r="AJ2">
+        <v>17</v>
+      </c>
+      <c r="AK2">
+        <v>25</v>
+      </c>
+      <c r="AL2">
+        <v>60</v>
+      </c>
+      <c r="AM2">
+        <v>220</v>
+      </c>
+      <c r="AN2">
+        <v>15.5</v>
+      </c>
+      <c r="AO2">
+        <v>240</v>
+      </c>
+      <c r="AP2">
+        <v>4.3</v>
+      </c>
+      <c r="AQ2">
+        <v>4.8</v>
+      </c>
+      <c r="AR2">
+        <v>5.7</v>
+      </c>
+      <c r="AS2">
+        <v>6</v>
+      </c>
+      <c r="AT2">
+        <v>3.3</v>
+      </c>
+      <c r="AU2">
+        <v>3.7</v>
+      </c>
+      <c r="AV2">
+        <v>5</v>
+      </c>
+      <c r="AW2">
+        <v>5.9</v>
+      </c>
+      <c r="AX2">
+        <v>3.7</v>
+      </c>
+      <c r="AY2">
+        <v>4.1</v>
+      </c>
+      <c r="AZ2">
+        <v>5</v>
+      </c>
+      <c r="BA2">
+        <v>5.9</v>
+      </c>
+      <c r="BB2">
+        <v>4.5</v>
+      </c>
+      <c r="BC2">
+        <v>4.9</v>
+      </c>
+      <c r="BD2">
+        <v>5.6</v>
+      </c>
+      <c r="BE2">
+        <v>6</v>
+      </c>
+      <c r="BF2">
+        <v>4.4</v>
+      </c>
+      <c r="BG2">
+        <v>6</v>
+      </c>
+      <c r="BH2">
+        <v>1000</v>
+      </c>
+      <c r="BI2">
+        <v>1.01</v>
+      </c>
+      <c r="BJ2">
+        <v>1000</v>
+      </c>
+      <c r="BK2">
+        <v>1.01</v>
+      </c>
+      <c r="BL2">
+        <v>1000</v>
+      </c>
+      <c r="BM2">
+        <v>1.01</v>
+      </c>
+      <c r="BN2">
+        <v>1000</v>
+      </c>
+      <c r="BO2">
+        <v>1.01</v>
+      </c>
+      <c r="BP2">
+        <v>1000</v>
+      </c>
+      <c r="BQ2">
+        <v>1.01</v>
+      </c>
+      <c r="BR2">
+        <v>1000</v>
+      </c>
+      <c r="BS2">
+        <v>1.01</v>
+      </c>
+      <c r="BT2">
+        <v>1000</v>
+      </c>
+      <c r="BU2">
+        <v>1.01</v>
+      </c>
+      <c r="BV2">
+        <v>1000</v>
+      </c>
+      <c r="BW2">
+        <v>1.01</v>
+      </c>
+      <c r="BX2">
+        <v>1000</v>
+      </c>
+      <c r="BY2">
+        <v>1.01</v>
+      </c>
+      <c r="BZ2">
+        <v>0</v>
+      </c>
+      <c r="CA2">
+        <v>0</v>
+      </c>
+      <c r="CB2" t="s">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -271,7 +271,7 @@
     <t>Independiente Yumbo</t>
   </si>
   <si>
-    <t>2026-08-05 01:57:35</t>
+    <t>2026-08-05 04:04:30</t>
   </si>
 </sst>
 </file>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -271,7 +271,7 @@
     <t>Independiente Yumbo</t>
   </si>
   <si>
-    <t>2026-08-05 04:04:30</t>
+    <t>2026-08-05 06:11:50</t>
   </si>
 </sst>
 </file>
@@ -871,7 +871,7 @@
         <v>1.73</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>5.4</v>
       </c>
       <c r="I2">
         <v>7.6</v>
@@ -880,16 +880,16 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L2">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M2">
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="O2">
         <v>1.37</v>
@@ -898,13 +898,13 @@
         <v>1.71</v>
       </c>
       <c r="Q2">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="R2">
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>3.4</v>
+        <v>1.05</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -1027,58 +1027,58 @@
         <v>6</v>
       </c>
       <c r="BH2">
-        <v>1000</v>
+        <v>3.65</v>
       </c>
       <c r="BI2">
-        <v>1.01</v>
+        <v>2.54</v>
       </c>
       <c r="BJ2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK2">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN2">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BP2">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ2">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BR2">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS2">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BT2">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU2">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV2">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BW2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BX2">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY2">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BZ2">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="112">
   <si>
     <t>League</t>
   </si>
@@ -259,19 +259,97 @@
     <t>Colombian Primera B</t>
   </si>
   <si>
+    <t>Japanese J League</t>
+  </si>
+  <si>
+    <t>South Korean K2 League</t>
+  </si>
+  <si>
+    <t>Icelandic 1 Deild</t>
+  </si>
+  <si>
     <t>2026-08-07</t>
   </si>
   <si>
     <t>01:10:00</t>
   </si>
   <si>
+    <t>10:25:00</t>
+  </si>
+  <si>
+    <t>10:30:00</t>
+  </si>
+  <si>
+    <t>19:15:00</t>
+  </si>
+  <si>
     <t>Real Cartagena</t>
   </si>
   <si>
+    <t>Yokohama FM</t>
+  </si>
+  <si>
+    <t>G-Osaka</t>
+  </si>
+  <si>
+    <t>Gimpo Citizen</t>
+  </si>
+  <si>
+    <t>Yongin FC</t>
+  </si>
+  <si>
+    <t>Gyeongnam</t>
+  </si>
+  <si>
+    <t>Hwaseong FC</t>
+  </si>
+  <si>
+    <t>Chungnam Asan</t>
+  </si>
+  <si>
+    <t>Suwon Bluewings</t>
+  </si>
+  <si>
+    <t>Afturelding</t>
+  </si>
+  <si>
+    <t>Leiknir R</t>
+  </si>
+  <si>
     <t>Independiente Yumbo</t>
   </si>
   <si>
-    <t>2026-08-05 06:11:50</t>
+    <t>Kashima</t>
+  </si>
+  <si>
+    <t>Urawa</t>
+  </si>
+  <si>
+    <t>Cheongju FC</t>
+  </si>
+  <si>
+    <t>Busan IPark</t>
+  </si>
+  <si>
+    <t>Daegu FC</t>
+  </si>
+  <si>
+    <t>Seoul E-Land FC</t>
+  </si>
+  <si>
+    <t>Ansan Greeners FC</t>
+  </si>
+  <si>
+    <t>Gimhae City</t>
+  </si>
+  <si>
+    <t>Grindavik</t>
+  </si>
+  <si>
+    <t>Fylkir</t>
+  </si>
+  <si>
+    <t>2026-08-05 08:18:51</t>
   </si>
 </sst>
 </file>
@@ -603,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB2"/>
+  <dimension ref="A1:CB12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -853,22 +931,22 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="E2" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="F2">
         <v>1.6</v>
       </c>
       <c r="G2">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="H2">
         <v>5.4</v>
@@ -895,7 +973,7 @@
         <v>1.37</v>
       </c>
       <c r="P2">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="Q2">
         <v>2.12</v>
@@ -916,7 +994,7 @@
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -937,7 +1015,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="AE2">
         <v>150</v>
@@ -949,7 +1027,7 @@
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AI2">
         <v>150</v>
@@ -973,58 +1051,58 @@
         <v>240</v>
       </c>
       <c r="AP2">
+        <v>4.1</v>
+      </c>
+      <c r="AQ2">
+        <v>4.6</v>
+      </c>
+      <c r="AR2">
+        <v>5.3</v>
+      </c>
+      <c r="AS2">
+        <v>5.6</v>
+      </c>
+      <c r="AT2">
+        <v>3.2</v>
+      </c>
+      <c r="AU2">
+        <v>3.5</v>
+      </c>
+      <c r="AV2">
+        <v>4.9</v>
+      </c>
+      <c r="AW2">
+        <v>5.5</v>
+      </c>
+      <c r="AX2">
+        <v>3.55</v>
+      </c>
+      <c r="AY2">
+        <v>3.95</v>
+      </c>
+      <c r="AZ2">
+        <v>4.8</v>
+      </c>
+      <c r="BA2">
+        <v>5.5</v>
+      </c>
+      <c r="BB2">
         <v>4.3</v>
       </c>
-      <c r="AQ2">
-        <v>4.8</v>
-      </c>
-      <c r="AR2">
-        <v>5.7</v>
-      </c>
-      <c r="AS2">
-        <v>6</v>
-      </c>
-      <c r="AT2">
-        <v>3.3</v>
-      </c>
-      <c r="AU2">
-        <v>3.7</v>
-      </c>
-      <c r="AV2">
-        <v>5</v>
-      </c>
-      <c r="AW2">
-        <v>5.9</v>
-      </c>
-      <c r="AX2">
-        <v>3.7</v>
-      </c>
-      <c r="AY2">
-        <v>4.1</v>
-      </c>
-      <c r="AZ2">
-        <v>5</v>
-      </c>
-      <c r="BA2">
-        <v>5.9</v>
-      </c>
-      <c r="BB2">
-        <v>4.5</v>
-      </c>
       <c r="BC2">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="BD2">
+        <v>5.2</v>
+      </c>
+      <c r="BE2">
         <v>5.6</v>
       </c>
-      <c r="BE2">
-        <v>6</v>
-      </c>
       <c r="BF2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="BG2">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="BH2">
         <v>3.65</v>
@@ -1087,7 +1165,2427 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="3" spans="1:80">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D3" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" t="s">
+        <v>101</v>
+      </c>
+      <c r="F3">
+        <v>4</v>
+      </c>
+      <c r="G3">
+        <v>4.6</v>
+      </c>
+      <c r="H3">
+        <v>2.02</v>
+      </c>
+      <c r="I3">
+        <v>2.14</v>
+      </c>
+      <c r="J3">
+        <v>3.35</v>
+      </c>
+      <c r="K3">
+        <v>3.6</v>
+      </c>
+      <c r="L3">
+        <v>1.37</v>
+      </c>
+      <c r="M3">
+        <v>1.08</v>
+      </c>
+      <c r="N3">
+        <v>3.3</v>
+      </c>
+      <c r="O3">
+        <v>1.37</v>
+      </c>
+      <c r="P3">
+        <v>1.79</v>
+      </c>
+      <c r="Q3">
+        <v>2.04</v>
+      </c>
+      <c r="R3">
+        <v>1.3</v>
+      </c>
+      <c r="S3">
+        <v>3.8</v>
+      </c>
+      <c r="T3">
+        <v>1.72</v>
+      </c>
+      <c r="U3">
+        <v>1.99</v>
+      </c>
+      <c r="V3">
+        <v>1.88</v>
+      </c>
+      <c r="W3">
+        <v>1.3</v>
+      </c>
+      <c r="X3">
+        <v>15.5</v>
+      </c>
+      <c r="Y3">
+        <v>10.5</v>
+      </c>
+      <c r="Z3">
+        <v>15</v>
+      </c>
+      <c r="AA3">
+        <v>32</v>
+      </c>
+      <c r="AB3">
+        <v>17</v>
+      </c>
+      <c r="AC3">
+        <v>9.6</v>
+      </c>
+      <c r="AD3">
+        <v>13</v>
+      </c>
+      <c r="AE3">
+        <v>29</v>
+      </c>
+      <c r="AF3">
+        <v>38</v>
+      </c>
+      <c r="AG3">
+        <v>21</v>
+      </c>
+      <c r="AH3">
+        <v>24</v>
+      </c>
+      <c r="AI3">
+        <v>50</v>
+      </c>
+      <c r="AJ3">
+        <v>120</v>
+      </c>
+      <c r="AK3">
+        <v>75</v>
+      </c>
+      <c r="AL3">
         <v>85</v>
+      </c>
+      <c r="AM3">
+        <v>150</v>
+      </c>
+      <c r="AN3">
+        <v>85</v>
+      </c>
+      <c r="AO3">
+        <v>22</v>
+      </c>
+      <c r="AP3">
+        <v>11</v>
+      </c>
+      <c r="AQ3">
+        <v>7.4</v>
+      </c>
+      <c r="AR3">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AS3">
+        <v>3.75</v>
+      </c>
+      <c r="AT3">
+        <v>12</v>
+      </c>
+      <c r="AU3">
+        <v>7</v>
+      </c>
+      <c r="AV3">
+        <v>9.4</v>
+      </c>
+      <c r="AW3">
+        <v>20</v>
+      </c>
+      <c r="AX3">
+        <v>3.8</v>
+      </c>
+      <c r="AY3">
+        <v>12.5</v>
+      </c>
+      <c r="AZ3">
+        <v>17</v>
+      </c>
+      <c r="BA3">
+        <v>3.9</v>
+      </c>
+      <c r="BB3">
+        <v>4.1</v>
+      </c>
+      <c r="BC3">
+        <v>4</v>
+      </c>
+      <c r="BD3">
+        <v>4</v>
+      </c>
+      <c r="BE3">
+        <v>4.1</v>
+      </c>
+      <c r="BF3">
+        <v>4</v>
+      </c>
+      <c r="BG3">
+        <v>13</v>
+      </c>
+      <c r="BH3">
+        <v>3.2</v>
+      </c>
+      <c r="BI3">
+        <v>2.58</v>
+      </c>
+      <c r="BJ3">
+        <v>10.5</v>
+      </c>
+      <c r="BK3">
+        <v>7.4</v>
+      </c>
+      <c r="BL3">
+        <v>1000</v>
+      </c>
+      <c r="BM3">
+        <v>1.01</v>
+      </c>
+      <c r="BN3">
+        <v>7.6</v>
+      </c>
+      <c r="BO3">
+        <v>5.6</v>
+      </c>
+      <c r="BP3">
+        <v>38</v>
+      </c>
+      <c r="BQ3">
+        <v>26</v>
+      </c>
+      <c r="BR3">
+        <v>50</v>
+      </c>
+      <c r="BS3">
+        <v>34</v>
+      </c>
+      <c r="BT3">
+        <v>4.7</v>
+      </c>
+      <c r="BU3">
+        <v>3.65</v>
+      </c>
+      <c r="BV3">
+        <v>15.5</v>
+      </c>
+      <c r="BW3">
+        <v>11</v>
+      </c>
+      <c r="BX3">
+        <v>32</v>
+      </c>
+      <c r="BY3">
+        <v>22</v>
+      </c>
+      <c r="BZ3">
+        <v>0</v>
+      </c>
+      <c r="CA3">
+        <v>0</v>
+      </c>
+      <c r="CB3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="4" spans="1:80">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4">
+        <v>2.4</v>
+      </c>
+      <c r="G4">
+        <v>2.58</v>
+      </c>
+      <c r="H4">
+        <v>3.1</v>
+      </c>
+      <c r="I4">
+        <v>3.4</v>
+      </c>
+      <c r="J4">
+        <v>3.3</v>
+      </c>
+      <c r="K4">
+        <v>3.6</v>
+      </c>
+      <c r="L4">
+        <v>1.36</v>
+      </c>
+      <c r="M4">
+        <v>1.06</v>
+      </c>
+      <c r="N4">
+        <v>3.5</v>
+      </c>
+      <c r="O4">
+        <v>1.35</v>
+      </c>
+      <c r="P4">
+        <v>1.85</v>
+      </c>
+      <c r="Q4">
+        <v>2.02</v>
+      </c>
+      <c r="R4">
+        <v>1.33</v>
+      </c>
+      <c r="S4">
+        <v>3.65</v>
+      </c>
+      <c r="T4">
+        <v>1.65</v>
+      </c>
+      <c r="U4">
+        <v>2.1</v>
+      </c>
+      <c r="V4">
+        <v>1.43</v>
+      </c>
+      <c r="W4">
+        <v>1.63</v>
+      </c>
+      <c r="X4">
+        <v>13.5</v>
+      </c>
+      <c r="Y4">
+        <v>12.5</v>
+      </c>
+      <c r="Z4">
+        <v>23</v>
+      </c>
+      <c r="AA4">
+        <v>60</v>
+      </c>
+      <c r="AB4">
+        <v>10.5</v>
+      </c>
+      <c r="AC4">
+        <v>7.8</v>
+      </c>
+      <c r="AD4">
+        <v>14.5</v>
+      </c>
+      <c r="AE4">
+        <v>40</v>
+      </c>
+      <c r="AF4">
+        <v>16</v>
+      </c>
+      <c r="AG4">
+        <v>12</v>
+      </c>
+      <c r="AH4">
+        <v>17.5</v>
+      </c>
+      <c r="AI4">
+        <v>75</v>
+      </c>
+      <c r="AJ4">
+        <v>36</v>
+      </c>
+      <c r="AK4">
+        <v>28</v>
+      </c>
+      <c r="AL4">
+        <v>42</v>
+      </c>
+      <c r="AM4">
+        <v>120</v>
+      </c>
+      <c r="AN4">
+        <v>23</v>
+      </c>
+      <c r="AO4">
+        <v>55</v>
+      </c>
+      <c r="AP4">
+        <v>11.5</v>
+      </c>
+      <c r="AQ4">
+        <v>10.5</v>
+      </c>
+      <c r="AR4">
+        <v>19.5</v>
+      </c>
+      <c r="AS4">
+        <v>10</v>
+      </c>
+      <c r="AT4">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU4">
+        <v>6.8</v>
+      </c>
+      <c r="AV4">
+        <v>12.5</v>
+      </c>
+      <c r="AW4">
+        <v>9.4</v>
+      </c>
+      <c r="AX4">
+        <v>14</v>
+      </c>
+      <c r="AY4">
+        <v>10</v>
+      </c>
+      <c r="AZ4">
+        <v>15.5</v>
+      </c>
+      <c r="BA4">
+        <v>34</v>
+      </c>
+      <c r="BB4">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC4">
+        <v>19.5</v>
+      </c>
+      <c r="BD4">
+        <v>28</v>
+      </c>
+      <c r="BE4">
+        <v>11</v>
+      </c>
+      <c r="BF4">
+        <v>16.5</v>
+      </c>
+      <c r="BG4">
+        <v>9.4</v>
+      </c>
+      <c r="BH4">
+        <v>3.25</v>
+      </c>
+      <c r="BI4">
+        <v>2.98</v>
+      </c>
+      <c r="BJ4">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BK4">
+        <v>7.2</v>
+      </c>
+      <c r="BL4">
+        <v>1000</v>
+      </c>
+      <c r="BM4">
+        <v>1.01</v>
+      </c>
+      <c r="BN4">
+        <v>5.4</v>
+      </c>
+      <c r="BO4">
+        <v>4.1</v>
+      </c>
+      <c r="BP4">
+        <v>19</v>
+      </c>
+      <c r="BQ4">
+        <v>13.5</v>
+      </c>
+      <c r="BR4">
+        <v>34</v>
+      </c>
+      <c r="BS4">
+        <v>23</v>
+      </c>
+      <c r="BT4">
+        <v>6.4</v>
+      </c>
+      <c r="BU4">
+        <v>4.8</v>
+      </c>
+      <c r="BV4">
+        <v>26</v>
+      </c>
+      <c r="BW4">
+        <v>18.5</v>
+      </c>
+      <c r="BX4">
+        <v>40</v>
+      </c>
+      <c r="BY4">
+        <v>27</v>
+      </c>
+      <c r="BZ4">
+        <v>0</v>
+      </c>
+      <c r="CA4">
+        <v>0</v>
+      </c>
+      <c r="CB4" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="1:80">
+      <c r="A5" t="s">
+        <v>82</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
+        <v>87</v>
+      </c>
+      <c r="D5" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" t="s">
+        <v>103</v>
+      </c>
+      <c r="F5">
+        <v>1.79</v>
+      </c>
+      <c r="G5">
+        <v>1.93</v>
+      </c>
+      <c r="H5">
+        <v>5</v>
+      </c>
+      <c r="I5">
+        <v>5.7</v>
+      </c>
+      <c r="J5">
+        <v>3.55</v>
+      </c>
+      <c r="K5">
+        <v>3.85</v>
+      </c>
+      <c r="L5">
+        <v>1.36</v>
+      </c>
+      <c r="M5">
+        <v>1.01</v>
+      </c>
+      <c r="N5">
+        <v>1.83</v>
+      </c>
+      <c r="O5">
+        <v>1.37</v>
+      </c>
+      <c r="P5">
+        <v>1.74</v>
+      </c>
+      <c r="Q5">
+        <v>2.14</v>
+      </c>
+      <c r="R5">
+        <v>1.21</v>
+      </c>
+      <c r="S5">
+        <v>3.35</v>
+      </c>
+      <c r="T5">
+        <v>1.01</v>
+      </c>
+      <c r="U5">
+        <v>1.01</v>
+      </c>
+      <c r="V5">
+        <v>1.21</v>
+      </c>
+      <c r="W5">
+        <v>2.06</v>
+      </c>
+      <c r="X5">
+        <v>1000</v>
+      </c>
+      <c r="Y5">
+        <v>1000</v>
+      </c>
+      <c r="Z5">
+        <v>1000</v>
+      </c>
+      <c r="AA5">
+        <v>1000</v>
+      </c>
+      <c r="AB5">
+        <v>1000</v>
+      </c>
+      <c r="AC5">
+        <v>1000</v>
+      </c>
+      <c r="AD5">
+        <v>1000</v>
+      </c>
+      <c r="AE5">
+        <v>1000</v>
+      </c>
+      <c r="AF5">
+        <v>1000</v>
+      </c>
+      <c r="AG5">
+        <v>1000</v>
+      </c>
+      <c r="AH5">
+        <v>1000</v>
+      </c>
+      <c r="AI5">
+        <v>1000</v>
+      </c>
+      <c r="AJ5">
+        <v>1000</v>
+      </c>
+      <c r="AK5">
+        <v>1000</v>
+      </c>
+      <c r="AL5">
+        <v>1000</v>
+      </c>
+      <c r="AM5">
+        <v>1000</v>
+      </c>
+      <c r="AN5">
+        <v>1000</v>
+      </c>
+      <c r="AO5">
+        <v>1000</v>
+      </c>
+      <c r="AP5">
+        <v>1.03</v>
+      </c>
+      <c r="AQ5">
+        <v>1.03</v>
+      </c>
+      <c r="AR5">
+        <v>1.03</v>
+      </c>
+      <c r="AS5">
+        <v>1.03</v>
+      </c>
+      <c r="AT5">
+        <v>1.03</v>
+      </c>
+      <c r="AU5">
+        <v>1.03</v>
+      </c>
+      <c r="AV5">
+        <v>1.03</v>
+      </c>
+      <c r="AW5">
+        <v>1.03</v>
+      </c>
+      <c r="AX5">
+        <v>1.03</v>
+      </c>
+      <c r="AY5">
+        <v>1.03</v>
+      </c>
+      <c r="AZ5">
+        <v>1.03</v>
+      </c>
+      <c r="BA5">
+        <v>1.03</v>
+      </c>
+      <c r="BB5">
+        <v>1.03</v>
+      </c>
+      <c r="BC5">
+        <v>1.03</v>
+      </c>
+      <c r="BD5">
+        <v>1.03</v>
+      </c>
+      <c r="BE5">
+        <v>1.03</v>
+      </c>
+      <c r="BF5">
+        <v>1.01</v>
+      </c>
+      <c r="BG5">
+        <v>1.01</v>
+      </c>
+      <c r="BH5">
+        <v>1000</v>
+      </c>
+      <c r="BI5">
+        <v>1.01</v>
+      </c>
+      <c r="BJ5">
+        <v>1000</v>
+      </c>
+      <c r="BK5">
+        <v>1.01</v>
+      </c>
+      <c r="BL5">
+        <v>1000</v>
+      </c>
+      <c r="BM5">
+        <v>1.01</v>
+      </c>
+      <c r="BN5">
+        <v>1000</v>
+      </c>
+      <c r="BO5">
+        <v>1.01</v>
+      </c>
+      <c r="BP5">
+        <v>1000</v>
+      </c>
+      <c r="BQ5">
+        <v>1.01</v>
+      </c>
+      <c r="BR5">
+        <v>1000</v>
+      </c>
+      <c r="BS5">
+        <v>1.01</v>
+      </c>
+      <c r="BT5">
+        <v>1000</v>
+      </c>
+      <c r="BU5">
+        <v>1.01</v>
+      </c>
+      <c r="BV5">
+        <v>1000</v>
+      </c>
+      <c r="BW5">
+        <v>1.01</v>
+      </c>
+      <c r="BX5">
+        <v>1000</v>
+      </c>
+      <c r="BY5">
+        <v>1.01</v>
+      </c>
+      <c r="BZ5">
+        <v>1000</v>
+      </c>
+      <c r="CA5">
+        <v>1.01</v>
+      </c>
+      <c r="CB5" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="6" spans="1:80">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>84</v>
+      </c>
+      <c r="C6" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" t="s">
+        <v>104</v>
+      </c>
+      <c r="F6">
+        <v>3.95</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <v>1.92</v>
+      </c>
+      <c r="I6">
+        <v>2.12</v>
+      </c>
+      <c r="J6">
+        <v>3.6</v>
+      </c>
+      <c r="K6">
+        <v>3.9</v>
+      </c>
+      <c r="L6">
+        <v>1.01</v>
+      </c>
+      <c r="M6">
+        <v>1.01</v>
+      </c>
+      <c r="N6">
+        <v>1.01</v>
+      </c>
+      <c r="O6">
+        <v>1.31</v>
+      </c>
+      <c r="P6">
+        <v>1.88</v>
+      </c>
+      <c r="Q6">
+        <v>1.95</v>
+      </c>
+      <c r="R6">
+        <v>1.18</v>
+      </c>
+      <c r="S6">
+        <v>1.95</v>
+      </c>
+      <c r="T6">
+        <v>1.01</v>
+      </c>
+      <c r="U6">
+        <v>1.01</v>
+      </c>
+      <c r="V6">
+        <v>1.89</v>
+      </c>
+      <c r="W6">
+        <v>1.27</v>
+      </c>
+      <c r="X6">
+        <v>1000</v>
+      </c>
+      <c r="Y6">
+        <v>1000</v>
+      </c>
+      <c r="Z6">
+        <v>1000</v>
+      </c>
+      <c r="AA6">
+        <v>1000</v>
+      </c>
+      <c r="AB6">
+        <v>1000</v>
+      </c>
+      <c r="AC6">
+        <v>1000</v>
+      </c>
+      <c r="AD6">
+        <v>1000</v>
+      </c>
+      <c r="AE6">
+        <v>1000</v>
+      </c>
+      <c r="AF6">
+        <v>1000</v>
+      </c>
+      <c r="AG6">
+        <v>1000</v>
+      </c>
+      <c r="AH6">
+        <v>1000</v>
+      </c>
+      <c r="AI6">
+        <v>1000</v>
+      </c>
+      <c r="AJ6">
+        <v>1000</v>
+      </c>
+      <c r="AK6">
+        <v>1000</v>
+      </c>
+      <c r="AL6">
+        <v>1000</v>
+      </c>
+      <c r="AM6">
+        <v>1000</v>
+      </c>
+      <c r="AN6">
+        <v>1000</v>
+      </c>
+      <c r="AO6">
+        <v>1000</v>
+      </c>
+      <c r="AP6">
+        <v>1.01</v>
+      </c>
+      <c r="AQ6">
+        <v>1.01</v>
+      </c>
+      <c r="AR6">
+        <v>1.01</v>
+      </c>
+      <c r="AS6">
+        <v>1.01</v>
+      </c>
+      <c r="AT6">
+        <v>1.01</v>
+      </c>
+      <c r="AU6">
+        <v>1.01</v>
+      </c>
+      <c r="AV6">
+        <v>1.01</v>
+      </c>
+      <c r="AW6">
+        <v>1.01</v>
+      </c>
+      <c r="AX6">
+        <v>1.01</v>
+      </c>
+      <c r="AY6">
+        <v>1.01</v>
+      </c>
+      <c r="AZ6">
+        <v>1.01</v>
+      </c>
+      <c r="BA6">
+        <v>1.01</v>
+      </c>
+      <c r="BB6">
+        <v>1.01</v>
+      </c>
+      <c r="BC6">
+        <v>1.01</v>
+      </c>
+      <c r="BD6">
+        <v>1.01</v>
+      </c>
+      <c r="BE6">
+        <v>1.01</v>
+      </c>
+      <c r="BF6">
+        <v>1.01</v>
+      </c>
+      <c r="BG6">
+        <v>1.01</v>
+      </c>
+      <c r="BH6">
+        <v>4.1</v>
+      </c>
+      <c r="BI6">
+        <v>2.66</v>
+      </c>
+      <c r="BJ6">
+        <v>1000</v>
+      </c>
+      <c r="BK6">
+        <v>1.01</v>
+      </c>
+      <c r="BL6">
+        <v>1000</v>
+      </c>
+      <c r="BM6">
+        <v>1.01</v>
+      </c>
+      <c r="BN6">
+        <v>1000</v>
+      </c>
+      <c r="BO6">
+        <v>1.01</v>
+      </c>
+      <c r="BP6">
+        <v>1000</v>
+      </c>
+      <c r="BQ6">
+        <v>1.01</v>
+      </c>
+      <c r="BR6">
+        <v>1000</v>
+      </c>
+      <c r="BS6">
+        <v>1.01</v>
+      </c>
+      <c r="BT6">
+        <v>1000</v>
+      </c>
+      <c r="BU6">
+        <v>1.01</v>
+      </c>
+      <c r="BV6">
+        <v>1000</v>
+      </c>
+      <c r="BW6">
+        <v>1.01</v>
+      </c>
+      <c r="BX6">
+        <v>1000</v>
+      </c>
+      <c r="BY6">
+        <v>1.01</v>
+      </c>
+      <c r="BZ6">
+        <v>1000</v>
+      </c>
+      <c r="CA6">
+        <v>1.01</v>
+      </c>
+      <c r="CB6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="7" spans="1:80">
+      <c r="A7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B7" t="s">
+        <v>84</v>
+      </c>
+      <c r="C7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F7">
+        <v>4.1</v>
+      </c>
+      <c r="G7">
+        <v>4.8</v>
+      </c>
+      <c r="H7">
+        <v>1.85</v>
+      </c>
+      <c r="I7">
+        <v>1.99</v>
+      </c>
+      <c r="J7">
+        <v>3.9</v>
+      </c>
+      <c r="K7">
+        <v>4.1</v>
+      </c>
+      <c r="L7">
+        <v>1.32</v>
+      </c>
+      <c r="M7">
+        <v>1.05</v>
+      </c>
+      <c r="N7">
+        <v>4.1</v>
+      </c>
+      <c r="O7">
+        <v>1.27</v>
+      </c>
+      <c r="P7">
+        <v>2.06</v>
+      </c>
+      <c r="Q7">
+        <v>1.79</v>
+      </c>
+      <c r="R7">
+        <v>1.42</v>
+      </c>
+      <c r="S7">
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <v>1.64</v>
+      </c>
+      <c r="U7">
+        <v>2.16</v>
+      </c>
+      <c r="V7">
+        <v>2</v>
+      </c>
+      <c r="W7">
+        <v>1.26</v>
+      </c>
+      <c r="X7">
+        <v>20</v>
+      </c>
+      <c r="Y7">
+        <v>12</v>
+      </c>
+      <c r="Z7">
+        <v>13</v>
+      </c>
+      <c r="AA7">
+        <v>25</v>
+      </c>
+      <c r="AB7">
+        <v>20</v>
+      </c>
+      <c r="AC7">
+        <v>10.5</v>
+      </c>
+      <c r="AD7">
+        <v>12</v>
+      </c>
+      <c r="AE7">
+        <v>23</v>
+      </c>
+      <c r="AF7">
+        <v>40</v>
+      </c>
+      <c r="AG7">
+        <v>21</v>
+      </c>
+      <c r="AH7">
+        <v>21</v>
+      </c>
+      <c r="AI7">
+        <v>38</v>
+      </c>
+      <c r="AJ7">
+        <v>110</v>
+      </c>
+      <c r="AK7">
+        <v>60</v>
+      </c>
+      <c r="AL7">
+        <v>65</v>
+      </c>
+      <c r="AM7">
+        <v>110</v>
+      </c>
+      <c r="AN7">
+        <v>60</v>
+      </c>
+      <c r="AO7">
+        <v>13.5</v>
+      </c>
+      <c r="AP7">
+        <v>13</v>
+      </c>
+      <c r="AQ7">
+        <v>7.8</v>
+      </c>
+      <c r="AR7">
+        <v>9.6</v>
+      </c>
+      <c r="AS7">
+        <v>16.5</v>
+      </c>
+      <c r="AT7">
+        <v>13</v>
+      </c>
+      <c r="AU7">
+        <v>7</v>
+      </c>
+      <c r="AV7">
+        <v>8</v>
+      </c>
+      <c r="AW7">
+        <v>14.5</v>
+      </c>
+      <c r="AX7">
+        <v>1.03</v>
+      </c>
+      <c r="AY7">
+        <v>13.5</v>
+      </c>
+      <c r="AZ7">
+        <v>13.5</v>
+      </c>
+      <c r="BA7">
+        <v>1.03</v>
+      </c>
+      <c r="BB7">
+        <v>1.03</v>
+      </c>
+      <c r="BC7">
+        <v>1.03</v>
+      </c>
+      <c r="BD7">
+        <v>1.03</v>
+      </c>
+      <c r="BE7">
+        <v>1.03</v>
+      </c>
+      <c r="BF7">
+        <v>38</v>
+      </c>
+      <c r="BG7">
+        <v>9</v>
+      </c>
+      <c r="BH7">
+        <v>3.75</v>
+      </c>
+      <c r="BI7">
+        <v>3</v>
+      </c>
+      <c r="BJ7">
+        <v>9.6</v>
+      </c>
+      <c r="BK7">
+        <v>7.4</v>
+      </c>
+      <c r="BL7">
+        <v>1000</v>
+      </c>
+      <c r="BM7">
+        <v>1.01</v>
+      </c>
+      <c r="BN7">
+        <v>8</v>
+      </c>
+      <c r="BO7">
+        <v>6</v>
+      </c>
+      <c r="BP7">
+        <v>1000</v>
+      </c>
+      <c r="BQ7">
+        <v>26</v>
+      </c>
+      <c r="BR7">
+        <v>1000</v>
+      </c>
+      <c r="BS7">
+        <v>30</v>
+      </c>
+      <c r="BT7">
+        <v>4.8</v>
+      </c>
+      <c r="BU7">
+        <v>3.8</v>
+      </c>
+      <c r="BV7">
+        <v>13</v>
+      </c>
+      <c r="BW7">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BX7">
+        <v>1000</v>
+      </c>
+      <c r="BY7">
+        <v>19</v>
+      </c>
+      <c r="BZ7">
+        <v>1000</v>
+      </c>
+      <c r="CA7">
+        <v>15.5</v>
+      </c>
+      <c r="CB7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:80">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+      <c r="B8" t="s">
+        <v>84</v>
+      </c>
+      <c r="C8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D8" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" t="s">
+        <v>106</v>
+      </c>
+      <c r="F8">
+        <v>2.94</v>
+      </c>
+      <c r="G8">
+        <v>3.4</v>
+      </c>
+      <c r="H8">
+        <v>2.3</v>
+      </c>
+      <c r="I8">
+        <v>2.58</v>
+      </c>
+      <c r="J8">
+        <v>3.5</v>
+      </c>
+      <c r="K8">
+        <v>3.9</v>
+      </c>
+      <c r="L8">
+        <v>1.01</v>
+      </c>
+      <c r="M8">
+        <v>1.06</v>
+      </c>
+      <c r="N8">
+        <v>4</v>
+      </c>
+      <c r="O8">
+        <v>1.24</v>
+      </c>
+      <c r="P8">
+        <v>2.08</v>
+      </c>
+      <c r="Q8">
+        <v>1.76</v>
+      </c>
+      <c r="R8">
+        <v>1.41</v>
+      </c>
+      <c r="S8">
+        <v>2.96</v>
+      </c>
+      <c r="T8">
+        <v>1.01</v>
+      </c>
+      <c r="U8">
+        <v>1.01</v>
+      </c>
+      <c r="V8">
+        <v>1.64</v>
+      </c>
+      <c r="W8">
+        <v>1.41</v>
+      </c>
+      <c r="X8">
+        <v>1000</v>
+      </c>
+      <c r="Y8">
+        <v>1000</v>
+      </c>
+      <c r="Z8">
+        <v>1000</v>
+      </c>
+      <c r="AA8">
+        <v>1000</v>
+      </c>
+      <c r="AB8">
+        <v>1000</v>
+      </c>
+      <c r="AC8">
+        <v>1000</v>
+      </c>
+      <c r="AD8">
+        <v>1000</v>
+      </c>
+      <c r="AE8">
+        <v>1000</v>
+      </c>
+      <c r="AF8">
+        <v>1000</v>
+      </c>
+      <c r="AG8">
+        <v>1000</v>
+      </c>
+      <c r="AH8">
+        <v>1000</v>
+      </c>
+      <c r="AI8">
+        <v>1000</v>
+      </c>
+      <c r="AJ8">
+        <v>1000</v>
+      </c>
+      <c r="AK8">
+        <v>1000</v>
+      </c>
+      <c r="AL8">
+        <v>1000</v>
+      </c>
+      <c r="AM8">
+        <v>1000</v>
+      </c>
+      <c r="AN8">
+        <v>1000</v>
+      </c>
+      <c r="AO8">
+        <v>1000</v>
+      </c>
+      <c r="AP8">
+        <v>1.03</v>
+      </c>
+      <c r="AQ8">
+        <v>1.03</v>
+      </c>
+      <c r="AR8">
+        <v>1.03</v>
+      </c>
+      <c r="AS8">
+        <v>1.03</v>
+      </c>
+      <c r="AT8">
+        <v>1.03</v>
+      </c>
+      <c r="AU8">
+        <v>1.03</v>
+      </c>
+      <c r="AV8">
+        <v>1.03</v>
+      </c>
+      <c r="AW8">
+        <v>1.03</v>
+      </c>
+      <c r="AX8">
+        <v>1.03</v>
+      </c>
+      <c r="AY8">
+        <v>1.03</v>
+      </c>
+      <c r="AZ8">
+        <v>1.03</v>
+      </c>
+      <c r="BA8">
+        <v>1.03</v>
+      </c>
+      <c r="BB8">
+        <v>1.03</v>
+      </c>
+      <c r="BC8">
+        <v>1.03</v>
+      </c>
+      <c r="BD8">
+        <v>1.03</v>
+      </c>
+      <c r="BE8">
+        <v>1.03</v>
+      </c>
+      <c r="BF8">
+        <v>1.01</v>
+      </c>
+      <c r="BG8">
+        <v>1.01</v>
+      </c>
+      <c r="BH8">
+        <v>1000</v>
+      </c>
+      <c r="BI8">
+        <v>1.01</v>
+      </c>
+      <c r="BJ8">
+        <v>1000</v>
+      </c>
+      <c r="BK8">
+        <v>1.01</v>
+      </c>
+      <c r="BL8">
+        <v>1000</v>
+      </c>
+      <c r="BM8">
+        <v>1.01</v>
+      </c>
+      <c r="BN8">
+        <v>1000</v>
+      </c>
+      <c r="BO8">
+        <v>1.01</v>
+      </c>
+      <c r="BP8">
+        <v>1000</v>
+      </c>
+      <c r="BQ8">
+        <v>1.01</v>
+      </c>
+      <c r="BR8">
+        <v>1000</v>
+      </c>
+      <c r="BS8">
+        <v>1.01</v>
+      </c>
+      <c r="BT8">
+        <v>1000</v>
+      </c>
+      <c r="BU8">
+        <v>1.01</v>
+      </c>
+      <c r="BV8">
+        <v>1000</v>
+      </c>
+      <c r="BW8">
+        <v>1.01</v>
+      </c>
+      <c r="BX8">
+        <v>1000</v>
+      </c>
+      <c r="BY8">
+        <v>1.01</v>
+      </c>
+      <c r="BZ8">
+        <v>1000</v>
+      </c>
+      <c r="CA8">
+        <v>1.01</v>
+      </c>
+      <c r="CB8" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:80">
+      <c r="A9" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" t="s">
+        <v>84</v>
+      </c>
+      <c r="C9" t="s">
+        <v>87</v>
+      </c>
+      <c r="D9" t="s">
+        <v>96</v>
+      </c>
+      <c r="E9" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9">
+        <v>1.53</v>
+      </c>
+      <c r="G9">
+        <v>1.64</v>
+      </c>
+      <c r="H9">
+        <v>6</v>
+      </c>
+      <c r="I9">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J9">
+        <v>4.1</v>
+      </c>
+      <c r="K9">
+        <v>4.9</v>
+      </c>
+      <c r="L9">
+        <v>1.28</v>
+      </c>
+      <c r="M9">
+        <v>1.05</v>
+      </c>
+      <c r="N9">
+        <v>4.1</v>
+      </c>
+      <c r="O9">
+        <v>1.26</v>
+      </c>
+      <c r="P9">
+        <v>2.08</v>
+      </c>
+      <c r="Q9">
+        <v>1.76</v>
+      </c>
+      <c r="R9">
+        <v>1.41</v>
+      </c>
+      <c r="S9">
+        <v>2.82</v>
+      </c>
+      <c r="T9">
+        <v>1.75</v>
+      </c>
+      <c r="U9">
+        <v>1.86</v>
+      </c>
+      <c r="V9">
+        <v>1.14</v>
+      </c>
+      <c r="W9">
+        <v>2.52</v>
+      </c>
+      <c r="X9">
+        <v>21</v>
+      </c>
+      <c r="Y9">
+        <v>27</v>
+      </c>
+      <c r="Z9">
+        <v>65</v>
+      </c>
+      <c r="AA9">
+        <v>220</v>
+      </c>
+      <c r="AB9">
+        <v>10.5</v>
+      </c>
+      <c r="AC9">
+        <v>11.5</v>
+      </c>
+      <c r="AD9">
+        <v>29</v>
+      </c>
+      <c r="AE9">
+        <v>110</v>
+      </c>
+      <c r="AF9">
+        <v>11.5</v>
+      </c>
+      <c r="AG9">
+        <v>11.5</v>
+      </c>
+      <c r="AH9">
+        <v>25</v>
+      </c>
+      <c r="AI9">
+        <v>100</v>
+      </c>
+      <c r="AJ9">
+        <v>17.5</v>
+      </c>
+      <c r="AK9">
+        <v>19</v>
+      </c>
+      <c r="AL9">
+        <v>40</v>
+      </c>
+      <c r="AM9">
+        <v>140</v>
+      </c>
+      <c r="AN9">
+        <v>9.4</v>
+      </c>
+      <c r="AO9">
+        <v>130</v>
+      </c>
+      <c r="AP9">
+        <v>13.5</v>
+      </c>
+      <c r="AQ9">
+        <v>17.5</v>
+      </c>
+      <c r="AR9">
+        <v>1.03</v>
+      </c>
+      <c r="AS9">
+        <v>1.03</v>
+      </c>
+      <c r="AT9">
+        <v>7</v>
+      </c>
+      <c r="AU9">
+        <v>7.8</v>
+      </c>
+      <c r="AV9">
+        <v>19</v>
+      </c>
+      <c r="AW9">
+        <v>1.03</v>
+      </c>
+      <c r="AX9">
+        <v>7.6</v>
+      </c>
+      <c r="AY9">
+        <v>7.8</v>
+      </c>
+      <c r="AZ9">
+        <v>16.5</v>
+      </c>
+      <c r="BA9">
+        <v>1.03</v>
+      </c>
+      <c r="BB9">
+        <v>11.5</v>
+      </c>
+      <c r="BC9">
+        <v>12.5</v>
+      </c>
+      <c r="BD9">
+        <v>1.03</v>
+      </c>
+      <c r="BE9">
+        <v>1.03</v>
+      </c>
+      <c r="BF9">
+        <v>6.4</v>
+      </c>
+      <c r="BG9">
+        <v>80</v>
+      </c>
+      <c r="BH9">
+        <v>1000</v>
+      </c>
+      <c r="BI9">
+        <v>1.01</v>
+      </c>
+      <c r="BJ9">
+        <v>1000</v>
+      </c>
+      <c r="BK9">
+        <v>1.01</v>
+      </c>
+      <c r="BL9">
+        <v>1000</v>
+      </c>
+      <c r="BM9">
+        <v>1.01</v>
+      </c>
+      <c r="BN9">
+        <v>1000</v>
+      </c>
+      <c r="BO9">
+        <v>1.01</v>
+      </c>
+      <c r="BP9">
+        <v>1000</v>
+      </c>
+      <c r="BQ9">
+        <v>1.01</v>
+      </c>
+      <c r="BR9">
+        <v>1000</v>
+      </c>
+      <c r="BS9">
+        <v>1.01</v>
+      </c>
+      <c r="BT9">
+        <v>1000</v>
+      </c>
+      <c r="BU9">
+        <v>1.01</v>
+      </c>
+      <c r="BV9">
+        <v>1000</v>
+      </c>
+      <c r="BW9">
+        <v>1.01</v>
+      </c>
+      <c r="BX9">
+        <v>1000</v>
+      </c>
+      <c r="BY9">
+        <v>1.01</v>
+      </c>
+      <c r="BZ9">
+        <v>1000</v>
+      </c>
+      <c r="CA9">
+        <v>1.01</v>
+      </c>
+      <c r="CB9" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="10" spans="1:80">
+      <c r="A10" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" t="s">
+        <v>84</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10">
+        <v>1.28</v>
+      </c>
+      <c r="G10">
+        <v>1.35</v>
+      </c>
+      <c r="H10">
+        <v>11.5</v>
+      </c>
+      <c r="I10">
+        <v>17</v>
+      </c>
+      <c r="J10">
+        <v>5.5</v>
+      </c>
+      <c r="K10">
+        <v>6.6</v>
+      </c>
+      <c r="L10">
+        <v>1.26</v>
+      </c>
+      <c r="M10">
+        <v>1.04</v>
+      </c>
+      <c r="N10">
+        <v>4.5</v>
+      </c>
+      <c r="O10">
+        <v>1.23</v>
+      </c>
+      <c r="P10">
+        <v>2.2</v>
+      </c>
+      <c r="Q10">
+        <v>1.6</v>
+      </c>
+      <c r="R10">
+        <v>1.47</v>
+      </c>
+      <c r="S10">
+        <v>2.72</v>
+      </c>
+      <c r="T10">
+        <v>1.97</v>
+      </c>
+      <c r="U10">
+        <v>1.6</v>
+      </c>
+      <c r="V10">
+        <v>1.06</v>
+      </c>
+      <c r="W10">
+        <v>3.85</v>
+      </c>
+      <c r="X10">
+        <v>26</v>
+      </c>
+      <c r="Y10">
+        <v>46</v>
+      </c>
+      <c r="Z10">
+        <v>150</v>
+      </c>
+      <c r="AA10">
+        <v>1000</v>
+      </c>
+      <c r="AB10">
+        <v>8.6</v>
+      </c>
+      <c r="AC10">
+        <v>16.5</v>
+      </c>
+      <c r="AD10">
+        <v>60</v>
+      </c>
+      <c r="AE10">
+        <v>290</v>
+      </c>
+      <c r="AF10">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AG10">
+        <v>13</v>
+      </c>
+      <c r="AH10">
+        <v>34</v>
+      </c>
+      <c r="AI10">
+        <v>220</v>
+      </c>
+      <c r="AJ10">
+        <v>12.5</v>
+      </c>
+      <c r="AK10">
+        <v>18</v>
+      </c>
+      <c r="AL10">
+        <v>55</v>
+      </c>
+      <c r="AM10">
+        <v>240</v>
+      </c>
+      <c r="AN10">
+        <v>6.4</v>
+      </c>
+      <c r="AO10">
+        <v>440</v>
+      </c>
+      <c r="AP10">
+        <v>15</v>
+      </c>
+      <c r="AQ10">
+        <v>1.03</v>
+      </c>
+      <c r="AR10">
+        <v>1.03</v>
+      </c>
+      <c r="AS10">
+        <v>1.03</v>
+      </c>
+      <c r="AT10">
+        <v>6.2</v>
+      </c>
+      <c r="AU10">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV10">
+        <v>1.03</v>
+      </c>
+      <c r="AW10">
+        <v>1.03</v>
+      </c>
+      <c r="AX10">
+        <v>5.8</v>
+      </c>
+      <c r="AY10">
+        <v>8</v>
+      </c>
+      <c r="AZ10">
+        <v>1.03</v>
+      </c>
+      <c r="BA10">
+        <v>1.03</v>
+      </c>
+      <c r="BB10">
+        <v>7.8</v>
+      </c>
+      <c r="BC10">
+        <v>10.5</v>
+      </c>
+      <c r="BD10">
+        <v>1.03</v>
+      </c>
+      <c r="BE10">
+        <v>1.03</v>
+      </c>
+      <c r="BF10">
+        <v>4.2</v>
+      </c>
+      <c r="BG10">
+        <v>85</v>
+      </c>
+      <c r="BH10">
+        <v>4.8</v>
+      </c>
+      <c r="BI10">
+        <v>3.2</v>
+      </c>
+      <c r="BJ10">
+        <v>15.5</v>
+      </c>
+      <c r="BK10">
+        <v>9.4</v>
+      </c>
+      <c r="BL10">
+        <v>1000</v>
+      </c>
+      <c r="BM10">
+        <v>1.01</v>
+      </c>
+      <c r="BN10">
+        <v>4.3</v>
+      </c>
+      <c r="BO10">
+        <v>2.92</v>
+      </c>
+      <c r="BP10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BQ10">
+        <v>5.5</v>
+      </c>
+      <c r="BR10">
+        <v>30</v>
+      </c>
+      <c r="BS10">
+        <v>17.5</v>
+      </c>
+      <c r="BT10">
+        <v>18</v>
+      </c>
+      <c r="BU10">
+        <v>11</v>
+      </c>
+      <c r="BV10">
+        <v>1000</v>
+      </c>
+      <c r="BW10">
+        <v>1.01</v>
+      </c>
+      <c r="BX10">
+        <v>120</v>
+      </c>
+      <c r="BY10">
+        <v>1.01</v>
+      </c>
+      <c r="BZ10">
+        <v>14.5</v>
+      </c>
+      <c r="CA10">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="CB10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:80">
+      <c r="A11" t="s">
+        <v>83</v>
+      </c>
+      <c r="B11" t="s">
+        <v>84</v>
+      </c>
+      <c r="C11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11">
+        <v>1.04</v>
+      </c>
+      <c r="G11">
+        <v>1000</v>
+      </c>
+      <c r="H11">
+        <v>1.04</v>
+      </c>
+      <c r="I11">
+        <v>1000</v>
+      </c>
+      <c r="J11">
+        <v>1.01</v>
+      </c>
+      <c r="K11">
+        <v>1000</v>
+      </c>
+      <c r="L11">
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <v>1.24</v>
+      </c>
+      <c r="Q11">
+        <v>1.01</v>
+      </c>
+      <c r="R11">
+        <v>0</v>
+      </c>
+      <c r="S11">
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <v>0</v>
+      </c>
+      <c r="U11">
+        <v>0</v>
+      </c>
+      <c r="V11">
+        <v>0</v>
+      </c>
+      <c r="W11">
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <v>0</v>
+      </c>
+      <c r="Y11">
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <v>0</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0</v>
+      </c>
+      <c r="AI11">
+        <v>0</v>
+      </c>
+      <c r="AJ11">
+        <v>0</v>
+      </c>
+      <c r="AK11">
+        <v>0</v>
+      </c>
+      <c r="AL11">
+        <v>0</v>
+      </c>
+      <c r="AM11">
+        <v>0</v>
+      </c>
+      <c r="AN11">
+        <v>0</v>
+      </c>
+      <c r="AO11">
+        <v>0</v>
+      </c>
+      <c r="AP11">
+        <v>0</v>
+      </c>
+      <c r="AQ11">
+        <v>0</v>
+      </c>
+      <c r="AR11">
+        <v>0</v>
+      </c>
+      <c r="AS11">
+        <v>0</v>
+      </c>
+      <c r="AT11">
+        <v>0</v>
+      </c>
+      <c r="AU11">
+        <v>0</v>
+      </c>
+      <c r="AV11">
+        <v>0</v>
+      </c>
+      <c r="AW11">
+        <v>0</v>
+      </c>
+      <c r="AX11">
+        <v>0</v>
+      </c>
+      <c r="AY11">
+        <v>0</v>
+      </c>
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+      <c r="BA11">
+        <v>0</v>
+      </c>
+      <c r="BB11">
+        <v>0</v>
+      </c>
+      <c r="BC11">
+        <v>0</v>
+      </c>
+      <c r="BD11">
+        <v>0</v>
+      </c>
+      <c r="BE11">
+        <v>0</v>
+      </c>
+      <c r="BF11">
+        <v>0</v>
+      </c>
+      <c r="BG11">
+        <v>0</v>
+      </c>
+      <c r="BH11">
+        <v>0</v>
+      </c>
+      <c r="BI11">
+        <v>0</v>
+      </c>
+      <c r="BJ11">
+        <v>0</v>
+      </c>
+      <c r="BK11">
+        <v>0</v>
+      </c>
+      <c r="BL11">
+        <v>0</v>
+      </c>
+      <c r="BM11">
+        <v>0</v>
+      </c>
+      <c r="BN11">
+        <v>0</v>
+      </c>
+      <c r="BO11">
+        <v>0</v>
+      </c>
+      <c r="BP11">
+        <v>0</v>
+      </c>
+      <c r="BQ11">
+        <v>0</v>
+      </c>
+      <c r="BR11">
+        <v>0</v>
+      </c>
+      <c r="BS11">
+        <v>0</v>
+      </c>
+      <c r="BT11">
+        <v>0</v>
+      </c>
+      <c r="BU11">
+        <v>0</v>
+      </c>
+      <c r="BV11">
+        <v>0</v>
+      </c>
+      <c r="BW11">
+        <v>0</v>
+      </c>
+      <c r="BX11">
+        <v>0</v>
+      </c>
+      <c r="BY11">
+        <v>0</v>
+      </c>
+      <c r="BZ11">
+        <v>0</v>
+      </c>
+      <c r="CA11">
+        <v>0</v>
+      </c>
+      <c r="CB11" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="12" spans="1:80">
+      <c r="A12" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D12" t="s">
+        <v>99</v>
+      </c>
+      <c r="E12" t="s">
+        <v>110</v>
+      </c>
+      <c r="F12">
+        <v>1.04</v>
+      </c>
+      <c r="G12">
+        <v>1000</v>
+      </c>
+      <c r="H12">
+        <v>1.04</v>
+      </c>
+      <c r="I12">
+        <v>1000</v>
+      </c>
+      <c r="J12">
+        <v>1.01</v>
+      </c>
+      <c r="K12">
+        <v>1000</v>
+      </c>
+      <c r="L12">
+        <v>0</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12">
+        <v>0</v>
+      </c>
+      <c r="P12">
+        <v>1.24</v>
+      </c>
+      <c r="Q12">
+        <v>1.01</v>
+      </c>
+      <c r="R12">
+        <v>0</v>
+      </c>
+      <c r="S12">
+        <v>0</v>
+      </c>
+      <c r="T12">
+        <v>0</v>
+      </c>
+      <c r="U12">
+        <v>0</v>
+      </c>
+      <c r="V12">
+        <v>0</v>
+      </c>
+      <c r="W12">
+        <v>0</v>
+      </c>
+      <c r="X12">
+        <v>0</v>
+      </c>
+      <c r="Y12">
+        <v>0</v>
+      </c>
+      <c r="Z12">
+        <v>0</v>
+      </c>
+      <c r="AA12">
+        <v>0</v>
+      </c>
+      <c r="AB12">
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <v>0</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0</v>
+      </c>
+      <c r="AI12">
+        <v>0</v>
+      </c>
+      <c r="AJ12">
+        <v>0</v>
+      </c>
+      <c r="AK12">
+        <v>0</v>
+      </c>
+      <c r="AL12">
+        <v>0</v>
+      </c>
+      <c r="AM12">
+        <v>0</v>
+      </c>
+      <c r="AN12">
+        <v>0</v>
+      </c>
+      <c r="AO12">
+        <v>0</v>
+      </c>
+      <c r="AP12">
+        <v>0</v>
+      </c>
+      <c r="AQ12">
+        <v>0</v>
+      </c>
+      <c r="AR12">
+        <v>0</v>
+      </c>
+      <c r="AS12">
+        <v>0</v>
+      </c>
+      <c r="AT12">
+        <v>0</v>
+      </c>
+      <c r="AU12">
+        <v>0</v>
+      </c>
+      <c r="AV12">
+        <v>0</v>
+      </c>
+      <c r="AW12">
+        <v>0</v>
+      </c>
+      <c r="AX12">
+        <v>0</v>
+      </c>
+      <c r="AY12">
+        <v>0</v>
+      </c>
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+      <c r="BA12">
+        <v>0</v>
+      </c>
+      <c r="BB12">
+        <v>0</v>
+      </c>
+      <c r="BC12">
+        <v>0</v>
+      </c>
+      <c r="BD12">
+        <v>0</v>
+      </c>
+      <c r="BE12">
+        <v>0</v>
+      </c>
+      <c r="BF12">
+        <v>0</v>
+      </c>
+      <c r="BG12">
+        <v>0</v>
+      </c>
+      <c r="BH12">
+        <v>0</v>
+      </c>
+      <c r="BI12">
+        <v>0</v>
+      </c>
+      <c r="BJ12">
+        <v>0</v>
+      </c>
+      <c r="BK12">
+        <v>0</v>
+      </c>
+      <c r="BL12">
+        <v>0</v>
+      </c>
+      <c r="BM12">
+        <v>0</v>
+      </c>
+      <c r="BN12">
+        <v>0</v>
+      </c>
+      <c r="BO12">
+        <v>0</v>
+      </c>
+      <c r="BP12">
+        <v>0</v>
+      </c>
+      <c r="BQ12">
+        <v>0</v>
+      </c>
+      <c r="BR12">
+        <v>0</v>
+      </c>
+      <c r="BS12">
+        <v>0</v>
+      </c>
+      <c r="BT12">
+        <v>0</v>
+      </c>
+      <c r="BU12">
+        <v>0</v>
+      </c>
+      <c r="BV12">
+        <v>0</v>
+      </c>
+      <c r="BW12">
+        <v>0</v>
+      </c>
+      <c r="BX12">
+        <v>0</v>
+      </c>
+      <c r="BY12">
+        <v>0</v>
+      </c>
+      <c r="BZ12">
+        <v>0</v>
+      </c>
+      <c r="CA12">
+        <v>0</v>
+      </c>
+      <c r="CB12" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
   <si>
     <t>League</t>
   </si>
@@ -265,6 +265,9 @@
     <t>South Korean K2 League</t>
   </si>
   <si>
+    <t>Chinese Super League</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -280,6 +283,9 @@
     <t>10:30:00</t>
   </si>
   <si>
+    <t>11:35:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -310,6 +316,9 @@
     <t>Suwon Bluewings</t>
   </si>
   <si>
+    <t>Beijing Guoan</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
@@ -343,13 +352,16 @@
     <t>Gimhae City</t>
   </si>
   <si>
+    <t>Shenzhen Peng City</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
     <t>Fylkir</t>
   </si>
   <si>
-    <t>2026-08-05 08:18:51</t>
+    <t>2026-08-05 10:26:28</t>
   </si>
 </sst>
 </file>
@@ -681,7 +693,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB12"/>
+  <dimension ref="A1:CB13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -931,16 +943,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="F2">
         <v>1.6</v>
@@ -1165,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1173,16 +1185,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E3" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1191,19 +1203,19 @@
         <v>4.6</v>
       </c>
       <c r="H3">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="J3">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K3">
         <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1218,31 +1230,31 @@
         <v>1.79</v>
       </c>
       <c r="Q3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T3">
-        <v>1.72</v>
+        <v>1.87</v>
       </c>
       <c r="U3">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="V3">
         <v>1.88</v>
       </c>
       <c r="W3">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="X3">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="Y3">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="Z3">
         <v>15</v>
@@ -1251,10 +1263,10 @@
         <v>32</v>
       </c>
       <c r="AB3">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AC3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AD3">
         <v>13</v>
@@ -1293,7 +1305,7 @@
         <v>22</v>
       </c>
       <c r="AP3">
-        <v>11</v>
+        <v>3.4</v>
       </c>
       <c r="AQ3">
         <v>7.4</v>
@@ -1302,7 +1314,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="AT3">
         <v>12</v>
@@ -1317,7 +1329,7 @@
         <v>20</v>
       </c>
       <c r="AX3">
-        <v>3.8</v>
+        <v>3.95</v>
       </c>
       <c r="AY3">
         <v>12.5</v>
@@ -1326,22 +1338,22 @@
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BB3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BC3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BD3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BE3">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF3">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="BG3">
         <v>13</v>
@@ -1350,55 +1362,55 @@
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>7.4</v>
+        <v>5.8</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN3">
         <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
         <v>38</v>
       </c>
       <c r="BQ3">
-        <v>26</v>
+        <v>9.6</v>
       </c>
       <c r="BR3">
         <v>50</v>
       </c>
       <c r="BS3">
-        <v>34</v>
+        <v>10</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU3">
         <v>3.65</v>
       </c>
       <c r="BV3">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="BW3">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="BX3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BY3">
-        <v>22</v>
+        <v>9.4</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1407,7 +1419,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1415,52 +1427,52 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E4" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="F4">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G4">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H4">
-        <v>3.1</v>
+        <v>2.96</v>
       </c>
       <c r="I4">
         <v>3.4</v>
       </c>
       <c r="J4">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M4">
         <v>1.06</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O4">
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="Q4">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
         <v>1.33</v>
@@ -1469,25 +1481,25 @@
         <v>3.65</v>
       </c>
       <c r="T4">
-        <v>1.65</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
         <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="X4">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA4">
         <v>60</v>
@@ -1499,7 +1511,7 @@
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE4">
         <v>40</v>
@@ -1520,7 +1532,7 @@
         <v>36</v>
       </c>
       <c r="AK4">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1529,10 +1541,10 @@
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="AO4">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="AP4">
         <v>11.5</v>
@@ -1544,7 +1556,7 @@
         <v>19.5</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -1556,7 +1568,7 @@
         <v>12.5</v>
       </c>
       <c r="AW4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1568,43 +1580,43 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="BB4">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="BC4">
-        <v>19.5</v>
+        <v>8.6</v>
       </c>
       <c r="BD4">
         <v>28</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BF4">
         <v>16.5</v>
       </c>
       <c r="BG4">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
       </c>
       <c r="BK4">
-        <v>7.2</v>
+        <v>6</v>
       </c>
       <c r="BL4">
         <v>1000</v>
       </c>
       <c r="BM4">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN4">
         <v>5.4</v>
@@ -1613,34 +1625,34 @@
         <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BQ4">
-        <v>13.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BR4">
         <v>34</v>
       </c>
       <c r="BS4">
-        <v>23</v>
+        <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>26</v>
       </c>
       <c r="BW4">
-        <v>18.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BX4">
         <v>40</v>
       </c>
       <c r="BY4">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="BZ4">
         <v>0</v>
@@ -1649,7 +1661,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1657,241 +1669,241 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E5" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F5">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="G5">
         <v>1.93</v>
       </c>
       <c r="H5">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="I5">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K5">
         <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="O5">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.35</v>
+        <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V5">
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP5">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ5">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AR5">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="AS5">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>1.03</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV5">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="AX5">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY5">
-        <v>1.03</v>
+        <v>7.6</v>
       </c>
       <c r="AZ5">
-        <v>1.03</v>
+        <v>16</v>
       </c>
       <c r="BA5">
-        <v>1.03</v>
+        <v>4.1</v>
       </c>
       <c r="BB5">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="BC5">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="BD5">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BE5">
-        <v>1.03</v>
+        <v>4.2</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BN5">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BQ5">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BR5">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BT5">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="BU5">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
         <v>1000</v>
       </c>
       <c r="BY5">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA5">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB5" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1899,22 +1911,22 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="E6" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="F6">
         <v>3.95</v>
       </c>
       <c r="G6">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="H6">
         <v>1.92</v>
@@ -1929,211 +1941,211 @@
         <v>3.9</v>
       </c>
       <c r="L6">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N6">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="O6">
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.88</v>
+        <v>1.8</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.18</v>
+        <v>1.29</v>
       </c>
       <c r="S6">
-        <v>1.95</v>
+        <v>3.45</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="W6">
         <v>1.27</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AP6">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ6">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AR6">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AT6">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV6">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AW6">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AX6">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AY6">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AZ6">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BB6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BC6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BD6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BE6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH6">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>2.66</v>
+        <v>2.7</v>
       </c>
       <c r="BJ6">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK6">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN6">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO6">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="BP6">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BQ6">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BS6">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BT6">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BU6">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BV6">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="BW6">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BX6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ6">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA6">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2141,16 +2153,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C7" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D7" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E7" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F7">
         <v>4.1</v>
@@ -2171,7 +2183,7 @@
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="M7">
         <v>1.05</v>
@@ -2195,7 +2207,7 @@
         <v>3</v>
       </c>
       <c r="T7">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="U7">
         <v>2.16</v>
@@ -2204,7 +2216,7 @@
         <v>2</v>
       </c>
       <c r="W7">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="X7">
         <v>20</v>
@@ -2213,7 +2225,7 @@
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AA7">
         <v>25</v>
@@ -2285,7 +2297,7 @@
         <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="AY7">
         <v>13.5</v>
@@ -2294,22 +2306,22 @@
         <v>13.5</v>
       </c>
       <c r="BA7">
-        <v>1.03</v>
+        <v>4.4</v>
       </c>
       <c r="BB7">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BC7">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD7">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE7">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF7">
-        <v>38</v>
+        <v>4.6</v>
       </c>
       <c r="BG7">
         <v>9</v>
@@ -2324,13 +2336,13 @@
         <v>9.6</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BN7">
         <v>8</v>
@@ -2342,13 +2354,13 @@
         <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="BR7">
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="BT7">
         <v>4.8</v>
@@ -2360,22 +2372,22 @@
         <v>13</v>
       </c>
       <c r="BW7">
-        <v>9.800000000000001</v>
+        <v>6.6</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>15.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2383,16 +2395,16 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D8" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E8" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="F8">
         <v>2.94</v>
@@ -2404,25 +2416,25 @@
         <v>2.3</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J8">
         <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L8">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>2.08</v>
@@ -2431,193 +2443,193 @@
         <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V8">
         <v>1.64</v>
       </c>
       <c r="W8">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AP8">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS8">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AT8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AU8">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AV8">
-        <v>1.03</v>
+        <v>9</v>
       </c>
       <c r="AW8">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AX8">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AY8">
-        <v>1.03</v>
+        <v>10.5</v>
       </c>
       <c r="AZ8">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BB8">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC8">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD8">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE8">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BF8">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH8">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="BI8">
-        <v>1.01</v>
+        <v>3</v>
       </c>
       <c r="BJ8">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="BK8">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN8">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="BO8">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP8">
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BT8">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU8">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="BW8">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2625,22 +2637,22 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C9" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E9" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="F9">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H9">
         <v>6</v>
@@ -2655,7 +2667,7 @@
         <v>4.9</v>
       </c>
       <c r="L9">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="M9">
         <v>1.05</v>
@@ -2676,19 +2688,19 @@
         <v>1.41</v>
       </c>
       <c r="S9">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="T9">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
-        <v>1.86</v>
+        <v>1.98</v>
       </c>
       <c r="V9">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="X9">
         <v>21</v>
@@ -2751,10 +2763,10 @@
         <v>17.5</v>
       </c>
       <c r="AR9">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS9">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT9">
         <v>7</v>
@@ -2766,7 +2778,7 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AX9">
         <v>7.6</v>
@@ -2778,7 +2790,7 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BB9">
         <v>11.5</v>
@@ -2787,79 +2799,79 @@
         <v>12.5</v>
       </c>
       <c r="BD9">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE9">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF9">
         <v>6.4</v>
       </c>
       <c r="BG9">
-        <v>80</v>
+        <v>5</v>
       </c>
       <c r="BH9">
-        <v>1000</v>
+        <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ9">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK9">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BL9">
         <v>1000</v>
       </c>
       <c r="BM9">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN9">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BO9">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BQ9">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BR9">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BS9">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BT9">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BU9">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV9">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BW9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX9">
         <v>1000</v>
       </c>
       <c r="BY9">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ9">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="CA9">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2867,16 +2879,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C10" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D10" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="F10">
         <v>1.28</v>
@@ -2888,10 +2900,10 @@
         <v>11.5</v>
       </c>
       <c r="I10">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="J10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="K10">
         <v>6.6</v>
@@ -2909,10 +2921,10 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q10">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="R10">
         <v>1.47</v>
@@ -2921,13 +2933,13 @@
         <v>2.72</v>
       </c>
       <c r="T10">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="U10">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
       <c r="V10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W10">
         <v>3.85</v>
@@ -2990,13 +3002,13 @@
         <v>15</v>
       </c>
       <c r="AQ10">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="AR10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS10">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AT10">
         <v>6.2</v>
@@ -3005,10 +3017,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="AW10">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX10">
         <v>5.8</v>
@@ -3017,10 +3029,10 @@
         <v>8</v>
       </c>
       <c r="AZ10">
-        <v>1.03</v>
+        <v>23</v>
       </c>
       <c r="BA10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BB10">
         <v>7.8</v>
@@ -3029,16 +3041,16 @@
         <v>10.5</v>
       </c>
       <c r="BD10">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BE10">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF10">
-        <v>4.2</v>
+        <v>4.7</v>
       </c>
       <c r="BG10">
-        <v>85</v>
+        <v>4.9</v>
       </c>
       <c r="BH10">
         <v>4.8</v>
@@ -3050,13 +3062,13 @@
         <v>15.5</v>
       </c>
       <c r="BK10">
-        <v>9.4</v>
+        <v>3.7</v>
       </c>
       <c r="BL10">
         <v>1000</v>
       </c>
       <c r="BM10">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BN10">
         <v>4.3</v>
@@ -3074,34 +3086,34 @@
         <v>30</v>
       </c>
       <c r="BS10">
-        <v>17.5</v>
+        <v>4.2</v>
       </c>
       <c r="BT10">
         <v>18</v>
       </c>
       <c r="BU10">
-        <v>11</v>
+        <v>3.85</v>
       </c>
       <c r="BV10">
         <v>1000</v>
       </c>
       <c r="BW10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BX10">
         <v>120</v>
       </c>
       <c r="BY10">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BZ10">
         <v>14.5</v>
       </c>
       <c r="CA10">
-        <v>8.800000000000001</v>
+        <v>3.65</v>
       </c>
       <c r="CB10" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3109,276 +3121,276 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="D11" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.42</v>
       </c>
       <c r="G11">
+        <v>1.46</v>
+      </c>
+      <c r="H11">
+        <v>7</v>
+      </c>
+      <c r="I11">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="J11">
+        <v>5.4</v>
+      </c>
+      <c r="K11">
+        <v>6.4</v>
+      </c>
+      <c r="L11">
+        <v>1.19</v>
+      </c>
+      <c r="M11">
+        <v>1.01</v>
+      </c>
+      <c r="N11">
+        <v>7.4</v>
+      </c>
+      <c r="O11">
+        <v>1.12</v>
+      </c>
+      <c r="P11">
+        <v>3.1</v>
+      </c>
+      <c r="Q11">
+        <v>1.39</v>
+      </c>
+      <c r="R11">
+        <v>1.87</v>
+      </c>
+      <c r="S11">
+        <v>1.96</v>
+      </c>
+      <c r="T11">
+        <v>1.61</v>
+      </c>
+      <c r="U11">
+        <v>2.32</v>
+      </c>
+      <c r="V11">
+        <v>1.13</v>
+      </c>
+      <c r="W11">
+        <v>3.1</v>
+      </c>
+      <c r="X11">
+        <v>42</v>
+      </c>
+      <c r="Y11">
+        <v>44</v>
+      </c>
+      <c r="Z11">
+        <v>85</v>
+      </c>
+      <c r="AA11">
+        <v>220</v>
+      </c>
+      <c r="AB11">
+        <v>17</v>
+      </c>
+      <c r="AC11">
+        <v>17</v>
+      </c>
+      <c r="AD11">
+        <v>34</v>
+      </c>
+      <c r="AE11">
+        <v>100</v>
+      </c>
+      <c r="AF11">
+        <v>14.5</v>
+      </c>
+      <c r="AG11">
+        <v>13</v>
+      </c>
+      <c r="AH11">
+        <v>24</v>
+      </c>
+      <c r="AI11">
+        <v>75</v>
+      </c>
+      <c r="AJ11">
+        <v>16</v>
+      </c>
+      <c r="AK11">
+        <v>16</v>
+      </c>
+      <c r="AL11">
+        <v>29</v>
+      </c>
+      <c r="AM11">
+        <v>85</v>
+      </c>
+      <c r="AN11">
+        <v>4.3</v>
+      </c>
+      <c r="AO11">
+        <v>75</v>
+      </c>
+      <c r="AP11">
+        <v>5.4</v>
+      </c>
+      <c r="AQ11">
+        <v>5.5</v>
+      </c>
+      <c r="AR11">
+        <v>5.9</v>
+      </c>
+      <c r="AS11">
+        <v>6</v>
+      </c>
+      <c r="AT11">
+        <v>12.5</v>
+      </c>
+      <c r="AU11">
+        <v>11</v>
+      </c>
+      <c r="AV11">
+        <v>5.3</v>
+      </c>
+      <c r="AW11">
+        <v>5.9</v>
+      </c>
+      <c r="AX11">
+        <v>9.4</v>
+      </c>
+      <c r="AY11">
+        <v>9.4</v>
+      </c>
+      <c r="AZ11">
+        <v>17.5</v>
+      </c>
+      <c r="BA11">
+        <v>5.8</v>
+      </c>
+      <c r="BB11">
+        <v>10.5</v>
+      </c>
+      <c r="BC11">
+        <v>10.5</v>
+      </c>
+      <c r="BD11">
+        <v>19</v>
+      </c>
+      <c r="BE11">
+        <v>5.9</v>
+      </c>
+      <c r="BF11">
+        <v>3.4</v>
+      </c>
+      <c r="BG11">
+        <v>5.8</v>
+      </c>
+      <c r="BH11">
+        <v>6.2</v>
+      </c>
+      <c r="BI11">
+        <v>4.3</v>
+      </c>
+      <c r="BJ11">
+        <v>11.5</v>
+      </c>
+      <c r="BK11">
+        <v>3.65</v>
+      </c>
+      <c r="BL11">
         <v>1000</v>
       </c>
-      <c r="H11">
-        <v>1.04</v>
-      </c>
-      <c r="I11">
+      <c r="BM11">
+        <v>5</v>
+      </c>
+      <c r="BN11">
+        <v>5.2</v>
+      </c>
+      <c r="BO11">
+        <v>3.7</v>
+      </c>
+      <c r="BP11">
+        <v>9.4</v>
+      </c>
+      <c r="BQ11">
+        <v>3.4</v>
+      </c>
+      <c r="BR11">
+        <v>20</v>
+      </c>
+      <c r="BS11">
+        <v>4.2</v>
+      </c>
+      <c r="BT11">
+        <v>13.5</v>
+      </c>
+      <c r="BU11">
+        <v>3.8</v>
+      </c>
+      <c r="BV11">
+        <v>60</v>
+      </c>
+      <c r="BW11">
+        <v>4.9</v>
+      </c>
+      <c r="BX11">
         <v>1000</v>
       </c>
-      <c r="J11">
-        <v>1.01</v>
-      </c>
-      <c r="K11">
-        <v>1000</v>
-      </c>
-      <c r="L11">
-        <v>0</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11">
-        <v>0</v>
-      </c>
-      <c r="P11">
-        <v>1.24</v>
-      </c>
-      <c r="Q11">
-        <v>1.01</v>
-      </c>
-      <c r="R11">
-        <v>0</v>
-      </c>
-      <c r="S11">
-        <v>0</v>
-      </c>
-      <c r="T11">
-        <v>0</v>
-      </c>
-      <c r="U11">
-        <v>0</v>
-      </c>
-      <c r="V11">
-        <v>0</v>
-      </c>
-      <c r="W11">
-        <v>0</v>
-      </c>
-      <c r="X11">
-        <v>0</v>
-      </c>
-      <c r="Y11">
-        <v>0</v>
-      </c>
-      <c r="Z11">
-        <v>0</v>
-      </c>
-      <c r="AA11">
-        <v>0</v>
-      </c>
-      <c r="AB11">
-        <v>0</v>
-      </c>
-      <c r="AC11">
-        <v>0</v>
-      </c>
-      <c r="AD11">
-        <v>0</v>
-      </c>
-      <c r="AE11">
-        <v>0</v>
-      </c>
-      <c r="AF11">
-        <v>0</v>
-      </c>
-      <c r="AG11">
-        <v>0</v>
-      </c>
-      <c r="AH11">
-        <v>0</v>
-      </c>
-      <c r="AI11">
-        <v>0</v>
-      </c>
-      <c r="AJ11">
-        <v>0</v>
-      </c>
-      <c r="AK11">
-        <v>0</v>
-      </c>
-      <c r="AL11">
-        <v>0</v>
-      </c>
-      <c r="AM11">
-        <v>0</v>
-      </c>
-      <c r="AN11">
-        <v>0</v>
-      </c>
-      <c r="AO11">
-        <v>0</v>
-      </c>
-      <c r="AP11">
-        <v>0</v>
-      </c>
-      <c r="AQ11">
-        <v>0</v>
-      </c>
-      <c r="AR11">
-        <v>0</v>
-      </c>
-      <c r="AS11">
-        <v>0</v>
-      </c>
-      <c r="AT11">
-        <v>0</v>
-      </c>
-      <c r="AU11">
-        <v>0</v>
-      </c>
-      <c r="AV11">
-        <v>0</v>
-      </c>
-      <c r="AW11">
-        <v>0</v>
-      </c>
-      <c r="AX11">
-        <v>0</v>
-      </c>
-      <c r="AY11">
-        <v>0</v>
-      </c>
-      <c r="AZ11">
-        <v>0</v>
-      </c>
-      <c r="BA11">
-        <v>0</v>
-      </c>
-      <c r="BB11">
-        <v>0</v>
-      </c>
-      <c r="BC11">
-        <v>0</v>
-      </c>
-      <c r="BD11">
-        <v>0</v>
-      </c>
-      <c r="BE11">
-        <v>0</v>
-      </c>
-      <c r="BF11">
-        <v>0</v>
-      </c>
-      <c r="BG11">
-        <v>0</v>
-      </c>
-      <c r="BH11">
-        <v>0</v>
-      </c>
-      <c r="BI11">
-        <v>0</v>
-      </c>
-      <c r="BJ11">
-        <v>0</v>
-      </c>
-      <c r="BK11">
-        <v>0</v>
-      </c>
-      <c r="BL11">
-        <v>0</v>
-      </c>
-      <c r="BM11">
-        <v>0</v>
-      </c>
-      <c r="BN11">
-        <v>0</v>
-      </c>
-      <c r="BO11">
-        <v>0</v>
-      </c>
-      <c r="BP11">
-        <v>0</v>
-      </c>
-      <c r="BQ11">
-        <v>0</v>
-      </c>
-      <c r="BR11">
-        <v>0</v>
-      </c>
-      <c r="BS11">
-        <v>0</v>
-      </c>
-      <c r="BT11">
-        <v>0</v>
-      </c>
-      <c r="BU11">
-        <v>0</v>
-      </c>
-      <c r="BV11">
-        <v>0</v>
-      </c>
-      <c r="BW11">
-        <v>0</v>
-      </c>
-      <c r="BX11">
-        <v>0</v>
-      </c>
       <c r="BY11">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="CB11" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D12" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.11</v>
       </c>
       <c r="I12">
         <v>1000</v>
       </c>
       <c r="J12">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="K12">
-        <v>1000</v>
+        <v>950</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3585,7 +3597,249 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>111</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="13" spans="1:80">
+      <c r="A13" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" t="s">
+        <v>102</v>
+      </c>
+      <c r="E13" t="s">
+        <v>114</v>
+      </c>
+      <c r="F13">
+        <v>1.04</v>
+      </c>
+      <c r="G13">
+        <v>1000</v>
+      </c>
+      <c r="H13">
+        <v>1.04</v>
+      </c>
+      <c r="I13">
+        <v>1000</v>
+      </c>
+      <c r="J13">
+        <v>1.01</v>
+      </c>
+      <c r="K13">
+        <v>950</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>1.24</v>
+      </c>
+      <c r="Q13">
+        <v>1.01</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="138">
   <si>
     <t>League</t>
   </si>
@@ -268,6 +268,12 @@
     <t>Chinese Super League</t>
   </si>
   <si>
+    <t>Czech 2 Liga</t>
+  </si>
+  <si>
+    <t>Hungarian NB I</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -286,6 +292,18 @@
     <t>11:35:00</t>
   </si>
   <si>
+    <t>15:00:00</t>
+  </si>
+  <si>
+    <t>15:30:00</t>
+  </si>
+  <si>
+    <t>15:45:00</t>
+  </si>
+  <si>
+    <t>16:00:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -319,6 +337,30 @@
     <t>Beijing Guoan</t>
   </si>
   <si>
+    <t>Slavia Praha B</t>
+  </si>
+  <si>
+    <t>MTK Budapest</t>
+  </si>
+  <si>
+    <t>Vysocina Jihlava</t>
+  </si>
+  <si>
+    <t>Usti Nad Labem</t>
+  </si>
+  <si>
+    <t>Prostejov</t>
+  </si>
+  <si>
+    <t>SFC Opava</t>
+  </si>
+  <si>
+    <t>FC Sellier &amp; Bellot Vlasim</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
     <t>Afturelding</t>
   </si>
   <si>
@@ -355,13 +397,37 @@
     <t>Shenzhen Peng City</t>
   </si>
   <si>
+    <t>Trinec</t>
+  </si>
+  <si>
+    <t>Puskas Akademia</t>
+  </si>
+  <si>
+    <t>FK Pribram</t>
+  </si>
+  <si>
+    <t>Arsenal Ceska Lipa</t>
+  </si>
+  <si>
+    <t>MFK Karvina</t>
+  </si>
+  <si>
+    <t>SK Kladno</t>
+  </si>
+  <si>
+    <t>Zizkov</t>
+  </si>
+  <si>
+    <t>H Slavia Kromeriz</t>
+  </si>
+  <si>
     <t>Grindavik</t>
   </si>
   <si>
     <t>Fylkir</t>
   </si>
   <si>
-    <t>2026-08-05 10:26:28</t>
+    <t>2026-08-05 12:33:42</t>
   </si>
 </sst>
 </file>
@@ -693,7 +759,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB13"/>
+  <dimension ref="A1:CB21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -943,16 +1009,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="E2" t="s">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="F2">
         <v>1.6</v>
@@ -961,7 +1027,7 @@
         <v>1.74</v>
       </c>
       <c r="H2">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>7.6</v>
@@ -970,7 +1036,7 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -982,7 +1048,7 @@
         <v>2.8</v>
       </c>
       <c r="O2">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="P2">
         <v>1.72</v>
@@ -994,7 +1060,7 @@
         <v>1.27</v>
       </c>
       <c r="S2">
-        <v>1.05</v>
+        <v>4</v>
       </c>
       <c r="T2">
         <v>2.08</v>
@@ -1033,13 +1099,13 @@
         <v>150</v>
       </c>
       <c r="AF2">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
       </c>
       <c r="AH2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AI2">
         <v>150</v>
@@ -1063,58 +1129,58 @@
         <v>240</v>
       </c>
       <c r="AP2">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="AQ2">
-        <v>4.6</v>
+        <v>15.5</v>
       </c>
       <c r="AR2">
+        <v>5</v>
+      </c>
+      <c r="AS2">
         <v>5.3</v>
       </c>
-      <c r="AS2">
-        <v>5.6</v>
-      </c>
       <c r="AT2">
-        <v>3.2</v>
+        <v>5.2</v>
       </c>
       <c r="AU2">
-        <v>3.5</v>
+        <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>4.9</v>
+        <v>18.5</v>
       </c>
       <c r="AW2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AX2">
-        <v>3.55</v>
+        <v>6.6</v>
       </c>
       <c r="AY2">
-        <v>3.95</v>
+        <v>7.6</v>
       </c>
       <c r="AZ2">
-        <v>4.8</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB2">
-        <v>4.3</v>
+        <v>12</v>
       </c>
       <c r="BC2">
-        <v>4.6</v>
+        <v>17</v>
       </c>
       <c r="BD2">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BE2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BF2">
-        <v>4.2</v>
+        <v>9.4</v>
       </c>
       <c r="BG2">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="BH2">
         <v>3.65</v>
@@ -1177,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1185,16 +1251,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" t="s">
-        <v>104</v>
+        <v>118</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1206,16 +1272,16 @@
         <v>2</v>
       </c>
       <c r="I3">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J3">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="K3">
         <v>3.6</v>
       </c>
       <c r="L3">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1233,10 +1299,10 @@
         <v>2.08</v>
       </c>
       <c r="R3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="T3">
         <v>1.87</v>
@@ -1245,7 +1311,7 @@
         <v>1.98</v>
       </c>
       <c r="V3">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="W3">
         <v>1.28</v>
@@ -1254,19 +1320,19 @@
         <v>15</v>
       </c>
       <c r="Y3">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="Z3">
         <v>15</v>
       </c>
       <c r="AA3">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="AB3">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AD3">
         <v>13</v>
@@ -1275,10 +1341,10 @@
         <v>29</v>
       </c>
       <c r="AF3">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="AG3">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AH3">
         <v>24</v>
@@ -1290,31 +1356,31 @@
         <v>120</v>
       </c>
       <c r="AK3">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AL3">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AM3">
         <v>150</v>
       </c>
       <c r="AN3">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AO3">
         <v>22</v>
       </c>
       <c r="AP3">
-        <v>3.4</v>
+        <v>11</v>
       </c>
       <c r="AQ3">
         <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AS3">
-        <v>3.9</v>
+        <v>5.3</v>
       </c>
       <c r="AT3">
         <v>12</v>
@@ -1329,31 +1395,31 @@
         <v>20</v>
       </c>
       <c r="AX3">
-        <v>3.95</v>
+        <v>5.5</v>
       </c>
       <c r="AY3">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AZ3">
         <v>17</v>
       </c>
       <c r="BA3">
-        <v>4</v>
+        <v>5.9</v>
       </c>
       <c r="BB3">
-        <v>4.3</v>
+        <v>6.2</v>
       </c>
       <c r="BC3">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BD3">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BE3">
-        <v>4.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF3">
-        <v>4.2</v>
+        <v>6</v>
       </c>
       <c r="BG3">
         <v>13</v>
@@ -1362,55 +1428,55 @@
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.56</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BN3">
         <v>7.6</v>
       </c>
       <c r="BO3">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BP3">
         <v>38</v>
       </c>
       <c r="BQ3">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="BR3">
         <v>50</v>
       </c>
       <c r="BS3">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BU3">
         <v>3.65</v>
       </c>
       <c r="BV3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="BY3">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1419,7 +1485,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1427,91 +1493,91 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="E4" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="F4">
         <v>2.42</v>
       </c>
       <c r="G4">
-        <v>2.62</v>
+        <v>2.52</v>
       </c>
       <c r="H4">
-        <v>2.96</v>
+        <v>3.25</v>
       </c>
       <c r="I4">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K4">
         <v>3.6</v>
       </c>
       <c r="L4">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.35</v>
       </c>
       <c r="P4">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R4">
         <v>1.33</v>
       </c>
       <c r="S4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="U4">
         <v>2.1</v>
       </c>
       <c r="V4">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W4">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z4">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA4">
         <v>60</v>
       </c>
       <c r="AB4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AC4">
         <v>7.8</v>
       </c>
       <c r="AD4">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE4">
         <v>40</v>
@@ -1526,13 +1592,13 @@
         <v>17.5</v>
       </c>
       <c r="AI4">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="AJ4">
         <v>36</v>
       </c>
       <c r="AK4">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AL4">
         <v>42</v>
@@ -1541,22 +1607,22 @@
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="AO4">
         <v>38</v>
       </c>
       <c r="AP4">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AQ4">
         <v>10.5</v>
       </c>
       <c r="AR4">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AS4">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -1565,10 +1631,10 @@
         <v>6.8</v>
       </c>
       <c r="AV4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AW4">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AX4">
         <v>14</v>
@@ -1580,31 +1646,31 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
+        <v>10.5</v>
+      </c>
+      <c r="BB4">
+        <v>9.6</v>
+      </c>
+      <c r="BC4">
         <v>9</v>
       </c>
-      <c r="BB4">
-        <v>8.4</v>
-      </c>
-      <c r="BC4">
-        <v>8.6</v>
-      </c>
       <c r="BD4">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="BE4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BF4">
-        <v>16.5</v>
+        <v>20</v>
       </c>
       <c r="BG4">
-        <v>8.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
       </c>
       <c r="BI4">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="BJ4">
         <v>9.800000000000001</v>
@@ -1625,10 +1691,10 @@
         <v>4.1</v>
       </c>
       <c r="BP4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BQ4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BR4">
         <v>34</v>
@@ -1637,10 +1703,10 @@
         <v>10.5</v>
       </c>
       <c r="BT4">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BV4">
         <v>26</v>
@@ -1661,7 +1727,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1669,31 +1735,31 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D5" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>106</v>
+        <v>120</v>
       </c>
       <c r="F5">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="G5">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="H5">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I5">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="J5">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K5">
         <v>3.85</v>
@@ -1711,19 +1777,19 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q5">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R5">
         <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.9</v>
+        <v>3.55</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
         <v>1.87</v>
@@ -1846,31 +1912,31 @@
         <v>3.15</v>
       </c>
       <c r="BI5">
-        <v>2.6</v>
+        <v>2.84</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP5">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BR5">
         <v>32</v>
@@ -1879,7 +1945,7 @@
         <v>10</v>
       </c>
       <c r="BT5">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BU5">
         <v>5.4</v>
@@ -1888,10 +1954,10 @@
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BX5">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BY5">
         <v>12</v>
@@ -1900,10 +1966,10 @@
         <v>29</v>
       </c>
       <c r="CA5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1911,16 +1977,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="E6" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="F6">
         <v>3.95</v>
@@ -1938,10 +2004,10 @@
         <v>3.6</v>
       </c>
       <c r="K6">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -1953,13 +2019,13 @@
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="S6">
         <v>3.45</v>
@@ -1968,10 +2034,10 @@
         <v>1.8</v>
       </c>
       <c r="U6">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="V6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -2088,25 +2154,25 @@
         <v>3.9</v>
       </c>
       <c r="BI6">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BJ6">
         <v>12</v>
       </c>
       <c r="BK6">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BL6">
         <v>1000</v>
       </c>
       <c r="BM6">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="BN6">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BO6">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BP6">
         <v>44</v>
@@ -2115,19 +2181,19 @@
         <v>4.3</v>
       </c>
       <c r="BR6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS6">
         <v>4.4</v>
       </c>
       <c r="BT6">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BU6">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV6">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BW6">
         <v>3.75</v>
@@ -2142,10 +2208,10 @@
         <v>32</v>
       </c>
       <c r="CA6">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2153,16 +2219,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="E7" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="F7">
         <v>4.1</v>
@@ -2183,10 +2249,10 @@
         <v>4.1</v>
       </c>
       <c r="L7">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="M7">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N7">
         <v>4.1</v>
@@ -2297,7 +2363,7 @@
         <v>14.5</v>
       </c>
       <c r="AX7">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AY7">
         <v>13.5</v>
@@ -2315,7 +2381,7 @@
         <v>4.6</v>
       </c>
       <c r="BD7">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE7">
         <v>4.8</v>
@@ -2330,7 +2396,7 @@
         <v>3.75</v>
       </c>
       <c r="BI7">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
         <v>9.6</v>
@@ -2387,7 +2453,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2395,28 +2461,28 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C8" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="E8" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="F8">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="G8">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="H8">
         <v>2.3</v>
       </c>
       <c r="I8">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="J8">
         <v>3.5</v>
@@ -2428,34 +2494,34 @@
         <v>1.32</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N8">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="O8">
         <v>1.26</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q8">
         <v>1.76</v>
       </c>
       <c r="R8">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S8">
-        <v>2.92</v>
+        <v>2.98</v>
       </c>
       <c r="T8">
         <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="W8">
         <v>1.42</v>
@@ -2491,7 +2557,7 @@
         <v>16</v>
       </c>
       <c r="AH8">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="AI8">
         <v>42</v>
@@ -2524,7 +2590,7 @@
         <v>12.5</v>
       </c>
       <c r="AS8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -2548,19 +2614,19 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
+        <v>4.5</v>
+      </c>
+      <c r="BB8">
         <v>4.6</v>
       </c>
-      <c r="BB8">
-        <v>4.7</v>
-      </c>
       <c r="BC8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BD8">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BE8">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
         <v>20</v>
@@ -2629,7 +2695,7 @@
         <v>7.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2637,16 +2703,16 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C9" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="E9" t="s">
-        <v>110</v>
+        <v>124</v>
       </c>
       <c r="F9">
         <v>1.56</v>
@@ -2661,7 +2727,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
         <v>4.9</v>
@@ -2679,28 +2745,28 @@
         <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.76</v>
+        <v>1.68</v>
       </c>
       <c r="R9">
         <v>1.41</v>
       </c>
       <c r="S9">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U9">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V9">
         <v>1.15</v>
       </c>
       <c r="W9">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="X9">
         <v>21</v>
@@ -2814,7 +2880,7 @@
         <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9">
         <v>11</v>
@@ -2832,7 +2898,7 @@
         <v>4.3</v>
       </c>
       <c r="BO9">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BP9">
         <v>10.5</v>
@@ -2871,7 +2937,7 @@
         <v>6.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2879,16 +2945,16 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D10" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E10" t="s">
-        <v>111</v>
+        <v>125</v>
       </c>
       <c r="F10">
         <v>1.28</v>
@@ -2897,13 +2963,13 @@
         <v>1.35</v>
       </c>
       <c r="H10">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="I10">
         <v>15</v>
       </c>
       <c r="J10">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="K10">
         <v>6.6</v>
@@ -2921,7 +2987,7 @@
         <v>1.23</v>
       </c>
       <c r="P10">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="Q10">
         <v>1.67</v>
@@ -2930,13 +2996,13 @@
         <v>1.47</v>
       </c>
       <c r="S10">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="T10">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="U10">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="V10">
         <v>1.07</v>
@@ -2951,16 +3017,16 @@
         <v>46</v>
       </c>
       <c r="Z10">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC10">
-        <v>16.5</v>
+        <v>14</v>
       </c>
       <c r="AD10">
         <v>60</v>
@@ -2969,31 +3035,31 @@
         <v>290</v>
       </c>
       <c r="AF10">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AG10">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AH10">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="AI10">
         <v>220</v>
       </c>
       <c r="AJ10">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="AK10">
-        <v>18</v>
+        <v>15.5</v>
       </c>
       <c r="AL10">
         <v>55</v>
       </c>
       <c r="AM10">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="AN10">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="AO10">
         <v>440</v>
@@ -3002,13 +3068,13 @@
         <v>15</v>
       </c>
       <c r="AQ10">
-        <v>4.5</v>
+        <v>6.6</v>
       </c>
       <c r="AR10">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="AS10">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="AT10">
         <v>6.2</v>
@@ -3017,10 +3083,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>4.6</v>
+        <v>6.8</v>
       </c>
       <c r="AW10">
-        <v>4.9</v>
+        <v>7.4</v>
       </c>
       <c r="AX10">
         <v>5.8</v>
@@ -3029,28 +3095,28 @@
         <v>8</v>
       </c>
       <c r="AZ10">
-        <v>23</v>
+        <v>6.2</v>
       </c>
       <c r="BA10">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BB10">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BC10">
         <v>10.5</v>
       </c>
       <c r="BD10">
-        <v>4.5</v>
+        <v>6.8</v>
       </c>
       <c r="BE10">
-        <v>4.8</v>
+        <v>7.4</v>
       </c>
       <c r="BF10">
         <v>4.7</v>
       </c>
       <c r="BG10">
-        <v>4.9</v>
+        <v>7.6</v>
       </c>
       <c r="BH10">
         <v>4.8</v>
@@ -3113,7 +3179,7 @@
         <v>3.65</v>
       </c>
       <c r="CB10" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3121,28 +3187,28 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C11" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D11" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E11" t="s">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F11">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="G11">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="H11">
         <v>7</v>
       </c>
       <c r="I11">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J11">
         <v>5.4</v>
@@ -3157,7 +3223,7 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="O11">
         <v>1.12</v>
@@ -3166,16 +3232,16 @@
         <v>3.1</v>
       </c>
       <c r="Q11">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="R11">
         <v>1.87</v>
       </c>
       <c r="S11">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="T11">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="U11">
         <v>2.32</v>
@@ -3187,10 +3253,10 @@
         <v>3.1</v>
       </c>
       <c r="X11">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y11">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="Z11">
         <v>85</v>
@@ -3199,16 +3265,16 @@
         <v>220</v>
       </c>
       <c r="AB11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AC11">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AD11">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE11">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF11">
         <v>14.5</v>
@@ -3223,7 +3289,7 @@
         <v>75</v>
       </c>
       <c r="AJ11">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="AK11">
         <v>16</v>
@@ -3235,37 +3301,37 @@
         <v>85</v>
       </c>
       <c r="AN11">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AO11">
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="AQ11">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
       <c r="AR11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AS11">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="AT11">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU11">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV11">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="AW11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX11">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AY11">
         <v>9.4</v>
@@ -3274,88 +3340,88 @@
         <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BB11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BC11">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD11">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="BE11">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF11">
         <v>3.4</v>
       </c>
       <c r="BG11">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="BH11">
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
       </c>
       <c r="BK11">
+        <v>3.7</v>
+      </c>
+      <c r="BL11">
+        <v>1000</v>
+      </c>
+      <c r="BM11">
+        <v>5.1</v>
+      </c>
+      <c r="BN11">
+        <v>5.1</v>
+      </c>
+      <c r="BO11">
         <v>3.65</v>
-      </c>
-      <c r="BL11">
-        <v>1000</v>
-      </c>
-      <c r="BM11">
-        <v>5</v>
-      </c>
-      <c r="BN11">
-        <v>5.2</v>
-      </c>
-      <c r="BO11">
-        <v>3.7</v>
       </c>
       <c r="BP11">
         <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="BR11">
         <v>20</v>
       </c>
       <c r="BS11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BV11">
         <v>60</v>
       </c>
       <c r="BW11">
+        <v>5</v>
+      </c>
+      <c r="BX11">
+        <v>1000</v>
+      </c>
+      <c r="BY11">
         <v>4.9</v>
-      </c>
-      <c r="BX11">
-        <v>1000</v>
-      </c>
-      <c r="BY11">
-        <v>4.8</v>
       </c>
       <c r="BZ11">
         <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3363,483 +3429,2419 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C12" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D12" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="E12" t="s">
-        <v>113</v>
+        <v>127</v>
       </c>
       <c r="F12">
+        <v>1.75</v>
+      </c>
+      <c r="G12">
+        <v>2.02</v>
+      </c>
+      <c r="H12">
+        <v>3.9</v>
+      </c>
+      <c r="I12">
+        <v>5.6</v>
+      </c>
+      <c r="J12">
+        <v>3.75</v>
+      </c>
+      <c r="K12">
+        <v>4.5</v>
+      </c>
+      <c r="L12">
+        <v>1.01</v>
+      </c>
+      <c r="M12">
         <v>1.05</v>
       </c>
-      <c r="G12">
-        <v>10.5</v>
-      </c>
-      <c r="H12">
-        <v>1.11</v>
-      </c>
-      <c r="I12">
-        <v>1000</v>
-      </c>
-      <c r="J12">
-        <v>1.1</v>
-      </c>
-      <c r="K12">
-        <v>950</v>
-      </c>
-      <c r="L12">
-        <v>0</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
       <c r="N12">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P12">
-        <v>1.24</v>
+        <v>1.98</v>
       </c>
       <c r="Q12">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE12">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ12">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA12">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>115</v>
+        <v>137</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
+        <v>85</v>
+      </c>
+      <c r="B13" t="s">
+        <v>87</v>
+      </c>
+      <c r="C13" t="s">
+        <v>93</v>
+      </c>
+      <c r="D13" t="s">
+        <v>108</v>
+      </c>
+      <c r="E13" t="s">
+        <v>128</v>
+      </c>
+      <c r="F13">
+        <v>2.72</v>
+      </c>
+      <c r="G13">
+        <v>3.1</v>
+      </c>
+      <c r="H13">
+        <v>2.44</v>
+      </c>
+      <c r="I13">
+        <v>2.84</v>
+      </c>
+      <c r="J13">
+        <v>3.6</v>
+      </c>
+      <c r="K13">
+        <v>3.9</v>
+      </c>
+      <c r="L13">
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <v>0</v>
+      </c>
+      <c r="P13">
+        <v>2.22</v>
+      </c>
+      <c r="Q13">
+        <v>1.68</v>
+      </c>
+      <c r="R13">
+        <v>0</v>
+      </c>
+      <c r="S13">
+        <v>0</v>
+      </c>
+      <c r="T13">
+        <v>0</v>
+      </c>
+      <c r="U13">
+        <v>0</v>
+      </c>
+      <c r="V13">
+        <v>0</v>
+      </c>
+      <c r="W13">
+        <v>0</v>
+      </c>
+      <c r="X13">
+        <v>0</v>
+      </c>
+      <c r="Y13">
+        <v>0</v>
+      </c>
+      <c r="Z13">
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <v>0</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0</v>
+      </c>
+      <c r="AI13">
+        <v>0</v>
+      </c>
+      <c r="AJ13">
+        <v>0</v>
+      </c>
+      <c r="AK13">
+        <v>0</v>
+      </c>
+      <c r="AL13">
+        <v>0</v>
+      </c>
+      <c r="AM13">
+        <v>0</v>
+      </c>
+      <c r="AN13">
+        <v>0</v>
+      </c>
+      <c r="AO13">
+        <v>0</v>
+      </c>
+      <c r="AP13">
+        <v>0</v>
+      </c>
+      <c r="AQ13">
+        <v>0</v>
+      </c>
+      <c r="AR13">
+        <v>0</v>
+      </c>
+      <c r="AS13">
+        <v>0</v>
+      </c>
+      <c r="AT13">
+        <v>0</v>
+      </c>
+      <c r="AU13">
+        <v>0</v>
+      </c>
+      <c r="AV13">
+        <v>0</v>
+      </c>
+      <c r="AW13">
+        <v>0</v>
+      </c>
+      <c r="AX13">
+        <v>0</v>
+      </c>
+      <c r="AY13">
+        <v>0</v>
+      </c>
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+      <c r="BA13">
+        <v>0</v>
+      </c>
+      <c r="BB13">
+        <v>0</v>
+      </c>
+      <c r="BC13">
+        <v>0</v>
+      </c>
+      <c r="BD13">
+        <v>0</v>
+      </c>
+      <c r="BE13">
+        <v>0</v>
+      </c>
+      <c r="BF13">
+        <v>0</v>
+      </c>
+      <c r="BG13">
+        <v>0</v>
+      </c>
+      <c r="BH13">
+        <v>0</v>
+      </c>
+      <c r="BI13">
+        <v>0</v>
+      </c>
+      <c r="BJ13">
+        <v>0</v>
+      </c>
+      <c r="BK13">
+        <v>0</v>
+      </c>
+      <c r="BL13">
+        <v>0</v>
+      </c>
+      <c r="BM13">
+        <v>0</v>
+      </c>
+      <c r="BN13">
+        <v>0</v>
+      </c>
+      <c r="BO13">
+        <v>0</v>
+      </c>
+      <c r="BP13">
+        <v>0</v>
+      </c>
+      <c r="BQ13">
+        <v>0</v>
+      </c>
+      <c r="BR13">
+        <v>0</v>
+      </c>
+      <c r="BS13">
+        <v>0</v>
+      </c>
+      <c r="BT13">
+        <v>0</v>
+      </c>
+      <c r="BU13">
+        <v>0</v>
+      </c>
+      <c r="BV13">
+        <v>0</v>
+      </c>
+      <c r="BW13">
+        <v>0</v>
+      </c>
+      <c r="BX13">
+        <v>0</v>
+      </c>
+      <c r="BY13">
+        <v>0</v>
+      </c>
+      <c r="BZ13">
+        <v>0</v>
+      </c>
+      <c r="CA13">
+        <v>0</v>
+      </c>
+      <c r="CB13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:80">
+      <c r="A14" t="s">
         <v>84</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C14" t="s">
+        <v>94</v>
+      </c>
+      <c r="D14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E14" t="s">
+        <v>129</v>
+      </c>
+      <c r="F14">
+        <v>2.02</v>
+      </c>
+      <c r="G14">
+        <v>2.46</v>
+      </c>
+      <c r="H14">
+        <v>3.2</v>
+      </c>
+      <c r="I14">
+        <v>4.3</v>
+      </c>
+      <c r="J14">
+        <v>3</v>
+      </c>
+      <c r="K14">
+        <v>4.1</v>
+      </c>
+      <c r="L14">
+        <v>1.39</v>
+      </c>
+      <c r="M14">
+        <v>1.07</v>
+      </c>
+      <c r="N14">
+        <v>3.15</v>
+      </c>
+      <c r="O14">
+        <v>1.31</v>
+      </c>
+      <c r="P14">
+        <v>1.74</v>
+      </c>
+      <c r="Q14">
+        <v>1.87</v>
+      </c>
+      <c r="R14">
+        <v>1.3</v>
+      </c>
+      <c r="S14">
+        <v>3</v>
+      </c>
+      <c r="T14">
+        <v>1.73</v>
+      </c>
+      <c r="U14">
+        <v>1.96</v>
+      </c>
+      <c r="V14">
+        <v>1.3</v>
+      </c>
+      <c r="W14">
+        <v>1.68</v>
+      </c>
+      <c r="X14">
+        <v>15.5</v>
+      </c>
+      <c r="Y14">
+        <v>15.5</v>
+      </c>
+      <c r="Z14">
+        <v>32</v>
+      </c>
+      <c r="AA14">
         <v>85</v>
       </c>
-      <c r="C13" t="s">
+      <c r="AB14">
+        <v>11</v>
+      </c>
+      <c r="AC14">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD14">
+        <v>18</v>
+      </c>
+      <c r="AE14">
+        <v>55</v>
+      </c>
+      <c r="AF14">
+        <v>16</v>
+      </c>
+      <c r="AG14">
+        <v>13</v>
+      </c>
+      <c r="AH14">
+        <v>21</v>
+      </c>
+      <c r="AI14">
+        <v>65</v>
+      </c>
+      <c r="AJ14">
+        <v>34</v>
+      </c>
+      <c r="AK14">
+        <v>29</v>
+      </c>
+      <c r="AL14">
+        <v>46</v>
+      </c>
+      <c r="AM14">
+        <v>120</v>
+      </c>
+      <c r="AN14">
+        <v>22</v>
+      </c>
+      <c r="AO14">
+        <v>60</v>
+      </c>
+      <c r="AP14">
+        <v>1.01</v>
+      </c>
+      <c r="AQ14">
+        <v>1.01</v>
+      </c>
+      <c r="AR14">
+        <v>1.01</v>
+      </c>
+      <c r="AS14">
+        <v>1.03</v>
+      </c>
+      <c r="AT14">
+        <v>1.01</v>
+      </c>
+      <c r="AU14">
+        <v>1.01</v>
+      </c>
+      <c r="AV14">
+        <v>1.01</v>
+      </c>
+      <c r="AW14">
+        <v>1.01</v>
+      </c>
+      <c r="AX14">
+        <v>1.01</v>
+      </c>
+      <c r="AY14">
+        <v>1.01</v>
+      </c>
+      <c r="AZ14">
+        <v>1.01</v>
+      </c>
+      <c r="BA14">
+        <v>1.03</v>
+      </c>
+      <c r="BB14">
+        <v>1.01</v>
+      </c>
+      <c r="BC14">
+        <v>1.01</v>
+      </c>
+      <c r="BD14">
+        <v>1.01</v>
+      </c>
+      <c r="BE14">
+        <v>1.03</v>
+      </c>
+      <c r="BF14">
+        <v>1.01</v>
+      </c>
+      <c r="BG14">
+        <v>1.01</v>
+      </c>
+      <c r="BH14">
+        <v>3.6</v>
+      </c>
+      <c r="BI14">
+        <v>2.74</v>
+      </c>
+      <c r="BJ14">
+        <v>11</v>
+      </c>
+      <c r="BK14">
+        <v>1.01</v>
+      </c>
+      <c r="BL14">
+        <v>1000</v>
+      </c>
+      <c r="BM14">
+        <v>1.01</v>
+      </c>
+      <c r="BN14">
+        <v>5.4</v>
+      </c>
+      <c r="BO14">
+        <v>1.01</v>
+      </c>
+      <c r="BP14">
+        <v>18</v>
+      </c>
+      <c r="BQ14">
+        <v>1.01</v>
+      </c>
+      <c r="BR14">
+        <v>34</v>
+      </c>
+      <c r="BS14">
+        <v>1.01</v>
+      </c>
+      <c r="BT14">
+        <v>7.6</v>
+      </c>
+      <c r="BU14">
+        <v>1.01</v>
+      </c>
+      <c r="BV14">
+        <v>34</v>
+      </c>
+      <c r="BW14">
+        <v>1.01</v>
+      </c>
+      <c r="BX14">
+        <v>1000</v>
+      </c>
+      <c r="BY14">
+        <v>1.01</v>
+      </c>
+      <c r="BZ14">
+        <v>32</v>
+      </c>
+      <c r="CA14">
+        <v>1.01</v>
+      </c>
+      <c r="CB14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:80">
+      <c r="A15" t="s">
+        <v>84</v>
+      </c>
+      <c r="B15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" t="s">
+        <v>95</v>
+      </c>
+      <c r="D15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15">
+        <v>1.61</v>
+      </c>
+      <c r="G15">
+        <v>1.94</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>6.6</v>
+      </c>
+      <c r="J15">
+        <v>3.8</v>
+      </c>
+      <c r="K15">
+        <v>5.1</v>
+      </c>
+      <c r="L15">
+        <v>1.26</v>
+      </c>
+      <c r="M15">
+        <v>1.04</v>
+      </c>
+      <c r="N15">
+        <v>1.01</v>
+      </c>
+      <c r="O15">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>2.08</v>
+      </c>
+      <c r="Q15">
+        <v>1.53</v>
+      </c>
+      <c r="R15">
+        <v>1.48</v>
+      </c>
+      <c r="S15">
+        <v>2.1</v>
+      </c>
+      <c r="T15">
+        <v>1.63</v>
+      </c>
+      <c r="U15">
+        <v>2.12</v>
+      </c>
+      <c r="V15">
+        <v>1.18</v>
+      </c>
+      <c r="W15">
+        <v>2.06</v>
+      </c>
+      <c r="X15">
+        <v>27</v>
+      </c>
+      <c r="Y15">
+        <v>27</v>
+      </c>
+      <c r="Z15">
+        <v>55</v>
+      </c>
+      <c r="AA15">
+        <v>140</v>
+      </c>
+      <c r="AB15">
+        <v>13.5</v>
+      </c>
+      <c r="AC15">
+        <v>12.5</v>
+      </c>
+      <c r="AD15">
+        <v>25</v>
+      </c>
+      <c r="AE15">
+        <v>75</v>
+      </c>
+      <c r="AF15">
+        <v>14.5</v>
+      </c>
+      <c r="AG15">
+        <v>12.5</v>
+      </c>
+      <c r="AH15">
+        <v>22</v>
+      </c>
+      <c r="AI15">
+        <v>70</v>
+      </c>
+      <c r="AJ15">
+        <v>22</v>
+      </c>
+      <c r="AK15">
+        <v>21</v>
+      </c>
+      <c r="AL15">
+        <v>36</v>
+      </c>
+      <c r="AM15">
+        <v>100</v>
+      </c>
+      <c r="AN15">
+        <v>9.6</v>
+      </c>
+      <c r="AO15">
+        <v>65</v>
+      </c>
+      <c r="AP15">
+        <v>1.03</v>
+      </c>
+      <c r="AQ15">
+        <v>1.03</v>
+      </c>
+      <c r="AR15">
+        <v>1.03</v>
+      </c>
+      <c r="AS15">
+        <v>1.03</v>
+      </c>
+      <c r="AT15">
+        <v>1.03</v>
+      </c>
+      <c r="AU15">
+        <v>1.03</v>
+      </c>
+      <c r="AV15">
+        <v>1.03</v>
+      </c>
+      <c r="AW15">
+        <v>1.03</v>
+      </c>
+      <c r="AX15">
+        <v>1.03</v>
+      </c>
+      <c r="AY15">
+        <v>1.03</v>
+      </c>
+      <c r="AZ15">
+        <v>1.03</v>
+      </c>
+      <c r="BA15">
+        <v>1.03</v>
+      </c>
+      <c r="BB15">
+        <v>1.03</v>
+      </c>
+      <c r="BC15">
+        <v>1.03</v>
+      </c>
+      <c r="BD15">
+        <v>1.03</v>
+      </c>
+      <c r="BE15">
+        <v>1.03</v>
+      </c>
+      <c r="BF15">
+        <v>6</v>
+      </c>
+      <c r="BG15">
+        <v>10</v>
+      </c>
+      <c r="BH15">
+        <v>4.5</v>
+      </c>
+      <c r="BI15">
+        <v>1.01</v>
+      </c>
+      <c r="BJ15">
+        <v>10.5</v>
+      </c>
+      <c r="BK15">
+        <v>1.01</v>
+      </c>
+      <c r="BL15">
+        <v>1000</v>
+      </c>
+      <c r="BM15">
+        <v>1.01</v>
+      </c>
+      <c r="BN15">
+        <v>5</v>
+      </c>
+      <c r="BO15">
+        <v>1.01</v>
+      </c>
+      <c r="BP15">
+        <v>12</v>
+      </c>
+      <c r="BQ15">
+        <v>1.01</v>
+      </c>
+      <c r="BR15">
+        <v>25</v>
+      </c>
+      <c r="BS15">
+        <v>1.01</v>
+      </c>
+      <c r="BT15">
+        <v>9.6</v>
+      </c>
+      <c r="BU15">
+        <v>1.01</v>
+      </c>
+      <c r="BV15">
+        <v>42</v>
+      </c>
+      <c r="BW15">
+        <v>1.01</v>
+      </c>
+      <c r="BX15">
+        <v>46</v>
+      </c>
+      <c r="BY15">
+        <v>1.01</v>
+      </c>
+      <c r="BZ15">
+        <v>17.5</v>
+      </c>
+      <c r="CA15">
+        <v>1.01</v>
+      </c>
+      <c r="CB15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:80">
+      <c r="A16" t="s">
+        <v>84</v>
+      </c>
+      <c r="B16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C16" t="s">
+        <v>95</v>
+      </c>
+      <c r="D16" t="s">
+        <v>111</v>
+      </c>
+      <c r="E16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F16">
+        <v>4.4</v>
+      </c>
+      <c r="G16">
+        <v>6.4</v>
+      </c>
+      <c r="H16">
+        <v>1.65</v>
+      </c>
+      <c r="I16">
+        <v>1.96</v>
+      </c>
+      <c r="J16">
+        <v>3</v>
+      </c>
+      <c r="K16">
+        <v>4.8</v>
+      </c>
+      <c r="L16">
+        <v>1.33</v>
+      </c>
+      <c r="M16">
+        <v>1.05</v>
+      </c>
+      <c r="N16">
+        <v>3.45</v>
+      </c>
+      <c r="O16">
+        <v>1.26</v>
+      </c>
+      <c r="P16">
+        <v>1.89</v>
+      </c>
+      <c r="Q16">
+        <v>1.73</v>
+      </c>
+      <c r="R16">
+        <v>1.34</v>
+      </c>
+      <c r="S16">
+        <v>2.84</v>
+      </c>
+      <c r="T16">
+        <v>1.71</v>
+      </c>
+      <c r="U16">
+        <v>1.96</v>
+      </c>
+      <c r="V16">
+        <v>2.04</v>
+      </c>
+      <c r="W16">
+        <v>1.18</v>
+      </c>
+      <c r="X16">
+        <v>19</v>
+      </c>
+      <c r="Y16">
+        <v>10.5</v>
+      </c>
+      <c r="Z16">
+        <v>13</v>
+      </c>
+      <c r="AA16">
+        <v>22</v>
+      </c>
+      <c r="AB16">
+        <v>22</v>
+      </c>
+      <c r="AC16">
+        <v>10.5</v>
+      </c>
+      <c r="AD16">
+        <v>12</v>
+      </c>
+      <c r="AE16">
+        <v>22</v>
+      </c>
+      <c r="AF16">
+        <v>48</v>
+      </c>
+      <c r="AG16">
+        <v>24</v>
+      </c>
+      <c r="AH16">
+        <v>23</v>
+      </c>
+      <c r="AI16">
+        <v>40</v>
+      </c>
+      <c r="AJ16">
+        <v>150</v>
+      </c>
+      <c r="AK16">
+        <v>80</v>
+      </c>
+      <c r="AL16">
+        <v>80</v>
+      </c>
+      <c r="AM16">
+        <v>120</v>
+      </c>
+      <c r="AN16">
         <v>90</v>
       </c>
-      <c r="D13" t="s">
-        <v>102</v>
-      </c>
-      <c r="E13" t="s">
+      <c r="AO16">
+        <v>12.5</v>
+      </c>
+      <c r="AP16">
+        <v>1.01</v>
+      </c>
+      <c r="AQ16">
+        <v>1.01</v>
+      </c>
+      <c r="AR16">
+        <v>1.01</v>
+      </c>
+      <c r="AS16">
+        <v>1.01</v>
+      </c>
+      <c r="AT16">
+        <v>1.01</v>
+      </c>
+      <c r="AU16">
+        <v>1.01</v>
+      </c>
+      <c r="AV16">
+        <v>1.01</v>
+      </c>
+      <c r="AW16">
+        <v>1.01</v>
+      </c>
+      <c r="AX16">
+        <v>1.01</v>
+      </c>
+      <c r="AY16">
+        <v>1.01</v>
+      </c>
+      <c r="AZ16">
+        <v>1.01</v>
+      </c>
+      <c r="BA16">
+        <v>1.01</v>
+      </c>
+      <c r="BB16">
+        <v>1.03</v>
+      </c>
+      <c r="BC16">
+        <v>1.03</v>
+      </c>
+      <c r="BD16">
+        <v>1.03</v>
+      </c>
+      <c r="BE16">
+        <v>1.03</v>
+      </c>
+      <c r="BF16">
+        <v>1.01</v>
+      </c>
+      <c r="BG16">
+        <v>1.01</v>
+      </c>
+      <c r="BH16">
+        <v>4.1</v>
+      </c>
+      <c r="BI16">
+        <v>1.01</v>
+      </c>
+      <c r="BJ16">
+        <v>11.5</v>
+      </c>
+      <c r="BK16">
+        <v>1.01</v>
+      </c>
+      <c r="BL16">
+        <v>1000</v>
+      </c>
+      <c r="BM16">
+        <v>1.01</v>
+      </c>
+      <c r="BN16">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO16">
+        <v>1.01</v>
+      </c>
+      <c r="BP16">
+        <v>50</v>
+      </c>
+      <c r="BQ16">
+        <v>1.01</v>
+      </c>
+      <c r="BR16">
+        <v>60</v>
+      </c>
+      <c r="BS16">
+        <v>1.01</v>
+      </c>
+      <c r="BT16">
+        <v>5</v>
+      </c>
+      <c r="BU16">
+        <v>1.01</v>
+      </c>
+      <c r="BV16">
+        <v>13.5</v>
+      </c>
+      <c r="BW16">
+        <v>1.01</v>
+      </c>
+      <c r="BX16">
+        <v>30</v>
+      </c>
+      <c r="BY16">
+        <v>1.01</v>
+      </c>
+      <c r="BZ16">
+        <v>24</v>
+      </c>
+      <c r="CA16">
+        <v>1.01</v>
+      </c>
+      <c r="CB16" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:80">
+      <c r="A17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D17" t="s">
+        <v>112</v>
+      </c>
+      <c r="E17" t="s">
+        <v>132</v>
+      </c>
+      <c r="F17">
+        <v>1.48</v>
+      </c>
+      <c r="G17">
+        <v>1.68</v>
+      </c>
+      <c r="H17">
+        <v>1.04</v>
+      </c>
+      <c r="I17">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J17">
+        <v>3.35</v>
+      </c>
+      <c r="K17">
+        <v>5.4</v>
+      </c>
+      <c r="L17">
+        <v>1.32</v>
+      </c>
+      <c r="M17">
+        <v>1.06</v>
+      </c>
+      <c r="N17">
+        <v>3.4</v>
+      </c>
+      <c r="O17">
+        <v>1.29</v>
+      </c>
+      <c r="P17">
+        <v>1.89</v>
+      </c>
+      <c r="Q17">
+        <v>1.73</v>
+      </c>
+      <c r="R17">
+        <v>1.34</v>
+      </c>
+      <c r="S17">
+        <v>2.88</v>
+      </c>
+      <c r="T17">
+        <v>1.92</v>
+      </c>
+      <c r="U17">
+        <v>1.84</v>
+      </c>
+      <c r="V17">
+        <v>1.12</v>
+      </c>
+      <c r="W17">
+        <v>2.46</v>
+      </c>
+      <c r="X17">
+        <v>19.5</v>
+      </c>
+      <c r="Y17">
+        <v>28</v>
+      </c>
+      <c r="Z17">
+        <v>75</v>
+      </c>
+      <c r="AA17">
+        <v>280</v>
+      </c>
+      <c r="AB17">
+        <v>9.4</v>
+      </c>
+      <c r="AC17">
+        <v>12</v>
+      </c>
+      <c r="AD17">
+        <v>34</v>
+      </c>
+      <c r="AE17">
+        <v>140</v>
+      </c>
+      <c r="AF17">
+        <v>10.5</v>
+      </c>
+      <c r="AG17">
+        <v>11.5</v>
+      </c>
+      <c r="AH17">
+        <v>28</v>
+      </c>
+      <c r="AI17">
+        <v>120</v>
+      </c>
+      <c r="AJ17">
+        <v>16.5</v>
+      </c>
+      <c r="AK17">
+        <v>19.5</v>
+      </c>
+      <c r="AL17">
+        <v>44</v>
+      </c>
+      <c r="AM17">
+        <v>160</v>
+      </c>
+      <c r="AN17">
+        <v>9.6</v>
+      </c>
+      <c r="AO17">
+        <v>180</v>
+      </c>
+      <c r="AP17">
+        <v>1.01</v>
+      </c>
+      <c r="AQ17">
+        <v>1.01</v>
+      </c>
+      <c r="AR17">
+        <v>1.03</v>
+      </c>
+      <c r="AS17">
+        <v>1.03</v>
+      </c>
+      <c r="AT17">
+        <v>1.01</v>
+      </c>
+      <c r="AU17">
+        <v>1.01</v>
+      </c>
+      <c r="AV17">
+        <v>1.01</v>
+      </c>
+      <c r="AW17">
+        <v>1.03</v>
+      </c>
+      <c r="AX17">
+        <v>1.01</v>
+      </c>
+      <c r="AY17">
+        <v>1.01</v>
+      </c>
+      <c r="AZ17">
+        <v>1.01</v>
+      </c>
+      <c r="BA17">
+        <v>1.03</v>
+      </c>
+      <c r="BB17">
+        <v>1.01</v>
+      </c>
+      <c r="BC17">
+        <v>1.01</v>
+      </c>
+      <c r="BD17">
+        <v>1.01</v>
+      </c>
+      <c r="BE17">
+        <v>1.03</v>
+      </c>
+      <c r="BF17">
+        <v>1.01</v>
+      </c>
+      <c r="BG17">
+        <v>1.01</v>
+      </c>
+      <c r="BH17">
+        <v>1000</v>
+      </c>
+      <c r="BI17">
+        <v>1.01</v>
+      </c>
+      <c r="BJ17">
+        <v>1000</v>
+      </c>
+      <c r="BK17">
+        <v>1.01</v>
+      </c>
+      <c r="BL17">
+        <v>1000</v>
+      </c>
+      <c r="BM17">
+        <v>1.01</v>
+      </c>
+      <c r="BN17">
+        <v>1000</v>
+      </c>
+      <c r="BO17">
+        <v>1.01</v>
+      </c>
+      <c r="BP17">
+        <v>1000</v>
+      </c>
+      <c r="BQ17">
+        <v>1.01</v>
+      </c>
+      <c r="BR17">
+        <v>1000</v>
+      </c>
+      <c r="BS17">
+        <v>1.01</v>
+      </c>
+      <c r="BT17">
+        <v>1000</v>
+      </c>
+      <c r="BU17">
+        <v>1.01</v>
+      </c>
+      <c r="BV17">
+        <v>1000</v>
+      </c>
+      <c r="BW17">
+        <v>1.01</v>
+      </c>
+      <c r="BX17">
+        <v>1000</v>
+      </c>
+      <c r="BY17">
+        <v>1.01</v>
+      </c>
+      <c r="BZ17">
+        <v>1000</v>
+      </c>
+      <c r="CA17">
+        <v>1.01</v>
+      </c>
+      <c r="CB17" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:80">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+      <c r="B18" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" t="s">
+        <v>113</v>
+      </c>
+      <c r="E18" t="s">
+        <v>133</v>
+      </c>
+      <c r="F18">
+        <v>1.04</v>
+      </c>
+      <c r="G18">
+        <v>1000</v>
+      </c>
+      <c r="H18">
+        <v>1.04</v>
+      </c>
+      <c r="I18">
+        <v>1000</v>
+      </c>
+      <c r="J18">
+        <v>1.03</v>
+      </c>
+      <c r="K18">
+        <v>950</v>
+      </c>
+      <c r="L18">
+        <v>1.01</v>
+      </c>
+      <c r="M18">
+        <v>1.01</v>
+      </c>
+      <c r="N18">
+        <v>1.25</v>
+      </c>
+      <c r="O18">
+        <v>1.2</v>
+      </c>
+      <c r="P18">
+        <v>1.25</v>
+      </c>
+      <c r="Q18">
+        <v>1.19</v>
+      </c>
+      <c r="R18">
+        <v>1.25</v>
+      </c>
+      <c r="S18">
+        <v>1.19</v>
+      </c>
+      <c r="T18">
+        <v>1.01</v>
+      </c>
+      <c r="U18">
+        <v>1.01</v>
+      </c>
+      <c r="V18">
+        <v>1.01</v>
+      </c>
+      <c r="W18">
+        <v>1.01</v>
+      </c>
+      <c r="X18">
+        <v>1000</v>
+      </c>
+      <c r="Y18">
+        <v>1000</v>
+      </c>
+      <c r="Z18">
+        <v>1000</v>
+      </c>
+      <c r="AA18">
+        <v>1000</v>
+      </c>
+      <c r="AB18">
+        <v>1000</v>
+      </c>
+      <c r="AC18">
+        <v>1000</v>
+      </c>
+      <c r="AD18">
+        <v>1000</v>
+      </c>
+      <c r="AE18">
+        <v>1000</v>
+      </c>
+      <c r="AF18">
+        <v>1000</v>
+      </c>
+      <c r="AG18">
+        <v>1000</v>
+      </c>
+      <c r="AH18">
+        <v>1000</v>
+      </c>
+      <c r="AI18">
+        <v>1000</v>
+      </c>
+      <c r="AJ18">
+        <v>1000</v>
+      </c>
+      <c r="AK18">
+        <v>1000</v>
+      </c>
+      <c r="AL18">
+        <v>1000</v>
+      </c>
+      <c r="AM18">
+        <v>1000</v>
+      </c>
+      <c r="AN18">
+        <v>1000</v>
+      </c>
+      <c r="AO18">
+        <v>1000</v>
+      </c>
+      <c r="AP18">
+        <v>1.03</v>
+      </c>
+      <c r="AQ18">
+        <v>1.03</v>
+      </c>
+      <c r="AR18">
+        <v>1.03</v>
+      </c>
+      <c r="AS18">
+        <v>1.03</v>
+      </c>
+      <c r="AT18">
+        <v>1.03</v>
+      </c>
+      <c r="AU18">
+        <v>1.03</v>
+      </c>
+      <c r="AV18">
+        <v>1.03</v>
+      </c>
+      <c r="AW18">
+        <v>1.03</v>
+      </c>
+      <c r="AX18">
+        <v>1.03</v>
+      </c>
+      <c r="AY18">
+        <v>1.03</v>
+      </c>
+      <c r="AZ18">
+        <v>1.03</v>
+      </c>
+      <c r="BA18">
+        <v>1.03</v>
+      </c>
+      <c r="BB18">
+        <v>1.03</v>
+      </c>
+      <c r="BC18">
+        <v>1.03</v>
+      </c>
+      <c r="BD18">
+        <v>1.03</v>
+      </c>
+      <c r="BE18">
+        <v>1.03</v>
+      </c>
+      <c r="BF18">
+        <v>1.01</v>
+      </c>
+      <c r="BG18">
+        <v>1.01</v>
+      </c>
+      <c r="BH18">
+        <v>1000</v>
+      </c>
+      <c r="BI18">
+        <v>1.01</v>
+      </c>
+      <c r="BJ18">
+        <v>1000</v>
+      </c>
+      <c r="BK18">
+        <v>1.01</v>
+      </c>
+      <c r="BL18">
+        <v>1000</v>
+      </c>
+      <c r="BM18">
+        <v>1.01</v>
+      </c>
+      <c r="BN18">
+        <v>1000</v>
+      </c>
+      <c r="BO18">
+        <v>1.01</v>
+      </c>
+      <c r="BP18">
+        <v>1000</v>
+      </c>
+      <c r="BQ18">
+        <v>1.01</v>
+      </c>
+      <c r="BR18">
+        <v>1000</v>
+      </c>
+      <c r="BS18">
+        <v>1.01</v>
+      </c>
+      <c r="BT18">
+        <v>1000</v>
+      </c>
+      <c r="BU18">
+        <v>1.01</v>
+      </c>
+      <c r="BV18">
+        <v>1000</v>
+      </c>
+      <c r="BW18">
+        <v>1.01</v>
+      </c>
+      <c r="BX18">
+        <v>1000</v>
+      </c>
+      <c r="BY18">
+        <v>1.01</v>
+      </c>
+      <c r="BZ18">
+        <v>1000</v>
+      </c>
+      <c r="CA18">
+        <v>1.01</v>
+      </c>
+      <c r="CB18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:80">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+      <c r="B19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C19" t="s">
+        <v>95</v>
+      </c>
+      <c r="D19" t="s">
         <v>114</v>
       </c>
-      <c r="F13">
+      <c r="E19" t="s">
+        <v>134</v>
+      </c>
+      <c r="F19">
         <v>1.04</v>
       </c>
-      <c r="G13">
-        <v>1000</v>
-      </c>
-      <c r="H13">
+      <c r="G19">
+        <v>1000</v>
+      </c>
+      <c r="H19">
         <v>1.04</v>
       </c>
-      <c r="I13">
-        <v>1000</v>
-      </c>
-      <c r="J13">
-        <v>1.01</v>
-      </c>
-      <c r="K13">
+      <c r="I19">
+        <v>970</v>
+      </c>
+      <c r="J19">
+        <v>1.03</v>
+      </c>
+      <c r="K19">
         <v>950</v>
       </c>
-      <c r="L13">
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <v>0</v>
-      </c>
-      <c r="P13">
+      <c r="L19">
+        <v>1.01</v>
+      </c>
+      <c r="M19">
+        <v>1.01</v>
+      </c>
+      <c r="N19">
+        <v>1.26</v>
+      </c>
+      <c r="O19">
+        <v>1.27</v>
+      </c>
+      <c r="P19">
+        <v>1.25</v>
+      </c>
+      <c r="Q19">
+        <v>1.27</v>
+      </c>
+      <c r="R19">
+        <v>1.25</v>
+      </c>
+      <c r="S19">
+        <v>1.27</v>
+      </c>
+      <c r="T19">
+        <v>1.01</v>
+      </c>
+      <c r="U19">
+        <v>1.01</v>
+      </c>
+      <c r="V19">
+        <v>1.01</v>
+      </c>
+      <c r="W19">
+        <v>1.01</v>
+      </c>
+      <c r="X19">
+        <v>1000</v>
+      </c>
+      <c r="Y19">
+        <v>1000</v>
+      </c>
+      <c r="Z19">
+        <v>1000</v>
+      </c>
+      <c r="AA19">
+        <v>1000</v>
+      </c>
+      <c r="AB19">
+        <v>1000</v>
+      </c>
+      <c r="AC19">
+        <v>1000</v>
+      </c>
+      <c r="AD19">
+        <v>1000</v>
+      </c>
+      <c r="AE19">
+        <v>1000</v>
+      </c>
+      <c r="AF19">
+        <v>1000</v>
+      </c>
+      <c r="AG19">
+        <v>1000</v>
+      </c>
+      <c r="AH19">
+        <v>1000</v>
+      </c>
+      <c r="AI19">
+        <v>1000</v>
+      </c>
+      <c r="AJ19">
+        <v>1000</v>
+      </c>
+      <c r="AK19">
+        <v>1000</v>
+      </c>
+      <c r="AL19">
+        <v>1000</v>
+      </c>
+      <c r="AM19">
+        <v>1000</v>
+      </c>
+      <c r="AN19">
+        <v>1000</v>
+      </c>
+      <c r="AO19">
+        <v>1000</v>
+      </c>
+      <c r="AP19">
+        <v>1.03</v>
+      </c>
+      <c r="AQ19">
+        <v>1.03</v>
+      </c>
+      <c r="AR19">
+        <v>1.03</v>
+      </c>
+      <c r="AS19">
+        <v>1.03</v>
+      </c>
+      <c r="AT19">
+        <v>1.03</v>
+      </c>
+      <c r="AU19">
+        <v>1.03</v>
+      </c>
+      <c r="AV19">
+        <v>1.03</v>
+      </c>
+      <c r="AW19">
+        <v>1.03</v>
+      </c>
+      <c r="AX19">
+        <v>1.03</v>
+      </c>
+      <c r="AY19">
+        <v>1.03</v>
+      </c>
+      <c r="AZ19">
+        <v>1.03</v>
+      </c>
+      <c r="BA19">
+        <v>1.03</v>
+      </c>
+      <c r="BB19">
+        <v>1.03</v>
+      </c>
+      <c r="BC19">
+        <v>1.03</v>
+      </c>
+      <c r="BD19">
+        <v>1.03</v>
+      </c>
+      <c r="BE19">
+        <v>1.03</v>
+      </c>
+      <c r="BF19">
+        <v>1.01</v>
+      </c>
+      <c r="BG19">
+        <v>1.01</v>
+      </c>
+      <c r="BH19">
+        <v>1000</v>
+      </c>
+      <c r="BI19">
+        <v>1.01</v>
+      </c>
+      <c r="BJ19">
+        <v>1000</v>
+      </c>
+      <c r="BK19">
+        <v>1.01</v>
+      </c>
+      <c r="BL19">
+        <v>1000</v>
+      </c>
+      <c r="BM19">
+        <v>1.01</v>
+      </c>
+      <c r="BN19">
+        <v>1000</v>
+      </c>
+      <c r="BO19">
+        <v>1.01</v>
+      </c>
+      <c r="BP19">
+        <v>1000</v>
+      </c>
+      <c r="BQ19">
+        <v>1.01</v>
+      </c>
+      <c r="BR19">
+        <v>1000</v>
+      </c>
+      <c r="BS19">
+        <v>1.01</v>
+      </c>
+      <c r="BT19">
+        <v>1000</v>
+      </c>
+      <c r="BU19">
+        <v>1.01</v>
+      </c>
+      <c r="BV19">
+        <v>1000</v>
+      </c>
+      <c r="BW19">
+        <v>1.01</v>
+      </c>
+      <c r="BX19">
+        <v>1000</v>
+      </c>
+      <c r="BY19">
+        <v>1.01</v>
+      </c>
+      <c r="BZ19">
+        <v>1000</v>
+      </c>
+      <c r="CA19">
+        <v>1.01</v>
+      </c>
+      <c r="CB19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:80">
+      <c r="A20" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C20" t="s">
+        <v>96</v>
+      </c>
+      <c r="D20" t="s">
+        <v>115</v>
+      </c>
+      <c r="E20" t="s">
+        <v>135</v>
+      </c>
+      <c r="F20">
+        <v>1.09</v>
+      </c>
+      <c r="G20">
+        <v>10.5</v>
+      </c>
+      <c r="H20">
+        <v>1.11</v>
+      </c>
+      <c r="I20">
+        <v>1000</v>
+      </c>
+      <c r="J20">
+        <v>1.1</v>
+      </c>
+      <c r="K20">
+        <v>950</v>
+      </c>
+      <c r="L20">
+        <v>0</v>
+      </c>
+      <c r="M20">
+        <v>0</v>
+      </c>
+      <c r="N20">
+        <v>0</v>
+      </c>
+      <c r="O20">
+        <v>0</v>
+      </c>
+      <c r="P20">
         <v>1.24</v>
       </c>
-      <c r="Q13">
-        <v>1.01</v>
-      </c>
-      <c r="R13">
-        <v>0</v>
-      </c>
-      <c r="S13">
-        <v>0</v>
-      </c>
-      <c r="T13">
-        <v>0</v>
-      </c>
-      <c r="U13">
-        <v>0</v>
-      </c>
-      <c r="V13">
-        <v>0</v>
-      </c>
-      <c r="W13">
-        <v>0</v>
-      </c>
-      <c r="X13">
-        <v>0</v>
-      </c>
-      <c r="Y13">
-        <v>0</v>
-      </c>
-      <c r="Z13">
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <v>0</v>
-      </c>
-      <c r="AG13">
-        <v>0</v>
-      </c>
-      <c r="AH13">
-        <v>0</v>
-      </c>
-      <c r="AI13">
-        <v>0</v>
-      </c>
-      <c r="AJ13">
-        <v>0</v>
-      </c>
-      <c r="AK13">
-        <v>0</v>
-      </c>
-      <c r="AL13">
-        <v>0</v>
-      </c>
-      <c r="AM13">
-        <v>0</v>
-      </c>
-      <c r="AN13">
-        <v>0</v>
-      </c>
-      <c r="AO13">
-        <v>0</v>
-      </c>
-      <c r="AP13">
-        <v>0</v>
-      </c>
-      <c r="AQ13">
-        <v>0</v>
-      </c>
-      <c r="AR13">
-        <v>0</v>
-      </c>
-      <c r="AS13">
-        <v>0</v>
-      </c>
-      <c r="AT13">
-        <v>0</v>
-      </c>
-      <c r="AU13">
-        <v>0</v>
-      </c>
-      <c r="AV13">
-        <v>0</v>
-      </c>
-      <c r="AW13">
-        <v>0</v>
-      </c>
-      <c r="AX13">
-        <v>0</v>
-      </c>
-      <c r="AY13">
-        <v>0</v>
-      </c>
-      <c r="AZ13">
-        <v>0</v>
-      </c>
-      <c r="BA13">
-        <v>0</v>
-      </c>
-      <c r="BB13">
-        <v>0</v>
-      </c>
-      <c r="BC13">
-        <v>0</v>
-      </c>
-      <c r="BD13">
-        <v>0</v>
-      </c>
-      <c r="BE13">
-        <v>0</v>
-      </c>
-      <c r="BF13">
-        <v>0</v>
-      </c>
-      <c r="BG13">
-        <v>0</v>
-      </c>
-      <c r="BH13">
-        <v>0</v>
-      </c>
-      <c r="BI13">
-        <v>0</v>
-      </c>
-      <c r="BJ13">
-        <v>0</v>
-      </c>
-      <c r="BK13">
-        <v>0</v>
-      </c>
-      <c r="BL13">
-        <v>0</v>
-      </c>
-      <c r="BM13">
-        <v>0</v>
-      </c>
-      <c r="BN13">
-        <v>0</v>
-      </c>
-      <c r="BO13">
-        <v>0</v>
-      </c>
-      <c r="BP13">
-        <v>0</v>
-      </c>
-      <c r="BQ13">
-        <v>0</v>
-      </c>
-      <c r="BR13">
-        <v>0</v>
-      </c>
-      <c r="BS13">
-        <v>0</v>
-      </c>
-      <c r="BT13">
-        <v>0</v>
-      </c>
-      <c r="BU13">
-        <v>0</v>
-      </c>
-      <c r="BV13">
-        <v>0</v>
-      </c>
-      <c r="BW13">
-        <v>0</v>
-      </c>
-      <c r="BX13">
-        <v>0</v>
-      </c>
-      <c r="BY13">
-        <v>0</v>
-      </c>
-      <c r="BZ13">
-        <v>0</v>
-      </c>
-      <c r="CA13">
-        <v>0</v>
-      </c>
-      <c r="CB13" t="s">
-        <v>115</v>
+      <c r="Q20">
+        <v>1.01</v>
+      </c>
+      <c r="R20">
+        <v>0</v>
+      </c>
+      <c r="S20">
+        <v>0</v>
+      </c>
+      <c r="T20">
+        <v>0</v>
+      </c>
+      <c r="U20">
+        <v>0</v>
+      </c>
+      <c r="V20">
+        <v>0</v>
+      </c>
+      <c r="W20">
+        <v>0</v>
+      </c>
+      <c r="X20">
+        <v>0</v>
+      </c>
+      <c r="Y20">
+        <v>0</v>
+      </c>
+      <c r="Z20">
+        <v>0</v>
+      </c>
+      <c r="AA20">
+        <v>0</v>
+      </c>
+      <c r="AB20">
+        <v>0</v>
+      </c>
+      <c r="AC20">
+        <v>0</v>
+      </c>
+      <c r="AD20">
+        <v>0</v>
+      </c>
+      <c r="AE20">
+        <v>0</v>
+      </c>
+      <c r="AF20">
+        <v>0</v>
+      </c>
+      <c r="AG20">
+        <v>0</v>
+      </c>
+      <c r="AH20">
+        <v>0</v>
+      </c>
+      <c r="AI20">
+        <v>0</v>
+      </c>
+      <c r="AJ20">
+        <v>0</v>
+      </c>
+      <c r="AK20">
+        <v>0</v>
+      </c>
+      <c r="AL20">
+        <v>0</v>
+      </c>
+      <c r="AM20">
+        <v>0</v>
+      </c>
+      <c r="AN20">
+        <v>0</v>
+      </c>
+      <c r="AO20">
+        <v>0</v>
+      </c>
+      <c r="AP20">
+        <v>0</v>
+      </c>
+      <c r="AQ20">
+        <v>0</v>
+      </c>
+      <c r="AR20">
+        <v>0</v>
+      </c>
+      <c r="AS20">
+        <v>0</v>
+      </c>
+      <c r="AT20">
+        <v>0</v>
+      </c>
+      <c r="AU20">
+        <v>0</v>
+      </c>
+      <c r="AV20">
+        <v>0</v>
+      </c>
+      <c r="AW20">
+        <v>0</v>
+      </c>
+      <c r="AX20">
+        <v>0</v>
+      </c>
+      <c r="AY20">
+        <v>0</v>
+      </c>
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+      <c r="BA20">
+        <v>0</v>
+      </c>
+      <c r="BB20">
+        <v>0</v>
+      </c>
+      <c r="BC20">
+        <v>0</v>
+      </c>
+      <c r="BD20">
+        <v>0</v>
+      </c>
+      <c r="BE20">
+        <v>0</v>
+      </c>
+      <c r="BF20">
+        <v>0</v>
+      </c>
+      <c r="BG20">
+        <v>0</v>
+      </c>
+      <c r="BH20">
+        <v>0</v>
+      </c>
+      <c r="BI20">
+        <v>0</v>
+      </c>
+      <c r="BJ20">
+        <v>0</v>
+      </c>
+      <c r="BK20">
+        <v>0</v>
+      </c>
+      <c r="BL20">
+        <v>0</v>
+      </c>
+      <c r="BM20">
+        <v>0</v>
+      </c>
+      <c r="BN20">
+        <v>0</v>
+      </c>
+      <c r="BO20">
+        <v>0</v>
+      </c>
+      <c r="BP20">
+        <v>0</v>
+      </c>
+      <c r="BQ20">
+        <v>0</v>
+      </c>
+      <c r="BR20">
+        <v>0</v>
+      </c>
+      <c r="BS20">
+        <v>0</v>
+      </c>
+      <c r="BT20">
+        <v>0</v>
+      </c>
+      <c r="BU20">
+        <v>0</v>
+      </c>
+      <c r="BV20">
+        <v>0</v>
+      </c>
+      <c r="BW20">
+        <v>0</v>
+      </c>
+      <c r="BX20">
+        <v>0</v>
+      </c>
+      <c r="BY20">
+        <v>0</v>
+      </c>
+      <c r="BZ20">
+        <v>0</v>
+      </c>
+      <c r="CA20">
+        <v>0</v>
+      </c>
+      <c r="CB20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:80">
+      <c r="A21" t="s">
+        <v>86</v>
+      </c>
+      <c r="B21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" t="s">
+        <v>116</v>
+      </c>
+      <c r="E21" t="s">
+        <v>136</v>
+      </c>
+      <c r="F21">
+        <v>1.04</v>
+      </c>
+      <c r="G21">
+        <v>1000</v>
+      </c>
+      <c r="H21">
+        <v>1.04</v>
+      </c>
+      <c r="I21">
+        <v>1000</v>
+      </c>
+      <c r="J21">
+        <v>1.01</v>
+      </c>
+      <c r="K21">
+        <v>950</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <v>1.24</v>
+      </c>
+      <c r="Q21">
+        <v>1.01</v>
+      </c>
+      <c r="R21">
+        <v>0</v>
+      </c>
+      <c r="S21">
+        <v>0</v>
+      </c>
+      <c r="T21">
+        <v>0</v>
+      </c>
+      <c r="U21">
+        <v>0</v>
+      </c>
+      <c r="V21">
+        <v>0</v>
+      </c>
+      <c r="W21">
+        <v>0</v>
+      </c>
+      <c r="X21">
+        <v>0</v>
+      </c>
+      <c r="Y21">
+        <v>0</v>
+      </c>
+      <c r="Z21">
+        <v>0</v>
+      </c>
+      <c r="AA21">
+        <v>0</v>
+      </c>
+      <c r="AB21">
+        <v>0</v>
+      </c>
+      <c r="AC21">
+        <v>0</v>
+      </c>
+      <c r="AD21">
+        <v>0</v>
+      </c>
+      <c r="AE21">
+        <v>0</v>
+      </c>
+      <c r="AF21">
+        <v>0</v>
+      </c>
+      <c r="AG21">
+        <v>0</v>
+      </c>
+      <c r="AH21">
+        <v>0</v>
+      </c>
+      <c r="AI21">
+        <v>0</v>
+      </c>
+      <c r="AJ21">
+        <v>0</v>
+      </c>
+      <c r="AK21">
+        <v>0</v>
+      </c>
+      <c r="AL21">
+        <v>0</v>
+      </c>
+      <c r="AM21">
+        <v>0</v>
+      </c>
+      <c r="AN21">
+        <v>0</v>
+      </c>
+      <c r="AO21">
+        <v>0</v>
+      </c>
+      <c r="AP21">
+        <v>0</v>
+      </c>
+      <c r="AQ21">
+        <v>0</v>
+      </c>
+      <c r="AR21">
+        <v>0</v>
+      </c>
+      <c r="AS21">
+        <v>0</v>
+      </c>
+      <c r="AT21">
+        <v>0</v>
+      </c>
+      <c r="AU21">
+        <v>0</v>
+      </c>
+      <c r="AV21">
+        <v>0</v>
+      </c>
+      <c r="AW21">
+        <v>0</v>
+      </c>
+      <c r="AX21">
+        <v>0</v>
+      </c>
+      <c r="AY21">
+        <v>0</v>
+      </c>
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+      <c r="BA21">
+        <v>0</v>
+      </c>
+      <c r="BB21">
+        <v>0</v>
+      </c>
+      <c r="BC21">
+        <v>0</v>
+      </c>
+      <c r="BD21">
+        <v>0</v>
+      </c>
+      <c r="BE21">
+        <v>0</v>
+      </c>
+      <c r="BF21">
+        <v>0</v>
+      </c>
+      <c r="BG21">
+        <v>0</v>
+      </c>
+      <c r="BH21">
+        <v>0</v>
+      </c>
+      <c r="BI21">
+        <v>0</v>
+      </c>
+      <c r="BJ21">
+        <v>0</v>
+      </c>
+      <c r="BK21">
+        <v>0</v>
+      </c>
+      <c r="BL21">
+        <v>0</v>
+      </c>
+      <c r="BM21">
+        <v>0</v>
+      </c>
+      <c r="BN21">
+        <v>0</v>
+      </c>
+      <c r="BO21">
+        <v>0</v>
+      </c>
+      <c r="BP21">
+        <v>0</v>
+      </c>
+      <c r="BQ21">
+        <v>0</v>
+      </c>
+      <c r="BR21">
+        <v>0</v>
+      </c>
+      <c r="BS21">
+        <v>0</v>
+      </c>
+      <c r="BT21">
+        <v>0</v>
+      </c>
+      <c r="BU21">
+        <v>0</v>
+      </c>
+      <c r="BV21">
+        <v>0</v>
+      </c>
+      <c r="BW21">
+        <v>0</v>
+      </c>
+      <c r="BX21">
+        <v>0</v>
+      </c>
+      <c r="BY21">
+        <v>0</v>
+      </c>
+      <c r="BZ21">
+        <v>0</v>
+      </c>
+      <c r="CA21">
+        <v>0</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>137</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="320" uniqueCount="196">
   <si>
     <t>League</t>
   </si>
@@ -274,6 +274,45 @@
     <t>Hungarian NB I</t>
   </si>
   <si>
+    <t>Polish I Liga</t>
+  </si>
+  <si>
+    <t>Estonian Premier League</t>
+  </si>
+  <si>
+    <t>Finnish Veikkausliiga</t>
+  </si>
+  <si>
+    <t>Austrian Erste Liga</t>
+  </si>
+  <si>
+    <t>Danish 2nd Division</t>
+  </si>
+  <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
+    <t>German 3 Liga</t>
+  </si>
+  <si>
+    <t>Norwegian Eliteserien</t>
+  </si>
+  <si>
+    <t>Czech 1 Liga</t>
+  </si>
+  <si>
+    <t>Danish Superliga</t>
+  </si>
+  <si>
+    <t>Austrian Bundesliga</t>
+  </si>
+  <si>
+    <t>Swedish Division 1</t>
+  </si>
+  <si>
+    <t>Swiss Challenge League</t>
+  </si>
+  <si>
     <t>Icelandic 1 Deild</t>
   </si>
   <si>
@@ -304,6 +343,21 @@
     <t>16:00:00</t>
   </si>
   <si>
+    <t>16:30:00</t>
+  </si>
+  <si>
+    <t>17:00:00</t>
+  </si>
+  <si>
+    <t>17:30:00</t>
+  </si>
+  <si>
+    <t>18:15:00</t>
+  </si>
+  <si>
+    <t>18:30:00</t>
+  </si>
+  <si>
     <t>19:15:00</t>
   </si>
   <si>
@@ -346,19 +400,79 @@
     <t>Vysocina Jihlava</t>
   </si>
   <si>
+    <t>Polonia Bytom</t>
+  </si>
+  <si>
+    <t>Kuressaare</t>
+  </si>
+  <si>
+    <t>Dukla Prague</t>
+  </si>
+  <si>
+    <t>SJK</t>
+  </si>
+  <si>
+    <t>SFC Opava</t>
+  </si>
+  <si>
+    <t>Prostejov</t>
+  </si>
+  <si>
     <t>Usti Nad Labem</t>
   </si>
   <si>
-    <t>Prostejov</t>
-  </si>
-  <si>
-    <t>SFC Opava</t>
-  </si>
-  <si>
     <t>FC Sellier &amp; Bellot Vlasim</t>
   </si>
   <si>
-    <t>Dukla Prague</t>
+    <t>FC Liefering</t>
+  </si>
+  <si>
+    <t>St Polten</t>
+  </si>
+  <si>
+    <t>Middelfart</t>
+  </si>
+  <si>
+    <t>Ostersunds FK</t>
+  </si>
+  <si>
+    <t>Waldhof Mannheim</t>
+  </si>
+  <si>
+    <t>Sandefjord</t>
+  </si>
+  <si>
+    <t>B93 Copenhagen</t>
+  </si>
+  <si>
+    <t>FC Zbrojovka Brno</t>
+  </si>
+  <si>
+    <t>Sonderjyske</t>
+  </si>
+  <si>
+    <t>SCR Altach</t>
+  </si>
+  <si>
+    <t>Enkopings SK</t>
+  </si>
+  <si>
+    <t>Kriens</t>
+  </si>
+  <si>
+    <t>Winterthur</t>
+  </si>
+  <si>
+    <t>Etoile Carouge</t>
+  </si>
+  <si>
+    <t>Aarau</t>
+  </si>
+  <si>
+    <t>FC Blau Weiss Linz</t>
+  </si>
+  <si>
+    <t>Polonia Warszawa</t>
   </si>
   <si>
     <t>Afturelding</t>
@@ -406,19 +520,79 @@
     <t>FK Pribram</t>
   </si>
   <si>
+    <t>Pogon Siedlce</t>
+  </si>
+  <si>
+    <t>Harju JK Laagri</t>
+  </si>
+  <si>
+    <t>H Slavia Kromeriz</t>
+  </si>
+  <si>
+    <t>Gnistan</t>
+  </si>
+  <si>
+    <t>SK Kladno</t>
+  </si>
+  <si>
+    <t>MFK Karvina</t>
+  </si>
+  <si>
     <t>Arsenal Ceska Lipa</t>
   </si>
   <si>
-    <t>MFK Karvina</t>
-  </si>
-  <si>
-    <t>SK Kladno</t>
-  </si>
-  <si>
     <t>Zizkov</t>
   </si>
   <si>
-    <t>H Slavia Kromeriz</t>
+    <t>WSC Hertha Wels</t>
+  </si>
+  <si>
+    <t>Austria Wien (A)</t>
+  </si>
+  <si>
+    <t>Brabrand</t>
+  </si>
+  <si>
+    <t>Sundsvall</t>
+  </si>
+  <si>
+    <t>Fortuna Dusseldorf</t>
+  </si>
+  <si>
+    <t>KFUM Oslo</t>
+  </si>
+  <si>
+    <t>Roskilde</t>
+  </si>
+  <si>
+    <t>Slovan Liberec</t>
+  </si>
+  <si>
+    <t>Viborg</t>
+  </si>
+  <si>
+    <t>WSG Wattens</t>
+  </si>
+  <si>
+    <t>Karlbergs BK</t>
+  </si>
+  <si>
+    <t>Yverdon Sport</t>
+  </si>
+  <si>
+    <t>FC Wil</t>
+  </si>
+  <si>
+    <t>Neuchatel Xamax</t>
+  </si>
+  <si>
+    <t>Stade Nyonnais</t>
+  </si>
+  <si>
+    <t>FC Wacker Innsbruck</t>
+  </si>
+  <si>
+    <t>Ruch Chorzow</t>
   </si>
   <si>
     <t>Grindavik</t>
@@ -427,7 +601,7 @@
     <t>Fylkir</t>
   </si>
   <si>
-    <t>2026-08-05 12:33:42</t>
+    <t>2026-08-05 14:41:37</t>
   </si>
 </sst>
 </file>
@@ -759,7 +933,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB21"/>
+  <dimension ref="A1:CB41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1009,19 +1183,19 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>101</v>
       </c>
       <c r="D2" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="E2" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="F2">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="G2">
         <v>1.74</v>
@@ -1036,7 +1210,7 @@
         <v>3.4</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -1045,10 +1219,10 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="O2">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P2">
         <v>1.72</v>
@@ -1078,13 +1252,13 @@
         <v>14.5</v>
       </c>
       <c r="Y2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="Z2">
         <v>70</v>
       </c>
       <c r="AA2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AB2">
         <v>7.2</v>
@@ -1093,7 +1267,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AD2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE2">
         <v>150</v>
@@ -1126,19 +1300,19 @@
         <v>15.5</v>
       </c>
       <c r="AO2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="AP2">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AQ2">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="AR2">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="AS2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AT2">
         <v>5.2</v>
@@ -1147,94 +1321,94 @@
         <v>6.6</v>
       </c>
       <c r="AV2">
-        <v>18.5</v>
+        <v>4.7</v>
       </c>
       <c r="AW2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AY2">
         <v>7.6</v>
       </c>
       <c r="AZ2">
-        <v>21</v>
+        <v>4.6</v>
       </c>
       <c r="BA2">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB2">
         <v>12</v>
       </c>
       <c r="BC2">
-        <v>17</v>
+        <v>4.5</v>
       </c>
       <c r="BD2">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF2">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BG2">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH2">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BI2">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="BJ2">
         <v>14</v>
       </c>
       <c r="BK2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BN2">
         <v>4.7</v>
       </c>
       <c r="BO2">
-        <v>2.4</v>
+        <v>3.15</v>
       </c>
       <c r="BP2">
         <v>14</v>
       </c>
       <c r="BQ2">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="BR2">
         <v>38</v>
       </c>
       <c r="BS2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT2">
         <v>12</v>
       </c>
       <c r="BU2">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="BV2">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="BW2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BX2">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1243,7 +1417,7 @@
         <v>0</v>
       </c>
       <c r="CB2" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1251,16 +1425,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="D3" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E3" t="s">
-        <v>118</v>
+        <v>156</v>
       </c>
       <c r="F3">
         <v>4</v>
@@ -1278,10 +1452,10 @@
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="L3">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1485,7 +1659,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1493,43 +1667,43 @@
         <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D4" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E4" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="F4">
         <v>2.42</v>
       </c>
       <c r="G4">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
         <v>3.25</v>
       </c>
       <c r="I4">
+        <v>3.35</v>
+      </c>
+      <c r="J4">
+        <v>3.35</v>
+      </c>
+      <c r="K4">
         <v>3.45</v>
       </c>
-      <c r="J4">
-        <v>3.3</v>
-      </c>
-      <c r="K4">
-        <v>3.6</v>
-      </c>
       <c r="L4">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="M4">
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O4">
         <v>1.35</v>
@@ -1538,7 +1712,7 @@
         <v>1.85</v>
       </c>
       <c r="Q4">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R4">
         <v>1.33</v>
@@ -1547,16 +1721,16 @@
         <v>3.6</v>
       </c>
       <c r="T4">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="U4">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="W4">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="X4">
         <v>13.5</v>
@@ -1574,7 +1748,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="AD4">
         <v>14.5</v>
@@ -1622,13 +1796,13 @@
         <v>19</v>
       </c>
       <c r="AS4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
       </c>
       <c r="AU4">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4">
         <v>12</v>
@@ -1646,25 +1820,25 @@
         <v>15.5</v>
       </c>
       <c r="BA4">
+        <v>12</v>
+      </c>
+      <c r="BB4">
+        <v>11.5</v>
+      </c>
+      <c r="BC4">
         <v>10.5</v>
       </c>
-      <c r="BB4">
-        <v>9.6</v>
-      </c>
-      <c r="BC4">
-        <v>9</v>
-      </c>
       <c r="BD4">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BE4">
-        <v>11.5</v>
+        <v>14.5</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>9.800000000000001</v>
+        <v>11.5</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
@@ -1727,7 +1901,7 @@
         <v>0</v>
       </c>
       <c r="CB4" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1735,49 +1909,49 @@
         <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C5" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E5" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G5">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="H5">
         <v>5</v>
       </c>
       <c r="I5">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J5">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="N5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="O5">
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -1786,10 +1960,10 @@
         <v>1.28</v>
       </c>
       <c r="S5">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T5">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="U5">
         <v>1.87</v>
@@ -1798,13 +1972,13 @@
         <v>1.21</v>
       </c>
       <c r="W5">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X5">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="Y5">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="Z5">
         <v>50</v>
@@ -1813,10 +1987,10 @@
         <v>180</v>
       </c>
       <c r="AB5">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC5">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD5">
         <v>26</v>
@@ -1825,7 +1999,7 @@
         <v>100</v>
       </c>
       <c r="AF5">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG5">
         <v>12.5</v>
@@ -1840,7 +2014,7 @@
         <v>25</v>
       </c>
       <c r="AK5">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL5">
         <v>55</v>
@@ -1849,13 +2023,13 @@
         <v>180</v>
       </c>
       <c r="AN5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO5">
         <v>140</v>
       </c>
       <c r="AP5">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AQ5">
         <v>11.5</v>
@@ -1867,7 +2041,7 @@
         <v>4.2</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AU5">
         <v>6.2</v>
@@ -1876,7 +2050,7 @@
         <v>15</v>
       </c>
       <c r="AW5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AX5">
         <v>7.8</v>
@@ -1888,10 +2062,10 @@
         <v>16</v>
       </c>
       <c r="BA5">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB5">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BC5">
         <v>15.5</v>
@@ -1909,22 +2083,22 @@
         <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="BI5">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="BJ5">
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
@@ -1936,40 +2110,40 @@
         <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="BT5">
         <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BX5">
         <v>65</v>
       </c>
       <c r="BY5">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BZ5">
         <v>29</v>
       </c>
       <c r="CA5">
-        <v>9.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="CB5" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -1977,16 +2151,16 @@
         <v>82</v>
       </c>
       <c r="B6" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D6" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E6" t="s">
-        <v>121</v>
+        <v>159</v>
       </c>
       <c r="F6">
         <v>3.95</v>
@@ -1995,7 +2169,7 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I6">
         <v>2.12</v>
@@ -2007,25 +2181,25 @@
         <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.07</v>
       </c>
       <c r="N6">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O6">
         <v>1.31</v>
       </c>
       <c r="P6">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="Q6">
         <v>1.95</v>
       </c>
       <c r="R6">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S6">
         <v>3.45</v>
@@ -2034,7 +2208,7 @@
         <v>1.8</v>
       </c>
       <c r="U6">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V6">
         <v>1.9</v>
@@ -2079,7 +2253,7 @@
         <v>46</v>
       </c>
       <c r="AJ6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK6">
         <v>70</v>
@@ -2094,13 +2268,13 @@
         <v>75</v>
       </c>
       <c r="AO6">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AP6">
         <v>10</v>
       </c>
       <c r="AQ6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AR6">
         <v>9.199999999999999</v>
@@ -2121,7 +2295,7 @@
         <v>16</v>
       </c>
       <c r="AX6">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="AY6">
         <v>12.5</v>
@@ -2130,31 +2304,31 @@
         <v>13.5</v>
       </c>
       <c r="BA6">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="BB6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BC6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BD6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BE6">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="BF6">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BG6">
         <v>11</v>
       </c>
       <c r="BH6">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BI6">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BJ6">
         <v>12</v>
@@ -2178,13 +2352,13 @@
         <v>44</v>
       </c>
       <c r="BQ6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BT6">
         <v>5.6</v>
@@ -2196,7 +2370,7 @@
         <v>17.5</v>
       </c>
       <c r="BW6">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="BX6">
         <v>36</v>
@@ -2211,7 +2385,7 @@
         <v>4.1</v>
       </c>
       <c r="CB6" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2219,16 +2393,16 @@
         <v>82</v>
       </c>
       <c r="B7" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C7" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D7" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E7" t="s">
-        <v>122</v>
+        <v>160</v>
       </c>
       <c r="F7">
         <v>4.1</v>
@@ -2237,67 +2411,67 @@
         <v>4.8</v>
       </c>
       <c r="H7">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="I7">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="J7">
         <v>3.9</v>
       </c>
       <c r="K7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="M7">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q7">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="R7">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="S7">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="T7">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V7">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="W7">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="X7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y7">
         <v>12</v>
       </c>
       <c r="Z7">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA7">
         <v>25</v>
       </c>
       <c r="AB7">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC7">
         <v>10.5</v>
@@ -2306,7 +2480,7 @@
         <v>12</v>
       </c>
       <c r="AE7">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AF7">
         <v>40</v>
@@ -2315,10 +2489,10 @@
         <v>21</v>
       </c>
       <c r="AH7">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AI7">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ7">
         <v>110</v>
@@ -2327,73 +2501,73 @@
         <v>60</v>
       </c>
       <c r="AL7">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM7">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN7">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO7">
+        <v>12.5</v>
+      </c>
+      <c r="AP7">
         <v>13.5</v>
       </c>
-      <c r="AP7">
-        <v>13</v>
-      </c>
       <c r="AQ7">
-        <v>7.8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR7">
-        <v>9.6</v>
+        <v>11</v>
       </c>
       <c r="AS7">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT7">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU7">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AX7">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="AY7">
         <v>13.5</v>
       </c>
       <c r="AZ7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BA7">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BB7">
+        <v>5</v>
+      </c>
+      <c r="BC7">
         <v>4.8</v>
       </c>
-      <c r="BC7">
-        <v>4.6</v>
-      </c>
       <c r="BD7">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE7">
+        <v>5</v>
+      </c>
+      <c r="BF7">
         <v>4.8</v>
       </c>
-      <c r="BF7">
-        <v>4.6</v>
-      </c>
       <c r="BG7">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="BH7">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="BI7">
         <v>3.35</v>
@@ -2444,7 +2618,7 @@
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
@@ -2453,7 +2627,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="CB7" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2461,19 +2635,19 @@
         <v>82</v>
       </c>
       <c r="B8" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D8" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>123</v>
+        <v>161</v>
       </c>
       <c r="F8">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="G8">
         <v>3.35</v>
@@ -2485,16 +2659,16 @@
         <v>2.58</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="K8">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.32</v>
       </c>
       <c r="M8">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
         <v>4</v>
@@ -2506,13 +2680,13 @@
         <v>2.06</v>
       </c>
       <c r="Q8">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R8">
         <v>1.41</v>
       </c>
       <c r="S8">
-        <v>2.98</v>
+        <v>2.96</v>
       </c>
       <c r="T8">
         <v>1.64</v>
@@ -2695,7 +2869,7 @@
         <v>7.4</v>
       </c>
       <c r="CB8" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2703,19 +2877,19 @@
         <v>82</v>
       </c>
       <c r="B9" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C9" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D9" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E9" t="s">
-        <v>124</v>
+        <v>162</v>
       </c>
       <c r="F9">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
         <v>1.65</v>
@@ -2727,7 +2901,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
         <v>4.9</v>
@@ -2748,7 +2922,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="R9">
         <v>1.41</v>
@@ -2757,16 +2931,16 @@
         <v>2.92</v>
       </c>
       <c r="T9">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U9">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V9">
         <v>1.15</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X9">
         <v>21</v>
@@ -2937,7 +3111,7 @@
         <v>6.6</v>
       </c>
       <c r="CB9" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -2945,19 +3119,19 @@
         <v>82</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C10" t="s">
-        <v>90</v>
+        <v>103</v>
       </c>
       <c r="D10" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E10" t="s">
-        <v>125</v>
+        <v>163</v>
       </c>
       <c r="F10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="G10">
         <v>1.35</v>
@@ -2966,37 +3140,37 @@
         <v>12</v>
       </c>
       <c r="I10">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="J10">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="K10">
         <v>6.6</v>
       </c>
       <c r="L10">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="M10">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="P10">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="Q10">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="R10">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="T10">
         <v>2.16</v>
@@ -3011,19 +3185,19 @@
         <v>3.85</v>
       </c>
       <c r="X10">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="Y10">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="Z10">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA10">
         <v>1000</v>
       </c>
       <c r="AB10">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC10">
         <v>14</v>
@@ -3068,13 +3242,13 @@
         <v>15</v>
       </c>
       <c r="AQ10">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR10">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AS10">
-        <v>7.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT10">
         <v>6.2</v>
@@ -3083,46 +3257,46 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="AW10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AX10">
         <v>5.8</v>
       </c>
       <c r="AY10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BA10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BB10">
+        <v>7.8</v>
+      </c>
+      <c r="BC10">
+        <v>11</v>
+      </c>
+      <c r="BD10">
         <v>7.6</v>
       </c>
-      <c r="BC10">
-        <v>10.5</v>
-      </c>
-      <c r="BD10">
-        <v>6.8</v>
-      </c>
       <c r="BE10">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="BF10">
+        <v>4.9</v>
+      </c>
+      <c r="BG10">
+        <v>8.6</v>
+      </c>
+      <c r="BH10">
         <v>4.7</v>
       </c>
-      <c r="BG10">
-        <v>7.6</v>
-      </c>
-      <c r="BH10">
-        <v>4.8</v>
-      </c>
       <c r="BI10">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BJ10">
         <v>15.5</v>
@@ -3143,10 +3317,10 @@
         <v>2.92</v>
       </c>
       <c r="BP10">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BQ10">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BR10">
         <v>30</v>
@@ -3173,13 +3347,13 @@
         <v>4.7</v>
       </c>
       <c r="BZ10">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="CA10">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3187,16 +3361,16 @@
         <v>83</v>
       </c>
       <c r="B11" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C11" t="s">
-        <v>91</v>
+        <v>104</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E11" t="s">
-        <v>126</v>
+        <v>164</v>
       </c>
       <c r="F11">
         <v>1.41</v>
@@ -3205,19 +3379,19 @@
         <v>1.43</v>
       </c>
       <c r="H11">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I11">
         <v>8.6</v>
       </c>
       <c r="J11">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="K11">
         <v>6.4</v>
       </c>
       <c r="L11">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="M11">
         <v>1.01</v>
@@ -3229,7 +3403,7 @@
         <v>1.12</v>
       </c>
       <c r="P11">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q11">
         <v>1.35</v>
@@ -3250,7 +3424,7 @@
         <v>1.13</v>
       </c>
       <c r="W11">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="X11">
         <v>44</v>
@@ -3277,7 +3451,7 @@
         <v>95</v>
       </c>
       <c r="AF11">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG11">
         <v>13</v>
@@ -3307,16 +3481,16 @@
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AQ11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AR11">
         <v>6.2</v>
       </c>
       <c r="AS11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AT11">
         <v>13</v>
@@ -3328,7 +3502,7 @@
         <v>5.6</v>
       </c>
       <c r="AW11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3361,7 +3535,7 @@
         <v>6.2</v>
       </c>
       <c r="BH11">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BI11">
         <v>4.2</v>
@@ -3376,7 +3550,7 @@
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BN11">
         <v>5.1</v>
@@ -3391,7 +3565,7 @@
         <v>3.45</v>
       </c>
       <c r="BR11">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BS11">
         <v>4.3</v>
@@ -3409,10 +3583,10 @@
         <v>5</v>
       </c>
       <c r="BX11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BY11">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BZ11">
         <v>10.5</v>
@@ -3421,7 +3595,7 @@
         <v>3.6</v>
       </c>
       <c r="CB11" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3429,31 +3603,31 @@
         <v>84</v>
       </c>
       <c r="B12" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C12" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
       <c r="D12" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E12" t="s">
-        <v>127</v>
+        <v>165</v>
       </c>
       <c r="F12">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="G12">
-        <v>2.02</v>
+        <v>1.79</v>
       </c>
       <c r="H12">
-        <v>3.9</v>
+        <v>5.1</v>
       </c>
       <c r="I12">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="K12">
         <v>4.5</v>
@@ -3465,22 +3639,22 @@
         <v>1.05</v>
       </c>
       <c r="N12">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P12">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="Q12">
-        <v>1.66</v>
+        <v>1.77</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="S12">
-        <v>2.42</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -3489,10 +3663,10 @@
         <v>1.01</v>
       </c>
       <c r="V12">
-        <v>1.21</v>
+        <v>1.18</v>
       </c>
       <c r="W12">
-        <v>1.98</v>
+        <v>2.26</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -3663,7 +3837,7 @@
         <v>1.01</v>
       </c>
       <c r="CB12" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3671,16 +3845,16 @@
         <v>85</v>
       </c>
       <c r="B13" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C13" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="D13" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E13" t="s">
-        <v>128</v>
+        <v>166</v>
       </c>
       <c r="F13">
         <v>2.72</v>
@@ -3713,10 +3887,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="Q13">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -3905,7 +4079,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3913,366 +4087,366 @@
         <v>84</v>
       </c>
       <c r="B14" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C14" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="D14" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E14" t="s">
-        <v>129</v>
+        <v>167</v>
       </c>
       <c r="F14">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G14">
-        <v>2.46</v>
+        <v>2.24</v>
       </c>
       <c r="H14">
+        <v>3.85</v>
+      </c>
+      <c r="I14">
+        <v>4.5</v>
+      </c>
+      <c r="J14">
+        <v>3.3</v>
+      </c>
+      <c r="K14">
+        <v>3.7</v>
+      </c>
+      <c r="L14">
+        <v>1.43</v>
+      </c>
+      <c r="M14">
+        <v>1.08</v>
+      </c>
+      <c r="N14">
         <v>3.2</v>
       </c>
-      <c r="I14">
-        <v>4.3</v>
-      </c>
-      <c r="J14">
-        <v>3</v>
-      </c>
-      <c r="K14">
-        <v>4.1</v>
-      </c>
-      <c r="L14">
-        <v>1.39</v>
-      </c>
-      <c r="M14">
-        <v>1.07</v>
-      </c>
-      <c r="N14">
-        <v>3.15</v>
-      </c>
       <c r="O14">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="P14">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="Q14">
-        <v>1.87</v>
+        <v>2.06</v>
       </c>
       <c r="R14">
         <v>1.3</v>
       </c>
       <c r="S14">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T14">
-        <v>1.73</v>
+        <v>1.84</v>
       </c>
       <c r="U14">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V14">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="X14">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="Z14">
+        <v>34</v>
+      </c>
+      <c r="AA14">
+        <v>100</v>
+      </c>
+      <c r="AB14">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC14">
+        <v>9</v>
+      </c>
+      <c r="AD14">
+        <v>17.5</v>
+      </c>
+      <c r="AE14">
+        <v>65</v>
+      </c>
+      <c r="AF14">
+        <v>15</v>
+      </c>
+      <c r="AG14">
+        <v>12.5</v>
+      </c>
+      <c r="AH14">
+        <v>22</v>
+      </c>
+      <c r="AI14">
+        <v>75</v>
+      </c>
+      <c r="AJ14">
         <v>32</v>
       </c>
-      <c r="AA14">
-        <v>85</v>
-      </c>
-      <c r="AB14">
-        <v>11</v>
-      </c>
-      <c r="AC14">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AD14">
-        <v>18</v>
-      </c>
-      <c r="AE14">
-        <v>55</v>
-      </c>
-      <c r="AF14">
-        <v>16</v>
-      </c>
-      <c r="AG14">
-        <v>13</v>
-      </c>
-      <c r="AH14">
-        <v>21</v>
-      </c>
-      <c r="AI14">
-        <v>65</v>
-      </c>
-      <c r="AJ14">
-        <v>34</v>
-      </c>
       <c r="AK14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AL14">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM14">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AN14">
         <v>22</v>
       </c>
       <c r="AO14">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="AS14">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BA14">
-        <v>1.03</v>
+        <v>5.2</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BE14">
-        <v>1.03</v>
+        <v>5.4</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BH14">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="BI14">
-        <v>2.74</v>
+        <v>2.86</v>
       </c>
       <c r="BJ14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BN14">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="BV14">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX14">
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ14">
         <v>32</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="B15" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C15" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D15" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E15" t="s">
-        <v>130</v>
+        <v>168</v>
       </c>
       <c r="F15">
-        <v>1.61</v>
+        <v>1.68</v>
       </c>
       <c r="G15">
-        <v>1.94</v>
+        <v>1.82</v>
       </c>
       <c r="H15">
-        <v>4</v>
+        <v>4.7</v>
       </c>
       <c r="I15">
         <v>6.6</v>
       </c>
       <c r="J15">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
-        <v>5.1</v>
+        <v>4.6</v>
       </c>
       <c r="L15">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N15">
         <v>1.01</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="P15">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q15">
-        <v>1.53</v>
+        <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
-        <v>2.1</v>
+        <v>2.66</v>
       </c>
       <c r="T15">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U15">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
         <v>1.18</v>
       </c>
       <c r="W15">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="X15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
         <v>1.03</v>
@@ -4323,234 +4497,234 @@
         <v>1.03</v>
       </c>
       <c r="BF15">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
         <v>4.5</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BN15">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BP15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BR15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BT15">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BV15">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BX15">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="BZ15">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B16" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D16" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="E16" t="s">
-        <v>131</v>
+        <v>169</v>
       </c>
       <c r="F16">
-        <v>4.4</v>
+        <v>2.82</v>
       </c>
       <c r="G16">
-        <v>6.4</v>
+        <v>3.3</v>
       </c>
       <c r="H16">
-        <v>1.65</v>
+        <v>2.3</v>
       </c>
       <c r="I16">
-        <v>1.96</v>
+        <v>2.6</v>
       </c>
       <c r="J16">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L16">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="O16">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="P16">
-        <v>1.89</v>
+        <v>2.12</v>
       </c>
       <c r="Q16">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="R16">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="S16">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T16">
-        <v>1.71</v>
+        <v>1.01</v>
       </c>
       <c r="U16">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V16">
-        <v>2.04</v>
+        <v>1.63</v>
       </c>
       <c r="W16">
-        <v>1.18</v>
+        <v>1.43</v>
       </c>
       <c r="X16">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB16">
         <v>1.03</v>
@@ -4571,13 +4745,13 @@
         <v>1.01</v>
       </c>
       <c r="BH16">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI16">
         <v>1.01</v>
       </c>
       <c r="BJ16">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
@@ -4589,49 +4763,49 @@
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO16">
         <v>1.01</v>
       </c>
       <c r="BP16">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU16">
         <v>1.01</v>
       </c>
       <c r="BV16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4639,130 +4813,130 @@
         <v>84</v>
       </c>
       <c r="B17" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C17" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E17" t="s">
-        <v>132</v>
+        <v>170</v>
       </c>
       <c r="F17">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="G17">
-        <v>1.68</v>
+        <v>1.94</v>
       </c>
       <c r="H17">
-        <v>1.04</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>9.199999999999999</v>
+        <v>970</v>
       </c>
       <c r="J17">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="K17">
-        <v>5.4</v>
+        <v>950</v>
       </c>
       <c r="L17">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="M17">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="N17">
-        <v>3.4</v>
+        <v>2.98</v>
       </c>
       <c r="O17">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P17">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q17">
-        <v>1.73</v>
+        <v>1.61</v>
       </c>
       <c r="R17">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
-        <v>2.88</v>
+        <v>2.64</v>
       </c>
       <c r="T17">
-        <v>1.92</v>
+        <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.12</v>
+        <v>1.02</v>
       </c>
       <c r="W17">
-        <v>2.46</v>
+        <v>2.06</v>
       </c>
       <c r="X17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z17">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AA17">
-        <v>280</v>
+        <v>1000</v>
       </c>
       <c r="AB17">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AC17">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AD17">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AE17">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AF17">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH17">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AI17">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AJ17">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AP17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR17">
         <v>1.03</v>
@@ -4771,37 +4945,37 @@
         <v>1.03</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW17">
         <v>1.03</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA17">
         <v>1.03</v>
       </c>
       <c r="BB17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE17">
         <v>1.03</v>
@@ -4873,42 +5047,42 @@
         <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B18" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C18" t="s">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E18" t="s">
-        <v>133</v>
+        <v>171</v>
       </c>
       <c r="F18">
-        <v>1.04</v>
+        <v>2.24</v>
       </c>
       <c r="G18">
-        <v>1000</v>
+        <v>2.4</v>
       </c>
       <c r="H18">
-        <v>1.04</v>
+        <v>2.98</v>
       </c>
       <c r="I18">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="J18">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="K18">
-        <v>950</v>
+        <v>4.1</v>
       </c>
       <c r="L18">
         <v>1.01</v>
@@ -4917,28 +5091,28 @@
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>1.25</v>
+        <v>4.5</v>
       </c>
       <c r="O18">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="P18">
-        <v>1.25</v>
+        <v>2.44</v>
       </c>
       <c r="Q18">
-        <v>1.19</v>
+        <v>1.58</v>
       </c>
       <c r="R18">
-        <v>1.25</v>
+        <v>1.5</v>
       </c>
       <c r="S18">
-        <v>1.19</v>
+        <v>2.2</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.43</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.34</v>
       </c>
       <c r="V18">
         <v>1.01</v>
@@ -5001,52 +5175,52 @@
         <v>1000</v>
       </c>
       <c r="AP18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5055,67 +5229,67 @@
         <v>1.01</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5123,178 +5297,178 @@
         <v>84</v>
       </c>
       <c r="B19" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C19" t="s">
+        <v>108</v>
+      </c>
+      <c r="D19" t="s">
+        <v>132</v>
+      </c>
+      <c r="E19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F19">
+        <v>1.61</v>
+      </c>
+      <c r="G19">
+        <v>1.76</v>
+      </c>
+      <c r="H19">
+        <v>5.5</v>
+      </c>
+      <c r="I19">
+        <v>6.8</v>
+      </c>
+      <c r="J19">
+        <v>3.95</v>
+      </c>
+      <c r="K19">
+        <v>4.4</v>
+      </c>
+      <c r="L19">
+        <v>1.37</v>
+      </c>
+      <c r="M19">
+        <v>1.06</v>
+      </c>
+      <c r="N19">
+        <v>3.6</v>
+      </c>
+      <c r="O19">
+        <v>1.29</v>
+      </c>
+      <c r="P19">
+        <v>1.96</v>
+      </c>
+      <c r="Q19">
+        <v>1.87</v>
+      </c>
+      <c r="R19">
+        <v>1.35</v>
+      </c>
+      <c r="S19">
+        <v>3.2</v>
+      </c>
+      <c r="T19">
+        <v>1.86</v>
+      </c>
+      <c r="U19">
+        <v>1.83</v>
+      </c>
+      <c r="V19">
+        <v>1.17</v>
+      </c>
+      <c r="W19">
+        <v>2.3</v>
+      </c>
+      <c r="X19">
+        <v>18.5</v>
+      </c>
+      <c r="Y19">
+        <v>23</v>
+      </c>
+      <c r="Z19">
+        <v>60</v>
+      </c>
+      <c r="AA19">
+        <v>190</v>
+      </c>
+      <c r="AB19">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AC19">
+        <v>11</v>
+      </c>
+      <c r="AD19">
+        <v>27</v>
+      </c>
+      <c r="AE19">
+        <v>100</v>
+      </c>
+      <c r="AF19">
+        <v>11.5</v>
+      </c>
+      <c r="AG19">
+        <v>11.5</v>
+      </c>
+      <c r="AH19">
+        <v>25</v>
+      </c>
+      <c r="AI19">
         <v>95</v>
       </c>
-      <c r="D19" t="s">
-        <v>114</v>
-      </c>
-      <c r="E19" t="s">
-        <v>134</v>
-      </c>
-      <c r="F19">
-        <v>1.04</v>
-      </c>
-      <c r="G19">
-        <v>1000</v>
-      </c>
-      <c r="H19">
-        <v>1.04</v>
-      </c>
-      <c r="I19">
-        <v>970</v>
-      </c>
-      <c r="J19">
-        <v>1.03</v>
-      </c>
-      <c r="K19">
-        <v>950</v>
-      </c>
-      <c r="L19">
-        <v>1.01</v>
-      </c>
-      <c r="M19">
-        <v>1.01</v>
-      </c>
-      <c r="N19">
-        <v>1.26</v>
-      </c>
-      <c r="O19">
-        <v>1.27</v>
-      </c>
-      <c r="P19">
-        <v>1.25</v>
-      </c>
-      <c r="Q19">
-        <v>1.27</v>
-      </c>
-      <c r="R19">
-        <v>1.25</v>
-      </c>
-      <c r="S19">
-        <v>1.27</v>
-      </c>
-      <c r="T19">
-        <v>1.01</v>
-      </c>
-      <c r="U19">
-        <v>1.01</v>
-      </c>
-      <c r="V19">
-        <v>1.01</v>
-      </c>
-      <c r="W19">
-        <v>1.01</v>
-      </c>
-      <c r="X19">
-        <v>1000</v>
-      </c>
-      <c r="Y19">
-        <v>1000</v>
-      </c>
-      <c r="Z19">
-        <v>1000</v>
-      </c>
-      <c r="AA19">
-        <v>1000</v>
-      </c>
-      <c r="AB19">
-        <v>1000</v>
-      </c>
-      <c r="AC19">
-        <v>1000</v>
-      </c>
-      <c r="AD19">
-        <v>1000</v>
-      </c>
-      <c r="AE19">
-        <v>1000</v>
-      </c>
-      <c r="AF19">
-        <v>1000</v>
-      </c>
-      <c r="AG19">
-        <v>1000</v>
-      </c>
-      <c r="AH19">
-        <v>1000</v>
-      </c>
-      <c r="AI19">
-        <v>1000</v>
-      </c>
       <c r="AJ19">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AK19">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL19">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM19">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AN19">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AO19">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AP19">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ19">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AR19">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AS19">
-        <v>1.03</v>
+        <v>5.1</v>
       </c>
       <c r="AT19">
-        <v>1.03</v>
+        <v>6.6</v>
       </c>
       <c r="AU19">
-        <v>1.03</v>
+        <v>7.2</v>
       </c>
       <c r="AV19">
-        <v>1.03</v>
+        <v>17</v>
       </c>
       <c r="AW19">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="AX19">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AY19">
-        <v>1.03</v>
+        <v>7.8</v>
       </c>
       <c r="AZ19">
-        <v>1.03</v>
+        <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB19">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="BC19">
-        <v>1.03</v>
+        <v>13.5</v>
       </c>
       <c r="BD19">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE19">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF19">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BG19">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5357,491 +5531,5331 @@
         <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B20" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="C20" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E20" t="s">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="F20">
-        <v>1.09</v>
+        <v>4.4</v>
       </c>
       <c r="G20">
+        <v>6.4</v>
+      </c>
+      <c r="H20">
+        <v>1.65</v>
+      </c>
+      <c r="I20">
+        <v>1.96</v>
+      </c>
+      <c r="J20">
+        <v>3</v>
+      </c>
+      <c r="K20">
+        <v>4.8</v>
+      </c>
+      <c r="L20">
+        <v>1.33</v>
+      </c>
+      <c r="M20">
+        <v>1.05</v>
+      </c>
+      <c r="N20">
+        <v>3.7</v>
+      </c>
+      <c r="O20">
+        <v>1.26</v>
+      </c>
+      <c r="P20">
+        <v>1.89</v>
+      </c>
+      <c r="Q20">
+        <v>1.73</v>
+      </c>
+      <c r="R20">
+        <v>1.34</v>
+      </c>
+      <c r="S20">
+        <v>2.96</v>
+      </c>
+      <c r="T20">
+        <v>1.71</v>
+      </c>
+      <c r="U20">
+        <v>1.96</v>
+      </c>
+      <c r="V20">
+        <v>2.04</v>
+      </c>
+      <c r="W20">
+        <v>1.18</v>
+      </c>
+      <c r="X20">
+        <v>19</v>
+      </c>
+      <c r="Y20">
         <v>10.5</v>
       </c>
-      <c r="H20">
-        <v>1.11</v>
-      </c>
-      <c r="I20">
-        <v>1000</v>
-      </c>
-      <c r="J20">
-        <v>1.1</v>
-      </c>
-      <c r="K20">
-        <v>950</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>1.24</v>
-      </c>
-      <c r="Q20">
-        <v>1.01</v>
-      </c>
-      <c r="R20">
-        <v>0</v>
-      </c>
-      <c r="S20">
-        <v>0</v>
-      </c>
-      <c r="T20">
-        <v>0</v>
-      </c>
-      <c r="U20">
-        <v>0</v>
-      </c>
-      <c r="V20">
-        <v>0</v>
-      </c>
-      <c r="W20">
-        <v>0</v>
-      </c>
-      <c r="X20">
-        <v>0</v>
-      </c>
-      <c r="Y20">
-        <v>0</v>
-      </c>
       <c r="Z20">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="CB20" t="s">
-        <v>137</v>
+        <v>195</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
+        <v>84</v>
+      </c>
+      <c r="B21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C21" t="s">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s">
+        <v>134</v>
+      </c>
+      <c r="E21" t="s">
+        <v>174</v>
+      </c>
+      <c r="F21">
+        <v>1.58</v>
+      </c>
+      <c r="G21">
+        <v>1.72</v>
+      </c>
+      <c r="H21">
+        <v>5.3</v>
+      </c>
+      <c r="I21">
+        <v>6.8</v>
+      </c>
+      <c r="J21">
+        <v>4.1</v>
+      </c>
+      <c r="K21">
+        <v>4.9</v>
+      </c>
+      <c r="L21">
+        <v>1.27</v>
+      </c>
+      <c r="M21">
+        <v>1.04</v>
+      </c>
+      <c r="N21">
+        <v>4.5</v>
+      </c>
+      <c r="O21">
+        <v>1.23</v>
+      </c>
+      <c r="P21">
+        <v>2.2</v>
+      </c>
+      <c r="Q21">
+        <v>1.67</v>
+      </c>
+      <c r="R21">
+        <v>1.48</v>
+      </c>
+      <c r="S21">
+        <v>2.68</v>
+      </c>
+      <c r="T21">
+        <v>1.74</v>
+      </c>
+      <c r="U21">
+        <v>2.1</v>
+      </c>
+      <c r="V21">
+        <v>1.17</v>
+      </c>
+      <c r="W21">
+        <v>2.38</v>
+      </c>
+      <c r="X21">
+        <v>25</v>
+      </c>
+      <c r="Y21">
+        <v>28</v>
+      </c>
+      <c r="Z21">
+        <v>60</v>
+      </c>
+      <c r="AA21">
+        <v>180</v>
+      </c>
+      <c r="AB21">
+        <v>12.5</v>
+      </c>
+      <c r="AC21">
+        <v>12.5</v>
+      </c>
+      <c r="AD21">
+        <v>27</v>
+      </c>
+      <c r="AE21">
+        <v>90</v>
+      </c>
+      <c r="AF21">
+        <v>13.5</v>
+      </c>
+      <c r="AG21">
+        <v>12.5</v>
+      </c>
+      <c r="AH21">
+        <v>24</v>
+      </c>
+      <c r="AI21">
+        <v>85</v>
+      </c>
+      <c r="AJ21">
+        <v>19.5</v>
+      </c>
+      <c r="AK21">
+        <v>20</v>
+      </c>
+      <c r="AL21">
+        <v>38</v>
+      </c>
+      <c r="AM21">
+        <v>120</v>
+      </c>
+      <c r="AN21">
+        <v>9.6</v>
+      </c>
+      <c r="AO21">
+        <v>90</v>
+      </c>
+      <c r="AP21">
+        <v>15</v>
+      </c>
+      <c r="AQ21">
+        <v>16.5</v>
+      </c>
+      <c r="AR21">
+        <v>1.01</v>
+      </c>
+      <c r="AS21">
+        <v>1.01</v>
+      </c>
+      <c r="AT21">
+        <v>7.4</v>
+      </c>
+      <c r="AU21">
+        <v>7.6</v>
+      </c>
+      <c r="AV21">
+        <v>16</v>
+      </c>
+      <c r="AW21">
+        <v>1.01</v>
+      </c>
+      <c r="AX21">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AZ21">
+        <v>14</v>
+      </c>
+      <c r="BA21">
+        <v>1.01</v>
+      </c>
+      <c r="BB21">
+        <v>11.5</v>
+      </c>
+      <c r="BC21">
+        <v>12</v>
+      </c>
+      <c r="BD21">
+        <v>1.03</v>
+      </c>
+      <c r="BE21">
+        <v>1.01</v>
+      </c>
+      <c r="BF21">
+        <v>5.9</v>
+      </c>
+      <c r="BG21">
+        <v>1.01</v>
+      </c>
+      <c r="BH21">
+        <v>4.2</v>
+      </c>
+      <c r="BI21">
+        <v>3.15</v>
+      </c>
+      <c r="BJ21">
+        <v>10.5</v>
+      </c>
+      <c r="BK21">
+        <v>5</v>
+      </c>
+      <c r="BL21">
+        <v>1000</v>
+      </c>
+      <c r="BM21">
+        <v>9</v>
+      </c>
+      <c r="BN21">
+        <v>4.5</v>
+      </c>
+      <c r="BO21">
+        <v>3.4</v>
+      </c>
+      <c r="BP21">
+        <v>11</v>
+      </c>
+      <c r="BQ21">
+        <v>5.2</v>
+      </c>
+      <c r="BR21">
+        <v>24</v>
+      </c>
+      <c r="BS21">
+        <v>7</v>
+      </c>
+      <c r="BT21">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BU21">
+        <v>4.9</v>
+      </c>
+      <c r="BV21">
+        <v>48</v>
+      </c>
+      <c r="BW21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BX21">
+        <v>50</v>
+      </c>
+      <c r="BY21">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="BZ21">
+        <v>17</v>
+      </c>
+      <c r="CA21">
+        <v>6.2</v>
+      </c>
+      <c r="CB21" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="22" spans="1:80">
+      <c r="A22" t="s">
+        <v>84</v>
+      </c>
+      <c r="B22" t="s">
+        <v>100</v>
+      </c>
+      <c r="C22" t="s">
+        <v>108</v>
+      </c>
+      <c r="D22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E22" t="s">
+        <v>175</v>
+      </c>
+      <c r="F22">
+        <v>1.98</v>
+      </c>
+      <c r="G22">
+        <v>2.3</v>
+      </c>
+      <c r="H22">
+        <v>3.3</v>
+      </c>
+      <c r="I22">
+        <v>4.3</v>
+      </c>
+      <c r="J22">
+        <v>3.5</v>
+      </c>
+      <c r="K22">
+        <v>5.2</v>
+      </c>
+      <c r="L22">
+        <v>1.01</v>
+      </c>
+      <c r="M22">
+        <v>1.01</v>
+      </c>
+      <c r="N22">
+        <v>3.65</v>
+      </c>
+      <c r="O22">
+        <v>1.22</v>
+      </c>
+      <c r="P22">
+        <v>2.02</v>
+      </c>
+      <c r="Q22">
+        <v>1.7</v>
+      </c>
+      <c r="R22">
+        <v>1.45</v>
+      </c>
+      <c r="S22">
+        <v>2.68</v>
+      </c>
+      <c r="T22">
+        <v>1.01</v>
+      </c>
+      <c r="U22">
+        <v>1.01</v>
+      </c>
+      <c r="V22">
+        <v>1.3</v>
+      </c>
+      <c r="W22">
+        <v>1.77</v>
+      </c>
+      <c r="X22">
+        <v>1000</v>
+      </c>
+      <c r="Y22">
+        <v>1000</v>
+      </c>
+      <c r="Z22">
+        <v>1000</v>
+      </c>
+      <c r="AA22">
+        <v>1000</v>
+      </c>
+      <c r="AB22">
+        <v>1000</v>
+      </c>
+      <c r="AC22">
+        <v>1000</v>
+      </c>
+      <c r="AD22">
+        <v>1000</v>
+      </c>
+      <c r="AE22">
+        <v>1000</v>
+      </c>
+      <c r="AF22">
+        <v>1000</v>
+      </c>
+      <c r="AG22">
+        <v>1000</v>
+      </c>
+      <c r="AH22">
+        <v>1000</v>
+      </c>
+      <c r="AI22">
+        <v>1000</v>
+      </c>
+      <c r="AJ22">
+        <v>1000</v>
+      </c>
+      <c r="AK22">
+        <v>1000</v>
+      </c>
+      <c r="AL22">
+        <v>1000</v>
+      </c>
+      <c r="AM22">
+        <v>1000</v>
+      </c>
+      <c r="AN22">
+        <v>1000</v>
+      </c>
+      <c r="AO22">
+        <v>1000</v>
+      </c>
+      <c r="AP22">
+        <v>1.03</v>
+      </c>
+      <c r="AQ22">
+        <v>1.03</v>
+      </c>
+      <c r="AR22">
+        <v>1.03</v>
+      </c>
+      <c r="AS22">
+        <v>1.03</v>
+      </c>
+      <c r="AT22">
+        <v>1.03</v>
+      </c>
+      <c r="AU22">
+        <v>1.03</v>
+      </c>
+      <c r="AV22">
+        <v>1.03</v>
+      </c>
+      <c r="AW22">
+        <v>1.03</v>
+      </c>
+      <c r="AX22">
+        <v>1.03</v>
+      </c>
+      <c r="AY22">
+        <v>1.03</v>
+      </c>
+      <c r="AZ22">
+        <v>1.03</v>
+      </c>
+      <c r="BA22">
+        <v>1.03</v>
+      </c>
+      <c r="BB22">
+        <v>1.03</v>
+      </c>
+      <c r="BC22">
+        <v>1.03</v>
+      </c>
+      <c r="BD22">
+        <v>1.03</v>
+      </c>
+      <c r="BE22">
+        <v>1.03</v>
+      </c>
+      <c r="BF22">
+        <v>1.01</v>
+      </c>
+      <c r="BG22">
+        <v>1.01</v>
+      </c>
+      <c r="BH22">
+        <v>1000</v>
+      </c>
+      <c r="BI22">
+        <v>1.01</v>
+      </c>
+      <c r="BJ22">
+        <v>1000</v>
+      </c>
+      <c r="BK22">
+        <v>1.01</v>
+      </c>
+      <c r="BL22">
+        <v>1000</v>
+      </c>
+      <c r="BM22">
+        <v>1.01</v>
+      </c>
+      <c r="BN22">
+        <v>1000</v>
+      </c>
+      <c r="BO22">
+        <v>1.01</v>
+      </c>
+      <c r="BP22">
+        <v>1000</v>
+      </c>
+      <c r="BQ22">
+        <v>1.01</v>
+      </c>
+      <c r="BR22">
+        <v>1000</v>
+      </c>
+      <c r="BS22">
+        <v>1.01</v>
+      </c>
+      <c r="BT22">
+        <v>1000</v>
+      </c>
+      <c r="BU22">
+        <v>1.01</v>
+      </c>
+      <c r="BV22">
+        <v>1000</v>
+      </c>
+      <c r="BW22">
+        <v>1.01</v>
+      </c>
+      <c r="BX22">
+        <v>1000</v>
+      </c>
+      <c r="BY22">
+        <v>1.01</v>
+      </c>
+      <c r="BZ22">
+        <v>1000</v>
+      </c>
+      <c r="CA22">
+        <v>1.01</v>
+      </c>
+      <c r="CB22" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="23" spans="1:80">
+      <c r="A23" t="s">
+        <v>89</v>
+      </c>
+      <c r="B23" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" t="s">
+        <v>136</v>
+      </c>
+      <c r="E23" t="s">
+        <v>176</v>
+      </c>
+      <c r="F23">
+        <v>1.96</v>
+      </c>
+      <c r="G23">
+        <v>2.18</v>
+      </c>
+      <c r="H23">
+        <v>3.35</v>
+      </c>
+      <c r="I23">
+        <v>3.95</v>
+      </c>
+      <c r="J23">
+        <v>3.85</v>
+      </c>
+      <c r="K23">
+        <v>4.6</v>
+      </c>
+      <c r="L23">
+        <v>1.01</v>
+      </c>
+      <c r="M23">
+        <v>1.01</v>
+      </c>
+      <c r="N23">
+        <v>4.4</v>
+      </c>
+      <c r="O23">
+        <v>1.16</v>
+      </c>
+      <c r="P23">
+        <v>2.48</v>
+      </c>
+      <c r="Q23">
+        <v>1.54</v>
+      </c>
+      <c r="R23">
+        <v>1.51</v>
+      </c>
+      <c r="S23">
+        <v>2.16</v>
+      </c>
+      <c r="T23">
+        <v>1.01</v>
+      </c>
+      <c r="U23">
+        <v>1.01</v>
+      </c>
+      <c r="V23">
+        <v>1.33</v>
+      </c>
+      <c r="W23">
+        <v>1.84</v>
+      </c>
+      <c r="X23">
+        <v>1000</v>
+      </c>
+      <c r="Y23">
+        <v>1000</v>
+      </c>
+      <c r="Z23">
+        <v>1000</v>
+      </c>
+      <c r="AA23">
+        <v>1000</v>
+      </c>
+      <c r="AB23">
+        <v>1000</v>
+      </c>
+      <c r="AC23">
+        <v>1000</v>
+      </c>
+      <c r="AD23">
+        <v>1000</v>
+      </c>
+      <c r="AE23">
+        <v>1000</v>
+      </c>
+      <c r="AF23">
+        <v>1000</v>
+      </c>
+      <c r="AG23">
+        <v>1000</v>
+      </c>
+      <c r="AH23">
+        <v>1000</v>
+      </c>
+      <c r="AI23">
+        <v>1000</v>
+      </c>
+      <c r="AJ23">
+        <v>1000</v>
+      </c>
+      <c r="AK23">
+        <v>1000</v>
+      </c>
+      <c r="AL23">
+        <v>1000</v>
+      </c>
+      <c r="AM23">
+        <v>1000</v>
+      </c>
+      <c r="AN23">
+        <v>1000</v>
+      </c>
+      <c r="AO23">
+        <v>1000</v>
+      </c>
+      <c r="AP23">
+        <v>1.03</v>
+      </c>
+      <c r="AQ23">
+        <v>1.03</v>
+      </c>
+      <c r="AR23">
+        <v>1.03</v>
+      </c>
+      <c r="AS23">
+        <v>1.03</v>
+      </c>
+      <c r="AT23">
+        <v>1.03</v>
+      </c>
+      <c r="AU23">
+        <v>1.03</v>
+      </c>
+      <c r="AV23">
+        <v>1.03</v>
+      </c>
+      <c r="AW23">
+        <v>1.03</v>
+      </c>
+      <c r="AX23">
+        <v>1.03</v>
+      </c>
+      <c r="AY23">
+        <v>1.03</v>
+      </c>
+      <c r="AZ23">
+        <v>1.03</v>
+      </c>
+      <c r="BA23">
+        <v>1.03</v>
+      </c>
+      <c r="BB23">
+        <v>1.03</v>
+      </c>
+      <c r="BC23">
+        <v>1.03</v>
+      </c>
+      <c r="BD23">
+        <v>1.03</v>
+      </c>
+      <c r="BE23">
+        <v>1.03</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>1.01</v>
+      </c>
+      <c r="BH23">
+        <v>1000</v>
+      </c>
+      <c r="BI23">
+        <v>1.01</v>
+      </c>
+      <c r="BJ23">
+        <v>1000</v>
+      </c>
+      <c r="BK23">
+        <v>1.01</v>
+      </c>
+      <c r="BL23">
+        <v>1000</v>
+      </c>
+      <c r="BM23">
+        <v>1.01</v>
+      </c>
+      <c r="BN23">
+        <v>1000</v>
+      </c>
+      <c r="BO23">
+        <v>1.01</v>
+      </c>
+      <c r="BP23">
+        <v>1000</v>
+      </c>
+      <c r="BQ23">
+        <v>1.01</v>
+      </c>
+      <c r="BR23">
+        <v>1000</v>
+      </c>
+      <c r="BS23">
+        <v>1.01</v>
+      </c>
+      <c r="BT23">
+        <v>1000</v>
+      </c>
+      <c r="BU23">
+        <v>1.01</v>
+      </c>
+      <c r="BV23">
+        <v>1000</v>
+      </c>
+      <c r="BW23">
+        <v>1.01</v>
+      </c>
+      <c r="BX23">
+        <v>1000</v>
+      </c>
+      <c r="BY23">
+        <v>1.01</v>
+      </c>
+      <c r="BZ23">
+        <v>1000</v>
+      </c>
+      <c r="CA23">
+        <v>1.01</v>
+      </c>
+      <c r="CB23" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="24" spans="1:80">
+      <c r="A24" t="s">
+        <v>89</v>
+      </c>
+      <c r="B24" t="s">
+        <v>100</v>
+      </c>
+      <c r="C24" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" t="s">
+        <v>137</v>
+      </c>
+      <c r="E24" t="s">
+        <v>177</v>
+      </c>
+      <c r="F24">
+        <v>1.46</v>
+      </c>
+      <c r="G24">
+        <v>1.54</v>
+      </c>
+      <c r="H24">
+        <v>6.6</v>
+      </c>
+      <c r="I24">
+        <v>8.4</v>
+      </c>
+      <c r="J24">
+        <v>4.8</v>
+      </c>
+      <c r="K24">
+        <v>5.4</v>
+      </c>
+      <c r="L24">
+        <v>1.01</v>
+      </c>
+      <c r="M24">
+        <v>1.03</v>
+      </c>
+      <c r="N24">
+        <v>4.4</v>
+      </c>
+      <c r="O24">
+        <v>1.13</v>
+      </c>
+      <c r="P24">
+        <v>2.56</v>
+      </c>
+      <c r="Q24">
+        <v>1.54</v>
+      </c>
+      <c r="R24">
+        <v>1.51</v>
+      </c>
+      <c r="S24">
+        <v>2.12</v>
+      </c>
+      <c r="T24">
+        <v>1.01</v>
+      </c>
+      <c r="U24">
+        <v>1.01</v>
+      </c>
+      <c r="V24">
+        <v>1.13</v>
+      </c>
+      <c r="W24">
+        <v>2.84</v>
+      </c>
+      <c r="X24">
+        <v>1000</v>
+      </c>
+      <c r="Y24">
+        <v>44</v>
+      </c>
+      <c r="Z24">
+        <v>1000</v>
+      </c>
+      <c r="AA24">
+        <v>1000</v>
+      </c>
+      <c r="AB24">
+        <v>16</v>
+      </c>
+      <c r="AC24">
+        <v>17</v>
+      </c>
+      <c r="AD24">
+        <v>38</v>
+      </c>
+      <c r="AE24">
+        <v>1000</v>
+      </c>
+      <c r="AF24">
+        <v>15</v>
+      </c>
+      <c r="AG24">
+        <v>14.5</v>
+      </c>
+      <c r="AH24">
+        <v>29</v>
+      </c>
+      <c r="AI24">
+        <v>1000</v>
+      </c>
+      <c r="AJ24">
+        <v>20</v>
+      </c>
+      <c r="AK24">
+        <v>20</v>
+      </c>
+      <c r="AL24">
+        <v>40</v>
+      </c>
+      <c r="AM24">
+        <v>1000</v>
+      </c>
+      <c r="AN24">
+        <v>1000</v>
+      </c>
+      <c r="AO24">
+        <v>1000</v>
+      </c>
+      <c r="AP24">
+        <v>1.03</v>
+      </c>
+      <c r="AQ24">
+        <v>18.5</v>
+      </c>
+      <c r="AR24">
+        <v>1.03</v>
+      </c>
+      <c r="AS24">
+        <v>1.03</v>
+      </c>
+      <c r="AT24">
+        <v>7.4</v>
+      </c>
+      <c r="AU24">
+        <v>7.8</v>
+      </c>
+      <c r="AV24">
+        <v>16.5</v>
+      </c>
+      <c r="AW24">
+        <v>1.03</v>
+      </c>
+      <c r="AX24">
+        <v>7.2</v>
+      </c>
+      <c r="AY24">
+        <v>6.8</v>
+      </c>
+      <c r="AZ24">
+        <v>13</v>
+      </c>
+      <c r="BA24">
+        <v>1.03</v>
+      </c>
+      <c r="BB24">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BC24">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BD24">
+        <v>17.5</v>
+      </c>
+      <c r="BE24">
+        <v>1.03</v>
+      </c>
+      <c r="BF24">
+        <v>1.01</v>
+      </c>
+      <c r="BG24">
+        <v>1.01</v>
+      </c>
+      <c r="BH24">
+        <v>5.8</v>
+      </c>
+      <c r="BI24">
+        <v>3.3</v>
+      </c>
+      <c r="BJ24">
+        <v>13.5</v>
+      </c>
+      <c r="BK24">
+        <v>1.01</v>
+      </c>
+      <c r="BL24">
+        <v>1000</v>
+      </c>
+      <c r="BM24">
+        <v>1.01</v>
+      </c>
+      <c r="BN24">
+        <v>5.8</v>
+      </c>
+      <c r="BO24">
+        <v>3.05</v>
+      </c>
+      <c r="BP24">
+        <v>12.5</v>
+      </c>
+      <c r="BQ24">
+        <v>1.01</v>
+      </c>
+      <c r="BR24">
+        <v>28</v>
+      </c>
+      <c r="BS24">
+        <v>1.01</v>
+      </c>
+      <c r="BT24">
+        <v>15</v>
+      </c>
+      <c r="BU24">
+        <v>1.01</v>
+      </c>
+      <c r="BV24">
+        <v>1000</v>
+      </c>
+      <c r="BW24">
+        <v>1.01</v>
+      </c>
+      <c r="BX24">
+        <v>1000</v>
+      </c>
+      <c r="BY24">
+        <v>1.01</v>
+      </c>
+      <c r="BZ24">
+        <v>17</v>
+      </c>
+      <c r="CA24">
+        <v>1.01</v>
+      </c>
+      <c r="CB24" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="25" spans="1:80">
+      <c r="A25" t="s">
+        <v>90</v>
+      </c>
+      <c r="B25" t="s">
+        <v>100</v>
+      </c>
+      <c r="C25" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" t="s">
+        <v>138</v>
+      </c>
+      <c r="E25" t="s">
+        <v>178</v>
+      </c>
+      <c r="F25">
+        <v>1.4</v>
+      </c>
+      <c r="G25">
+        <v>1.77</v>
+      </c>
+      <c r="H25">
+        <v>4.1</v>
+      </c>
+      <c r="I25">
+        <v>110</v>
+      </c>
+      <c r="J25">
+        <v>4.1</v>
+      </c>
+      <c r="K25">
+        <v>950</v>
+      </c>
+      <c r="L25">
+        <v>1.01</v>
+      </c>
+      <c r="M25">
+        <v>1.01</v>
+      </c>
+      <c r="N25">
+        <v>2.06</v>
+      </c>
+      <c r="O25">
+        <v>1.2</v>
+      </c>
+      <c r="P25">
+        <v>2.04</v>
+      </c>
+      <c r="Q25">
+        <v>1.47</v>
+      </c>
+      <c r="R25">
+        <v>1.35</v>
+      </c>
+      <c r="S25">
+        <v>2.42</v>
+      </c>
+      <c r="T25">
+        <v>1.01</v>
+      </c>
+      <c r="U25">
+        <v>1.01</v>
+      </c>
+      <c r="V25">
+        <v>1.04</v>
+      </c>
+      <c r="W25">
+        <v>2.28</v>
+      </c>
+      <c r="X25">
+        <v>1000</v>
+      </c>
+      <c r="Y25">
+        <v>1000</v>
+      </c>
+      <c r="Z25">
+        <v>1000</v>
+      </c>
+      <c r="AA25">
+        <v>1000</v>
+      </c>
+      <c r="AB25">
+        <v>1000</v>
+      </c>
+      <c r="AC25">
+        <v>1000</v>
+      </c>
+      <c r="AD25">
+        <v>1000</v>
+      </c>
+      <c r="AE25">
+        <v>1000</v>
+      </c>
+      <c r="AF25">
+        <v>1000</v>
+      </c>
+      <c r="AG25">
+        <v>1000</v>
+      </c>
+      <c r="AH25">
+        <v>1000</v>
+      </c>
+      <c r="AI25">
+        <v>1000</v>
+      </c>
+      <c r="AJ25">
+        <v>1000</v>
+      </c>
+      <c r="AK25">
+        <v>1000</v>
+      </c>
+      <c r="AL25">
+        <v>1000</v>
+      </c>
+      <c r="AM25">
+        <v>1000</v>
+      </c>
+      <c r="AN25">
+        <v>1000</v>
+      </c>
+      <c r="AO25">
+        <v>1000</v>
+      </c>
+      <c r="AP25">
+        <v>1.03</v>
+      </c>
+      <c r="AQ25">
+        <v>1.03</v>
+      </c>
+      <c r="AR25">
+        <v>1.03</v>
+      </c>
+      <c r="AS25">
+        <v>1.03</v>
+      </c>
+      <c r="AT25">
+        <v>1.03</v>
+      </c>
+      <c r="AU25">
+        <v>1.03</v>
+      </c>
+      <c r="AV25">
+        <v>1.03</v>
+      </c>
+      <c r="AW25">
+        <v>1.03</v>
+      </c>
+      <c r="AX25">
+        <v>1.03</v>
+      </c>
+      <c r="AY25">
+        <v>1.03</v>
+      </c>
+      <c r="AZ25">
+        <v>1.03</v>
+      </c>
+      <c r="BA25">
+        <v>1.03</v>
+      </c>
+      <c r="BB25">
+        <v>1.03</v>
+      </c>
+      <c r="BC25">
+        <v>1.03</v>
+      </c>
+      <c r="BD25">
+        <v>1.03</v>
+      </c>
+      <c r="BE25">
+        <v>1.03</v>
+      </c>
+      <c r="BF25">
+        <v>1.01</v>
+      </c>
+      <c r="BG25">
+        <v>1.01</v>
+      </c>
+      <c r="BH25">
+        <v>1000</v>
+      </c>
+      <c r="BI25">
+        <v>1.01</v>
+      </c>
+      <c r="BJ25">
+        <v>1000</v>
+      </c>
+      <c r="BK25">
+        <v>1.01</v>
+      </c>
+      <c r="BL25">
+        <v>1000</v>
+      </c>
+      <c r="BM25">
+        <v>1.01</v>
+      </c>
+      <c r="BN25">
+        <v>1000</v>
+      </c>
+      <c r="BO25">
+        <v>1.01</v>
+      </c>
+      <c r="BP25">
+        <v>1000</v>
+      </c>
+      <c r="BQ25">
+        <v>1.01</v>
+      </c>
+      <c r="BR25">
+        <v>1000</v>
+      </c>
+      <c r="BS25">
+        <v>1.01</v>
+      </c>
+      <c r="BT25">
+        <v>1000</v>
+      </c>
+      <c r="BU25">
+        <v>1.01</v>
+      </c>
+      <c r="BV25">
+        <v>1000</v>
+      </c>
+      <c r="BW25">
+        <v>1.01</v>
+      </c>
+      <c r="BX25">
+        <v>1000</v>
+      </c>
+      <c r="BY25">
+        <v>1.01</v>
+      </c>
+      <c r="BZ25">
+        <v>1000</v>
+      </c>
+      <c r="CA25">
+        <v>1.01</v>
+      </c>
+      <c r="CB25" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="26" spans="1:80">
+      <c r="A26" t="s">
+        <v>91</v>
+      </c>
+      <c r="B26" t="s">
+        <v>100</v>
+      </c>
+      <c r="C26" t="s">
+        <v>110</v>
+      </c>
+      <c r="D26" t="s">
+        <v>139</v>
+      </c>
+      <c r="E26" t="s">
+        <v>179</v>
+      </c>
+      <c r="F26">
+        <v>1.5</v>
+      </c>
+      <c r="G26">
+        <v>1.53</v>
+      </c>
+      <c r="H26">
+        <v>7.4</v>
+      </c>
+      <c r="I26">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="J26">
+        <v>4.3</v>
+      </c>
+      <c r="K26">
+        <v>4.8</v>
+      </c>
+      <c r="L26">
+        <v>1.01</v>
+      </c>
+      <c r="M26">
+        <v>1.01</v>
+      </c>
+      <c r="N26">
+        <v>3.75</v>
+      </c>
+      <c r="O26">
+        <v>1.28</v>
+      </c>
+      <c r="P26">
+        <v>2.02</v>
+      </c>
+      <c r="Q26">
+        <v>1.86</v>
+      </c>
+      <c r="R26">
+        <v>1.37</v>
+      </c>
+      <c r="S26">
+        <v>3.05</v>
+      </c>
+      <c r="T26">
+        <v>1.01</v>
+      </c>
+      <c r="U26">
+        <v>1.67</v>
+      </c>
+      <c r="V26">
+        <v>1.12</v>
+      </c>
+      <c r="W26">
+        <v>2.88</v>
+      </c>
+      <c r="X26">
+        <v>1000</v>
+      </c>
+      <c r="Y26">
+        <v>1000</v>
+      </c>
+      <c r="Z26">
+        <v>1000</v>
+      </c>
+      <c r="AA26">
+        <v>1000</v>
+      </c>
+      <c r="AB26">
+        <v>1000</v>
+      </c>
+      <c r="AC26">
+        <v>1000</v>
+      </c>
+      <c r="AD26">
+        <v>1000</v>
+      </c>
+      <c r="AE26">
+        <v>1000</v>
+      </c>
+      <c r="AF26">
+        <v>1000</v>
+      </c>
+      <c r="AG26">
+        <v>1000</v>
+      </c>
+      <c r="AH26">
+        <v>1000</v>
+      </c>
+      <c r="AI26">
+        <v>1000</v>
+      </c>
+      <c r="AJ26">
+        <v>1000</v>
+      </c>
+      <c r="AK26">
+        <v>1000</v>
+      </c>
+      <c r="AL26">
+        <v>1000</v>
+      </c>
+      <c r="AM26">
+        <v>1000</v>
+      </c>
+      <c r="AN26">
+        <v>1000</v>
+      </c>
+      <c r="AO26">
+        <v>1000</v>
+      </c>
+      <c r="AP26">
+        <v>1.01</v>
+      </c>
+      <c r="AQ26">
+        <v>1.01</v>
+      </c>
+      <c r="AR26">
+        <v>1.01</v>
+      </c>
+      <c r="AS26">
+        <v>1.01</v>
+      </c>
+      <c r="AT26">
+        <v>1.01</v>
+      </c>
+      <c r="AU26">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV26">
+        <v>1.01</v>
+      </c>
+      <c r="AW26">
+        <v>1.01</v>
+      </c>
+      <c r="AX26">
+        <v>1.01</v>
+      </c>
+      <c r="AY26">
+        <v>1.01</v>
+      </c>
+      <c r="AZ26">
+        <v>18.5</v>
+      </c>
+      <c r="BA26">
+        <v>1.01</v>
+      </c>
+      <c r="BB26">
+        <v>1.01</v>
+      </c>
+      <c r="BC26">
+        <v>1.01</v>
+      </c>
+      <c r="BD26">
+        <v>1.01</v>
+      </c>
+      <c r="BE26">
+        <v>40</v>
+      </c>
+      <c r="BF26">
+        <v>1.01</v>
+      </c>
+      <c r="BG26">
+        <v>1.01</v>
+      </c>
+      <c r="BH26">
+        <v>4.2</v>
+      </c>
+      <c r="BI26">
+        <v>2.88</v>
+      </c>
+      <c r="BJ26">
+        <v>16</v>
+      </c>
+      <c r="BK26">
+        <v>7</v>
+      </c>
+      <c r="BL26">
+        <v>1000</v>
+      </c>
+      <c r="BM26">
+        <v>21</v>
+      </c>
+      <c r="BN26">
+        <v>5.4</v>
+      </c>
+      <c r="BO26">
+        <v>2.72</v>
+      </c>
+      <c r="BP26">
+        <v>13.5</v>
+      </c>
+      <c r="BQ26">
+        <v>5.9</v>
+      </c>
+      <c r="BR26">
+        <v>38</v>
+      </c>
+      <c r="BS26">
+        <v>15.5</v>
+      </c>
+      <c r="BT26">
+        <v>16</v>
+      </c>
+      <c r="BU26">
+        <v>6.8</v>
+      </c>
+      <c r="BV26">
+        <v>1000</v>
+      </c>
+      <c r="BW26">
+        <v>21</v>
+      </c>
+      <c r="BX26">
+        <v>1000</v>
+      </c>
+      <c r="BY26">
+        <v>21</v>
+      </c>
+      <c r="BZ26">
+        <v>0</v>
+      </c>
+      <c r="CA26">
+        <v>0</v>
+      </c>
+      <c r="CB26" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="27" spans="1:80">
+      <c r="A27" t="s">
+        <v>92</v>
+      </c>
+      <c r="B27" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" t="s">
+        <v>110</v>
+      </c>
+      <c r="D27" t="s">
+        <v>140</v>
+      </c>
+      <c r="E27" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27">
+        <v>3.15</v>
+      </c>
+      <c r="G27">
+        <v>3.45</v>
+      </c>
+      <c r="H27">
+        <v>2.18</v>
+      </c>
+      <c r="I27">
+        <v>2.34</v>
+      </c>
+      <c r="J27">
+        <v>3.65</v>
+      </c>
+      <c r="K27">
+        <v>4</v>
+      </c>
+      <c r="L27">
+        <v>1.01</v>
+      </c>
+      <c r="M27">
+        <v>1.05</v>
+      </c>
+      <c r="N27">
+        <v>4.5</v>
+      </c>
+      <c r="O27">
+        <v>1.23</v>
+      </c>
+      <c r="P27">
+        <v>2.2</v>
+      </c>
+      <c r="Q27">
+        <v>1.68</v>
+      </c>
+      <c r="R27">
+        <v>1.48</v>
+      </c>
+      <c r="S27">
+        <v>2.72</v>
+      </c>
+      <c r="T27">
+        <v>1.61</v>
+      </c>
+      <c r="U27">
+        <v>2.36</v>
+      </c>
+      <c r="V27">
+        <v>1.74</v>
+      </c>
+      <c r="W27">
+        <v>1.4</v>
+      </c>
+      <c r="X27">
+        <v>24</v>
+      </c>
+      <c r="Y27">
+        <v>15</v>
+      </c>
+      <c r="Z27">
+        <v>19.5</v>
+      </c>
+      <c r="AA27">
+        <v>29</v>
+      </c>
+      <c r="AB27">
+        <v>19.5</v>
+      </c>
+      <c r="AC27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AD27">
+        <v>13.5</v>
+      </c>
+      <c r="AE27">
+        <v>27</v>
+      </c>
+      <c r="AF27">
+        <v>27</v>
+      </c>
+      <c r="AG27">
+        <v>15</v>
+      </c>
+      <c r="AH27">
+        <v>19.5</v>
+      </c>
+      <c r="AI27">
+        <v>32</v>
+      </c>
+      <c r="AJ27">
+        <v>70</v>
+      </c>
+      <c r="AK27">
+        <v>44</v>
+      </c>
+      <c r="AL27">
+        <v>48</v>
+      </c>
+      <c r="AM27">
+        <v>85</v>
+      </c>
+      <c r="AN27">
+        <v>28</v>
+      </c>
+      <c r="AO27">
+        <v>13.5</v>
+      </c>
+      <c r="AP27">
+        <v>14.5</v>
+      </c>
+      <c r="AQ27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AR27">
+        <v>11.5</v>
+      </c>
+      <c r="AS27">
+        <v>20</v>
+      </c>
+      <c r="AT27">
+        <v>11.5</v>
+      </c>
+      <c r="AU27">
+        <v>6.8</v>
+      </c>
+      <c r="AV27">
+        <v>8.4</v>
+      </c>
+      <c r="AW27">
+        <v>15.5</v>
+      </c>
+      <c r="AX27">
+        <v>18.5</v>
+      </c>
+      <c r="AY27">
+        <v>10.5</v>
+      </c>
+      <c r="AZ27">
+        <v>11.5</v>
+      </c>
+      <c r="BA27">
+        <v>5</v>
+      </c>
+      <c r="BB27">
+        <v>5.4</v>
+      </c>
+      <c r="BC27">
+        <v>5.2</v>
+      </c>
+      <c r="BD27">
+        <v>5.3</v>
+      </c>
+      <c r="BE27">
+        <v>5.5</v>
+      </c>
+      <c r="BF27">
+        <v>19.5</v>
+      </c>
+      <c r="BG27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BH27">
+        <v>5.2</v>
+      </c>
+      <c r="BI27">
+        <v>2.8</v>
+      </c>
+      <c r="BJ27">
+        <v>13</v>
+      </c>
+      <c r="BK27">
+        <v>5.6</v>
+      </c>
+      <c r="BL27">
+        <v>1000</v>
+      </c>
+      <c r="BM27">
+        <v>21</v>
+      </c>
+      <c r="BN27">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BO27">
+        <v>4.4</v>
+      </c>
+      <c r="BP27">
+        <v>36</v>
+      </c>
+      <c r="BQ27">
+        <v>14.5</v>
+      </c>
+      <c r="BR27">
+        <v>46</v>
+      </c>
+      <c r="BS27">
+        <v>18.5</v>
+      </c>
+      <c r="BT27">
+        <v>7.6</v>
+      </c>
+      <c r="BU27">
+        <v>3.55</v>
+      </c>
+      <c r="BV27">
+        <v>22</v>
+      </c>
+      <c r="BW27">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BX27">
+        <v>36</v>
+      </c>
+      <c r="BY27">
+        <v>15</v>
+      </c>
+      <c r="BZ27">
+        <v>28</v>
+      </c>
+      <c r="CA27">
+        <v>11.5</v>
+      </c>
+      <c r="CB27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:80">
+      <c r="A28" t="s">
+        <v>93</v>
+      </c>
+      <c r="B28" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" t="s">
+        <v>110</v>
+      </c>
+      <c r="D28" t="s">
+        <v>141</v>
+      </c>
+      <c r="E28" t="s">
+        <v>181</v>
+      </c>
+      <c r="F28">
+        <v>2.08</v>
+      </c>
+      <c r="G28">
+        <v>2.18</v>
+      </c>
+      <c r="H28">
+        <v>3.55</v>
+      </c>
+      <c r="I28">
+        <v>3.8</v>
+      </c>
+      <c r="J28">
+        <v>3.7</v>
+      </c>
+      <c r="K28">
+        <v>3.95</v>
+      </c>
+      <c r="L28">
+        <v>1.01</v>
+      </c>
+      <c r="M28">
+        <v>1.01</v>
+      </c>
+      <c r="N28">
+        <v>3.85</v>
+      </c>
+      <c r="O28">
+        <v>1.23</v>
+      </c>
+      <c r="P28">
+        <v>2.18</v>
+      </c>
+      <c r="Q28">
+        <v>1.74</v>
+      </c>
+      <c r="R28">
+        <v>1.39</v>
+      </c>
+      <c r="S28">
+        <v>2.48</v>
+      </c>
+      <c r="T28">
+        <v>1.01</v>
+      </c>
+      <c r="U28">
+        <v>2.12</v>
+      </c>
+      <c r="V28">
+        <v>1.35</v>
+      </c>
+      <c r="W28">
+        <v>1.84</v>
+      </c>
+      <c r="X28">
+        <v>1000</v>
+      </c>
+      <c r="Y28">
+        <v>1000</v>
+      </c>
+      <c r="Z28">
+        <v>1000</v>
+      </c>
+      <c r="AA28">
+        <v>1000</v>
+      </c>
+      <c r="AB28">
+        <v>1000</v>
+      </c>
+      <c r="AC28">
+        <v>1000</v>
+      </c>
+      <c r="AD28">
+        <v>1000</v>
+      </c>
+      <c r="AE28">
+        <v>1000</v>
+      </c>
+      <c r="AF28">
+        <v>1000</v>
+      </c>
+      <c r="AG28">
+        <v>1000</v>
+      </c>
+      <c r="AH28">
+        <v>1000</v>
+      </c>
+      <c r="AI28">
+        <v>1000</v>
+      </c>
+      <c r="AJ28">
+        <v>1000</v>
+      </c>
+      <c r="AK28">
+        <v>1000</v>
+      </c>
+      <c r="AL28">
+        <v>1000</v>
+      </c>
+      <c r="AM28">
+        <v>1000</v>
+      </c>
+      <c r="AN28">
+        <v>1000</v>
+      </c>
+      <c r="AO28">
+        <v>1000</v>
+      </c>
+      <c r="AP28">
+        <v>1.03</v>
+      </c>
+      <c r="AQ28">
+        <v>1.03</v>
+      </c>
+      <c r="AR28">
+        <v>1.03</v>
+      </c>
+      <c r="AS28">
+        <v>1.03</v>
+      </c>
+      <c r="AT28">
+        <v>1.03</v>
+      </c>
+      <c r="AU28">
+        <v>1.03</v>
+      </c>
+      <c r="AV28">
+        <v>1.03</v>
+      </c>
+      <c r="AW28">
+        <v>1.03</v>
+      </c>
+      <c r="AX28">
+        <v>1.03</v>
+      </c>
+      <c r="AY28">
+        <v>1.03</v>
+      </c>
+      <c r="AZ28">
+        <v>1.03</v>
+      </c>
+      <c r="BA28">
+        <v>1.03</v>
+      </c>
+      <c r="BB28">
+        <v>1.03</v>
+      </c>
+      <c r="BC28">
+        <v>1.03</v>
+      </c>
+      <c r="BD28">
+        <v>1.03</v>
+      </c>
+      <c r="BE28">
+        <v>1.03</v>
+      </c>
+      <c r="BF28">
+        <v>1.01</v>
+      </c>
+      <c r="BG28">
+        <v>1.01</v>
+      </c>
+      <c r="BH28">
+        <v>1000</v>
+      </c>
+      <c r="BI28">
+        <v>1.01</v>
+      </c>
+      <c r="BJ28">
+        <v>1000</v>
+      </c>
+      <c r="BK28">
+        <v>1.01</v>
+      </c>
+      <c r="BL28">
+        <v>1000</v>
+      </c>
+      <c r="BM28">
+        <v>1.01</v>
+      </c>
+      <c r="BN28">
+        <v>1000</v>
+      </c>
+      <c r="BO28">
+        <v>1.01</v>
+      </c>
+      <c r="BP28">
+        <v>1000</v>
+      </c>
+      <c r="BQ28">
+        <v>1.01</v>
+      </c>
+      <c r="BR28">
+        <v>1000</v>
+      </c>
+      <c r="BS28">
+        <v>1.01</v>
+      </c>
+      <c r="BT28">
+        <v>1000</v>
+      </c>
+      <c r="BU28">
+        <v>1.01</v>
+      </c>
+      <c r="BV28">
+        <v>1000</v>
+      </c>
+      <c r="BW28">
+        <v>1.01</v>
+      </c>
+      <c r="BX28">
+        <v>1000</v>
+      </c>
+      <c r="BY28">
+        <v>1.01</v>
+      </c>
+      <c r="BZ28">
+        <v>1000</v>
+      </c>
+      <c r="CA28">
+        <v>1.01</v>
+      </c>
+      <c r="CB28" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="29" spans="1:80">
+      <c r="A29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" t="s">
+        <v>110</v>
+      </c>
+      <c r="D29" t="s">
+        <v>142</v>
+      </c>
+      <c r="E29" t="s">
+        <v>182</v>
+      </c>
+      <c r="F29">
+        <v>1.02</v>
+      </c>
+      <c r="G29">
+        <v>2.06</v>
+      </c>
+      <c r="H29">
+        <v>3.4</v>
+      </c>
+      <c r="I29">
+        <v>1000</v>
+      </c>
+      <c r="J29">
+        <v>3.95</v>
+      </c>
+      <c r="K29">
+        <v>950</v>
+      </c>
+      <c r="L29">
+        <v>1.01</v>
+      </c>
+      <c r="M29">
+        <v>1.01</v>
+      </c>
+      <c r="N29">
+        <v>2.16</v>
+      </c>
+      <c r="O29">
+        <v>1.16</v>
+      </c>
+      <c r="P29">
+        <v>2.16</v>
+      </c>
+      <c r="Q29">
+        <v>1.4</v>
+      </c>
+      <c r="R29">
+        <v>1.47</v>
+      </c>
+      <c r="S29">
+        <v>2.06</v>
+      </c>
+      <c r="T29">
+        <v>1.01</v>
+      </c>
+      <c r="U29">
+        <v>1.01</v>
+      </c>
+      <c r="V29">
+        <v>1.01</v>
+      </c>
+      <c r="W29">
+        <v>1.94</v>
+      </c>
+      <c r="X29">
+        <v>1000</v>
+      </c>
+      <c r="Y29">
+        <v>1000</v>
+      </c>
+      <c r="Z29">
+        <v>1000</v>
+      </c>
+      <c r="AA29">
+        <v>1000</v>
+      </c>
+      <c r="AB29">
+        <v>1000</v>
+      </c>
+      <c r="AC29">
+        <v>1000</v>
+      </c>
+      <c r="AD29">
+        <v>1000</v>
+      </c>
+      <c r="AE29">
+        <v>1000</v>
+      </c>
+      <c r="AF29">
+        <v>1000</v>
+      </c>
+      <c r="AG29">
+        <v>1000</v>
+      </c>
+      <c r="AH29">
+        <v>1000</v>
+      </c>
+      <c r="AI29">
+        <v>1000</v>
+      </c>
+      <c r="AJ29">
+        <v>1000</v>
+      </c>
+      <c r="AK29">
+        <v>1000</v>
+      </c>
+      <c r="AL29">
+        <v>1000</v>
+      </c>
+      <c r="AM29">
+        <v>1000</v>
+      </c>
+      <c r="AN29">
+        <v>1000</v>
+      </c>
+      <c r="AO29">
+        <v>1000</v>
+      </c>
+      <c r="AP29">
+        <v>1.03</v>
+      </c>
+      <c r="AQ29">
+        <v>1.03</v>
+      </c>
+      <c r="AR29">
+        <v>1.03</v>
+      </c>
+      <c r="AS29">
+        <v>1.03</v>
+      </c>
+      <c r="AT29">
+        <v>1.03</v>
+      </c>
+      <c r="AU29">
+        <v>1.03</v>
+      </c>
+      <c r="AV29">
+        <v>1.03</v>
+      </c>
+      <c r="AW29">
+        <v>1.03</v>
+      </c>
+      <c r="AX29">
+        <v>1.03</v>
+      </c>
+      <c r="AY29">
+        <v>1.03</v>
+      </c>
+      <c r="AZ29">
+        <v>1.03</v>
+      </c>
+      <c r="BA29">
+        <v>1.03</v>
+      </c>
+      <c r="BB29">
+        <v>1.03</v>
+      </c>
+      <c r="BC29">
+        <v>1.03</v>
+      </c>
+      <c r="BD29">
+        <v>1.03</v>
+      </c>
+      <c r="BE29">
+        <v>1.03</v>
+      </c>
+      <c r="BF29">
+        <v>1.01</v>
+      </c>
+      <c r="BG29">
+        <v>1.01</v>
+      </c>
+      <c r="BH29">
+        <v>1000</v>
+      </c>
+      <c r="BI29">
+        <v>1.01</v>
+      </c>
+      <c r="BJ29">
+        <v>1000</v>
+      </c>
+      <c r="BK29">
+        <v>1.01</v>
+      </c>
+      <c r="BL29">
+        <v>1000</v>
+      </c>
+      <c r="BM29">
+        <v>1.01</v>
+      </c>
+      <c r="BN29">
+        <v>1000</v>
+      </c>
+      <c r="BO29">
+        <v>1.01</v>
+      </c>
+      <c r="BP29">
+        <v>1000</v>
+      </c>
+      <c r="BQ29">
+        <v>1.01</v>
+      </c>
+      <c r="BR29">
+        <v>1000</v>
+      </c>
+      <c r="BS29">
+        <v>1.01</v>
+      </c>
+      <c r="BT29">
+        <v>1000</v>
+      </c>
+      <c r="BU29">
+        <v>1.01</v>
+      </c>
+      <c r="BV29">
+        <v>1000</v>
+      </c>
+      <c r="BW29">
+        <v>1.01</v>
+      </c>
+      <c r="BX29">
+        <v>1000</v>
+      </c>
+      <c r="BY29">
+        <v>1.01</v>
+      </c>
+      <c r="BZ29">
+        <v>1000</v>
+      </c>
+      <c r="CA29">
+        <v>1.01</v>
+      </c>
+      <c r="CB29" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="30" spans="1:80">
+      <c r="A30" t="s">
+        <v>94</v>
+      </c>
+      <c r="B30" t="s">
+        <v>100</v>
+      </c>
+      <c r="C30" t="s">
+        <v>110</v>
+      </c>
+      <c r="D30" t="s">
+        <v>143</v>
+      </c>
+      <c r="E30" t="s">
+        <v>183</v>
+      </c>
+      <c r="F30">
+        <v>2.52</v>
+      </c>
+      <c r="G30">
+        <v>2.88</v>
+      </c>
+      <c r="H30">
+        <v>2.76</v>
+      </c>
+      <c r="I30">
+        <v>3.15</v>
+      </c>
+      <c r="J30">
+        <v>3.4</v>
+      </c>
+      <c r="K30">
+        <v>3.75</v>
+      </c>
+      <c r="L30">
+        <v>1.01</v>
+      </c>
+      <c r="M30">
+        <v>1.01</v>
+      </c>
+      <c r="N30">
+        <v>3.6</v>
+      </c>
+      <c r="O30">
+        <v>1.28</v>
+      </c>
+      <c r="P30">
+        <v>1.94</v>
+      </c>
+      <c r="Q30">
+        <v>1.9</v>
+      </c>
+      <c r="R30">
+        <v>1.34</v>
+      </c>
+      <c r="S30">
+        <v>3.1</v>
+      </c>
+      <c r="T30">
+        <v>1.01</v>
+      </c>
+      <c r="U30">
+        <v>2.12</v>
+      </c>
+      <c r="V30">
+        <v>1.46</v>
+      </c>
+      <c r="W30">
+        <v>1.53</v>
+      </c>
+      <c r="X30">
+        <v>17.5</v>
+      </c>
+      <c r="Y30">
+        <v>1000</v>
+      </c>
+      <c r="Z30">
+        <v>1000</v>
+      </c>
+      <c r="AA30">
+        <v>1000</v>
+      </c>
+      <c r="AB30">
+        <v>1000</v>
+      </c>
+      <c r="AC30">
+        <v>9.6</v>
+      </c>
+      <c r="AD30">
+        <v>1000</v>
+      </c>
+      <c r="AE30">
+        <v>40</v>
+      </c>
+      <c r="AF30">
+        <v>22</v>
+      </c>
+      <c r="AG30">
+        <v>1000</v>
+      </c>
+      <c r="AH30">
+        <v>1000</v>
+      </c>
+      <c r="AI30">
+        <v>1000</v>
+      </c>
+      <c r="AJ30">
+        <v>1000</v>
+      </c>
+      <c r="AK30">
+        <v>36</v>
+      </c>
+      <c r="AL30">
+        <v>1000</v>
+      </c>
+      <c r="AM30">
+        <v>1000</v>
+      </c>
+      <c r="AN30">
+        <v>1000</v>
+      </c>
+      <c r="AO30">
+        <v>1000</v>
+      </c>
+      <c r="AP30">
+        <v>1.25</v>
+      </c>
+      <c r="AQ30">
+        <v>1.35</v>
+      </c>
+      <c r="AR30">
+        <v>1.35</v>
+      </c>
+      <c r="AS30">
+        <v>1.35</v>
+      </c>
+      <c r="AT30">
+        <v>1.35</v>
+      </c>
+      <c r="AU30">
+        <v>1.18</v>
+      </c>
+      <c r="AV30">
+        <v>1.35</v>
+      </c>
+      <c r="AW30">
+        <v>1.3</v>
+      </c>
+      <c r="AX30">
+        <v>1.27</v>
+      </c>
+      <c r="AY30">
+        <v>1.35</v>
+      </c>
+      <c r="AZ30">
+        <v>1.35</v>
+      </c>
+      <c r="BA30">
+        <v>1.35</v>
+      </c>
+      <c r="BB30">
+        <v>1.35</v>
+      </c>
+      <c r="BC30">
+        <v>1.3</v>
+      </c>
+      <c r="BD30">
+        <v>1.35</v>
+      </c>
+      <c r="BE30">
+        <v>1.35</v>
+      </c>
+      <c r="BF30">
+        <v>1.35</v>
+      </c>
+      <c r="BG30">
+        <v>1.35</v>
+      </c>
+      <c r="BH30">
+        <v>4.4</v>
+      </c>
+      <c r="BI30">
+        <v>2.78</v>
+      </c>
+      <c r="BJ30">
+        <v>13</v>
+      </c>
+      <c r="BK30">
+        <v>6.2</v>
+      </c>
+      <c r="BL30">
+        <v>1000</v>
+      </c>
+      <c r="BM30">
+        <v>21</v>
+      </c>
+      <c r="BN30">
+        <v>7.8</v>
+      </c>
+      <c r="BO30">
+        <v>3.85</v>
+      </c>
+      <c r="BP30">
+        <v>29</v>
+      </c>
+      <c r="BQ30">
+        <v>12.5</v>
+      </c>
+      <c r="BR30">
+        <v>46</v>
+      </c>
+      <c r="BS30">
+        <v>20</v>
+      </c>
+      <c r="BT30">
+        <v>8</v>
+      </c>
+      <c r="BU30">
+        <v>4.1</v>
+      </c>
+      <c r="BV30">
+        <v>30</v>
+      </c>
+      <c r="BW30">
+        <v>14</v>
+      </c>
+      <c r="BX30">
+        <v>48</v>
+      </c>
+      <c r="BY30">
+        <v>21</v>
+      </c>
+      <c r="BZ30">
+        <v>38</v>
+      </c>
+      <c r="CA30">
+        <v>16.5</v>
+      </c>
+      <c r="CB30" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="31" spans="1:80">
+      <c r="A31" t="s">
+        <v>95</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31" t="s">
+        <v>110</v>
+      </c>
+      <c r="D31" t="s">
+        <v>144</v>
+      </c>
+      <c r="E31" t="s">
+        <v>184</v>
+      </c>
+      <c r="F31">
+        <v>3.2</v>
+      </c>
+      <c r="G31">
+        <v>3.25</v>
+      </c>
+      <c r="H31">
+        <v>2.28</v>
+      </c>
+      <c r="I31">
+        <v>2.34</v>
+      </c>
+      <c r="J31">
+        <v>3.85</v>
+      </c>
+      <c r="K31">
+        <v>3.9</v>
+      </c>
+      <c r="L31">
+        <v>1.01</v>
+      </c>
+      <c r="M31">
+        <v>1.01</v>
+      </c>
+      <c r="N31">
+        <v>2.36</v>
+      </c>
+      <c r="O31">
+        <v>1.21</v>
+      </c>
+      <c r="P31">
+        <v>2.36</v>
+      </c>
+      <c r="Q31">
+        <v>1.56</v>
+      </c>
+      <c r="R31">
+        <v>1.46</v>
+      </c>
+      <c r="S31">
+        <v>2.3</v>
+      </c>
+      <c r="T31">
+        <v>1.01</v>
+      </c>
+      <c r="U31">
+        <v>1.01</v>
+      </c>
+      <c r="V31">
+        <v>1.74</v>
+      </c>
+      <c r="W31">
+        <v>1.44</v>
+      </c>
+      <c r="X31">
+        <v>30</v>
+      </c>
+      <c r="Y31">
+        <v>19</v>
+      </c>
+      <c r="Z31">
+        <v>24</v>
+      </c>
+      <c r="AA31">
+        <v>40</v>
+      </c>
+      <c r="AB31">
+        <v>23</v>
+      </c>
+      <c r="AC31">
+        <v>13</v>
+      </c>
+      <c r="AD31">
+        <v>16</v>
+      </c>
+      <c r="AE31">
+        <v>30</v>
+      </c>
+      <c r="AF31">
+        <v>34</v>
+      </c>
+      <c r="AG31">
+        <v>20</v>
+      </c>
+      <c r="AH31">
+        <v>21</v>
+      </c>
+      <c r="AI31">
+        <v>40</v>
+      </c>
+      <c r="AJ31">
+        <v>70</v>
+      </c>
+      <c r="AK31">
+        <v>46</v>
+      </c>
+      <c r="AL31">
+        <v>50</v>
+      </c>
+      <c r="AM31">
+        <v>90</v>
+      </c>
+      <c r="AN31">
+        <v>1000</v>
+      </c>
+      <c r="AO31">
+        <v>1000</v>
+      </c>
+      <c r="AP31">
+        <v>2.24</v>
+      </c>
+      <c r="AQ31">
+        <v>10</v>
+      </c>
+      <c r="AR31">
+        <v>2.2</v>
+      </c>
+      <c r="AS31">
+        <v>2.28</v>
+      </c>
+      <c r="AT31">
+        <v>2.18</v>
+      </c>
+      <c r="AU31">
+        <v>2.04</v>
+      </c>
+      <c r="AV31">
+        <v>2.1</v>
+      </c>
+      <c r="AW31">
+        <v>2.24</v>
+      </c>
+      <c r="AX31">
+        <v>18</v>
+      </c>
+      <c r="AY31">
+        <v>10</v>
+      </c>
+      <c r="AZ31">
+        <v>2.16</v>
+      </c>
+      <c r="BA31">
+        <v>2.28</v>
+      </c>
+      <c r="BB31">
+        <v>2.34</v>
+      </c>
+      <c r="BC31">
+        <v>2.3</v>
+      </c>
+      <c r="BD31">
+        <v>2.3</v>
+      </c>
+      <c r="BE31">
+        <v>2.36</v>
+      </c>
+      <c r="BF31">
+        <v>2.42</v>
+      </c>
+      <c r="BG31">
+        <v>2.42</v>
+      </c>
+      <c r="BH31">
+        <v>1000</v>
+      </c>
+      <c r="BI31">
+        <v>2.92</v>
+      </c>
+      <c r="BJ31">
+        <v>12</v>
+      </c>
+      <c r="BK31">
+        <v>5.8</v>
+      </c>
+      <c r="BL31">
+        <v>1000</v>
+      </c>
+      <c r="BM31">
+        <v>21</v>
+      </c>
+      <c r="BN31">
+        <v>9</v>
+      </c>
+      <c r="BO31">
+        <v>4.5</v>
+      </c>
+      <c r="BP31">
+        <v>30</v>
+      </c>
+      <c r="BQ31">
+        <v>14</v>
+      </c>
+      <c r="BR31">
+        <v>40</v>
+      </c>
+      <c r="BS31">
+        <v>18.5</v>
+      </c>
+      <c r="BT31">
+        <v>7.4</v>
+      </c>
+      <c r="BU31">
+        <v>3.8</v>
+      </c>
+      <c r="BV31">
+        <v>21</v>
+      </c>
+      <c r="BW31">
+        <v>9.6</v>
+      </c>
+      <c r="BX31">
+        <v>34</v>
+      </c>
+      <c r="BY31">
+        <v>15</v>
+      </c>
+      <c r="BZ31">
+        <v>25</v>
+      </c>
+      <c r="CA31">
+        <v>11.5</v>
+      </c>
+      <c r="CB31" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="32" spans="1:80">
+      <c r="A32" t="s">
+        <v>96</v>
+      </c>
+      <c r="B32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C32" t="s">
+        <v>111</v>
+      </c>
+      <c r="D32" t="s">
+        <v>145</v>
+      </c>
+      <c r="E32" t="s">
+        <v>185</v>
+      </c>
+      <c r="F32">
+        <v>2.18</v>
+      </c>
+      <c r="G32">
+        <v>2.34</v>
+      </c>
+      <c r="H32">
+        <v>3.65</v>
+      </c>
+      <c r="I32">
+        <v>4.2</v>
+      </c>
+      <c r="J32">
+        <v>3.25</v>
+      </c>
+      <c r="K32">
+        <v>3.5</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.01</v>
+      </c>
+      <c r="N32">
+        <v>1.72</v>
+      </c>
+      <c r="O32">
+        <v>1.01</v>
+      </c>
+      <c r="P32">
+        <v>1.72</v>
+      </c>
+      <c r="Q32">
+        <v>2.2</v>
+      </c>
+      <c r="R32">
+        <v>1.07</v>
+      </c>
+      <c r="S32">
+        <v>3.55</v>
+      </c>
+      <c r="T32">
+        <v>1.01</v>
+      </c>
+      <c r="U32">
+        <v>1.01</v>
+      </c>
+      <c r="V32">
+        <v>1.31</v>
+      </c>
+      <c r="W32">
+        <v>1.74</v>
+      </c>
+      <c r="X32">
+        <v>1000</v>
+      </c>
+      <c r="Y32">
+        <v>1000</v>
+      </c>
+      <c r="Z32">
+        <v>1000</v>
+      </c>
+      <c r="AA32">
+        <v>1000</v>
+      </c>
+      <c r="AB32">
+        <v>1000</v>
+      </c>
+      <c r="AC32">
+        <v>1000</v>
+      </c>
+      <c r="AD32">
+        <v>1000</v>
+      </c>
+      <c r="AE32">
+        <v>1000</v>
+      </c>
+      <c r="AF32">
+        <v>1000</v>
+      </c>
+      <c r="AG32">
+        <v>1000</v>
+      </c>
+      <c r="AH32">
+        <v>1000</v>
+      </c>
+      <c r="AI32">
+        <v>1000</v>
+      </c>
+      <c r="AJ32">
+        <v>1000</v>
+      </c>
+      <c r="AK32">
+        <v>1000</v>
+      </c>
+      <c r="AL32">
+        <v>1000</v>
+      </c>
+      <c r="AM32">
+        <v>1000</v>
+      </c>
+      <c r="AN32">
+        <v>1000</v>
+      </c>
+      <c r="AO32">
+        <v>1000</v>
+      </c>
+      <c r="AP32">
+        <v>1.01</v>
+      </c>
+      <c r="AQ32">
+        <v>1.01</v>
+      </c>
+      <c r="AR32">
+        <v>1.01</v>
+      </c>
+      <c r="AS32">
+        <v>1.01</v>
+      </c>
+      <c r="AT32">
+        <v>1.01</v>
+      </c>
+      <c r="AU32">
+        <v>1.01</v>
+      </c>
+      <c r="AV32">
+        <v>1.01</v>
+      </c>
+      <c r="AW32">
+        <v>1.01</v>
+      </c>
+      <c r="AX32">
+        <v>1.01</v>
+      </c>
+      <c r="AY32">
+        <v>1.01</v>
+      </c>
+      <c r="AZ32">
+        <v>1.01</v>
+      </c>
+      <c r="BA32">
+        <v>1.01</v>
+      </c>
+      <c r="BB32">
+        <v>1.01</v>
+      </c>
+      <c r="BC32">
+        <v>1.01</v>
+      </c>
+      <c r="BD32">
+        <v>1.01</v>
+      </c>
+      <c r="BE32">
+        <v>1.01</v>
+      </c>
+      <c r="BF32">
+        <v>1.01</v>
+      </c>
+      <c r="BG32">
+        <v>1.01</v>
+      </c>
+      <c r="BH32">
+        <v>1000</v>
+      </c>
+      <c r="BI32">
+        <v>1.01</v>
+      </c>
+      <c r="BJ32">
+        <v>1000</v>
+      </c>
+      <c r="BK32">
+        <v>1.01</v>
+      </c>
+      <c r="BL32">
+        <v>1000</v>
+      </c>
+      <c r="BM32">
+        <v>1.01</v>
+      </c>
+      <c r="BN32">
+        <v>1000</v>
+      </c>
+      <c r="BO32">
+        <v>1.01</v>
+      </c>
+      <c r="BP32">
+        <v>1000</v>
+      </c>
+      <c r="BQ32">
+        <v>1.01</v>
+      </c>
+      <c r="BR32">
+        <v>1000</v>
+      </c>
+      <c r="BS32">
+        <v>1.01</v>
+      </c>
+      <c r="BT32">
+        <v>1000</v>
+      </c>
+      <c r="BU32">
+        <v>1.01</v>
+      </c>
+      <c r="BV32">
+        <v>1000</v>
+      </c>
+      <c r="BW32">
+        <v>1.01</v>
+      </c>
+      <c r="BX32">
+        <v>1000</v>
+      </c>
+      <c r="BY32">
+        <v>1.01</v>
+      </c>
+      <c r="BZ32">
+        <v>1000</v>
+      </c>
+      <c r="CA32">
+        <v>1.01</v>
+      </c>
+      <c r="CB32" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:80">
+      <c r="A33" t="s">
+        <v>97</v>
+      </c>
+      <c r="B33" t="s">
+        <v>100</v>
+      </c>
+      <c r="C33" t="s">
+        <v>111</v>
+      </c>
+      <c r="D33" t="s">
+        <v>146</v>
+      </c>
+      <c r="E33" t="s">
+        <v>186</v>
+      </c>
+      <c r="F33">
+        <v>1.04</v>
+      </c>
+      <c r="G33">
+        <v>1000</v>
+      </c>
+      <c r="H33">
+        <v>1.04</v>
+      </c>
+      <c r="I33">
+        <v>1000</v>
+      </c>
+      <c r="J33">
+        <v>1.01</v>
+      </c>
+      <c r="K33">
+        <v>950</v>
+      </c>
+      <c r="L33">
+        <v>1.01</v>
+      </c>
+      <c r="M33">
+        <v>1.01</v>
+      </c>
+      <c r="N33">
+        <v>1.25</v>
+      </c>
+      <c r="O33">
+        <v>1.16</v>
+      </c>
+      <c r="P33">
+        <v>1.25</v>
+      </c>
+      <c r="Q33">
+        <v>1.16</v>
+      </c>
+      <c r="R33">
+        <v>1.24</v>
+      </c>
+      <c r="S33">
+        <v>1.16</v>
+      </c>
+      <c r="T33">
+        <v>1.01</v>
+      </c>
+      <c r="U33">
+        <v>1.01</v>
+      </c>
+      <c r="V33">
+        <v>1.01</v>
+      </c>
+      <c r="W33">
+        <v>1.01</v>
+      </c>
+      <c r="X33">
+        <v>1000</v>
+      </c>
+      <c r="Y33">
+        <v>1000</v>
+      </c>
+      <c r="Z33">
+        <v>1000</v>
+      </c>
+      <c r="AA33">
+        <v>1000</v>
+      </c>
+      <c r="AB33">
+        <v>1000</v>
+      </c>
+      <c r="AC33">
+        <v>1000</v>
+      </c>
+      <c r="AD33">
+        <v>1000</v>
+      </c>
+      <c r="AE33">
+        <v>1000</v>
+      </c>
+      <c r="AF33">
+        <v>1000</v>
+      </c>
+      <c r="AG33">
+        <v>1000</v>
+      </c>
+      <c r="AH33">
+        <v>1000</v>
+      </c>
+      <c r="AI33">
+        <v>1000</v>
+      </c>
+      <c r="AJ33">
+        <v>1000</v>
+      </c>
+      <c r="AK33">
+        <v>1000</v>
+      </c>
+      <c r="AL33">
+        <v>1000</v>
+      </c>
+      <c r="AM33">
+        <v>1000</v>
+      </c>
+      <c r="AN33">
+        <v>1000</v>
+      </c>
+      <c r="AO33">
+        <v>1000</v>
+      </c>
+      <c r="AP33">
+        <v>1.01</v>
+      </c>
+      <c r="AQ33">
+        <v>1.01</v>
+      </c>
+      <c r="AR33">
+        <v>1.01</v>
+      </c>
+      <c r="AS33">
+        <v>1.01</v>
+      </c>
+      <c r="AT33">
+        <v>1.01</v>
+      </c>
+      <c r="AU33">
+        <v>1.01</v>
+      </c>
+      <c r="AV33">
+        <v>1.01</v>
+      </c>
+      <c r="AW33">
+        <v>1.01</v>
+      </c>
+      <c r="AX33">
+        <v>1.01</v>
+      </c>
+      <c r="AY33">
+        <v>1.01</v>
+      </c>
+      <c r="AZ33">
+        <v>1.01</v>
+      </c>
+      <c r="BA33">
+        <v>1.01</v>
+      </c>
+      <c r="BB33">
+        <v>1.01</v>
+      </c>
+      <c r="BC33">
+        <v>1.01</v>
+      </c>
+      <c r="BD33">
+        <v>1.01</v>
+      </c>
+      <c r="BE33">
+        <v>1.01</v>
+      </c>
+      <c r="BF33">
+        <v>1.01</v>
+      </c>
+      <c r="BG33">
+        <v>1.01</v>
+      </c>
+      <c r="BH33">
+        <v>1000</v>
+      </c>
+      <c r="BI33">
+        <v>1.01</v>
+      </c>
+      <c r="BJ33">
+        <v>1000</v>
+      </c>
+      <c r="BK33">
+        <v>1.01</v>
+      </c>
+      <c r="BL33">
+        <v>1000</v>
+      </c>
+      <c r="BM33">
+        <v>1.01</v>
+      </c>
+      <c r="BN33">
+        <v>1000</v>
+      </c>
+      <c r="BO33">
+        <v>1.01</v>
+      </c>
+      <c r="BP33">
+        <v>1000</v>
+      </c>
+      <c r="BQ33">
+        <v>1.01</v>
+      </c>
+      <c r="BR33">
+        <v>1000</v>
+      </c>
+      <c r="BS33">
+        <v>1.01</v>
+      </c>
+      <c r="BT33">
+        <v>1000</v>
+      </c>
+      <c r="BU33">
+        <v>1.01</v>
+      </c>
+      <c r="BV33">
+        <v>1000</v>
+      </c>
+      <c r="BW33">
+        <v>1.01</v>
+      </c>
+      <c r="BX33">
+        <v>1000</v>
+      </c>
+      <c r="BY33">
+        <v>1.01</v>
+      </c>
+      <c r="BZ33">
+        <v>1000</v>
+      </c>
+      <c r="CA33">
+        <v>1.01</v>
+      </c>
+      <c r="CB33" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="34" spans="1:80">
+      <c r="A34" t="s">
+        <v>98</v>
+      </c>
+      <c r="B34" t="s">
+        <v>100</v>
+      </c>
+      <c r="C34" t="s">
+        <v>111</v>
+      </c>
+      <c r="D34" t="s">
+        <v>147</v>
+      </c>
+      <c r="E34" t="s">
+        <v>187</v>
+      </c>
+      <c r="F34">
+        <v>3.45</v>
+      </c>
+      <c r="G34">
+        <v>4.4</v>
+      </c>
+      <c r="H34">
+        <v>1.91</v>
+      </c>
+      <c r="I34">
+        <v>2.1</v>
+      </c>
+      <c r="J34">
+        <v>4.1</v>
+      </c>
+      <c r="K34">
+        <v>5.4</v>
+      </c>
+      <c r="L34">
+        <v>1.01</v>
+      </c>
+      <c r="M34">
+        <v>1.01</v>
+      </c>
+      <c r="N34">
+        <v>4.8</v>
+      </c>
+      <c r="O34">
+        <v>1.13</v>
+      </c>
+      <c r="P34">
+        <v>2.68</v>
+      </c>
+      <c r="Q34">
+        <v>1.42</v>
+      </c>
+      <c r="R34">
+        <v>1.66</v>
+      </c>
+      <c r="S34">
+        <v>2.16</v>
+      </c>
+      <c r="T34">
+        <v>1.01</v>
+      </c>
+      <c r="U34">
+        <v>1.01</v>
+      </c>
+      <c r="V34">
+        <v>1.9</v>
+      </c>
+      <c r="W34">
+        <v>1.33</v>
+      </c>
+      <c r="X34">
+        <v>1000</v>
+      </c>
+      <c r="Y34">
+        <v>1000</v>
+      </c>
+      <c r="Z34">
+        <v>1000</v>
+      </c>
+      <c r="AA34">
+        <v>1000</v>
+      </c>
+      <c r="AB34">
+        <v>1000</v>
+      </c>
+      <c r="AC34">
+        <v>1000</v>
+      </c>
+      <c r="AD34">
+        <v>1000</v>
+      </c>
+      <c r="AE34">
+        <v>1000</v>
+      </c>
+      <c r="AF34">
+        <v>1000</v>
+      </c>
+      <c r="AG34">
+        <v>1000</v>
+      </c>
+      <c r="AH34">
+        <v>1000</v>
+      </c>
+      <c r="AI34">
+        <v>1000</v>
+      </c>
+      <c r="AJ34">
+        <v>1000</v>
+      </c>
+      <c r="AK34">
+        <v>1000</v>
+      </c>
+      <c r="AL34">
+        <v>1000</v>
+      </c>
+      <c r="AM34">
+        <v>1000</v>
+      </c>
+      <c r="AN34">
+        <v>1000</v>
+      </c>
+      <c r="AO34">
+        <v>1000</v>
+      </c>
+      <c r="AP34">
+        <v>1.01</v>
+      </c>
+      <c r="AQ34">
+        <v>1.01</v>
+      </c>
+      <c r="AR34">
+        <v>1.01</v>
+      </c>
+      <c r="AS34">
+        <v>1.01</v>
+      </c>
+      <c r="AT34">
+        <v>1.01</v>
+      </c>
+      <c r="AU34">
+        <v>1.01</v>
+      </c>
+      <c r="AV34">
+        <v>1.01</v>
+      </c>
+      <c r="AW34">
+        <v>1.01</v>
+      </c>
+      <c r="AX34">
+        <v>1.01</v>
+      </c>
+      <c r="AY34">
+        <v>1.01</v>
+      </c>
+      <c r="AZ34">
+        <v>1.01</v>
+      </c>
+      <c r="BA34">
+        <v>1.01</v>
+      </c>
+      <c r="BB34">
+        <v>1.01</v>
+      </c>
+      <c r="BC34">
+        <v>1.01</v>
+      </c>
+      <c r="BD34">
+        <v>1.01</v>
+      </c>
+      <c r="BE34">
+        <v>1.01</v>
+      </c>
+      <c r="BF34">
+        <v>1.01</v>
+      </c>
+      <c r="BG34">
+        <v>1.01</v>
+      </c>
+      <c r="BH34">
+        <v>6.4</v>
+      </c>
+      <c r="BI34">
+        <v>3.2</v>
+      </c>
+      <c r="BJ34">
+        <v>12.5</v>
+      </c>
+      <c r="BK34">
+        <v>5.4</v>
+      </c>
+      <c r="BL34">
+        <v>1000</v>
+      </c>
+      <c r="BM34">
+        <v>21</v>
+      </c>
+      <c r="BN34">
+        <v>10.5</v>
+      </c>
+      <c r="BO34">
+        <v>4.8</v>
+      </c>
+      <c r="BP34">
+        <v>36</v>
+      </c>
+      <c r="BQ34">
+        <v>14.5</v>
+      </c>
+      <c r="BR34">
+        <v>40</v>
+      </c>
+      <c r="BS34">
+        <v>16.5</v>
+      </c>
+      <c r="BT34">
+        <v>7.6</v>
+      </c>
+      <c r="BU34">
+        <v>3.55</v>
+      </c>
+      <c r="BV34">
+        <v>18.5</v>
+      </c>
+      <c r="BW34">
+        <v>8</v>
+      </c>
+      <c r="BX34">
+        <v>30</v>
+      </c>
+      <c r="BY34">
+        <v>12</v>
+      </c>
+      <c r="BZ34">
+        <v>0</v>
+      </c>
+      <c r="CA34">
+        <v>0</v>
+      </c>
+      <c r="CB34" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="35" spans="1:80">
+      <c r="A35" t="s">
+        <v>98</v>
+      </c>
+      <c r="B35" t="s">
+        <v>100</v>
+      </c>
+      <c r="C35" t="s">
+        <v>111</v>
+      </c>
+      <c r="D35" t="s">
+        <v>148</v>
+      </c>
+      <c r="E35" t="s">
+        <v>188</v>
+      </c>
+      <c r="F35">
+        <v>1.9</v>
+      </c>
+      <c r="G35">
+        <v>2.08</v>
+      </c>
+      <c r="H35">
+        <v>3.5</v>
+      </c>
+      <c r="I35">
+        <v>4.2</v>
+      </c>
+      <c r="J35">
+        <v>4</v>
+      </c>
+      <c r="K35">
+        <v>4.5</v>
+      </c>
+      <c r="L35">
+        <v>1.01</v>
+      </c>
+      <c r="M35">
+        <v>1.01</v>
+      </c>
+      <c r="N35">
+        <v>4.4</v>
+      </c>
+      <c r="O35">
+        <v>1.16</v>
+      </c>
+      <c r="P35">
+        <v>2.42</v>
+      </c>
+      <c r="Q35">
+        <v>1.57</v>
+      </c>
+      <c r="R35">
+        <v>1.49</v>
+      </c>
+      <c r="S35">
+        <v>2.14</v>
+      </c>
+      <c r="T35">
+        <v>1.01</v>
+      </c>
+      <c r="U35">
+        <v>1.01</v>
+      </c>
+      <c r="V35">
+        <v>1.31</v>
+      </c>
+      <c r="W35">
+        <v>1.92</v>
+      </c>
+      <c r="X35">
+        <v>1000</v>
+      </c>
+      <c r="Y35">
+        <v>1000</v>
+      </c>
+      <c r="Z35">
+        <v>1000</v>
+      </c>
+      <c r="AA35">
+        <v>1000</v>
+      </c>
+      <c r="AB35">
+        <v>1000</v>
+      </c>
+      <c r="AC35">
+        <v>1000</v>
+      </c>
+      <c r="AD35">
+        <v>1000</v>
+      </c>
+      <c r="AE35">
+        <v>1000</v>
+      </c>
+      <c r="AF35">
+        <v>1000</v>
+      </c>
+      <c r="AG35">
+        <v>1000</v>
+      </c>
+      <c r="AH35">
+        <v>1000</v>
+      </c>
+      <c r="AI35">
+        <v>1000</v>
+      </c>
+      <c r="AJ35">
+        <v>1000</v>
+      </c>
+      <c r="AK35">
+        <v>1000</v>
+      </c>
+      <c r="AL35">
+        <v>1000</v>
+      </c>
+      <c r="AM35">
+        <v>1000</v>
+      </c>
+      <c r="AN35">
+        <v>1000</v>
+      </c>
+      <c r="AO35">
+        <v>1000</v>
+      </c>
+      <c r="AP35">
+        <v>1.01</v>
+      </c>
+      <c r="AQ35">
+        <v>1.01</v>
+      </c>
+      <c r="AR35">
+        <v>1.01</v>
+      </c>
+      <c r="AS35">
+        <v>1.01</v>
+      </c>
+      <c r="AT35">
+        <v>1.01</v>
+      </c>
+      <c r="AU35">
+        <v>1.01</v>
+      </c>
+      <c r="AV35">
+        <v>1.01</v>
+      </c>
+      <c r="AW35">
+        <v>1.01</v>
+      </c>
+      <c r="AX35">
+        <v>1.01</v>
+      </c>
+      <c r="AY35">
+        <v>1.01</v>
+      </c>
+      <c r="AZ35">
+        <v>1.01</v>
+      </c>
+      <c r="BA35">
+        <v>1.01</v>
+      </c>
+      <c r="BB35">
+        <v>1.01</v>
+      </c>
+      <c r="BC35">
+        <v>1.01</v>
+      </c>
+      <c r="BD35">
+        <v>1.01</v>
+      </c>
+      <c r="BE35">
+        <v>1.01</v>
+      </c>
+      <c r="BF35">
+        <v>1.01</v>
+      </c>
+      <c r="BG35">
+        <v>1.01</v>
+      </c>
+      <c r="BH35">
+        <v>1000</v>
+      </c>
+      <c r="BI35">
+        <v>1.01</v>
+      </c>
+      <c r="BJ35">
+        <v>1000</v>
+      </c>
+      <c r="BK35">
+        <v>1.01</v>
+      </c>
+      <c r="BL35">
+        <v>1000</v>
+      </c>
+      <c r="BM35">
+        <v>1.01</v>
+      </c>
+      <c r="BN35">
+        <v>1000</v>
+      </c>
+      <c r="BO35">
+        <v>1.01</v>
+      </c>
+      <c r="BP35">
+        <v>1000</v>
+      </c>
+      <c r="BQ35">
+        <v>1.01</v>
+      </c>
+      <c r="BR35">
+        <v>1000</v>
+      </c>
+      <c r="BS35">
+        <v>1.01</v>
+      </c>
+      <c r="BT35">
+        <v>1000</v>
+      </c>
+      <c r="BU35">
+        <v>1.01</v>
+      </c>
+      <c r="BV35">
+        <v>1000</v>
+      </c>
+      <c r="BW35">
+        <v>1.01</v>
+      </c>
+      <c r="BX35">
+        <v>1000</v>
+      </c>
+      <c r="BY35">
+        <v>1.01</v>
+      </c>
+      <c r="BZ35">
+        <v>0</v>
+      </c>
+      <c r="CA35">
+        <v>0</v>
+      </c>
+      <c r="CB35" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="36" spans="1:80">
+      <c r="A36" t="s">
+        <v>98</v>
+      </c>
+      <c r="B36" t="s">
+        <v>100</v>
+      </c>
+      <c r="C36" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" t="s">
+        <v>149</v>
+      </c>
+      <c r="E36" t="s">
+        <v>189</v>
+      </c>
+      <c r="F36">
+        <v>2.52</v>
+      </c>
+      <c r="G36">
+        <v>2.84</v>
+      </c>
+      <c r="H36">
+        <v>2.48</v>
+      </c>
+      <c r="I36">
+        <v>2.8</v>
+      </c>
+      <c r="J36">
+        <v>3.85</v>
+      </c>
+      <c r="K36">
+        <v>5.1</v>
+      </c>
+      <c r="L36">
+        <v>0</v>
+      </c>
+      <c r="M36">
+        <v>0</v>
+      </c>
+      <c r="N36">
+        <v>0</v>
+      </c>
+      <c r="O36">
+        <v>0</v>
+      </c>
+      <c r="P36">
+        <v>2.6</v>
+      </c>
+      <c r="Q36">
+        <v>1.48</v>
+      </c>
+      <c r="R36">
+        <v>0</v>
+      </c>
+      <c r="S36">
+        <v>0</v>
+      </c>
+      <c r="T36">
+        <v>0</v>
+      </c>
+      <c r="U36">
+        <v>0</v>
+      </c>
+      <c r="V36">
+        <v>0</v>
+      </c>
+      <c r="W36">
+        <v>0</v>
+      </c>
+      <c r="X36">
+        <v>0</v>
+      </c>
+      <c r="Y36">
+        <v>0</v>
+      </c>
+      <c r="Z36">
+        <v>0</v>
+      </c>
+      <c r="AA36">
+        <v>0</v>
+      </c>
+      <c r="AB36">
+        <v>0</v>
+      </c>
+      <c r="AC36">
+        <v>0</v>
+      </c>
+      <c r="AD36">
+        <v>0</v>
+      </c>
+      <c r="AE36">
+        <v>0</v>
+      </c>
+      <c r="AF36">
+        <v>0</v>
+      </c>
+      <c r="AG36">
+        <v>0</v>
+      </c>
+      <c r="AH36">
+        <v>0</v>
+      </c>
+      <c r="AI36">
+        <v>0</v>
+      </c>
+      <c r="AJ36">
+        <v>0</v>
+      </c>
+      <c r="AK36">
+        <v>0</v>
+      </c>
+      <c r="AL36">
+        <v>0</v>
+      </c>
+      <c r="AM36">
+        <v>0</v>
+      </c>
+      <c r="AN36">
+        <v>0</v>
+      </c>
+      <c r="AO36">
+        <v>0</v>
+      </c>
+      <c r="AP36">
+        <v>0</v>
+      </c>
+      <c r="AQ36">
+        <v>0</v>
+      </c>
+      <c r="AR36">
+        <v>0</v>
+      </c>
+      <c r="AS36">
+        <v>0</v>
+      </c>
+      <c r="AT36">
+        <v>0</v>
+      </c>
+      <c r="AU36">
+        <v>0</v>
+      </c>
+      <c r="AV36">
+        <v>0</v>
+      </c>
+      <c r="AW36">
+        <v>0</v>
+      </c>
+      <c r="AX36">
+        <v>0</v>
+      </c>
+      <c r="AY36">
+        <v>0</v>
+      </c>
+      <c r="AZ36">
+        <v>0</v>
+      </c>
+      <c r="BA36">
+        <v>0</v>
+      </c>
+      <c r="BB36">
+        <v>0</v>
+      </c>
+      <c r="BC36">
+        <v>0</v>
+      </c>
+      <c r="BD36">
+        <v>0</v>
+      </c>
+      <c r="BE36">
+        <v>0</v>
+      </c>
+      <c r="BF36">
+        <v>0</v>
+      </c>
+      <c r="BG36">
+        <v>0</v>
+      </c>
+      <c r="BH36">
+        <v>0</v>
+      </c>
+      <c r="BI36">
+        <v>0</v>
+      </c>
+      <c r="BJ36">
+        <v>0</v>
+      </c>
+      <c r="BK36">
+        <v>0</v>
+      </c>
+      <c r="BL36">
+        <v>0</v>
+      </c>
+      <c r="BM36">
+        <v>0</v>
+      </c>
+      <c r="BN36">
+        <v>0</v>
+      </c>
+      <c r="BO36">
+        <v>0</v>
+      </c>
+      <c r="BP36">
+        <v>0</v>
+      </c>
+      <c r="BQ36">
+        <v>0</v>
+      </c>
+      <c r="BR36">
+        <v>0</v>
+      </c>
+      <c r="BS36">
+        <v>0</v>
+      </c>
+      <c r="BT36">
+        <v>0</v>
+      </c>
+      <c r="BU36">
+        <v>0</v>
+      </c>
+      <c r="BV36">
+        <v>0</v>
+      </c>
+      <c r="BW36">
+        <v>0</v>
+      </c>
+      <c r="BX36">
+        <v>0</v>
+      </c>
+      <c r="BY36">
+        <v>0</v>
+      </c>
+      <c r="BZ36">
+        <v>0</v>
+      </c>
+      <c r="CA36">
+        <v>0</v>
+      </c>
+      <c r="CB36" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="37" spans="1:80">
+      <c r="A37" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" t="s">
+        <v>100</v>
+      </c>
+      <c r="C37" t="s">
+        <v>112</v>
+      </c>
+      <c r="D37" t="s">
+        <v>150</v>
+      </c>
+      <c r="E37" t="s">
+        <v>190</v>
+      </c>
+      <c r="F37">
+        <v>1.42</v>
+      </c>
+      <c r="G37">
+        <v>1.5</v>
+      </c>
+      <c r="H37">
+        <v>7</v>
+      </c>
+      <c r="I37">
+        <v>9.6</v>
+      </c>
+      <c r="J37">
+        <v>5.1</v>
+      </c>
+      <c r="K37">
+        <v>5.7</v>
+      </c>
+      <c r="L37">
+        <v>0</v>
+      </c>
+      <c r="M37">
+        <v>0</v>
+      </c>
+      <c r="N37">
+        <v>0</v>
+      </c>
+      <c r="O37">
+        <v>0</v>
+      </c>
+      <c r="P37">
+        <v>2.64</v>
+      </c>
+      <c r="Q37">
+        <v>1.44</v>
+      </c>
+      <c r="R37">
+        <v>0</v>
+      </c>
+      <c r="S37">
+        <v>0</v>
+      </c>
+      <c r="T37">
+        <v>0</v>
+      </c>
+      <c r="U37">
+        <v>0</v>
+      </c>
+      <c r="V37">
+        <v>0</v>
+      </c>
+      <c r="W37">
+        <v>0</v>
+      </c>
+      <c r="X37">
+        <v>0</v>
+      </c>
+      <c r="Y37">
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <v>0</v>
+      </c>
+      <c r="AA37">
+        <v>0</v>
+      </c>
+      <c r="AB37">
+        <v>0</v>
+      </c>
+      <c r="AC37">
+        <v>0</v>
+      </c>
+      <c r="AD37">
+        <v>0</v>
+      </c>
+      <c r="AE37">
+        <v>0</v>
+      </c>
+      <c r="AF37">
+        <v>0</v>
+      </c>
+      <c r="AG37">
+        <v>0</v>
+      </c>
+      <c r="AH37">
+        <v>0</v>
+      </c>
+      <c r="AI37">
+        <v>0</v>
+      </c>
+      <c r="AJ37">
+        <v>0</v>
+      </c>
+      <c r="AK37">
+        <v>0</v>
+      </c>
+      <c r="AL37">
+        <v>0</v>
+      </c>
+      <c r="AM37">
+        <v>0</v>
+      </c>
+      <c r="AN37">
+        <v>0</v>
+      </c>
+      <c r="AO37">
+        <v>0</v>
+      </c>
+      <c r="AP37">
+        <v>0</v>
+      </c>
+      <c r="AQ37">
+        <v>0</v>
+      </c>
+      <c r="AR37">
+        <v>0</v>
+      </c>
+      <c r="AS37">
+        <v>0</v>
+      </c>
+      <c r="AT37">
+        <v>0</v>
+      </c>
+      <c r="AU37">
+        <v>0</v>
+      </c>
+      <c r="AV37">
+        <v>0</v>
+      </c>
+      <c r="AW37">
+        <v>0</v>
+      </c>
+      <c r="AX37">
+        <v>0</v>
+      </c>
+      <c r="AY37">
+        <v>0</v>
+      </c>
+      <c r="AZ37">
+        <v>0</v>
+      </c>
+      <c r="BA37">
+        <v>0</v>
+      </c>
+      <c r="BB37">
+        <v>0</v>
+      </c>
+      <c r="BC37">
+        <v>0</v>
+      </c>
+      <c r="BD37">
+        <v>0</v>
+      </c>
+      <c r="BE37">
+        <v>0</v>
+      </c>
+      <c r="BF37">
+        <v>0</v>
+      </c>
+      <c r="BG37">
+        <v>0</v>
+      </c>
+      <c r="BH37">
+        <v>0</v>
+      </c>
+      <c r="BI37">
+        <v>0</v>
+      </c>
+      <c r="BJ37">
+        <v>0</v>
+      </c>
+      <c r="BK37">
+        <v>0</v>
+      </c>
+      <c r="BL37">
+        <v>0</v>
+      </c>
+      <c r="BM37">
+        <v>0</v>
+      </c>
+      <c r="BN37">
+        <v>0</v>
+      </c>
+      <c r="BO37">
+        <v>0</v>
+      </c>
+      <c r="BP37">
+        <v>0</v>
+      </c>
+      <c r="BQ37">
+        <v>0</v>
+      </c>
+      <c r="BR37">
+        <v>0</v>
+      </c>
+      <c r="BS37">
+        <v>0</v>
+      </c>
+      <c r="BT37">
+        <v>0</v>
+      </c>
+      <c r="BU37">
+        <v>0</v>
+      </c>
+      <c r="BV37">
+        <v>0</v>
+      </c>
+      <c r="BW37">
+        <v>0</v>
+      </c>
+      <c r="BX37">
+        <v>0</v>
+      </c>
+      <c r="BY37">
+        <v>0</v>
+      </c>
+      <c r="BZ37">
+        <v>0</v>
+      </c>
+      <c r="CA37">
+        <v>0</v>
+      </c>
+      <c r="CB37" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="38" spans="1:80">
+      <c r="A38" t="s">
+        <v>89</v>
+      </c>
+      <c r="B38" t="s">
+        <v>100</v>
+      </c>
+      <c r="C38" t="s">
+        <v>113</v>
+      </c>
+      <c r="D38" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" t="s">
+        <v>191</v>
+      </c>
+      <c r="F38">
+        <v>1.61</v>
+      </c>
+      <c r="G38">
+        <v>1.74</v>
+      </c>
+      <c r="H38">
+        <v>5.1</v>
+      </c>
+      <c r="I38">
+        <v>6.6</v>
+      </c>
+      <c r="J38">
+        <v>4.2</v>
+      </c>
+      <c r="K38">
+        <v>5</v>
+      </c>
+      <c r="L38">
+        <v>0</v>
+      </c>
+      <c r="M38">
+        <v>0</v>
+      </c>
+      <c r="N38">
+        <v>0</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>2.38</v>
+      </c>
+      <c r="Q38">
+        <v>1.59</v>
+      </c>
+      <c r="R38">
+        <v>0</v>
+      </c>
+      <c r="S38">
+        <v>0</v>
+      </c>
+      <c r="T38">
+        <v>0</v>
+      </c>
+      <c r="U38">
+        <v>0</v>
+      </c>
+      <c r="V38">
+        <v>0</v>
+      </c>
+      <c r="W38">
+        <v>0</v>
+      </c>
+      <c r="X38">
+        <v>0</v>
+      </c>
+      <c r="Y38">
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <v>0</v>
+      </c>
+      <c r="AA38">
+        <v>0</v>
+      </c>
+      <c r="AB38">
+        <v>0</v>
+      </c>
+      <c r="AC38">
+        <v>0</v>
+      </c>
+      <c r="AD38">
+        <v>0</v>
+      </c>
+      <c r="AE38">
+        <v>0</v>
+      </c>
+      <c r="AF38">
+        <v>0</v>
+      </c>
+      <c r="AG38">
+        <v>0</v>
+      </c>
+      <c r="AH38">
+        <v>0</v>
+      </c>
+      <c r="AI38">
+        <v>0</v>
+      </c>
+      <c r="AJ38">
+        <v>0</v>
+      </c>
+      <c r="AK38">
+        <v>0</v>
+      </c>
+      <c r="AL38">
+        <v>0</v>
+      </c>
+      <c r="AM38">
+        <v>0</v>
+      </c>
+      <c r="AN38">
+        <v>0</v>
+      </c>
+      <c r="AO38">
+        <v>0</v>
+      </c>
+      <c r="AP38">
+        <v>0</v>
+      </c>
+      <c r="AQ38">
+        <v>0</v>
+      </c>
+      <c r="AR38">
+        <v>0</v>
+      </c>
+      <c r="AS38">
+        <v>0</v>
+      </c>
+      <c r="AT38">
+        <v>0</v>
+      </c>
+      <c r="AU38">
+        <v>0</v>
+      </c>
+      <c r="AV38">
+        <v>0</v>
+      </c>
+      <c r="AW38">
+        <v>0</v>
+      </c>
+      <c r="AX38">
+        <v>0</v>
+      </c>
+      <c r="AY38">
+        <v>0</v>
+      </c>
+      <c r="AZ38">
+        <v>0</v>
+      </c>
+      <c r="BA38">
+        <v>0</v>
+      </c>
+      <c r="BB38">
+        <v>0</v>
+      </c>
+      <c r="BC38">
+        <v>0</v>
+      </c>
+      <c r="BD38">
+        <v>0</v>
+      </c>
+      <c r="BE38">
+        <v>0</v>
+      </c>
+      <c r="BF38">
+        <v>0</v>
+      </c>
+      <c r="BG38">
+        <v>0</v>
+      </c>
+      <c r="BH38">
+        <v>0</v>
+      </c>
+      <c r="BI38">
+        <v>0</v>
+      </c>
+      <c r="BJ38">
+        <v>0</v>
+      </c>
+      <c r="BK38">
+        <v>0</v>
+      </c>
+      <c r="BL38">
+        <v>0</v>
+      </c>
+      <c r="BM38">
+        <v>0</v>
+      </c>
+      <c r="BN38">
+        <v>0</v>
+      </c>
+      <c r="BO38">
+        <v>0</v>
+      </c>
+      <c r="BP38">
+        <v>0</v>
+      </c>
+      <c r="BQ38">
+        <v>0</v>
+      </c>
+      <c r="BR38">
+        <v>0</v>
+      </c>
+      <c r="BS38">
+        <v>0</v>
+      </c>
+      <c r="BT38">
+        <v>0</v>
+      </c>
+      <c r="BU38">
+        <v>0</v>
+      </c>
+      <c r="BV38">
+        <v>0</v>
+      </c>
+      <c r="BW38">
+        <v>0</v>
+      </c>
+      <c r="BX38">
+        <v>0</v>
+      </c>
+      <c r="BY38">
+        <v>0</v>
+      </c>
+      <c r="BZ38">
+        <v>0</v>
+      </c>
+      <c r="CA38">
+        <v>0</v>
+      </c>
+      <c r="CB38" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="39" spans="1:80">
+      <c r="A39" t="s">
         <v>86</v>
       </c>
-      <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" t="s">
-        <v>96</v>
-      </c>
-      <c r="D21" t="s">
-        <v>116</v>
-      </c>
-      <c r="E21" t="s">
-        <v>136</v>
-      </c>
-      <c r="F21">
-        <v>1.04</v>
-      </c>
-      <c r="G21">
-        <v>1000</v>
-      </c>
-      <c r="H21">
-        <v>1.04</v>
-      </c>
-      <c r="I21">
-        <v>1000</v>
-      </c>
-      <c r="J21">
-        <v>1.01</v>
-      </c>
-      <c r="K21">
+      <c r="B39" t="s">
+        <v>100</v>
+      </c>
+      <c r="C39" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" t="s">
+        <v>152</v>
+      </c>
+      <c r="E39" t="s">
+        <v>192</v>
+      </c>
+      <c r="F39">
+        <v>2.16</v>
+      </c>
+      <c r="G39">
+        <v>2.42</v>
+      </c>
+      <c r="H39">
+        <v>3.15</v>
+      </c>
+      <c r="I39">
+        <v>3.65</v>
+      </c>
+      <c r="J39">
+        <v>3.45</v>
+      </c>
+      <c r="K39">
+        <v>3.95</v>
+      </c>
+      <c r="L39">
+        <v>0</v>
+      </c>
+      <c r="M39">
+        <v>0</v>
+      </c>
+      <c r="N39">
+        <v>0</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>2.04</v>
+      </c>
+      <c r="Q39">
+        <v>1.77</v>
+      </c>
+      <c r="R39">
+        <v>0</v>
+      </c>
+      <c r="S39">
+        <v>0</v>
+      </c>
+      <c r="T39">
+        <v>0</v>
+      </c>
+      <c r="U39">
+        <v>0</v>
+      </c>
+      <c r="V39">
+        <v>0</v>
+      </c>
+      <c r="W39">
+        <v>0</v>
+      </c>
+      <c r="X39">
+        <v>0</v>
+      </c>
+      <c r="Y39">
+        <v>0</v>
+      </c>
+      <c r="Z39">
+        <v>0</v>
+      </c>
+      <c r="AA39">
+        <v>0</v>
+      </c>
+      <c r="AB39">
+        <v>0</v>
+      </c>
+      <c r="AC39">
+        <v>0</v>
+      </c>
+      <c r="AD39">
+        <v>0</v>
+      </c>
+      <c r="AE39">
+        <v>0</v>
+      </c>
+      <c r="AF39">
+        <v>0</v>
+      </c>
+      <c r="AG39">
+        <v>0</v>
+      </c>
+      <c r="AH39">
+        <v>0</v>
+      </c>
+      <c r="AI39">
+        <v>0</v>
+      </c>
+      <c r="AJ39">
+        <v>0</v>
+      </c>
+      <c r="AK39">
+        <v>0</v>
+      </c>
+      <c r="AL39">
+        <v>0</v>
+      </c>
+      <c r="AM39">
+        <v>0</v>
+      </c>
+      <c r="AN39">
+        <v>0</v>
+      </c>
+      <c r="AO39">
+        <v>0</v>
+      </c>
+      <c r="AP39">
+        <v>0</v>
+      </c>
+      <c r="AQ39">
+        <v>0</v>
+      </c>
+      <c r="AR39">
+        <v>0</v>
+      </c>
+      <c r="AS39">
+        <v>0</v>
+      </c>
+      <c r="AT39">
+        <v>0</v>
+      </c>
+      <c r="AU39">
+        <v>0</v>
+      </c>
+      <c r="AV39">
+        <v>0</v>
+      </c>
+      <c r="AW39">
+        <v>0</v>
+      </c>
+      <c r="AX39">
+        <v>0</v>
+      </c>
+      <c r="AY39">
+        <v>0</v>
+      </c>
+      <c r="AZ39">
+        <v>0</v>
+      </c>
+      <c r="BA39">
+        <v>0</v>
+      </c>
+      <c r="BB39">
+        <v>0</v>
+      </c>
+      <c r="BC39">
+        <v>0</v>
+      </c>
+      <c r="BD39">
+        <v>0</v>
+      </c>
+      <c r="BE39">
+        <v>0</v>
+      </c>
+      <c r="BF39">
+        <v>0</v>
+      </c>
+      <c r="BG39">
+        <v>0</v>
+      </c>
+      <c r="BH39">
+        <v>0</v>
+      </c>
+      <c r="BI39">
+        <v>0</v>
+      </c>
+      <c r="BJ39">
+        <v>0</v>
+      </c>
+      <c r="BK39">
+        <v>0</v>
+      </c>
+      <c r="BL39">
+        <v>0</v>
+      </c>
+      <c r="BM39">
+        <v>0</v>
+      </c>
+      <c r="BN39">
+        <v>0</v>
+      </c>
+      <c r="BO39">
+        <v>0</v>
+      </c>
+      <c r="BP39">
+        <v>0</v>
+      </c>
+      <c r="BQ39">
+        <v>0</v>
+      </c>
+      <c r="BR39">
+        <v>0</v>
+      </c>
+      <c r="BS39">
+        <v>0</v>
+      </c>
+      <c r="BT39">
+        <v>0</v>
+      </c>
+      <c r="BU39">
+        <v>0</v>
+      </c>
+      <c r="BV39">
+        <v>0</v>
+      </c>
+      <c r="BW39">
+        <v>0</v>
+      </c>
+      <c r="BX39">
+        <v>0</v>
+      </c>
+      <c r="BY39">
+        <v>0</v>
+      </c>
+      <c r="BZ39">
+        <v>0</v>
+      </c>
+      <c r="CA39">
+        <v>0</v>
+      </c>
+      <c r="CB39" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="40" spans="1:80">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" t="s">
+        <v>114</v>
+      </c>
+      <c r="D40" t="s">
+        <v>153</v>
+      </c>
+      <c r="E40" t="s">
+        <v>193</v>
+      </c>
+      <c r="F40">
+        <v>1.11</v>
+      </c>
+      <c r="G40">
+        <v>10.5</v>
+      </c>
+      <c r="H40">
+        <v>1.11</v>
+      </c>
+      <c r="I40">
+        <v>1000</v>
+      </c>
+      <c r="J40">
+        <v>1.1</v>
+      </c>
+      <c r="K40">
         <v>950</v>
       </c>
-      <c r="L21">
-        <v>0</v>
-      </c>
-      <c r="M21">
-        <v>0</v>
-      </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
-      <c r="O21">
-        <v>0</v>
-      </c>
-      <c r="P21">
+      <c r="L40">
+        <v>0</v>
+      </c>
+      <c r="M40">
+        <v>0</v>
+      </c>
+      <c r="N40">
+        <v>0</v>
+      </c>
+      <c r="O40">
+        <v>0</v>
+      </c>
+      <c r="P40">
         <v>1.24</v>
       </c>
-      <c r="Q21">
-        <v>1.01</v>
-      </c>
-      <c r="R21">
-        <v>0</v>
-      </c>
-      <c r="S21">
-        <v>0</v>
-      </c>
-      <c r="T21">
-        <v>0</v>
-      </c>
-      <c r="U21">
-        <v>0</v>
-      </c>
-      <c r="V21">
-        <v>0</v>
-      </c>
-      <c r="W21">
-        <v>0</v>
-      </c>
-      <c r="X21">
-        <v>0</v>
-      </c>
-      <c r="Y21">
-        <v>0</v>
-      </c>
-      <c r="Z21">
-        <v>0</v>
-      </c>
-      <c r="AA21">
-        <v>0</v>
-      </c>
-      <c r="AB21">
-        <v>0</v>
-      </c>
-      <c r="AC21">
-        <v>0</v>
-      </c>
-      <c r="AD21">
-        <v>0</v>
-      </c>
-      <c r="AE21">
-        <v>0</v>
-      </c>
-      <c r="AF21">
-        <v>0</v>
-      </c>
-      <c r="AG21">
-        <v>0</v>
-      </c>
-      <c r="AH21">
-        <v>0</v>
-      </c>
-      <c r="AI21">
-        <v>0</v>
-      </c>
-      <c r="AJ21">
-        <v>0</v>
-      </c>
-      <c r="AK21">
-        <v>0</v>
-      </c>
-      <c r="AL21">
-        <v>0</v>
-      </c>
-      <c r="AM21">
-        <v>0</v>
-      </c>
-      <c r="AN21">
-        <v>0</v>
-      </c>
-      <c r="AO21">
-        <v>0</v>
-      </c>
-      <c r="AP21">
-        <v>0</v>
-      </c>
-      <c r="AQ21">
-        <v>0</v>
-      </c>
-      <c r="AR21">
-        <v>0</v>
-      </c>
-      <c r="AS21">
-        <v>0</v>
-      </c>
-      <c r="AT21">
-        <v>0</v>
-      </c>
-      <c r="AU21">
-        <v>0</v>
-      </c>
-      <c r="AV21">
-        <v>0</v>
-      </c>
-      <c r="AW21">
-        <v>0</v>
-      </c>
-      <c r="AX21">
-        <v>0</v>
-      </c>
-      <c r="AY21">
-        <v>0</v>
-      </c>
-      <c r="AZ21">
-        <v>0</v>
-      </c>
-      <c r="BA21">
-        <v>0</v>
-      </c>
-      <c r="BB21">
-        <v>0</v>
-      </c>
-      <c r="BC21">
-        <v>0</v>
-      </c>
-      <c r="BD21">
-        <v>0</v>
-      </c>
-      <c r="BE21">
-        <v>0</v>
-      </c>
-      <c r="BF21">
-        <v>0</v>
-      </c>
-      <c r="BG21">
-        <v>0</v>
-      </c>
-      <c r="BH21">
-        <v>0</v>
-      </c>
-      <c r="BI21">
-        <v>0</v>
-      </c>
-      <c r="BJ21">
-        <v>0</v>
-      </c>
-      <c r="BK21">
-        <v>0</v>
-      </c>
-      <c r="BL21">
-        <v>0</v>
-      </c>
-      <c r="BM21">
-        <v>0</v>
-      </c>
-      <c r="BN21">
-        <v>0</v>
-      </c>
-      <c r="BO21">
-        <v>0</v>
-      </c>
-      <c r="BP21">
-        <v>0</v>
-      </c>
-      <c r="BQ21">
-        <v>0</v>
-      </c>
-      <c r="BR21">
-        <v>0</v>
-      </c>
-      <c r="BS21">
-        <v>0</v>
-      </c>
-      <c r="BT21">
-        <v>0</v>
-      </c>
-      <c r="BU21">
-        <v>0</v>
-      </c>
-      <c r="BV21">
-        <v>0</v>
-      </c>
-      <c r="BW21">
-        <v>0</v>
-      </c>
-      <c r="BX21">
-        <v>0</v>
-      </c>
-      <c r="BY21">
-        <v>0</v>
-      </c>
-      <c r="BZ21">
-        <v>0</v>
-      </c>
-      <c r="CA21">
-        <v>0</v>
-      </c>
-      <c r="CB21" t="s">
-        <v>137</v>
+      <c r="Q40">
+        <v>1.01</v>
+      </c>
+      <c r="R40">
+        <v>0</v>
+      </c>
+      <c r="S40">
+        <v>0</v>
+      </c>
+      <c r="T40">
+        <v>0</v>
+      </c>
+      <c r="U40">
+        <v>0</v>
+      </c>
+      <c r="V40">
+        <v>0</v>
+      </c>
+      <c r="W40">
+        <v>0</v>
+      </c>
+      <c r="X40">
+        <v>0</v>
+      </c>
+      <c r="Y40">
+        <v>0</v>
+      </c>
+      <c r="Z40">
+        <v>0</v>
+      </c>
+      <c r="AA40">
+        <v>0</v>
+      </c>
+      <c r="AB40">
+        <v>0</v>
+      </c>
+      <c r="AC40">
+        <v>0</v>
+      </c>
+      <c r="AD40">
+        <v>0</v>
+      </c>
+      <c r="AE40">
+        <v>0</v>
+      </c>
+      <c r="AF40">
+        <v>0</v>
+      </c>
+      <c r="AG40">
+        <v>0</v>
+      </c>
+      <c r="AH40">
+        <v>0</v>
+      </c>
+      <c r="AI40">
+        <v>0</v>
+      </c>
+      <c r="AJ40">
+        <v>0</v>
+      </c>
+      <c r="AK40">
+        <v>0</v>
+      </c>
+      <c r="AL40">
+        <v>0</v>
+      </c>
+      <c r="AM40">
+        <v>0</v>
+      </c>
+      <c r="AN40">
+        <v>0</v>
+      </c>
+      <c r="AO40">
+        <v>0</v>
+      </c>
+      <c r="AP40">
+        <v>0</v>
+      </c>
+      <c r="AQ40">
+        <v>0</v>
+      </c>
+      <c r="AR40">
+        <v>0</v>
+      </c>
+      <c r="AS40">
+        <v>0</v>
+      </c>
+      <c r="AT40">
+        <v>0</v>
+      </c>
+      <c r="AU40">
+        <v>0</v>
+      </c>
+      <c r="AV40">
+        <v>0</v>
+      </c>
+      <c r="AW40">
+        <v>0</v>
+      </c>
+      <c r="AX40">
+        <v>0</v>
+      </c>
+      <c r="AY40">
+        <v>0</v>
+      </c>
+      <c r="AZ40">
+        <v>0</v>
+      </c>
+      <c r="BA40">
+        <v>0</v>
+      </c>
+      <c r="BB40">
+        <v>0</v>
+      </c>
+      <c r="BC40">
+        <v>0</v>
+      </c>
+      <c r="BD40">
+        <v>0</v>
+      </c>
+      <c r="BE40">
+        <v>0</v>
+      </c>
+      <c r="BF40">
+        <v>0</v>
+      </c>
+      <c r="BG40">
+        <v>0</v>
+      </c>
+      <c r="BH40">
+        <v>0</v>
+      </c>
+      <c r="BI40">
+        <v>0</v>
+      </c>
+      <c r="BJ40">
+        <v>0</v>
+      </c>
+      <c r="BK40">
+        <v>0</v>
+      </c>
+      <c r="BL40">
+        <v>0</v>
+      </c>
+      <c r="BM40">
+        <v>0</v>
+      </c>
+      <c r="BN40">
+        <v>0</v>
+      </c>
+      <c r="BO40">
+        <v>0</v>
+      </c>
+      <c r="BP40">
+        <v>0</v>
+      </c>
+      <c r="BQ40">
+        <v>0</v>
+      </c>
+      <c r="BR40">
+        <v>0</v>
+      </c>
+      <c r="BS40">
+        <v>0</v>
+      </c>
+      <c r="BT40">
+        <v>0</v>
+      </c>
+      <c r="BU40">
+        <v>0</v>
+      </c>
+      <c r="BV40">
+        <v>0</v>
+      </c>
+      <c r="BW40">
+        <v>0</v>
+      </c>
+      <c r="BX40">
+        <v>0</v>
+      </c>
+      <c r="BY40">
+        <v>0</v>
+      </c>
+      <c r="BZ40">
+        <v>0</v>
+      </c>
+      <c r="CA40">
+        <v>0</v>
+      </c>
+      <c r="CB40" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="41" spans="1:80">
+      <c r="A41" t="s">
+        <v>99</v>
+      </c>
+      <c r="B41" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" t="s">
+        <v>114</v>
+      </c>
+      <c r="D41" t="s">
+        <v>154</v>
+      </c>
+      <c r="E41" t="s">
+        <v>194</v>
+      </c>
+      <c r="F41">
+        <v>1.25</v>
+      </c>
+      <c r="G41">
+        <v>1000</v>
+      </c>
+      <c r="H41">
+        <v>1.25</v>
+      </c>
+      <c r="I41">
+        <v>1000</v>
+      </c>
+      <c r="J41">
+        <v>1.01</v>
+      </c>
+      <c r="K41">
+        <v>950</v>
+      </c>
+      <c r="L41">
+        <v>0</v>
+      </c>
+      <c r="M41">
+        <v>0</v>
+      </c>
+      <c r="N41">
+        <v>0</v>
+      </c>
+      <c r="O41">
+        <v>0</v>
+      </c>
+      <c r="P41">
+        <v>1.24</v>
+      </c>
+      <c r="Q41">
+        <v>1.01</v>
+      </c>
+      <c r="R41">
+        <v>0</v>
+      </c>
+      <c r="S41">
+        <v>0</v>
+      </c>
+      <c r="T41">
+        <v>0</v>
+      </c>
+      <c r="U41">
+        <v>0</v>
+      </c>
+      <c r="V41">
+        <v>0</v>
+      </c>
+      <c r="W41">
+        <v>0</v>
+      </c>
+      <c r="X41">
+        <v>0</v>
+      </c>
+      <c r="Y41">
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <v>0</v>
+      </c>
+      <c r="AA41">
+        <v>0</v>
+      </c>
+      <c r="AB41">
+        <v>0</v>
+      </c>
+      <c r="AC41">
+        <v>0</v>
+      </c>
+      <c r="AD41">
+        <v>0</v>
+      </c>
+      <c r="AE41">
+        <v>0</v>
+      </c>
+      <c r="AF41">
+        <v>0</v>
+      </c>
+      <c r="AG41">
+        <v>0</v>
+      </c>
+      <c r="AH41">
+        <v>0</v>
+      </c>
+      <c r="AI41">
+        <v>0</v>
+      </c>
+      <c r="AJ41">
+        <v>0</v>
+      </c>
+      <c r="AK41">
+        <v>0</v>
+      </c>
+      <c r="AL41">
+        <v>0</v>
+      </c>
+      <c r="AM41">
+        <v>0</v>
+      </c>
+      <c r="AN41">
+        <v>0</v>
+      </c>
+      <c r="AO41">
+        <v>0</v>
+      </c>
+      <c r="AP41">
+        <v>0</v>
+      </c>
+      <c r="AQ41">
+        <v>0</v>
+      </c>
+      <c r="AR41">
+        <v>0</v>
+      </c>
+      <c r="AS41">
+        <v>0</v>
+      </c>
+      <c r="AT41">
+        <v>0</v>
+      </c>
+      <c r="AU41">
+        <v>0</v>
+      </c>
+      <c r="AV41">
+        <v>0</v>
+      </c>
+      <c r="AW41">
+        <v>0</v>
+      </c>
+      <c r="AX41">
+        <v>0</v>
+      </c>
+      <c r="AY41">
+        <v>0</v>
+      </c>
+      <c r="AZ41">
+        <v>0</v>
+      </c>
+      <c r="BA41">
+        <v>0</v>
+      </c>
+      <c r="BB41">
+        <v>0</v>
+      </c>
+      <c r="BC41">
+        <v>0</v>
+      </c>
+      <c r="BD41">
+        <v>0</v>
+      </c>
+      <c r="BE41">
+        <v>0</v>
+      </c>
+      <c r="BF41">
+        <v>0</v>
+      </c>
+      <c r="BG41">
+        <v>0</v>
+      </c>
+      <c r="BH41">
+        <v>0</v>
+      </c>
+      <c r="BI41">
+        <v>0</v>
+      </c>
+      <c r="BJ41">
+        <v>0</v>
+      </c>
+      <c r="BK41">
+        <v>0</v>
+      </c>
+      <c r="BL41">
+        <v>0</v>
+      </c>
+      <c r="BM41">
+        <v>0</v>
+      </c>
+      <c r="BN41">
+        <v>0</v>
+      </c>
+      <c r="BO41">
+        <v>0</v>
+      </c>
+      <c r="BP41">
+        <v>0</v>
+      </c>
+      <c r="BQ41">
+        <v>0</v>
+      </c>
+      <c r="BR41">
+        <v>0</v>
+      </c>
+      <c r="BS41">
+        <v>0</v>
+      </c>
+      <c r="BT41">
+        <v>0</v>
+      </c>
+      <c r="BU41">
+        <v>0</v>
+      </c>
+      <c r="BV41">
+        <v>0</v>
+      </c>
+      <c r="BW41">
+        <v>0</v>
+      </c>
+      <c r="BX41">
+        <v>0</v>
+      </c>
+      <c r="BY41">
+        <v>0</v>
+      </c>
+      <c r="BZ41">
+        <v>0</v>
+      </c>
+      <c r="CA41">
+        <v>0</v>
+      </c>
+      <c r="CB41" t="s">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -862,7 +862,7 @@
     <t>Cusco FC</t>
   </si>
   <si>
-    <t>2026-08-05 16:52:06</t>
+    <t>2026-08-05 19:02:54</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1459,7 @@
         <v>1.64</v>
       </c>
       <c r="G2">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="H2">
         <v>6</v>
@@ -1471,7 +1471,7 @@
         <v>3.55</v>
       </c>
       <c r="K2">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L2">
         <v>1.38</v>
@@ -1480,16 +1480,16 @@
         <v>1.08</v>
       </c>
       <c r="N2">
-        <v>2.78</v>
+        <v>3.05</v>
       </c>
       <c r="O2">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="P2">
         <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="R2">
         <v>1.27</v>
@@ -1507,7 +1507,7 @@
         <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="X2">
         <v>14.5</v>
@@ -1579,10 +1579,10 @@
         <v>5.2</v>
       </c>
       <c r="AU2">
-        <v>6.6</v>
+        <v>3.35</v>
       </c>
       <c r="AV2">
-        <v>4.5</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
         <v>5.1</v>
@@ -1600,7 +1600,7 @@
         <v>5.1</v>
       </c>
       <c r="BB2">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="BC2">
         <v>4.3</v>
@@ -1701,22 +1701,22 @@
         <v>4</v>
       </c>
       <c r="G3">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H3">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="I3">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="J3">
         <v>3.35</v>
       </c>
       <c r="K3">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L3">
-        <v>1.45</v>
+        <v>1.37</v>
       </c>
       <c r="M3">
         <v>1.08</v>
@@ -1728,7 +1728,7 @@
         <v>1.37</v>
       </c>
       <c r="P3">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q3">
         <v>2.08</v>
@@ -1743,13 +1743,13 @@
         <v>1.87</v>
       </c>
       <c r="U3">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V3">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="W3">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="X3">
         <v>15</v>
@@ -1788,7 +1788,7 @@
         <v>50</v>
       </c>
       <c r="AJ3">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AK3">
         <v>60</v>
@@ -1863,40 +1863,40 @@
         <v>3.2</v>
       </c>
       <c r="BI3">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ3">
         <v>10.5</v>
       </c>
       <c r="BK3">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL3">
         <v>1000</v>
       </c>
       <c r="BM3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BN3">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BO3">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="BP3">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BQ3">
         <v>10.5</v>
       </c>
       <c r="BR3">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BS3">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BT3">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BU3">
         <v>3.65</v>
@@ -1905,13 +1905,13 @@
         <v>15.5</v>
       </c>
       <c r="BW3">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BX3">
         <v>32</v>
       </c>
       <c r="BY3">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BZ3">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>210</v>
       </c>
       <c r="F4">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G4">
         <v>2.54</v>
@@ -1955,7 +1955,7 @@
         <v>3.35</v>
       </c>
       <c r="K4">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1973,7 +1973,7 @@
         <v>1.84</v>
       </c>
       <c r="Q4">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="R4">
         <v>1.33</v>
@@ -2081,7 +2081,7 @@
         <v>9</v>
       </c>
       <c r="BA4">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB4">
         <v>11.5</v>
@@ -2182,7 +2182,7 @@
         <v>211</v>
       </c>
       <c r="F5">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="G5">
         <v>1.9</v>
@@ -2200,7 +2200,7 @@
         <v>3.9</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2442,7 +2442,7 @@
         <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -2547,7 +2547,7 @@
         <v>10.5</v>
       </c>
       <c r="AU6">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AV6">
         <v>7.8</v>
@@ -2684,19 +2684,19 @@
         <v>4.2</v>
       </c>
       <c r="L7">
-        <v>1.31</v>
+        <v>1.01</v>
       </c>
       <c r="M7">
         <v>1.05</v>
       </c>
       <c r="N7">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O7">
         <v>1.26</v>
       </c>
       <c r="P7">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q7">
         <v>1.75</v>
@@ -2705,7 +2705,7 @@
         <v>1.45</v>
       </c>
       <c r="S7">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="T7">
         <v>1.71</v>
@@ -2786,7 +2786,7 @@
         <v>4.3</v>
       </c>
       <c r="AT7">
-        <v>13.5</v>
+        <v>15</v>
       </c>
       <c r="AU7">
         <v>8</v>
@@ -2831,7 +2831,7 @@
         <v>3.8</v>
       </c>
       <c r="BI7">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="BJ7">
         <v>9.6</v>
@@ -2908,7 +2908,7 @@
         <v>214</v>
       </c>
       <c r="F8">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="G8">
         <v>3.35</v>
@@ -2923,10 +2923,10 @@
         <v>3.45</v>
       </c>
       <c r="K8">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="L8">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
         <v>1.05</v>
@@ -2950,10 +2950,10 @@
         <v>2.96</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U8">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="V8">
         <v>1.63</v>
@@ -3150,7 +3150,7 @@
         <v>215</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="G9">
         <v>1.65</v>
@@ -3159,10 +3159,10 @@
         <v>6</v>
       </c>
       <c r="I9">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="J9">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K9">
         <v>4.9</v>
@@ -3180,10 +3180,10 @@
         <v>1.26</v>
       </c>
       <c r="P9">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="R9">
         <v>1.41</v>
@@ -3192,10 +3192,10 @@
         <v>2.96</v>
       </c>
       <c r="T9">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="U9">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V9">
         <v>1.15</v>
@@ -3315,7 +3315,7 @@
         <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ9">
         <v>11</v>
@@ -3419,7 +3419,7 @@
         <v>4.2</v>
       </c>
       <c r="O10">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P10">
         <v>2.14</v>
@@ -3443,7 +3443,7 @@
         <v>1.07</v>
       </c>
       <c r="W10">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="X10">
         <v>24</v>
@@ -3667,7 +3667,7 @@
         <v>3.05</v>
       </c>
       <c r="Q11">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="R11">
         <v>1.87</v>
@@ -3676,7 +3676,7 @@
         <v>1.96</v>
       </c>
       <c r="T11">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="U11">
         <v>2.32</v>
@@ -3703,7 +3703,7 @@
         <v>15.5</v>
       </c>
       <c r="AC11">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AD11">
         <v>32</v>
@@ -3742,13 +3742,13 @@
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="AQ11">
         <v>6</v>
       </c>
       <c r="AR11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AS11">
         <v>6.6</v>
@@ -3760,7 +3760,7 @@
         <v>12</v>
       </c>
       <c r="AV11">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AW11">
         <v>6.4</v>
@@ -3775,7 +3775,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
@@ -3787,13 +3787,13 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF11">
         <v>3.4</v>
       </c>
       <c r="BG11">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BH11">
         <v>6</v>
@@ -3891,7 +3891,7 @@
         <v>3.95</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3909,13 +3909,13 @@
         <v>2.1</v>
       </c>
       <c r="Q12">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="R12">
         <v>1.38</v>
       </c>
       <c r="S12">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -4118,7 +4118,7 @@
         <v>219</v>
       </c>
       <c r="F13">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="G13">
         <v>3.1</v>
@@ -4127,7 +4127,7 @@
         <v>2.44</v>
       </c>
       <c r="I13">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="J13">
         <v>3.6</v>
@@ -4142,7 +4142,7 @@
         <v>1.03</v>
       </c>
       <c r="N13">
-        <v>3.45</v>
+        <v>4.4</v>
       </c>
       <c r="O13">
         <v>1.22</v>
@@ -4154,7 +4154,7 @@
         <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="S13">
         <v>2.44</v>
@@ -4166,7 +4166,7 @@
         <v>2.16</v>
       </c>
       <c r="V13">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W13">
         <v>1.47</v>
@@ -4360,22 +4360,22 @@
         <v>220</v>
       </c>
       <c r="F14">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G14">
         <v>2.14</v>
       </c>
       <c r="H14">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="I14">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J14">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="K14">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L14">
         <v>1.39</v>
@@ -4408,19 +4408,19 @@
         <v>1.94</v>
       </c>
       <c r="V14">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="W14">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="X14">
         <v>14.5</v>
       </c>
       <c r="Y14">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z14">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AA14">
         <v>110</v>
@@ -4450,7 +4450,7 @@
         <v>80</v>
       </c>
       <c r="AJ14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="AK14">
         <v>24</v>
@@ -4465,13 +4465,13 @@
         <v>19.5</v>
       </c>
       <c r="AO14">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AP14">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ14">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AR14">
         <v>5</v>
@@ -4486,13 +4486,13 @@
         <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AW14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AX14">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AY14">
         <v>8</v>
@@ -4504,64 +4504,64 @@
         <v>5.4</v>
       </c>
       <c r="BB14">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BC14">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD14">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE14">
         <v>5.6</v>
       </c>
       <c r="BF14">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG14">
         <v>5.4</v>
       </c>
       <c r="BH14">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="BI14">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BJ14">
         <v>10.5</v>
       </c>
       <c r="BK14">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="BL14">
         <v>1000</v>
       </c>
       <c r="BM14">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BN14">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BO14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BP14">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BQ14">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BR14">
         <v>1000</v>
       </c>
       <c r="BS14">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BT14">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BU14">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BV14">
         <v>1000</v>
@@ -4573,13 +4573,13 @@
         <v>1000</v>
       </c>
       <c r="BY14">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="BZ14">
         <v>1000</v>
       </c>
       <c r="CA14">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB14" t="s">
         <v>282</v>
@@ -4638,7 +4638,7 @@
         <v>1.71</v>
       </c>
       <c r="R15">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S15">
         <v>2.66</v>
@@ -4844,22 +4844,22 @@
         <v>222</v>
       </c>
       <c r="F16">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G16">
         <v>3.1</v>
       </c>
       <c r="H16">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="I16">
-        <v>2.62</v>
+        <v>2.8</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4868,7 +4868,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="O16">
         <v>1.22</v>
@@ -4877,10 +4877,10 @@
         <v>2.22</v>
       </c>
       <c r="Q16">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
         <v>2.58</v>
@@ -4892,7 +4892,7 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="W16">
         <v>1.47</v>
@@ -5092,16 +5092,16 @@
         <v>1.78</v>
       </c>
       <c r="H17">
-        <v>5.2</v>
+        <v>4.8</v>
       </c>
       <c r="I17">
-        <v>11</v>
+        <v>9.6</v>
       </c>
       <c r="J17">
         <v>3.8</v>
       </c>
       <c r="K17">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -5346,7 +5346,7 @@
         <v>4</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.25</v>
       </c>
       <c r="M18">
         <v>1.04</v>
@@ -5364,7 +5364,7 @@
         <v>1.62</v>
       </c>
       <c r="R18">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S18">
         <v>2.48</v>
@@ -5582,13 +5582,13 @@
         <v>6.8</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K19">
         <v>4.9</v>
       </c>
       <c r="L19">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="M19">
         <v>1.06</v>
@@ -5630,10 +5630,10 @@
         <v>23</v>
       </c>
       <c r="Z19">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AA19">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AB19">
         <v>9.800000000000001</v>
@@ -5645,7 +5645,7 @@
         <v>27</v>
       </c>
       <c r="AE19">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AF19">
         <v>11.5</v>
@@ -5675,7 +5675,7 @@
         <v>11.5</v>
       </c>
       <c r="AO19">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AP19">
         <v>12</v>
@@ -5699,7 +5699,7 @@
         <v>17</v>
       </c>
       <c r="AW19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AX19">
         <v>7.8</v>
@@ -5711,7 +5711,7 @@
         <v>16.5</v>
       </c>
       <c r="BA19">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BB19">
         <v>12.5</v>
@@ -5720,16 +5720,16 @@
         <v>13.5</v>
       </c>
       <c r="BD19">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="BE19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BF19">
         <v>7.8</v>
       </c>
       <c r="BG19">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BH19">
         <v>1000</v>
@@ -5824,34 +5824,34 @@
         <v>1.96</v>
       </c>
       <c r="J20">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="K20">
         <v>4.8</v>
       </c>
       <c r="L20">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="M20">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O20">
         <v>1.26</v>
       </c>
       <c r="P20">
-        <v>1.89</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.73</v>
+        <v>1.26</v>
       </c>
       <c r="R20">
-        <v>1.34</v>
+        <v>1.24</v>
       </c>
       <c r="S20">
-        <v>2.84</v>
+        <v>1.26</v>
       </c>
       <c r="T20">
         <v>1.71</v>
@@ -6054,7 +6054,7 @@
         <v>227</v>
       </c>
       <c r="F21">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="G21">
         <v>1.72</v>
@@ -6087,7 +6087,7 @@
         <v>2.2</v>
       </c>
       <c r="Q21">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="R21">
         <v>1.47</v>
@@ -6096,7 +6096,7 @@
         <v>2.6</v>
       </c>
       <c r="T21">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="U21">
         <v>2.1</v>
@@ -6168,10 +6168,10 @@
         <v>16.5</v>
       </c>
       <c r="AR21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AT21">
         <v>7.4</v>
@@ -6183,7 +6183,7 @@
         <v>16</v>
       </c>
       <c r="AW21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AX21">
         <v>8</v>
@@ -6195,7 +6195,7 @@
         <v>14</v>
       </c>
       <c r="BA21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BB21">
         <v>11.5</v>
@@ -6204,16 +6204,16 @@
         <v>12</v>
       </c>
       <c r="BD21">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF21">
         <v>5.9</v>
       </c>
       <c r="BG21">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH21">
         <v>4.2</v>
@@ -6296,22 +6296,22 @@
         <v>228</v>
       </c>
       <c r="F22">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="G22">
         <v>2.16</v>
       </c>
       <c r="H22">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="I22">
         <v>4.5</v>
       </c>
       <c r="J22">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6323,7 +6323,7 @@
         <v>3.7</v>
       </c>
       <c r="O22">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P22">
         <v>2.06</v>
@@ -6332,7 +6332,7 @@
         <v>1.71</v>
       </c>
       <c r="R22">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="S22">
         <v>2.72</v>
@@ -6541,13 +6541,13 @@
         <v>1.97</v>
       </c>
       <c r="G23">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="H23">
         <v>3.35</v>
       </c>
       <c r="I23">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="J23">
         <v>3.95</v>
@@ -6562,22 +6562,22 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="O23">
         <v>1.16</v>
       </c>
       <c r="P23">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="Q23">
         <v>1.54</v>
       </c>
       <c r="R23">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S23">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="T23">
         <v>1.01</v>
@@ -6882,22 +6882,22 @@
         <v>1000</v>
       </c>
       <c r="AN24">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AO24">
         <v>1000</v>
       </c>
       <c r="AP24">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AQ24">
         <v>18.5</v>
       </c>
       <c r="AR24">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AS24">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AT24">
         <v>7.4</v>
@@ -6909,7 +6909,7 @@
         <v>16.5</v>
       </c>
       <c r="AW24">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="AX24">
         <v>7.2</v>
@@ -6921,7 +6921,7 @@
         <v>13</v>
       </c>
       <c r="BA24">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BB24">
         <v>8.800000000000001</v>
@@ -6933,34 +6933,34 @@
         <v>17.5</v>
       </c>
       <c r="BE24">
-        <v>1.03</v>
+        <v>2.64</v>
       </c>
       <c r="BF24">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BG24">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="BH24">
         <v>5.8</v>
       </c>
       <c r="BI24">
-        <v>1.52</v>
+        <v>3.4</v>
       </c>
       <c r="BJ24">
         <v>13.5</v>
       </c>
       <c r="BK24">
-        <v>1.79</v>
+        <v>2.6</v>
       </c>
       <c r="BL24">
         <v>1000</v>
       </c>
       <c r="BM24">
-        <v>2.06</v>
+        <v>3.2</v>
       </c>
       <c r="BN24">
-        <v>1000</v>
+        <v>5.8</v>
       </c>
       <c r="BO24">
         <v>3.15</v>
@@ -6969,37 +6969,37 @@
         <v>12.5</v>
       </c>
       <c r="BQ24">
-        <v>1.78</v>
+        <v>2.56</v>
       </c>
       <c r="BR24">
         <v>28</v>
       </c>
       <c r="BS24">
-        <v>1.93</v>
+        <v>2.88</v>
       </c>
       <c r="BT24">
         <v>15</v>
       </c>
       <c r="BU24">
-        <v>1.82</v>
+        <v>2.64</v>
       </c>
       <c r="BV24">
         <v>1000</v>
       </c>
       <c r="BW24">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="BX24">
         <v>1000</v>
       </c>
       <c r="BY24">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="BZ24">
         <v>17</v>
       </c>
       <c r="CA24">
-        <v>1.85</v>
+        <v>2.7</v>
       </c>
       <c r="CB24" t="s">
         <v>282</v>
@@ -7037,7 +7037,7 @@
         <v>4.3</v>
       </c>
       <c r="K25">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7273,10 +7273,10 @@
         <v>7.4</v>
       </c>
       <c r="I26">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J26">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K26">
         <v>4.8</v>
@@ -7300,7 +7300,7 @@
         <v>1.86</v>
       </c>
       <c r="R26">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S26">
         <v>3.1</v>
@@ -7518,7 +7518,7 @@
         <v>110</v>
       </c>
       <c r="J27">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7760,22 +7760,22 @@
         <v>3.8</v>
       </c>
       <c r="J28">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
         <v>4.3</v>
       </c>
       <c r="O28">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="P28">
         <v>2.18</v>
@@ -7784,16 +7784,16 @@
         <v>1.73</v>
       </c>
       <c r="R28">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S28">
-        <v>2.52</v>
+        <v>2.84</v>
       </c>
       <c r="T28">
-        <v>1.53</v>
+        <v>1.65</v>
       </c>
       <c r="U28">
-        <v>2.1</v>
+        <v>2.32</v>
       </c>
       <c r="V28">
         <v>1.35</v>
@@ -7802,112 +7802,112 @@
         <v>1.84</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AE28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ28">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AN28">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8020,13 +8020,13 @@
         <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="Q29">
         <v>1.68</v>
       </c>
       <c r="R29">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="S29">
         <v>2.72</v>
@@ -8283,7 +8283,7 @@
         <v>1.12</v>
       </c>
       <c r="W30">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8483,7 +8483,7 @@
         <v>2.76</v>
       </c>
       <c r="I31">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J31">
         <v>3.4</v>
@@ -8498,37 +8498,37 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="O31">
         <v>1.28</v>
       </c>
       <c r="P31">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q31">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="R31">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S31">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="T31">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U31">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="V31">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="W31">
         <v>1.54</v>
       </c>
       <c r="X31">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="Y31">
         <v>1000</v>
@@ -8543,7 +8543,7 @@
         <v>1000</v>
       </c>
       <c r="AC31">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD31">
         <v>1000</v>
@@ -8552,13 +8552,13 @@
         <v>40</v>
       </c>
       <c r="AF31">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AG31">
         <v>1000</v>
       </c>
       <c r="AH31">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI31">
         <v>1000</v>
@@ -8573,7 +8573,7 @@
         <v>1000</v>
       </c>
       <c r="AM31">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN31">
         <v>1000</v>
@@ -8582,58 +8582,58 @@
         <v>1000</v>
       </c>
       <c r="AP31">
-        <v>1.25</v>
+        <v>1.12</v>
       </c>
       <c r="AQ31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AR31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AS31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AT31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="AU31">
+        <v>1.19</v>
+      </c>
+      <c r="AV31">
+        <v>1.19</v>
+      </c>
+      <c r="AW31">
+        <v>1.16</v>
+      </c>
+      <c r="AX31">
+        <v>1.19</v>
+      </c>
+      <c r="AY31">
+        <v>1.19</v>
+      </c>
+      <c r="AZ31">
+        <v>1.13</v>
+      </c>
+      <c r="BA31">
+        <v>1.19</v>
+      </c>
+      <c r="BB31">
+        <v>1.19</v>
+      </c>
+      <c r="BC31">
+        <v>1.16</v>
+      </c>
+      <c r="BD31">
+        <v>1.19</v>
+      </c>
+      <c r="BE31">
         <v>1.18</v>
       </c>
-      <c r="AV31">
-        <v>1.35</v>
-      </c>
-      <c r="AW31">
-        <v>1.3</v>
-      </c>
-      <c r="AX31">
-        <v>1.27</v>
-      </c>
-      <c r="AY31">
-        <v>1.35</v>
-      </c>
-      <c r="AZ31">
-        <v>1.35</v>
-      </c>
-      <c r="BA31">
-        <v>1.35</v>
-      </c>
-      <c r="BB31">
-        <v>1.35</v>
-      </c>
-      <c r="BC31">
-        <v>1.3</v>
-      </c>
-      <c r="BD31">
-        <v>1.35</v>
-      </c>
-      <c r="BE31">
-        <v>1.35</v>
-      </c>
       <c r="BF31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="BG31">
-        <v>1.35</v>
+        <v>1.19</v>
       </c>
       <c r="BH31">
         <v>1000</v>
@@ -8725,7 +8725,7 @@
         <v>2.28</v>
       </c>
       <c r="I32">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J32">
         <v>3.85</v>
@@ -8740,7 +8740,7 @@
         <v>1.04</v>
       </c>
       <c r="N32">
-        <v>3.7</v>
+        <v>5</v>
       </c>
       <c r="O32">
         <v>1.21</v>
@@ -8749,133 +8749,133 @@
         <v>2.36</v>
       </c>
       <c r="Q32">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="R32">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="S32">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="T32">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="U32">
-        <v>2.22</v>
+        <v>2.5</v>
       </c>
       <c r="V32">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W32">
         <v>1.44</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="Y32">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="Z32">
+        <v>17.5</v>
+      </c>
+      <c r="AA32">
+        <v>30</v>
+      </c>
+      <c r="AB32">
+        <v>17</v>
+      </c>
+      <c r="AC32">
+        <v>9.4</v>
+      </c>
+      <c r="AD32">
+        <v>11.5</v>
+      </c>
+      <c r="AE32">
+        <v>22</v>
+      </c>
+      <c r="AF32">
+        <v>25</v>
+      </c>
+      <c r="AG32">
+        <v>14.5</v>
+      </c>
+      <c r="AH32">
+        <v>15.5</v>
+      </c>
+      <c r="AI32">
+        <v>30</v>
+      </c>
+      <c r="AJ32">
+        <v>60</v>
+      </c>
+      <c r="AK32">
+        <v>32</v>
+      </c>
+      <c r="AL32">
+        <v>38</v>
+      </c>
+      <c r="AM32">
+        <v>75</v>
+      </c>
+      <c r="AN32">
         <v>23</v>
       </c>
-      <c r="AA32">
-        <v>40</v>
-      </c>
-      <c r="AB32">
-        <v>23</v>
-      </c>
-      <c r="AC32">
+      <c r="AO32">
         <v>13</v>
       </c>
-      <c r="AD32">
-        <v>16</v>
-      </c>
-      <c r="AE32">
+      <c r="AP32">
+        <v>8</v>
+      </c>
+      <c r="AQ32">
+        <v>12</v>
+      </c>
+      <c r="AR32">
+        <v>15</v>
+      </c>
+      <c r="AS32">
+        <v>8.4</v>
+      </c>
+      <c r="AT32">
+        <v>14.5</v>
+      </c>
+      <c r="AU32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV32">
+        <v>10</v>
+      </c>
+      <c r="AW32">
+        <v>7.6</v>
+      </c>
+      <c r="AX32">
+        <v>8</v>
+      </c>
+      <c r="AY32">
+        <v>12.5</v>
+      </c>
+      <c r="AZ32">
+        <v>13.5</v>
+      </c>
+      <c r="BA32">
+        <v>8.4</v>
+      </c>
+      <c r="BB32">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC32">
+        <v>8.6</v>
+      </c>
+      <c r="BD32">
         <v>30</v>
       </c>
-      <c r="AF32">
-        <v>34</v>
-      </c>
-      <c r="AG32">
-        <v>20</v>
-      </c>
-      <c r="AH32">
-        <v>21</v>
-      </c>
-      <c r="AI32">
-        <v>40</v>
-      </c>
-      <c r="AJ32">
-        <v>70</v>
-      </c>
-      <c r="AK32">
-        <v>46</v>
-      </c>
-      <c r="AL32">
-        <v>50</v>
-      </c>
-      <c r="AM32">
-        <v>90</v>
-      </c>
-      <c r="AN32">
-        <v>1000</v>
-      </c>
-      <c r="AO32">
-        <v>1000</v>
-      </c>
-      <c r="AP32">
-        <v>2.24</v>
-      </c>
-      <c r="AQ32">
+      <c r="BE32">
         <v>10</v>
       </c>
-      <c r="AR32">
-        <v>2.04</v>
-      </c>
-      <c r="AS32">
-        <v>2.12</v>
-      </c>
-      <c r="AT32">
-        <v>2.04</v>
-      </c>
-      <c r="AU32">
-        <v>1.92</v>
-      </c>
-      <c r="AV32">
-        <v>1.97</v>
-      </c>
-      <c r="AW32">
-        <v>2.08</v>
-      </c>
-      <c r="AX32">
-        <v>18</v>
-      </c>
-      <c r="AY32">
-        <v>10</v>
-      </c>
-      <c r="AZ32">
-        <v>2.02</v>
-      </c>
-      <c r="BA32">
-        <v>2.12</v>
-      </c>
-      <c r="BB32">
-        <v>2.18</v>
-      </c>
-      <c r="BC32">
-        <v>2.14</v>
-      </c>
-      <c r="BD32">
-        <v>2.14</v>
-      </c>
-      <c r="BE32">
-        <v>2.18</v>
-      </c>
       <c r="BF32">
-        <v>2.24</v>
+        <v>17</v>
       </c>
       <c r="BG32">
-        <v>2.24</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -9009,7 +9009,7 @@
         <v>1.33</v>
       </c>
       <c r="W33">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X33">
         <v>12</v>
@@ -9030,13 +9030,13 @@
         <v>8</v>
       </c>
       <c r="AD33">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AE33">
         <v>55</v>
       </c>
       <c r="AF33">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AG33">
         <v>12</v>
@@ -9075,7 +9075,7 @@
         <v>20</v>
       </c>
       <c r="AS33">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AT33">
         <v>7.2</v>
@@ -9087,7 +9087,7 @@
         <v>12</v>
       </c>
       <c r="AW33">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AX33">
         <v>10.5</v>
@@ -9099,25 +9099,25 @@
         <v>17.5</v>
       </c>
       <c r="BA33">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB33">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="BC33">
         <v>20</v>
       </c>
       <c r="BD33">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="BE33">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF33">
         <v>17.5</v>
       </c>
       <c r="BG33">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9212,7 +9212,7 @@
         <v>110</v>
       </c>
       <c r="J34">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K34">
         <v>950</v>
@@ -9233,13 +9233,13 @@
         <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="R34">
         <v>1.25</v>
       </c>
       <c r="S34">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -9248,10 +9248,10 @@
         <v>1.01</v>
       </c>
       <c r="V34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W34">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X34">
         <v>1000</v>
@@ -9445,10 +9445,10 @@
         <v>3.45</v>
       </c>
       <c r="G35">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="H35">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="I35">
         <v>2.1</v>
@@ -9487,7 +9487,7 @@
         <v>1.02</v>
       </c>
       <c r="U35">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V35">
         <v>1.9</v>
@@ -9717,7 +9717,7 @@
         <v>2.42</v>
       </c>
       <c r="Q36">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="R36">
         <v>1.5</v>
@@ -9950,22 +9950,22 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="O37">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="P37">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="Q37">
         <v>1.53</v>
       </c>
       <c r="R37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="S37">
-        <v>2.46</v>
+        <v>2.42</v>
       </c>
       <c r="T37">
         <v>1.55</v>
@@ -9995,7 +9995,7 @@
         <v>15.5</v>
       </c>
       <c r="AC37">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD37">
         <v>13.5</v>
@@ -10013,19 +10013,19 @@
         <v>16</v>
       </c>
       <c r="AI37">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AJ37">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AK37">
         <v>27</v>
       </c>
       <c r="AL37">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AM37">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AN37">
         <v>19</v>
@@ -10055,7 +10055,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="AX37">
         <v>17.5</v>
@@ -10070,7 +10070,7 @@
         <v>5.9</v>
       </c>
       <c r="BB37">
-        <v>30</v>
+        <v>6</v>
       </c>
       <c r="BC37">
         <v>21</v>
@@ -10177,10 +10177,10 @@
         <v>2.84</v>
       </c>
       <c r="I38">
+        <v>3.2</v>
+      </c>
+      <c r="J38">
         <v>3.25</v>
-      </c>
-      <c r="J38">
-        <v>3.2</v>
       </c>
       <c r="K38">
         <v>3.55</v>
@@ -10207,7 +10207,7 @@
         <v>1.26</v>
       </c>
       <c r="S38">
-        <v>3.6</v>
+        <v>3.35</v>
       </c>
       <c r="T38">
         <v>1.66</v>
@@ -10216,7 +10216,7 @@
         <v>1.87</v>
       </c>
       <c r="V38">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="W38">
         <v>1.52</v>
@@ -10333,19 +10333,19 @@
         <v>1000</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>1.83</v>
       </c>
       <c r="BJ38">
         <v>13.5</v>
       </c>
       <c r="BK38">
-        <v>6.4</v>
+        <v>1.62</v>
       </c>
       <c r="BL38">
         <v>1000</v>
       </c>
       <c r="BM38">
-        <v>21</v>
+        <v>1.83</v>
       </c>
       <c r="BN38">
         <v>7.6</v>
@@ -10357,13 +10357,13 @@
         <v>30</v>
       </c>
       <c r="BQ38">
-        <v>13.5</v>
+        <v>1.73</v>
       </c>
       <c r="BR38">
         <v>50</v>
       </c>
       <c r="BS38">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BT38">
         <v>8</v>
@@ -10375,19 +10375,19 @@
         <v>34</v>
       </c>
       <c r="BW38">
-        <v>15</v>
+        <v>1.74</v>
       </c>
       <c r="BX38">
         <v>50</v>
       </c>
       <c r="BY38">
-        <v>21</v>
+        <v>1.77</v>
       </c>
       <c r="BZ38">
         <v>46</v>
       </c>
       <c r="CA38">
-        <v>20</v>
+        <v>1.77</v>
       </c>
       <c r="CB38" t="s">
         <v>282</v>
@@ -10410,13 +10410,13 @@
         <v>245</v>
       </c>
       <c r="F39">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="G39">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>1.04</v>
       </c>
       <c r="I39">
         <v>110</v>
@@ -10425,7 +10425,7 @@
         <v>4.1</v>
       </c>
       <c r="K39">
-        <v>4.5</v>
+        <v>950</v>
       </c>
       <c r="L39">
         <v>1.01</v>
@@ -10461,7 +10461,7 @@
         <v>1.19</v>
       </c>
       <c r="W39">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10655,7 +10655,7 @@
         <v>2.26</v>
       </c>
       <c r="G40">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H40">
         <v>2.68</v>
@@ -10688,7 +10688,7 @@
         <v>1.46</v>
       </c>
       <c r="R40">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S40">
         <v>2.04</v>
@@ -11160,7 +11160,7 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="O42">
         <v>1.19</v>
@@ -11181,7 +11181,7 @@
         <v>1.5</v>
       </c>
       <c r="U42">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="V42">
         <v>1.67</v>
@@ -11384,10 +11384,10 @@
         <v>2.62</v>
       </c>
       <c r="H43">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="I43">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="J43">
         <v>3.85</v>
@@ -11399,7 +11399,7 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N43">
         <v>4.2</v>
@@ -11414,19 +11414,19 @@
         <v>1.56</v>
       </c>
       <c r="R43">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="S43">
         <v>2.38</v>
       </c>
       <c r="T43">
-        <v>1.52</v>
+        <v>1.47</v>
       </c>
       <c r="U43">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="V43">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="W43">
         <v>1.61</v>
@@ -11543,19 +11543,19 @@
         <v>1000</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="BJ43">
         <v>11.5</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>1.75</v>
       </c>
       <c r="BL43">
         <v>1000</v>
       </c>
       <c r="BM43">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="BN43">
         <v>7.8</v>
@@ -11567,13 +11567,13 @@
         <v>23</v>
       </c>
       <c r="BQ43">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="BR43">
         <v>34</v>
       </c>
       <c r="BS43">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="BT43">
         <v>8.800000000000001</v>
@@ -11585,19 +11585,19 @@
         <v>28</v>
       </c>
       <c r="BW43">
-        <v>1.01</v>
+        <v>1.93</v>
       </c>
       <c r="BX43">
         <v>38</v>
       </c>
       <c r="BY43">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="BZ43">
         <v>23</v>
       </c>
       <c r="CA43">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="CB43" t="s">
         <v>282</v>
@@ -11644,7 +11644,7 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="O44">
         <v>1.12</v>
@@ -11653,16 +11653,16 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="R44">
         <v>1.71</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T44">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U44">
         <v>1.01</v>
@@ -12107,7 +12107,7 @@
         <v>2.5</v>
       </c>
       <c r="G46">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H46">
         <v>2.5</v>
@@ -12128,7 +12128,7 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.66</v>
+        <v>5.1</v>
       </c>
       <c r="O46">
         <v>1.13</v>
@@ -12137,13 +12137,13 @@
         <v>2.6</v>
       </c>
       <c r="Q46">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R46">
         <v>1.59</v>
       </c>
       <c r="S46">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="T46">
         <v>1.01</v>
@@ -12155,7 +12155,7 @@
         <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12212,52 +12212,52 @@
         <v>1000</v>
       </c>
       <c r="AP46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE46">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF46">
         <v>1.01</v>
@@ -12379,13 +12379,13 @@
         <v>2.8</v>
       </c>
       <c r="Q47">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="R47">
-        <v>1.52</v>
+        <v>1.68</v>
       </c>
       <c r="S47">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="T47">
         <v>1.01</v>
@@ -12454,52 +12454,52 @@
         <v>1000</v>
       </c>
       <c r="AP47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE47">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF47">
         <v>1.01</v>
@@ -12588,22 +12588,22 @@
         <v>254</v>
       </c>
       <c r="F48">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="G48">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="H48">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="I48">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="J48">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="K48">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="L48">
         <v>1.01</v>
@@ -12612,13 +12612,13 @@
         <v>1.05</v>
       </c>
       <c r="N48">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O48">
         <v>1.24</v>
       </c>
       <c r="P48">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q48">
         <v>1.71</v>
@@ -12630,106 +12630,106 @@
         <v>2.8</v>
       </c>
       <c r="T48">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="U48">
-        <v>1.76</v>
+        <v>1.94</v>
       </c>
       <c r="V48">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="W48">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="X48">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Y48">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="Z48">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AA48">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AB48">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AC48">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD48">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE48">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AF48">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AG48">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AH48">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI48">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AJ48">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK48">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL48">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM48">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN48">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AO48">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP48">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AQ48">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR48">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="AS48">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AT48">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AU48">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="AV48">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AW48">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AX48">
         <v>1.01</v>
       </c>
       <c r="AY48">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AZ48">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA48">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB48">
         <v>1.01</v>
@@ -12747,7 +12747,7 @@
         <v>1.01</v>
       </c>
       <c r="BG48">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH48">
         <v>1000</v>
@@ -12830,28 +12830,28 @@
         <v>255</v>
       </c>
       <c r="F49">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="G49">
         <v>2.62</v>
       </c>
       <c r="H49">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I49">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="J49">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K49">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L49">
         <v>1.33</v>
       </c>
       <c r="M49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N49">
         <v>3.4</v>
@@ -12866,7 +12866,7 @@
         <v>2</v>
       </c>
       <c r="R49">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="S49">
         <v>3.45</v>
@@ -12875,10 +12875,10 @@
         <v>1.67</v>
       </c>
       <c r="U49">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="V49">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="W49">
         <v>1.61</v>
@@ -12896,7 +12896,7 @@
         <v>65</v>
       </c>
       <c r="AB49">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AC49">
         <v>8.199999999999999</v>
@@ -12908,7 +12908,7 @@
         <v>44</v>
       </c>
       <c r="AF49">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AG49">
         <v>13.5</v>
@@ -12923,7 +12923,7 @@
         <v>40</v>
       </c>
       <c r="AK49">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AL49">
         <v>48</v>
@@ -12947,19 +12947,19 @@
         <v>17</v>
       </c>
       <c r="AS49">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="AT49">
         <v>7.8</v>
       </c>
       <c r="AU49">
-        <v>6</v>
+        <v>6.6</v>
       </c>
       <c r="AV49">
         <v>10.5</v>
       </c>
       <c r="AW49">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="AX49">
         <v>12</v>
@@ -12971,25 +12971,25 @@
         <v>13</v>
       </c>
       <c r="BA49">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BB49">
-        <v>26</v>
+        <v>1.03</v>
       </c>
       <c r="BC49">
         <v>21</v>
       </c>
       <c r="BD49">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BE49">
-        <v>70</v>
+        <v>1.01</v>
       </c>
       <c r="BF49">
         <v>17</v>
       </c>
       <c r="BG49">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BH49">
         <v>1000</v>
@@ -13075,10 +13075,10 @@
         <v>2.16</v>
       </c>
       <c r="G50">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H50">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I50">
         <v>3.65</v>
@@ -13087,7 +13087,7 @@
         <v>3.55</v>
       </c>
       <c r="K50">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L50">
         <v>1.27</v>
@@ -13096,7 +13096,7 @@
         <v>1.04</v>
       </c>
       <c r="N50">
-        <v>2.06</v>
+        <v>3.6</v>
       </c>
       <c r="O50">
         <v>1.24</v>
@@ -13108,16 +13108,16 @@
         <v>1.77</v>
       </c>
       <c r="R50">
-        <v>1.18</v>
+        <v>1.4</v>
       </c>
       <c r="S50">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="T50">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U50">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V50">
         <v>1.37</v>
@@ -13129,43 +13129,43 @@
         <v>1000</v>
       </c>
       <c r="Y50">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z50">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA50">
         <v>1000</v>
       </c>
       <c r="AB50">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AC50">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD50">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE50">
         <v>1000</v>
       </c>
       <c r="AF50">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG50">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH50">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI50">
         <v>1000</v>
       </c>
       <c r="AJ50">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK50">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AL50">
         <v>1000</v>
@@ -13180,52 +13180,52 @@
         <v>1000</v>
       </c>
       <c r="AP50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ50">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR50">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AS50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT50">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AU50">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AV50">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX50">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AY50">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ50">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BA50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB50">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BC50">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BD50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE50">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF50">
         <v>1.01</v>
@@ -13317,13 +13317,13 @@
         <v>2.3</v>
       </c>
       <c r="G51">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="H51">
         <v>2.98</v>
       </c>
       <c r="I51">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J51">
         <v>3.65</v>
@@ -13350,7 +13350,7 @@
         <v>1.71</v>
       </c>
       <c r="R51">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="S51">
         <v>2.66</v>
@@ -13362,7 +13362,7 @@
         <v>2.52</v>
       </c>
       <c r="V51">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="W51">
         <v>1.75</v>
@@ -13416,7 +13416,7 @@
         <v>65</v>
       </c>
       <c r="AN51">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO51">
         <v>24</v>
@@ -13443,7 +13443,7 @@
         <v>11</v>
       </c>
       <c r="AW51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX51">
         <v>15</v>
@@ -13458,7 +13458,7 @@
         <v>6.8</v>
       </c>
       <c r="BB51">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BC51">
         <v>19</v>
@@ -13586,7 +13586,7 @@
         <v>1.15</v>
       </c>
       <c r="P52">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q52">
         <v>1.59</v>
@@ -13831,7 +13831,7 @@
         <v>1.97</v>
       </c>
       <c r="Q53">
-        <v>1.77</v>
+        <v>1.9</v>
       </c>
       <c r="R53">
         <v>1.31</v>
@@ -13855,7 +13855,7 @@
         <v>1000</v>
       </c>
       <c r="Y53">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z53">
         <v>1000</v>
@@ -13870,7 +13870,7 @@
         <v>11.5</v>
       </c>
       <c r="AD53">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AE53">
         <v>1000</v>
@@ -13888,10 +13888,10 @@
         <v>1000</v>
       </c>
       <c r="AJ53">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AK53">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL53">
         <v>1000</v>
@@ -13906,28 +13906,28 @@
         <v>1000</v>
       </c>
       <c r="AP53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AQ53">
-        <v>1.51</v>
+        <v>11</v>
       </c>
       <c r="AR53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AS53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AT53">
         <v>6.2</v>
       </c>
       <c r="AU53">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="AV53">
-        <v>1.51</v>
+        <v>12</v>
       </c>
       <c r="AW53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="AX53">
         <v>7.8</v>
@@ -13936,28 +13936,28 @@
         <v>6.8</v>
       </c>
       <c r="AZ53">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="BA53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="BB53">
-        <v>1.51</v>
+        <v>13.5</v>
       </c>
       <c r="BC53">
-        <v>1.51</v>
+        <v>12.5</v>
       </c>
       <c r="BD53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="BE53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="BF53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="BG53">
-        <v>1.51</v>
+        <v>1.95</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -14049,7 +14049,7 @@
         <v>3.6</v>
       </c>
       <c r="I54">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J54">
         <v>3.65</v>
@@ -14073,7 +14073,7 @@
         <v>2.1</v>
       </c>
       <c r="Q54">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="R54">
         <v>1.38</v>
@@ -14088,7 +14088,7 @@
         <v>1.01</v>
       </c>
       <c r="V54">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W54">
         <v>1.83</v>
@@ -14282,7 +14282,7 @@
         <v>261</v>
       </c>
       <c r="F55">
-        <v>2.74</v>
+        <v>2.92</v>
       </c>
       <c r="G55">
         <v>4.1</v>
@@ -14297,7 +14297,7 @@
         <v>2.96</v>
       </c>
       <c r="K55">
-        <v>6.6</v>
+        <v>5.8</v>
       </c>
       <c r="L55">
         <v>1.31</v>
@@ -14309,7 +14309,7 @@
         <v>3.6</v>
       </c>
       <c r="O55">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="P55">
         <v>1.78</v>
@@ -14318,10 +14318,10 @@
         <v>1.86</v>
       </c>
       <c r="R55">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="S55">
-        <v>1.86</v>
+        <v>2.56</v>
       </c>
       <c r="T55">
         <v>1.01</v>
@@ -14390,52 +14390,52 @@
         <v>1000</v>
       </c>
       <c r="AP55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE55">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF55">
         <v>1.01</v>
@@ -14548,10 +14548,10 @@
         <v>1.01</v>
       </c>
       <c r="N56">
-        <v>2.36</v>
+        <v>2.5</v>
       </c>
       <c r="O56">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P56">
         <v>2.36</v>
@@ -14632,52 +14632,52 @@
         <v>1000</v>
       </c>
       <c r="AP56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE56">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF56">
         <v>1.01</v>
@@ -14766,16 +14766,16 @@
         <v>263</v>
       </c>
       <c r="F57">
-        <v>2.4</v>
+        <v>5.9</v>
       </c>
       <c r="G57">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="H57">
         <v>1.42</v>
       </c>
       <c r="I57">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="J57">
         <v>4.6</v>
@@ -14814,7 +14814,7 @@
         <v>1.01</v>
       </c>
       <c r="V57">
-        <v>2.96</v>
+        <v>2.78</v>
       </c>
       <c r="W57">
         <v>1.1</v>
@@ -14874,52 +14874,52 @@
         <v>1000</v>
       </c>
       <c r="AP57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF57">
         <v>1.01</v>
@@ -15020,10 +15020,10 @@
         <v>5</v>
       </c>
       <c r="J58">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K58">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L58">
         <v>1.29</v>
@@ -15041,7 +15041,7 @@
         <v>2</v>
       </c>
       <c r="Q58">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R58">
         <v>1.39</v>
@@ -15050,10 +15050,10 @@
         <v>3.15</v>
       </c>
       <c r="T58">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="U58">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="V58">
         <v>1.25</v>
@@ -15116,76 +15116,76 @@
         <v>60</v>
       </c>
       <c r="AP58">
-        <v>12</v>
+        <v>4.2</v>
       </c>
       <c r="AQ58">
-        <v>12.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR58">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="AS58">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="AT58">
-        <v>8.6</v>
+        <v>3.65</v>
       </c>
       <c r="AU58">
-        <v>7.6</v>
+        <v>3.55</v>
       </c>
       <c r="AV58">
-        <v>13</v>
+        <v>4.3</v>
       </c>
       <c r="AW58">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="AX58">
-        <v>9.800000000000001</v>
+        <v>3.95</v>
       </c>
       <c r="AY58">
-        <v>9.199999999999999</v>
+        <v>3.8</v>
       </c>
       <c r="AZ58">
-        <v>13.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA58">
-        <v>8.800000000000001</v>
+        <v>5.1</v>
       </c>
       <c r="BB58">
-        <v>17.5</v>
+        <v>4.5</v>
       </c>
       <c r="BC58">
-        <v>15.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD58">
-        <v>8.800000000000001</v>
+        <v>4.8</v>
       </c>
       <c r="BE58">
-        <v>8.800000000000001</v>
+        <v>5.2</v>
       </c>
       <c r="BF58">
-        <v>10</v>
+        <v>3.95</v>
       </c>
       <c r="BG58">
-        <v>8.800000000000001</v>
+        <v>5</v>
       </c>
       <c r="BH58">
         <v>1000</v>
       </c>
       <c r="BI58">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="BJ58">
         <v>13</v>
       </c>
       <c r="BK58">
-        <v>6.2</v>
+        <v>1.69</v>
       </c>
       <c r="BL58">
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>21</v>
+        <v>1.94</v>
       </c>
       <c r="BN58">
         <v>6.4</v>
@@ -15197,13 +15197,13 @@
         <v>19</v>
       </c>
       <c r="BQ58">
-        <v>8.800000000000001</v>
+        <v>1.76</v>
       </c>
       <c r="BR58">
         <v>38</v>
       </c>
       <c r="BS58">
-        <v>16.5</v>
+        <v>1.85</v>
       </c>
       <c r="BT58">
         <v>10</v>
@@ -15215,13 +15215,13 @@
         <v>48</v>
       </c>
       <c r="BW58">
-        <v>21</v>
+        <v>1.87</v>
       </c>
       <c r="BX58">
         <v>1000</v>
       </c>
       <c r="BY58">
-        <v>21</v>
+        <v>1.88</v>
       </c>
       <c r="BZ58">
         <v>0</v>
@@ -15262,7 +15262,7 @@
         <v>110</v>
       </c>
       <c r="J59">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="K59">
         <v>950</v>
@@ -15358,52 +15358,52 @@
         <v>1000</v>
       </c>
       <c r="AP59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE59">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF59">
         <v>1.01</v>
@@ -15531,10 +15531,10 @@
         <v>1.41</v>
       </c>
       <c r="S60">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="U60">
         <v>1.02</v>
@@ -15737,7 +15737,7 @@
         <v>1.86</v>
       </c>
       <c r="G61">
-        <v>2.42</v>
+        <v>2.2</v>
       </c>
       <c r="H61">
         <v>3.5</v>
@@ -15758,7 +15758,7 @@
         <v>1.01</v>
       </c>
       <c r="N61">
-        <v>3.2</v>
+        <v>2.76</v>
       </c>
       <c r="O61">
         <v>1.23</v>
@@ -15785,7 +15785,7 @@
         <v>1.26</v>
       </c>
       <c r="W61">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="X61">
         <v>1000</v>
@@ -15842,52 +15842,52 @@
         <v>1000</v>
       </c>
       <c r="AP61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE61">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF61">
         <v>1.01</v>
@@ -15988,25 +15988,25 @@
         <v>2.94</v>
       </c>
       <c r="J62">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K62">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="L62">
         <v>1.31</v>
       </c>
       <c r="M62">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N62">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="O62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P62">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q62">
         <v>1.91</v>
@@ -16015,7 +16015,7 @@
         <v>1.31</v>
       </c>
       <c r="S62">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T62">
         <v>1.01</v>
@@ -16218,7 +16218,7 @@
         <v>269</v>
       </c>
       <c r="F63">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="G63">
         <v>2.92</v>
@@ -16233,7 +16233,7 @@
         <v>3</v>
       </c>
       <c r="K63">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="L63">
         <v>1.32</v>
@@ -16242,7 +16242,7 @@
         <v>1.01</v>
       </c>
       <c r="N63">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="O63">
         <v>1.3</v>
@@ -16326,52 +16326,52 @@
         <v>1000</v>
       </c>
       <c r="AP63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE63">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF63">
         <v>1.01</v>
@@ -16484,7 +16484,7 @@
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="O64">
         <v>1.15</v>
@@ -16502,10 +16502,10 @@
         <v>2.2</v>
       </c>
       <c r="T64">
-        <v>1.76</v>
+        <v>1.01</v>
       </c>
       <c r="U64">
-        <v>1.74</v>
+        <v>1.01</v>
       </c>
       <c r="V64">
         <v>1.01</v>
@@ -16568,52 +16568,52 @@
         <v>1000</v>
       </c>
       <c r="AP64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE64">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF64">
         <v>1.01</v>
@@ -16810,52 +16810,52 @@
         <v>1000</v>
       </c>
       <c r="AP65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE65">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF65">
         <v>1.01</v>
@@ -16944,13 +16944,13 @@
         <v>272</v>
       </c>
       <c r="F66">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="G66">
         <v>2.36</v>
       </c>
       <c r="H66">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I66">
         <v>4.8</v>
@@ -16959,7 +16959,7 @@
         <v>3.15</v>
       </c>
       <c r="K66">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="L66">
         <v>1.39</v>
@@ -16968,7 +16968,7 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="O66">
         <v>1.02</v>
@@ -16977,7 +16977,7 @@
         <v>1.64</v>
       </c>
       <c r="Q66">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="R66">
         <v>1.21</v>
@@ -17186,13 +17186,13 @@
         <v>273</v>
       </c>
       <c r="F67">
-        <v>1.99</v>
+        <v>2.14</v>
       </c>
       <c r="G67">
         <v>2.4</v>
       </c>
       <c r="H67">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="I67">
         <v>4.3</v>
@@ -17213,16 +17213,16 @@
         <v>1.01</v>
       </c>
       <c r="O67">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P67">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="Q67">
         <v>1.93</v>
       </c>
       <c r="R67">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="S67">
         <v>2.96</v>
@@ -17428,10 +17428,10 @@
         <v>274</v>
       </c>
       <c r="F68">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="G68">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H68">
         <v>2.34</v>
@@ -17443,7 +17443,7 @@
         <v>3.05</v>
       </c>
       <c r="K68">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="L68">
         <v>1.46</v>
@@ -17673,55 +17673,55 @@
         <v>1.27</v>
       </c>
       <c r="G69">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="H69">
         <v>11.5</v>
       </c>
       <c r="I69">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="J69">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="K69">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L69">
         <v>1.01</v>
       </c>
       <c r="M69">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N69">
-        <v>5</v>
+        <v>6.6</v>
       </c>
       <c r="O69">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="P69">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q69">
         <v>1.45</v>
       </c>
       <c r="R69">
-        <v>1.65</v>
+        <v>1.75</v>
       </c>
       <c r="S69">
-        <v>1.8</v>
+        <v>2.12</v>
       </c>
       <c r="T69">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="U69">
-        <v>1.81</v>
+        <v>1.92</v>
       </c>
       <c r="V69">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="W69">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="X69">
         <v>32</v>
@@ -17730,16 +17730,16 @@
         <v>65</v>
       </c>
       <c r="Z69">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AA69">
         <v>650</v>
       </c>
       <c r="AB69">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC69">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AD69">
         <v>50</v>
@@ -17748,13 +17748,13 @@
         <v>220</v>
       </c>
       <c r="AF69">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AG69">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AH69">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AI69">
         <v>170</v>
@@ -17763,73 +17763,73 @@
         <v>10.5</v>
       </c>
       <c r="AK69">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AL69">
         <v>36</v>
       </c>
       <c r="AM69">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AN69">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="AO69">
-        <v>210</v>
+        <v>190</v>
       </c>
       <c r="AP69">
-        <v>7.4</v>
+        <v>27</v>
       </c>
       <c r="AQ69">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="AR69">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="AS69">
-        <v>5</v>
+        <v>16.5</v>
       </c>
       <c r="AT69">
+        <v>10.5</v>
+      </c>
+      <c r="AU69">
+        <v>14</v>
+      </c>
+      <c r="AV69">
+        <v>40</v>
+      </c>
+      <c r="AW69">
+        <v>15.5</v>
+      </c>
+      <c r="AX69">
+        <v>8.4</v>
+      </c>
+      <c r="AY69">
         <v>10</v>
       </c>
-      <c r="AU69">
-        <v>12</v>
-      </c>
-      <c r="AV69">
-        <v>34</v>
-      </c>
-      <c r="AW69">
-        <v>4.9</v>
-      </c>
-      <c r="AX69">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AY69">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AZ69">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BA69">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BB69">
         <v>9.199999999999999</v>
       </c>
       <c r="BC69">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BD69">
         <v>26</v>
       </c>
       <c r="BE69">
-        <v>9.199999999999999</v>
+        <v>15</v>
       </c>
       <c r="BF69">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="BG69">
-        <v>4.9</v>
+        <v>15.5</v>
       </c>
       <c r="BH69">
         <v>1000</v>
@@ -18020,52 +18020,52 @@
         <v>1000</v>
       </c>
       <c r="AP70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE70">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF70">
         <v>1.01</v>
@@ -18163,7 +18163,7 @@
         <v>5.1</v>
       </c>
       <c r="I71">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -18178,7 +18178,7 @@
         <v>1.01</v>
       </c>
       <c r="N71">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="O71">
         <v>1.26</v>
@@ -18187,22 +18187,22 @@
         <v>2.1</v>
       </c>
       <c r="Q71">
-        <v>1.77</v>
+        <v>1.67</v>
       </c>
       <c r="R71">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S71">
-        <v>2.84</v>
+        <v>2.6</v>
       </c>
       <c r="T71">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U71">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V71">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W71">
         <v>2.28</v>
@@ -18211,7 +18211,7 @@
         <v>1000</v>
       </c>
       <c r="Y71">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z71">
         <v>1000</v>
@@ -18220,22 +18220,22 @@
         <v>1000</v>
       </c>
       <c r="AB71">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC71">
         <v>13</v>
       </c>
       <c r="AD71">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE71">
         <v>1000</v>
       </c>
       <c r="AF71">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AG71">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH71">
         <v>26</v>
@@ -18244,76 +18244,76 @@
         <v>1000</v>
       </c>
       <c r="AJ71">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK71">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AL71">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM71">
         <v>1000</v>
       </c>
       <c r="AN71">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO71">
         <v>1000</v>
       </c>
       <c r="AP71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="AQ71">
-        <v>1.13</v>
+        <v>13</v>
       </c>
       <c r="AR71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="AS71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="AT71">
-        <v>1.13</v>
+        <v>6.4</v>
       </c>
       <c r="AU71">
-        <v>1.04</v>
+        <v>1.98</v>
       </c>
       <c r="AV71">
-        <v>1.13</v>
+        <v>13.5</v>
       </c>
       <c r="AW71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="AX71">
-        <v>1.13</v>
+        <v>7.2</v>
       </c>
       <c r="AY71">
-        <v>1.13</v>
+        <v>6.6</v>
       </c>
       <c r="AZ71">
-        <v>1.08</v>
+        <v>2.14</v>
       </c>
       <c r="BA71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="BB71">
-        <v>1.13</v>
+        <v>11.5</v>
       </c>
       <c r="BC71">
-        <v>1.13</v>
+        <v>11</v>
       </c>
       <c r="BD71">
-        <v>1.13</v>
+        <v>2.22</v>
       </c>
       <c r="BE71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="BF71">
-        <v>1.13</v>
+        <v>6.2</v>
       </c>
       <c r="BG71">
-        <v>1.13</v>
+        <v>2.34</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -18402,28 +18402,28 @@
         <v>3.35</v>
       </c>
       <c r="H72">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I72">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="J72">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K72">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="L72">
         <v>1.01</v>
       </c>
       <c r="M72">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N72">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O72">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="P72">
         <v>1.92</v>
@@ -18444,19 +18444,19 @@
         <v>2.18</v>
       </c>
       <c r="V72">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="W72">
         <v>1.42</v>
       </c>
       <c r="X72">
-        <v>14</v>
+        <v>970</v>
       </c>
       <c r="Y72">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Z72">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="AA72">
         <v>36</v>
@@ -18471,7 +18471,7 @@
         <v>12</v>
       </c>
       <c r="AE72">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF72">
         <v>23</v>
@@ -18480,7 +18480,7 @@
         <v>14</v>
       </c>
       <c r="AH72">
-        <v>16.5</v>
+        <v>970</v>
       </c>
       <c r="AI72">
         <v>40</v>
@@ -18489,10 +18489,10 @@
         <v>55</v>
       </c>
       <c r="AK72">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AL72">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM72">
         <v>100</v>
@@ -18513,7 +18513,7 @@
         <v>14.5</v>
       </c>
       <c r="AS72">
-        <v>9.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT72">
         <v>11</v>
@@ -18525,10 +18525,10 @@
         <v>10</v>
       </c>
       <c r="AW72">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AX72">
-        <v>8.4</v>
+        <v>17.5</v>
       </c>
       <c r="AY72">
         <v>12</v>
@@ -18537,22 +18537,22 @@
         <v>14</v>
       </c>
       <c r="BA72">
+        <v>9</v>
+      </c>
+      <c r="BB72">
+        <v>9.6</v>
+      </c>
+      <c r="BC72">
+        <v>27</v>
+      </c>
+      <c r="BD72">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE72">
         <v>10</v>
       </c>
-      <c r="BB72">
-        <v>10.5</v>
-      </c>
-      <c r="BC72">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BD72">
-        <v>10</v>
-      </c>
-      <c r="BE72">
-        <v>11.5</v>
-      </c>
       <c r="BF72">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BG72">
         <v>16</v>
@@ -18561,61 +18561,61 @@
         <v>1000</v>
       </c>
       <c r="BI72">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="BJ72">
         <v>12.5</v>
       </c>
       <c r="BK72">
-        <v>6.4</v>
+        <v>1.64</v>
       </c>
       <c r="BL72">
         <v>1000</v>
       </c>
       <c r="BM72">
-        <v>22</v>
+        <v>1.88</v>
       </c>
       <c r="BN72">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BO72">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BP72">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BQ72">
-        <v>16</v>
+        <v>1.79</v>
       </c>
       <c r="BR72">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BS72">
-        <v>22</v>
+        <v>1.82</v>
       </c>
       <c r="BT72">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BU72">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="BV72">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BW72">
-        <v>12</v>
+        <v>1.76</v>
       </c>
       <c r="BX72">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BY72">
-        <v>20</v>
+        <v>1.81</v>
       </c>
       <c r="BZ72">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="CA72">
-        <v>17.5</v>
+        <v>1.8</v>
       </c>
       <c r="CB72" t="s">
         <v>282</v>
@@ -18638,7 +18638,7 @@
         <v>279</v>
       </c>
       <c r="F73">
-        <v>1.13</v>
+        <v>1.15</v>
       </c>
       <c r="G73">
         <v>110</v>
@@ -18647,10 +18647,10 @@
         <v>1.11</v>
       </c>
       <c r="I73">
-        <v>530</v>
+        <v>110</v>
       </c>
       <c r="J73">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="K73">
         <v>950</v>
@@ -18671,7 +18671,7 @@
         <v>1.25</v>
       </c>
       <c r="Q73">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="R73">
         <v>1.24</v>
@@ -18746,52 +18746,52 @@
         <v>1000</v>
       </c>
       <c r="AP73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE73">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF73">
         <v>1.01</v>
@@ -18880,19 +18880,19 @@
         <v>280</v>
       </c>
       <c r="F74">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G74">
         <v>110</v>
       </c>
       <c r="H74">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="I74">
         <v>110</v>
       </c>
       <c r="J74">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="K74">
         <v>950</v>
@@ -18913,13 +18913,13 @@
         <v>1.25</v>
       </c>
       <c r="Q74">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="R74">
         <v>1.24</v>
       </c>
       <c r="S74">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T74">
         <v>1.01</v>
@@ -18928,10 +18928,10 @@
         <v>1.01</v>
       </c>
       <c r="V74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W74">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X74">
         <v>1000</v>
@@ -18988,52 +18988,52 @@
         <v>1000</v>
       </c>
       <c r="AP74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AQ74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AR74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AS74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AT74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AV74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AW74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AY74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AZ74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BA74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BB74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BC74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BE74">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BF74">
         <v>1.01</v>
@@ -19122,220 +19122,220 @@
         <v>281</v>
       </c>
       <c r="F75">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="G75">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="H75">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="L75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N75">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O75">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="P75">
-        <v>1.24</v>
+        <v>1.8</v>
       </c>
       <c r="Q75">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R75">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S75">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="T75">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="U75">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V75">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="W75">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="X75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX75">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY75">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ75">
         <v>0</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -862,7 +862,7 @@
     <t>Cusco FC</t>
   </si>
   <si>
-    <t>2026-08-05 19:02:54</t>
+    <t>2026-08-05 21:13:17</t>
   </si>
 </sst>
 </file>
@@ -1465,7 +1465,7 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
         <v>3.55</v>
@@ -1501,10 +1501,10 @@
         <v>2.08</v>
       </c>
       <c r="U2">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
         <v>2.28</v>
@@ -1525,7 +1525,7 @@
         <v>7.2</v>
       </c>
       <c r="AC2">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD2">
         <v>32</v>
@@ -1567,7 +1567,7 @@
         <v>3.9</v>
       </c>
       <c r="AQ2">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AR2">
         <v>4.9</v>
@@ -1585,7 +1585,7 @@
         <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AX2">
         <v>6.8</v>
@@ -1594,16 +1594,16 @@
         <v>7.6</v>
       </c>
       <c r="AZ2">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BA2">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB2">
         <v>4.2</v>
       </c>
       <c r="BC2">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BD2">
         <v>4.9</v>
@@ -1707,7 +1707,7 @@
         <v>2.02</v>
       </c>
       <c r="I3">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J3">
         <v>3.35</v>
@@ -1731,25 +1731,25 @@
         <v>1.81</v>
       </c>
       <c r="Q3">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="R3">
         <v>1.3</v>
       </c>
       <c r="S3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="T3">
         <v>1.87</v>
       </c>
       <c r="U3">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="V3">
         <v>1.85</v>
       </c>
       <c r="W3">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="X3">
         <v>15</v>
@@ -1943,7 +1943,7 @@
         <v>2.44</v>
       </c>
       <c r="G4">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H4">
         <v>3.25</v>
@@ -1952,7 +1952,7 @@
         <v>3.4</v>
       </c>
       <c r="J4">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1964,7 +1964,7 @@
         <v>1.08</v>
       </c>
       <c r="N4">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O4">
         <v>1.35</v>
@@ -1976,7 +1976,7 @@
         <v>2.1</v>
       </c>
       <c r="R4">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S4">
         <v>3.65</v>
@@ -1994,7 +1994,7 @@
         <v>1.64</v>
       </c>
       <c r="X4">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Y4">
         <v>12.5</v>
@@ -2009,7 +2009,7 @@
         <v>10</v>
       </c>
       <c r="AC4">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD4">
         <v>14.5</v>
@@ -2042,7 +2042,7 @@
         <v>120</v>
       </c>
       <c r="AN4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="AO4">
         <v>38</v>
@@ -2057,7 +2057,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -2078,28 +2078,28 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="BA4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BB4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BC4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BD4">
         <v>10.5</v>
       </c>
       <c r="BE4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
@@ -2141,7 +2141,7 @@
         <v>6.4</v>
       </c>
       <c r="BU4">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BV4">
         <v>26</v>
@@ -2197,10 +2197,10 @@
         <v>3.6</v>
       </c>
       <c r="K5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2212,7 +2212,7 @@
         <v>1.39</v>
       </c>
       <c r="P5">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q5">
         <v>2.14</v>
@@ -2224,10 +2224,10 @@
         <v>3.9</v>
       </c>
       <c r="T5">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="U5">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="V5">
         <v>1.21</v>
@@ -2245,7 +2245,7 @@
         <v>50</v>
       </c>
       <c r="AA5">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB5">
         <v>9.199999999999999</v>
@@ -2344,7 +2344,7 @@
         <v>4.2</v>
       </c>
       <c r="BH5">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
         <v>2.6</v>
@@ -2353,55 +2353,55 @@
         <v>11</v>
       </c>
       <c r="BK5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BL5">
         <v>1000</v>
       </c>
       <c r="BM5">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="BN5">
         <v>4.4</v>
       </c>
       <c r="BO5">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BP5">
         <v>13.5</v>
       </c>
       <c r="BQ5">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BR5">
         <v>32</v>
       </c>
       <c r="BS5">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BT5">
         <v>8.6</v>
       </c>
       <c r="BU5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BV5">
         <v>1000</v>
       </c>
       <c r="BW5">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX5">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BY5">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BZ5">
         <v>29</v>
       </c>
       <c r="CA5">
-        <v>9.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="CB5" t="s">
         <v>282</v>
@@ -2433,7 +2433,7 @@
         <v>1.91</v>
       </c>
       <c r="I6">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="J6">
         <v>3.65</v>
@@ -2460,7 +2460,7 @@
         <v>1.92</v>
       </c>
       <c r="R6">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="S6">
         <v>3.35</v>
@@ -2472,7 +2472,7 @@
         <v>2.04</v>
       </c>
       <c r="V6">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -2526,7 +2526,7 @@
         <v>120</v>
       </c>
       <c r="AN6">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AO6">
         <v>15</v>
@@ -2574,10 +2574,10 @@
         <v>4.4</v>
       </c>
       <c r="BD6">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BE6">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="BF6">
         <v>4.4</v>
@@ -2613,13 +2613,13 @@
         <v>44</v>
       </c>
       <c r="BQ6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BR6">
         <v>55</v>
       </c>
       <c r="BS6">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BT6">
         <v>5.6</v>
@@ -2628,7 +2628,7 @@
         <v>3.65</v>
       </c>
       <c r="BV6">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BW6">
         <v>3.7</v>
@@ -2675,7 +2675,7 @@
         <v>1.88</v>
       </c>
       <c r="I7">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="J7">
         <v>3.95</v>
@@ -2705,7 +2705,7 @@
         <v>1.45</v>
       </c>
       <c r="S7">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T7">
         <v>1.71</v>
@@ -2768,7 +2768,7 @@
         <v>95</v>
       </c>
       <c r="AN7">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AO7">
         <v>12.5</v>
@@ -2777,22 +2777,22 @@
         <v>13.5</v>
       </c>
       <c r="AQ7">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR7">
         <v>11</v>
       </c>
       <c r="AS7">
-        <v>4.3</v>
+        <v>16.5</v>
       </c>
       <c r="AT7">
         <v>15</v>
       </c>
       <c r="AU7">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV7">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW7">
         <v>14</v>
@@ -2807,7 +2807,7 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="BB7">
         <v>5</v>
@@ -2819,7 +2819,7 @@
         <v>4.8</v>
       </c>
       <c r="BE7">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BF7">
         <v>4.8</v>
@@ -2831,19 +2831,19 @@
         <v>3.8</v>
       </c>
       <c r="BI7">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="BJ7">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="BK7">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="BL7">
         <v>1000</v>
       </c>
       <c r="BM7">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BN7">
         <v>8</v>
@@ -2861,7 +2861,7 @@
         <v>1000</v>
       </c>
       <c r="BS7">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BT7">
         <v>4.8</v>
@@ -2873,19 +2873,19 @@
         <v>13</v>
       </c>
       <c r="BW7">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BX7">
         <v>1000</v>
       </c>
       <c r="BY7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ7">
         <v>1000</v>
       </c>
       <c r="CA7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="CB7" t="s">
         <v>282</v>
@@ -2908,7 +2908,7 @@
         <v>214</v>
       </c>
       <c r="F8">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="G8">
         <v>3.35</v>
@@ -2917,52 +2917,52 @@
         <v>2.3</v>
       </c>
       <c r="I8">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="J8">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K8">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N8">
         <v>4</v>
       </c>
       <c r="O8">
-        <v>1.27</v>
+        <v>1.24</v>
       </c>
       <c r="P8">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="Q8">
         <v>1.78</v>
       </c>
       <c r="R8">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S8">
-        <v>2.96</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
+        <v>1.65</v>
+      </c>
+      <c r="U8">
+        <v>2.26</v>
+      </c>
+      <c r="V8">
         <v>1.64</v>
-      </c>
-      <c r="U8">
-        <v>2.24</v>
-      </c>
-      <c r="V8">
-        <v>1.63</v>
       </c>
       <c r="W8">
         <v>1.42</v>
       </c>
       <c r="X8">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="Y8">
         <v>14</v>
@@ -2974,7 +2974,7 @@
         <v>38</v>
       </c>
       <c r="AB8">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AC8">
         <v>9.800000000000001</v>
@@ -2986,7 +2986,7 @@
         <v>29</v>
       </c>
       <c r="AF8">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG8">
         <v>16</v>
@@ -2995,7 +2995,7 @@
         <v>19</v>
       </c>
       <c r="AI8">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ8">
         <v>60</v>
@@ -3013,7 +3013,7 @@
         <v>32</v>
       </c>
       <c r="AO8">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AP8">
         <v>13</v>
@@ -3037,7 +3037,7 @@
         <v>9</v>
       </c>
       <c r="AW8">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AX8">
         <v>17</v>
@@ -3049,43 +3049,43 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BB8">
         <v>4.6</v>
       </c>
       <c r="BC8">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="BD8">
         <v>4.5</v>
       </c>
       <c r="BE8">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="BF8">
         <v>20</v>
       </c>
       <c r="BG8">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BH8">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BI8">
         <v>3</v>
       </c>
       <c r="BJ8">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BK8">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="BL8">
         <v>1000</v>
       </c>
       <c r="BM8">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BN8">
         <v>6.6</v>
@@ -3097,37 +3097,37 @@
         <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BR8">
         <v>1000</v>
       </c>
       <c r="BS8">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BT8">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="BU8">
         <v>4.3</v>
       </c>
       <c r="BV8">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BW8">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="BX8">
         <v>1000</v>
       </c>
       <c r="BY8">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BZ8">
         <v>1000</v>
       </c>
       <c r="CA8">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB8" t="s">
         <v>282</v>
@@ -3150,19 +3150,19 @@
         <v>215</v>
       </c>
       <c r="F9">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="G9">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H9">
         <v>6</v>
       </c>
       <c r="I9">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J9">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="K9">
         <v>4.9</v>
@@ -3183,7 +3183,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.68</v>
+        <v>1.76</v>
       </c>
       <c r="R9">
         <v>1.41</v>
@@ -3201,7 +3201,7 @@
         <v>1.15</v>
       </c>
       <c r="W9">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="X9">
         <v>21</v>
@@ -3252,7 +3252,7 @@
         <v>140</v>
       </c>
       <c r="AN9">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AO9">
         <v>130</v>
@@ -3261,7 +3261,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ9">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR9">
         <v>4.8</v>
@@ -3279,7 +3279,7 @@
         <v>19</v>
       </c>
       <c r="AW9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AX9">
         <v>7.6</v>
@@ -3291,7 +3291,7 @@
         <v>16.5</v>
       </c>
       <c r="BA9">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BB9">
         <v>11.5</v>
@@ -3315,7 +3315,7 @@
         <v>3.9</v>
       </c>
       <c r="BI9">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="BJ9">
         <v>11</v>
@@ -3398,7 +3398,7 @@
         <v>1.36</v>
       </c>
       <c r="H10">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="I10">
         <v>14.5</v>
@@ -3407,7 +3407,7 @@
         <v>5.5</v>
       </c>
       <c r="K10">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L10">
         <v>1.27</v>
@@ -3416,7 +3416,7 @@
         <v>1.05</v>
       </c>
       <c r="N10">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O10">
         <v>1.26</v>
@@ -3431,10 +3431,10 @@
         <v>1.44</v>
       </c>
       <c r="S10">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T10">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="U10">
         <v>1.8</v>
@@ -3443,13 +3443,13 @@
         <v>1.07</v>
       </c>
       <c r="W10">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="X10">
         <v>24</v>
       </c>
       <c r="Y10">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z10">
         <v>150</v>
@@ -3494,7 +3494,7 @@
         <v>250</v>
       </c>
       <c r="AN10">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AO10">
         <v>440</v>
@@ -3503,25 +3503,25 @@
         <v>15</v>
       </c>
       <c r="AQ10">
-        <v>6.8</v>
+        <v>28</v>
       </c>
       <c r="AR10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS10">
-        <v>8.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AT10">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AU10">
         <v>9.800000000000001</v>
       </c>
       <c r="AV10">
-        <v>7.2</v>
+        <v>32</v>
       </c>
       <c r="AW10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AX10">
         <v>5.8</v>
@@ -3530,28 +3530,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AZ10">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BA10">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC10">
         <v>11</v>
       </c>
       <c r="BD10">
-        <v>7.2</v>
+        <v>30</v>
       </c>
       <c r="BE10">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF10">
         <v>4.9</v>
       </c>
       <c r="BG10">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BH10">
         <v>4.7</v>
@@ -3652,13 +3652,13 @@
         <v>6.4</v>
       </c>
       <c r="L11">
-        <v>1.2</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="O11">
         <v>1.12</v>
@@ -3736,22 +3736,22 @@
         <v>85</v>
       </c>
       <c r="AN11">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="AO11">
         <v>75</v>
       </c>
       <c r="AP11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AQ11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AR11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AS11">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AT11">
         <v>13</v>
@@ -3760,10 +3760,10 @@
         <v>12</v>
       </c>
       <c r="AV11">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="AW11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX11">
         <v>10.5</v>
@@ -3775,7 +3775,7 @@
         <v>17.5</v>
       </c>
       <c r="BA11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BB11">
         <v>11.5</v>
@@ -3787,16 +3787,16 @@
         <v>21</v>
       </c>
       <c r="BE11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BF11">
         <v>3.4</v>
       </c>
       <c r="BG11">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BH11">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BI11">
         <v>4.2</v>
@@ -3805,13 +3805,13 @@
         <v>11.5</v>
       </c>
       <c r="BK11">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="BL11">
         <v>1000</v>
       </c>
       <c r="BM11">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="BN11">
         <v>5.1</v>
@@ -3823,37 +3823,37 @@
         <v>9.4</v>
       </c>
       <c r="BQ11">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="BR11">
         <v>21</v>
       </c>
       <c r="BS11">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BT11">
         <v>13.5</v>
       </c>
       <c r="BU11">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="BV11">
         <v>60</v>
       </c>
       <c r="BW11">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="BX11">
         <v>55</v>
       </c>
       <c r="BY11">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="BZ11">
         <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="CB11" t="s">
         <v>282</v>
@@ -3891,7 +3891,7 @@
         <v>3.95</v>
       </c>
       <c r="K12">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L12">
         <v>1.28</v>
@@ -3912,10 +3912,10 @@
         <v>1.75</v>
       </c>
       <c r="R12">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="S12">
-        <v>2.88</v>
+        <v>2.54</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -4118,7 +4118,7 @@
         <v>219</v>
       </c>
       <c r="F13">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="G13">
         <v>3.1</v>
@@ -4127,7 +4127,7 @@
         <v>2.44</v>
       </c>
       <c r="I13">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
       <c r="J13">
         <v>3.6</v>
@@ -4154,7 +4154,7 @@
         <v>1.69</v>
       </c>
       <c r="R13">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="S13">
         <v>2.44</v>
@@ -4166,7 +4166,7 @@
         <v>2.16</v>
       </c>
       <c r="V13">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="W13">
         <v>1.47</v>
@@ -4483,7 +4483,7 @@
         <v>6.4</v>
       </c>
       <c r="AU14">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AV14">
         <v>13</v>
@@ -4844,7 +4844,7 @@
         <v>222</v>
       </c>
       <c r="F16">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="G16">
         <v>3.1</v>
@@ -4853,10 +4853,10 @@
         <v>2.4</v>
       </c>
       <c r="I16">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="J16">
-        <v>3.3</v>
+        <v>3.65</v>
       </c>
       <c r="K16">
         <v>4.5</v>
@@ -4892,7 +4892,7 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="W16">
         <v>1.47</v>
@@ -5086,22 +5086,22 @@
         <v>223</v>
       </c>
       <c r="F17">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G17">
         <v>1.78</v>
       </c>
       <c r="H17">
-        <v>4.8</v>
+        <v>5.2</v>
       </c>
       <c r="I17">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="J17">
         <v>3.8</v>
       </c>
       <c r="K17">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -5119,10 +5119,10 @@
         <v>1.9</v>
       </c>
       <c r="Q17">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="R17">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="S17">
         <v>2.74</v>
@@ -5134,7 +5134,7 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W17">
         <v>2.28</v>
@@ -5346,10 +5346,10 @@
         <v>4</v>
       </c>
       <c r="L18">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N18">
         <v>4.4</v>
@@ -5373,7 +5373,7 @@
         <v>1.43</v>
       </c>
       <c r="U18">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="V18">
         <v>1.01</v>
@@ -5493,55 +5493,55 @@
         <v>1000</v>
       </c>
       <c r="BI18">
-        <v>2.2</v>
+        <v>1.01</v>
       </c>
       <c r="BJ18">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK18">
-        <v>1.84</v>
+        <v>1.01</v>
       </c>
       <c r="BL18">
         <v>1000</v>
       </c>
       <c r="BM18">
-        <v>2.16</v>
+        <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="BO18">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BP18">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="BQ18">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="BR18">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BS18">
-        <v>2.06</v>
+        <v>1.01</v>
       </c>
       <c r="BT18">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="BU18">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV18">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BW18">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="BX18">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BY18">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="BZ18">
         <v>0</v>
@@ -5612,10 +5612,10 @@
         <v>3.25</v>
       </c>
       <c r="T19">
-        <v>1.89</v>
+        <v>1.11</v>
       </c>
       <c r="U19">
-        <v>1.83</v>
+        <v>1.11</v>
       </c>
       <c r="V19">
         <v>1.17</v>
@@ -5854,7 +5854,7 @@
         <v>1.26</v>
       </c>
       <c r="T20">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U20">
         <v>1.96</v>
@@ -5974,64 +5974,64 @@
         <v>3.55</v>
       </c>
       <c r="BH20">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>2.38</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
         <v>1000</v>
       </c>
       <c r="BM20">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>2.66</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>4.6</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
         <v>282</v>
@@ -6063,7 +6063,7 @@
         <v>5.3</v>
       </c>
       <c r="I21">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="J21">
         <v>4.2</v>
@@ -6093,7 +6093,7 @@
         <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="T21">
         <v>1.74</v>
@@ -6102,7 +6102,7 @@
         <v>2.1</v>
       </c>
       <c r="V21">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W21">
         <v>2.38</v>
@@ -6332,16 +6332,16 @@
         <v>1.71</v>
       </c>
       <c r="R22">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S22">
         <v>2.72</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V22">
         <v>1.28</v>
@@ -6562,7 +6562,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="O23">
         <v>1.16</v>
@@ -6580,10 +6580,10 @@
         <v>2.14</v>
       </c>
       <c r="T23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U23">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V23">
         <v>1.33</v>
@@ -6795,7 +6795,7 @@
         <v>4.8</v>
       </c>
       <c r="K24">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6813,10 +6813,10 @@
         <v>2.56</v>
       </c>
       <c r="Q24">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="R24">
-        <v>1.51</v>
+        <v>1.61</v>
       </c>
       <c r="S24">
         <v>2.14</v>
@@ -7049,7 +7049,7 @@
         <v>3.05</v>
       </c>
       <c r="O25">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P25">
         <v>2.06</v>
@@ -7058,7 +7058,7 @@
         <v>1.55</v>
       </c>
       <c r="R25">
-        <v>1.49</v>
+        <v>1.37</v>
       </c>
       <c r="S25">
         <v>2.4</v>
@@ -7518,7 +7518,7 @@
         <v>110</v>
       </c>
       <c r="J27">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7530,7 +7530,7 @@
         <v>1.01</v>
       </c>
       <c r="N27">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O27">
         <v>1.23</v>
@@ -7542,7 +7542,7 @@
         <v>1.23</v>
       </c>
       <c r="R27">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S27">
         <v>1.23</v>
@@ -7554,10 +7554,10 @@
         <v>1.01</v>
       </c>
       <c r="V27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W27">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7772,10 +7772,10 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28">
         <v>2.18</v>
@@ -7805,7 +7805,7 @@
         <v>19</v>
       </c>
       <c r="Y28">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="Z28">
         <v>34</v>
@@ -7814,25 +7814,25 @@
         <v>80</v>
       </c>
       <c r="AB28">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC28">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD28">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE28">
         <v>48</v>
       </c>
       <c r="AF28">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AG28">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH28">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI28">
         <v>55</v>
@@ -7841,7 +7841,7 @@
         <v>32</v>
       </c>
       <c r="AK28">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL28">
         <v>38</v>
@@ -7850,7 +7850,7 @@
         <v>75</v>
       </c>
       <c r="AN28">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AO28">
         <v>38</v>
@@ -7862,10 +7862,10 @@
         <v>14</v>
       </c>
       <c r="AR28">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AS28">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="AT28">
         <v>10</v>
@@ -7877,7 +7877,7 @@
         <v>13</v>
       </c>
       <c r="AW28">
-        <v>4.1</v>
+        <v>32</v>
       </c>
       <c r="AX28">
         <v>13</v>
@@ -7889,25 +7889,25 @@
         <v>14</v>
       </c>
       <c r="BA28">
-        <v>4.2</v>
+        <v>36</v>
       </c>
       <c r="BB28">
-        <v>3.95</v>
+        <v>4.7</v>
       </c>
       <c r="BC28">
         <v>18.5</v>
       </c>
       <c r="BD28">
-        <v>4</v>
+        <v>4.8</v>
       </c>
       <c r="BE28">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BF28">
         <v>9.6</v>
       </c>
       <c r="BG28">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8035,7 +8035,7 @@
         <v>1.61</v>
       </c>
       <c r="U29">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="V29">
         <v>1.71</v>
@@ -8152,64 +8152,64 @@
         <v>10</v>
       </c>
       <c r="BH29">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BI29">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="BJ29">
         <v>12.5</v>
       </c>
       <c r="BK29">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="BL29">
         <v>1000</v>
       </c>
       <c r="BM29">
-        <v>2.96</v>
+        <v>2.9</v>
       </c>
       <c r="BN29">
         <v>9.6</v>
       </c>
       <c r="BO29">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="BP29">
         <v>34</v>
       </c>
       <c r="BQ29">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="BR29">
         <v>46</v>
       </c>
       <c r="BS29">
-        <v>2.78</v>
+        <v>2.74</v>
       </c>
       <c r="BT29">
         <v>7.6</v>
       </c>
       <c r="BU29">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BV29">
         <v>23</v>
       </c>
       <c r="BW29">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
       <c r="BX29">
         <v>38</v>
       </c>
       <c r="BY29">
-        <v>2.76</v>
+        <v>2.7</v>
       </c>
       <c r="BZ29">
         <v>29</v>
       </c>
       <c r="CA29">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="CB29" t="s">
         <v>282</v>
@@ -8235,7 +8235,7 @@
         <v>1.5</v>
       </c>
       <c r="G30">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="H30">
         <v>3.85</v>
@@ -8283,7 +8283,7 @@
         <v>1.12</v>
       </c>
       <c r="W30">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="X30">
         <v>1000</v>
@@ -8519,7 +8519,7 @@
         <v>1.64</v>
       </c>
       <c r="U31">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V31">
         <v>1.47</v>
@@ -8988,7 +8988,7 @@
         <v>1.4</v>
       </c>
       <c r="P33">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="Q33">
         <v>2.2</v>
@@ -9224,7 +9224,7 @@
         <v>1.01</v>
       </c>
       <c r="N34">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="O34">
         <v>1.16</v>
@@ -9239,7 +9239,7 @@
         <v>1.25</v>
       </c>
       <c r="S34">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T34">
         <v>1.01</v>
@@ -9463,7 +9463,7 @@
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="N35">
         <v>4.8</v>
@@ -9484,7 +9484,7 @@
         <v>2.16</v>
       </c>
       <c r="T35">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U35">
         <v>1.01</v>
@@ -9496,7 +9496,7 @@
         <v>1.33</v>
       </c>
       <c r="X35">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="Y35">
         <v>19.5</v>
@@ -9550,7 +9550,7 @@
         <v>1000</v>
       </c>
       <c r="AP35">
-        <v>1.03</v>
+        <v>19</v>
       </c>
       <c r="AQ35">
         <v>10.5</v>
@@ -9684,16 +9684,16 @@
         <v>242</v>
       </c>
       <c r="F36">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="G36">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H36">
         <v>3.55</v>
       </c>
       <c r="I36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J36">
         <v>4</v>
@@ -9705,7 +9705,7 @@
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N36">
         <v>2.42</v>
@@ -9717,7 +9717,7 @@
         <v>2.42</v>
       </c>
       <c r="Q36">
-        <v>1.57</v>
+        <v>1.49</v>
       </c>
       <c r="R36">
         <v>1.5</v>
@@ -9726,16 +9726,16 @@
         <v>2.16</v>
       </c>
       <c r="T36">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U36">
         <v>1.01</v>
       </c>
       <c r="V36">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W36">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
       <c r="X36">
         <v>32</v>
@@ -9744,7 +9744,7 @@
         <v>28</v>
       </c>
       <c r="Z36">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA36">
         <v>1000</v>
@@ -9774,7 +9774,7 @@
         <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK36">
         <v>26</v>
@@ -9792,7 +9792,7 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>1.03</v>
+        <v>15</v>
       </c>
       <c r="AQ36">
         <v>12.5</v>
@@ -9828,13 +9828,13 @@
         <v>1.03</v>
       </c>
       <c r="BB36">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BC36">
         <v>12</v>
       </c>
       <c r="BD36">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BE36">
         <v>1.03</v>
@@ -9929,10 +9929,10 @@
         <v>2.54</v>
       </c>
       <c r="G37">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="H37">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="I37">
         <v>2.88</v>
@@ -9950,16 +9950,16 @@
         <v>1.04</v>
       </c>
       <c r="N37">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="O37">
         <v>1.2</v>
       </c>
       <c r="P37">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R37">
         <v>1.53</v>
@@ -10028,10 +10028,10 @@
         <v>70</v>
       </c>
       <c r="AN37">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AO37">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AP37">
         <v>18.5</v>
@@ -10055,7 +10055,7 @@
         <v>10.5</v>
       </c>
       <c r="AW37">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="AX37">
         <v>17.5</v>
@@ -10067,10 +10067,10 @@
         <v>12.5</v>
       </c>
       <c r="BA37">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BB37">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BC37">
         <v>21</v>
@@ -10079,7 +10079,7 @@
         <v>26</v>
       </c>
       <c r="BE37">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="BF37">
         <v>11.5</v>
@@ -10180,7 +10180,7 @@
         <v>3.2</v>
       </c>
       <c r="J38">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K38">
         <v>3.55</v>
@@ -10204,10 +10204,10 @@
         <v>2.06</v>
       </c>
       <c r="R38">
-        <v>1.26</v>
+        <v>1.18</v>
       </c>
       <c r="S38">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="T38">
         <v>1.66</v>
@@ -10652,10 +10652,10 @@
         <v>246</v>
       </c>
       <c r="F40">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G40">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="H40">
         <v>2.68</v>
@@ -10685,19 +10685,19 @@
         <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R40">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S40">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="T40">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="U40">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="V40">
         <v>1.47</v>
@@ -11160,16 +11160,16 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="O42">
         <v>1.19</v>
       </c>
       <c r="P42">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q42">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="R42">
         <v>1.51</v>
@@ -11178,10 +11178,10 @@
         <v>2.46</v>
       </c>
       <c r="T42">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="U42">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="V42">
         <v>1.67</v>
@@ -11390,7 +11390,7 @@
         <v>3.15</v>
       </c>
       <c r="J43">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="K43">
         <v>4.3</v>
@@ -11399,16 +11399,16 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N43">
         <v>4.2</v>
       </c>
       <c r="O43">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P43">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="Q43">
         <v>1.56</v>
@@ -11420,7 +11420,7 @@
         <v>2.38</v>
       </c>
       <c r="T43">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U43">
         <v>1.01</v>
@@ -11653,7 +11653,7 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="R44">
         <v>1.71</v>
@@ -11662,10 +11662,10 @@
         <v>2.08</v>
       </c>
       <c r="T44">
-        <v>1.54</v>
+        <v>1.11</v>
       </c>
       <c r="U44">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V44">
         <v>1.14</v>
@@ -11862,7 +11862,7 @@
         <v>251</v>
       </c>
       <c r="F45">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="G45">
         <v>1.4</v>
@@ -11904,10 +11904,10 @@
         <v>2.66</v>
       </c>
       <c r="T45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U45">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V45">
         <v>1.08</v>
@@ -12134,7 +12134,7 @@
         <v>1.13</v>
       </c>
       <c r="P46">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="Q46">
         <v>1.49</v>
@@ -12146,7 +12146,7 @@
         <v>2.2</v>
       </c>
       <c r="T46">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="U46">
         <v>1.01</v>
@@ -12600,7 +12600,7 @@
         <v>1.58</v>
       </c>
       <c r="J48">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K48">
         <v>5.2</v>
@@ -12639,7 +12639,7 @@
         <v>2.72</v>
       </c>
       <c r="W48">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X48">
         <v>23</v>
@@ -12702,7 +12702,7 @@
         <v>6.8</v>
       </c>
       <c r="AR48">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AS48">
         <v>10</v>
@@ -12711,40 +12711,40 @@
         <v>18.5</v>
       </c>
       <c r="AU48">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV48">
         <v>7.4</v>
       </c>
       <c r="AW48">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX48">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AY48">
-        <v>20</v>
+        <v>3.95</v>
       </c>
       <c r="AZ48">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA48">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BB48">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BC48">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BD48">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE48">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BF48">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BG48">
         <v>5.4</v>
@@ -12878,7 +12878,7 @@
         <v>2.08</v>
       </c>
       <c r="V49">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W49">
         <v>1.61</v>
@@ -12902,7 +12902,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AD49">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="AE49">
         <v>44</v>
@@ -12914,7 +12914,7 @@
         <v>13.5</v>
       </c>
       <c r="AH49">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AI49">
         <v>60</v>
@@ -13075,7 +13075,7 @@
         <v>2.16</v>
       </c>
       <c r="G50">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H50">
         <v>3.2</v>
@@ -13087,7 +13087,7 @@
         <v>3.55</v>
       </c>
       <c r="K50">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="L50">
         <v>1.27</v>
@@ -13096,22 +13096,22 @@
         <v>1.04</v>
       </c>
       <c r="N50">
-        <v>3.6</v>
+        <v>2.18</v>
       </c>
       <c r="O50">
         <v>1.24</v>
       </c>
       <c r="P50">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q50">
         <v>1.77</v>
       </c>
       <c r="R50">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S50">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="T50">
         <v>1.53</v>
@@ -13168,7 +13168,7 @@
         <v>34</v>
       </c>
       <c r="AL50">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AM50">
         <v>1000</v>
@@ -13317,13 +13317,13 @@
         <v>2.3</v>
       </c>
       <c r="G51">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="H51">
         <v>2.98</v>
       </c>
       <c r="I51">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J51">
         <v>3.65</v>
@@ -13362,13 +13362,13 @@
         <v>2.52</v>
       </c>
       <c r="V51">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.75</v>
+        <v>1.68</v>
       </c>
       <c r="X51">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="Y51">
         <v>17</v>
@@ -13398,7 +13398,7 @@
         <v>12</v>
       </c>
       <c r="AH51">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AI51">
         <v>38</v>
@@ -13822,7 +13822,7 @@
         <v>1.05</v>
       </c>
       <c r="N53">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="O53">
         <v>1.29</v>
@@ -14040,7 +14040,7 @@
         <v>260</v>
       </c>
       <c r="F54">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="G54">
         <v>2.2</v>
@@ -14282,7 +14282,7 @@
         <v>261</v>
       </c>
       <c r="F55">
-        <v>2.92</v>
+        <v>2.74</v>
       </c>
       <c r="G55">
         <v>4.1</v>
@@ -14291,13 +14291,13 @@
         <v>2.06</v>
       </c>
       <c r="I55">
-        <v>2.82</v>
+        <v>2.6</v>
       </c>
       <c r="J55">
         <v>2.96</v>
       </c>
       <c r="K55">
-        <v>5.8</v>
+        <v>6.6</v>
       </c>
       <c r="L55">
         <v>1.31</v>
@@ -14306,10 +14306,10 @@
         <v>1.01</v>
       </c>
       <c r="N55">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="O55">
-        <v>1.18</v>
+        <v>1.01</v>
       </c>
       <c r="P55">
         <v>1.78</v>
@@ -14330,7 +14330,7 @@
         <v>1.01</v>
       </c>
       <c r="V55">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="W55">
         <v>1.32</v>
@@ -14766,7 +14766,7 @@
         <v>263</v>
       </c>
       <c r="F57">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
       <c r="G57">
         <v>10.5</v>
@@ -14775,10 +14775,10 @@
         <v>1.42</v>
       </c>
       <c r="I57">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="J57">
-        <v>4.6</v>
+        <v>3.75</v>
       </c>
       <c r="K57">
         <v>5.7</v>
@@ -14808,10 +14808,10 @@
         <v>2.46</v>
       </c>
       <c r="T57">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U57">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V57">
         <v>2.78</v>
@@ -15274,13 +15274,13 @@
         <v>1.01</v>
       </c>
       <c r="N59">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="O59">
         <v>1.01</v>
       </c>
       <c r="P59">
-        <v>1.24</v>
+        <v>1.26</v>
       </c>
       <c r="Q59">
         <v>1.27</v>
@@ -15492,7 +15492,7 @@
         <v>266</v>
       </c>
       <c r="F60">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="G60">
         <v>1.52</v>
@@ -15534,13 +15534,13 @@
         <v>2.78</v>
       </c>
       <c r="T60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="U60">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V60">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="W60">
         <v>2.92</v>
@@ -15758,7 +15758,7 @@
         <v>1.01</v>
       </c>
       <c r="N61">
-        <v>2.76</v>
+        <v>2.22</v>
       </c>
       <c r="O61">
         <v>1.23</v>
@@ -15773,7 +15773,7 @@
         <v>1.36</v>
       </c>
       <c r="S61">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="T61">
         <v>1.01</v>
@@ -15997,7 +15997,7 @@
         <v>1.31</v>
       </c>
       <c r="M62">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N62">
         <v>3.6</v>
@@ -16009,7 +16009,7 @@
         <v>1.91</v>
       </c>
       <c r="Q62">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="R62">
         <v>1.31</v>
@@ -16018,10 +16018,10 @@
         <v>3.25</v>
       </c>
       <c r="T62">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U62">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V62">
         <v>1.51</v>
@@ -16218,13 +16218,13 @@
         <v>269</v>
       </c>
       <c r="F63">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="G63">
-        <v>2.92</v>
+        <v>2.72</v>
       </c>
       <c r="H63">
-        <v>2.88</v>
+        <v>2.66</v>
       </c>
       <c r="I63">
         <v>3.8</v>
@@ -16233,7 +16233,7 @@
         <v>3</v>
       </c>
       <c r="K63">
-        <v>4.6</v>
+        <v>5.8</v>
       </c>
       <c r="L63">
         <v>1.32</v>
@@ -16254,10 +16254,10 @@
         <v>1.79</v>
       </c>
       <c r="R63">
-        <v>1.33</v>
+        <v>1.27</v>
       </c>
       <c r="S63">
-        <v>3</v>
+        <v>2.94</v>
       </c>
       <c r="T63">
         <v>1.01</v>
@@ -16269,7 +16269,7 @@
         <v>1.35</v>
       </c>
       <c r="W63">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="X63">
         <v>1000</v>
@@ -16484,7 +16484,7 @@
         <v>1.01</v>
       </c>
       <c r="N64">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="O64">
         <v>1.15</v>
@@ -16947,19 +16947,19 @@
         <v>2.08</v>
       </c>
       <c r="G66">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="H66">
         <v>3.75</v>
       </c>
       <c r="I66">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J66">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K66">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L66">
         <v>1.39</v>
@@ -16968,7 +16968,7 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>2.84</v>
+        <v>2.92</v>
       </c>
       <c r="O66">
         <v>1.02</v>
@@ -16977,7 +16977,7 @@
         <v>1.64</v>
       </c>
       <c r="Q66">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R66">
         <v>1.21</v>
@@ -16992,10 +16992,10 @@
         <v>1.01</v>
       </c>
       <c r="V66">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="W66">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X66">
         <v>1000</v>
@@ -17192,7 +17192,7 @@
         <v>2.4</v>
       </c>
       <c r="H67">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="I67">
         <v>4.3</v>
@@ -17201,7 +17201,7 @@
         <v>3.3</v>
       </c>
       <c r="K67">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L67">
         <v>1.31</v>
@@ -17210,13 +17210,13 @@
         <v>1.01</v>
       </c>
       <c r="N67">
-        <v>1.01</v>
+        <v>2.92</v>
       </c>
       <c r="O67">
         <v>1.3</v>
       </c>
       <c r="P67">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="Q67">
         <v>1.93</v>
@@ -17733,7 +17733,7 @@
         <v>150</v>
       </c>
       <c r="AA69">
-        <v>650</v>
+        <v>620</v>
       </c>
       <c r="AB69">
         <v>12.5</v>
@@ -17787,7 +17787,7 @@
         <v>15</v>
       </c>
       <c r="AS69">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="AT69">
         <v>10.5</v>
@@ -17927,7 +17927,7 @@
         <v>2.62</v>
       </c>
       <c r="K70">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -17936,7 +17936,7 @@
         <v>1.01</v>
       </c>
       <c r="N70">
-        <v>3.45</v>
+        <v>2.44</v>
       </c>
       <c r="O70">
         <v>1.2</v>
@@ -18154,16 +18154,16 @@
         <v>277</v>
       </c>
       <c r="F71">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="G71">
         <v>1.78</v>
       </c>
       <c r="H71">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I71">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J71">
         <v>4</v>
@@ -18175,25 +18175,25 @@
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N71">
         <v>1.01</v>
       </c>
       <c r="O71">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P71">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q71">
         <v>1.67</v>
       </c>
       <c r="R71">
-        <v>1.37</v>
+        <v>1.21</v>
       </c>
       <c r="S71">
-        <v>2.6</v>
+        <v>2.78</v>
       </c>
       <c r="T71">
         <v>1.56</v>
@@ -18202,118 +18202,118 @@
         <v>1.8</v>
       </c>
       <c r="V71">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W71">
         <v>2.28</v>
       </c>
       <c r="X71">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y71">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z71">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AA71">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB71">
-        <v>13</v>
+        <v>10.5</v>
       </c>
       <c r="AC71">
-        <v>13</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD71">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="AE71">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AF71">
+        <v>12</v>
+      </c>
+      <c r="AG71">
+        <v>10.5</v>
+      </c>
+      <c r="AH71">
+        <v>970</v>
+      </c>
+      <c r="AI71">
+        <v>75</v>
+      </c>
+      <c r="AJ71">
+        <v>970</v>
+      </c>
+      <c r="AK71">
+        <v>18</v>
+      </c>
+      <c r="AL71">
+        <v>34</v>
+      </c>
+      <c r="AM71">
+        <v>110</v>
+      </c>
+      <c r="AN71">
+        <v>9.6</v>
+      </c>
+      <c r="AO71">
+        <v>80</v>
+      </c>
+      <c r="AP71">
+        <v>14</v>
+      </c>
+      <c r="AQ71">
+        <v>17</v>
+      </c>
+      <c r="AR71">
+        <v>32</v>
+      </c>
+      <c r="AS71">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AT71">
+        <v>8.4</v>
+      </c>
+      <c r="AU71">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AV71">
+        <v>17.5</v>
+      </c>
+      <c r="AW71">
+        <v>7.8</v>
+      </c>
+      <c r="AX71">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY71">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AZ71">
+        <v>16</v>
+      </c>
+      <c r="BA71">
+        <v>7.8</v>
+      </c>
+      <c r="BB71">
         <v>15.5</v>
       </c>
-      <c r="AG71">
+      <c r="BC71">
         <v>14.5</v>
       </c>
-      <c r="AH71">
-        <v>26</v>
-      </c>
-      <c r="AI71">
-        <v>1000</v>
-      </c>
-      <c r="AJ71">
-        <v>25</v>
-      </c>
-      <c r="AK71">
-        <v>25</v>
-      </c>
-      <c r="AL71">
-        <v>46</v>
-      </c>
-      <c r="AM71">
-        <v>1000</v>
-      </c>
-      <c r="AN71">
-        <v>13</v>
-      </c>
-      <c r="AO71">
-        <v>1000</v>
-      </c>
-      <c r="AP71">
-        <v>2.34</v>
-      </c>
-      <c r="AQ71">
-        <v>13</v>
-      </c>
-      <c r="AR71">
-        <v>2.34</v>
-      </c>
-      <c r="AS71">
-        <v>2.34</v>
-      </c>
-      <c r="AT71">
-        <v>6.4</v>
-      </c>
-      <c r="AU71">
-        <v>1.98</v>
-      </c>
-      <c r="AV71">
-        <v>13.5</v>
-      </c>
-      <c r="AW71">
-        <v>2.34</v>
-      </c>
-      <c r="AX71">
-        <v>7.2</v>
-      </c>
-      <c r="AY71">
-        <v>6.6</v>
-      </c>
-      <c r="AZ71">
-        <v>2.14</v>
-      </c>
-      <c r="BA71">
-        <v>2.34</v>
-      </c>
-      <c r="BB71">
-        <v>11.5</v>
-      </c>
-      <c r="BC71">
-        <v>11</v>
-      </c>
       <c r="BD71">
-        <v>2.22</v>
+        <v>6.8</v>
       </c>
       <c r="BE71">
-        <v>2.34</v>
+        <v>8</v>
       </c>
       <c r="BF71">
-        <v>6.2</v>
+        <v>8</v>
       </c>
       <c r="BG71">
-        <v>2.34</v>
+        <v>7.8</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -18402,7 +18402,7 @@
         <v>3.35</v>
       </c>
       <c r="H72">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="I72">
         <v>2.64</v>
@@ -18456,7 +18456,7 @@
         <v>11.5</v>
       </c>
       <c r="Z72">
-        <v>19.5</v>
+        <v>970</v>
       </c>
       <c r="AA72">
         <v>36</v>
@@ -18513,7 +18513,7 @@
         <v>14.5</v>
       </c>
       <c r="AS72">
-        <v>8.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AT72">
         <v>11</v>
@@ -18525,10 +18525,10 @@
         <v>10</v>
       </c>
       <c r="AW72">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AX72">
-        <v>17.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY72">
         <v>12</v>
@@ -18537,22 +18537,22 @@
         <v>14</v>
       </c>
       <c r="BA72">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB72">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BC72">
-        <v>27</v>
+        <v>9.4</v>
       </c>
       <c r="BD72">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BE72">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF72">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BG72">
         <v>16</v>
@@ -18638,7 +18638,7 @@
         <v>279</v>
       </c>
       <c r="F73">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="G73">
         <v>110</v>
@@ -18662,7 +18662,7 @@
         <v>1.01</v>
       </c>
       <c r="N73">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O73">
         <v>1.09</v>
@@ -18674,7 +18674,7 @@
         <v>1.08</v>
       </c>
       <c r="R73">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S73">
         <v>1.09</v>
@@ -18880,19 +18880,19 @@
         <v>280</v>
       </c>
       <c r="F74">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="G74">
         <v>110</v>
       </c>
       <c r="H74">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="I74">
         <v>110</v>
       </c>
       <c r="J74">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="K74">
         <v>950</v>
@@ -18904,7 +18904,7 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="O74">
         <v>1.13</v>
@@ -18916,7 +18916,7 @@
         <v>1.12</v>
       </c>
       <c r="R74">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S74">
         <v>1.12</v>
@@ -19122,22 +19122,22 @@
         <v>281</v>
       </c>
       <c r="F75">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="G75">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="H75">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I75">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="J75">
         <v>3.15</v>
       </c>
       <c r="K75">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="L75">
         <v>1.01</v>
@@ -19164,16 +19164,16 @@
         <v>3.15</v>
       </c>
       <c r="T75">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="U75">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V75">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="W75">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="X75">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-07.xlsx
@@ -862,7 +862,7 @@
     <t>Cusco FC</t>
   </si>
   <si>
-    <t>2026-08-05 21:13:17</t>
+    <t>2026-08-05 23:23:14</t>
   </si>
 </sst>
 </file>
@@ -1456,7 +1456,7 @@
         <v>208</v>
       </c>
       <c r="F2">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="G2">
         <v>1.78</v>
@@ -1465,22 +1465,22 @@
         <v>6</v>
       </c>
       <c r="I2">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="K2">
         <v>4</v>
       </c>
       <c r="L2">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M2">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N2">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O2">
         <v>1.4</v>
@@ -1489,31 +1489,31 @@
         <v>1.72</v>
       </c>
       <c r="Q2">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R2">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="S2">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="T2">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U2">
         <v>1.77</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
         <v>2.28</v>
       </c>
       <c r="X2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Z2">
         <v>65</v>
@@ -1534,10 +1534,10 @@
         <v>140</v>
       </c>
       <c r="AF2">
+        <v>11.5</v>
+      </c>
+      <c r="AG2">
         <v>11</v>
-      </c>
-      <c r="AG2">
-        <v>12.5</v>
       </c>
       <c r="AH2">
         <v>27</v>
@@ -1564,28 +1564,28 @@
         <v>220</v>
       </c>
       <c r="AP2">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
       <c r="AQ2">
-        <v>4.3</v>
+        <v>13</v>
       </c>
       <c r="AR2">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
       <c r="AS2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="AT2">
         <v>5.2</v>
       </c>
       <c r="AU2">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="AV2">
         <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="AX2">
         <v>6.8</v>
@@ -1594,49 +1594,49 @@
         <v>7.6</v>
       </c>
       <c r="AZ2">
-        <v>4.5</v>
+        <v>21</v>
       </c>
       <c r="BA2">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB2">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="BC2">
-        <v>4.4</v>
+        <v>5.1</v>
       </c>
       <c r="BD2">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="BE2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BF2">
         <v>10</v>
       </c>
       <c r="BG2">
-        <v>5.2</v>
+        <v>5.6</v>
       </c>
       <c r="BH2">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="BI2">
-        <v>2.52</v>
+        <v>2.48</v>
       </c>
       <c r="BJ2">
         <v>14</v>
       </c>
       <c r="BK2">
-        <v>3.6</v>
+        <v>8.6</v>
       </c>
       <c r="BL2">
         <v>1000</v>
       </c>
       <c r="BM2">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BN2">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="BO2">
         <v>3.15</v>
@@ -1645,31 +1645,31 @@
         <v>14.5</v>
       </c>
       <c r="BQ2">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="BR2">
         <v>40</v>
       </c>
       <c r="BS2">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
       <c r="BT2">
         <v>11.5</v>
       </c>
       <c r="BU2">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="BV2">
         <v>80</v>
       </c>
       <c r="BW2">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BX2">
         <v>90</v>
       </c>
       <c r="BY2">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="BZ2">
         <v>0</v>
@@ -1943,7 +1943,7 @@
         <v>2.44</v>
       </c>
       <c r="G4">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="H4">
         <v>3.25</v>
@@ -1952,7 +1952,7 @@
         <v>3.4</v>
       </c>
       <c r="J4">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K4">
         <v>3.4</v>
@@ -1997,10 +1997,10 @@
         <v>13.5</v>
       </c>
       <c r="Y4">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Z4">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AA4">
         <v>60</v>
@@ -2057,7 +2057,7 @@
         <v>20</v>
       </c>
       <c r="AS4">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AT4">
         <v>8.800000000000001</v>
@@ -2078,28 +2078,28 @@
         <v>10</v>
       </c>
       <c r="AZ4">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="BA4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BB4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BC4">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="BD4">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BE4">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BF4">
         <v>20</v>
       </c>
       <c r="BG4">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH4">
         <v>3.25</v>
@@ -2200,7 +2200,7 @@
         <v>3.85</v>
       </c>
       <c r="L5">
-        <v>1.46</v>
+        <v>1.38</v>
       </c>
       <c r="M5">
         <v>1.08</v>
@@ -2218,7 +2218,7 @@
         <v>2.14</v>
       </c>
       <c r="R5">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S5">
         <v>3.9</v>
@@ -2430,10 +2430,10 @@
         <v>4.7</v>
       </c>
       <c r="H6">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="I6">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="J6">
         <v>3.65</v>
@@ -2442,7 +2442,7 @@
         <v>4.5</v>
       </c>
       <c r="L6">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="M6">
         <v>1.07</v>
@@ -2472,7 +2472,7 @@
         <v>2.04</v>
       </c>
       <c r="V6">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="W6">
         <v>1.27</v>
@@ -2735,7 +2735,7 @@
         <v>21</v>
       </c>
       <c r="AC7">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AD7">
         <v>12</v>
@@ -2777,28 +2777,28 @@
         <v>13.5</v>
       </c>
       <c r="AQ7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AR7">
         <v>11</v>
       </c>
       <c r="AS7">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="AT7">
         <v>15</v>
       </c>
       <c r="AU7">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AV7">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW7">
         <v>14</v>
       </c>
       <c r="AX7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AY7">
         <v>13.5</v>
@@ -2807,25 +2807,25 @@
         <v>13</v>
       </c>
       <c r="BA7">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BB7">
+        <v>5.3</v>
+      </c>
+      <c r="BC7">
         <v>5</v>
       </c>
-      <c r="BC7">
-        <v>4.8</v>
-      </c>
       <c r="BD7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BE7">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="BF7">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BG7">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH7">
         <v>3.8</v>
@@ -2950,7 +2950,7 @@
         <v>2.84</v>
       </c>
       <c r="T8">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="U8">
         <v>2.26</v>
@@ -2983,7 +2983,7 @@
         <v>13.5</v>
       </c>
       <c r="AE8">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="AF8">
         <v>27</v>
@@ -3022,10 +3022,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AR8">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AT8">
         <v>10.5</v>
@@ -3049,19 +3049,19 @@
         <v>12.5</v>
       </c>
       <c r="BA8">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BB8">
+        <v>4.7</v>
+      </c>
+      <c r="BC8">
+        <v>4.5</v>
+      </c>
+      <c r="BD8">
         <v>4.6</v>
       </c>
-      <c r="BC8">
-        <v>4.4</v>
-      </c>
-      <c r="BD8">
-        <v>4.5</v>
-      </c>
       <c r="BE8">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BF8">
         <v>20</v>
@@ -3150,7 +3150,7 @@
         <v>215</v>
       </c>
       <c r="F9">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G9">
         <v>1.64</v>
@@ -3183,7 +3183,7 @@
         <v>2.06</v>
       </c>
       <c r="Q9">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R9">
         <v>1.41</v>
@@ -3267,10 +3267,10 @@
         <v>4.8</v>
       </c>
       <c r="AS9">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AT9">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AU9">
         <v>7.8</v>
@@ -3524,7 +3524,7 @@
         <v>8.4</v>
       </c>
       <c r="AX10">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AY10">
         <v>8.199999999999999</v>
@@ -3664,7 +3664,7 @@
         <v>1.12</v>
       </c>
       <c r="P11">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q11">
         <v>1.35</v>
@@ -3799,7 +3799,7 @@
         <v>6.2</v>
       </c>
       <c r="BI11">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BJ11">
         <v>11.5</v>
@@ -3814,7 +3814,7 @@
         <v>5</v>
       </c>
       <c r="BN11">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BO11">
         <v>3.65</v>
@@ -3826,7 +3826,7 @@
         <v>3.4</v>
       </c>
       <c r="BR11">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BS11">
         <v>4.2</v>
@@ -3844,7 +3844,7 @@
         <v>4.9</v>
       </c>
       <c r="BX11">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BY11">
         <v>4.8</v>
@@ -3853,7 +3853,7 @@
         <v>10.5</v>
       </c>
       <c r="CA11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="CB11" t="s">
         <v>282</v>
@@ -3876,58 +3876,58 @@
         <v>218</v>
       </c>
       <c r="F12">
-        <v>1.68</v>
+        <v>1.57</v>
       </c>
       <c r="G12">
-        <v>1.79</v>
+        <v>1.89</v>
       </c>
       <c r="H12">
-        <v>5.1</v>
+        <v>4.1</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J12">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="K12">
-        <v>4.5</v>
+        <v>8.4</v>
       </c>
       <c r="L12">
         <v>1.28</v>
       </c>
       <c r="M12">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="N12">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="O12">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="P12">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="Q12">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="S12">
         <v>2.54</v>
       </c>
       <c r="T12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U12">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V12">
-        <v>1.18</v>
+        <v>1.16</v>
       </c>
       <c r="W12">
-        <v>2.26</v>
+        <v>2.12</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4118,7 +4118,7 @@
         <v>219</v>
       </c>
       <c r="F13">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="G13">
         <v>3.1</v>
@@ -4468,10 +4468,10 @@
         <v>80</v>
       </c>
       <c r="AP14">
-        <v>9.800000000000001</v>
+        <v>4.1</v>
       </c>
       <c r="AQ14">
-        <v>10.5</v>
+        <v>4.3</v>
       </c>
       <c r="AR14">
         <v>5</v>
@@ -4480,34 +4480,34 @@
         <v>5.5</v>
       </c>
       <c r="AT14">
-        <v>6.4</v>
+        <v>3.55</v>
       </c>
       <c r="AU14">
-        <v>6.8</v>
+        <v>3.6</v>
       </c>
       <c r="AV14">
-        <v>13</v>
+        <v>4.5</v>
       </c>
       <c r="AW14">
         <v>5.4</v>
       </c>
       <c r="AX14">
-        <v>9.6</v>
+        <v>4</v>
       </c>
       <c r="AY14">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="AZ14">
-        <v>15</v>
+        <v>4.6</v>
       </c>
       <c r="BA14">
         <v>5.4</v>
       </c>
       <c r="BB14">
-        <v>19.5</v>
+        <v>4.8</v>
       </c>
       <c r="BC14">
-        <v>18</v>
+        <v>4.7</v>
       </c>
       <c r="BD14">
         <v>5.2</v>
@@ -4516,7 +4516,7 @@
         <v>5.6</v>
       </c>
       <c r="BF14">
-        <v>14</v>
+        <v>4.5</v>
       </c>
       <c r="BG14">
         <v>5.4</v>
@@ -4611,10 +4611,10 @@
         <v>4.7</v>
       </c>
       <c r="I15">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
         <v>4.6</v>
@@ -4626,7 +4626,7 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.01</v>
+        <v>1.1</v>
       </c>
       <c r="O15">
         <v>1.22</v>
@@ -4644,10 +4644,10 @@
         <v>2.66</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V15">
         <v>1.18</v>
@@ -4844,22 +4844,22 @@
         <v>222</v>
       </c>
       <c r="F16">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G16">
         <v>3.1</v>
       </c>
       <c r="H16">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="I16">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="J16">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4868,7 +4868,7 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
         <v>1.22</v>
@@ -5086,10 +5086,10 @@
         <v>223</v>
       </c>
       <c r="F17">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G17">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="H17">
         <v>5.2</v>
@@ -5098,10 +5098,10 @@
         <v>10.5</v>
       </c>
       <c r="J17">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K17">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="L17">
         <v>1.29</v>
@@ -5122,16 +5122,16 @@
         <v>1.8</v>
       </c>
       <c r="R17">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="S17">
         <v>2.74</v>
       </c>
       <c r="T17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V17">
         <v>1.1</v>
@@ -5349,7 +5349,7 @@
         <v>1.01</v>
       </c>
       <c r="M18">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N18">
         <v>4.4</v>
@@ -5373,7 +5373,7 @@
         <v>1.43</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V18">
         <v>1.01</v>
@@ -5582,7 +5582,7 @@
         <v>6.8</v>
       </c>
       <c r="J19">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
         <v>4.9</v>
@@ -5812,22 +5812,22 @@
         <v>226</v>
       </c>
       <c r="F20">
-        <v>4.4</v>
+        <v>1.04</v>
       </c>
       <c r="G20">
-        <v>6.4</v>
+        <v>990</v>
       </c>
       <c r="H20">
-        <v>1.65</v>
+        <v>1.04</v>
       </c>
       <c r="I20">
-        <v>1.96</v>
+        <v>990</v>
       </c>
       <c r="J20">
-        <v>3.55</v>
+        <v>1.04</v>
       </c>
       <c r="K20">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5848,130 +5848,130 @@
         <v>1.26</v>
       </c>
       <c r="R20">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="S20">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="T20">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U20">
-        <v>1.96</v>
+        <v>1.11</v>
       </c>
       <c r="V20">
-        <v>2.04</v>
+        <v>1.02</v>
       </c>
       <c r="W20">
-        <v>1.18</v>
+        <v>1.02</v>
       </c>
       <c r="X20">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>4.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>4.8</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
         <v>1000</v>
@@ -6057,7 +6057,7 @@
         <v>1.58</v>
       </c>
       <c r="G21">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="H21">
         <v>5.3</v>
@@ -6066,7 +6066,7 @@
         <v>6.4</v>
       </c>
       <c r="J21">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K21">
         <v>4.9</v>
@@ -6084,28 +6084,28 @@
         <v>1.23</v>
       </c>
       <c r="P21">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="Q21">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R21">
         <v>1.47</v>
       </c>
       <c r="S21">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="T21">
-        <v>1.74</v>
+        <v>1.11</v>
       </c>
       <c r="U21">
-        <v>2.1</v>
+        <v>1.11</v>
       </c>
       <c r="V21">
         <v>1.18</v>
       </c>
       <c r="W21">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="X21">
         <v>25</v>
@@ -6162,10 +6162,10 @@
         <v>90</v>
       </c>
       <c r="AP21">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ21">
-        <v>16.5</v>
+        <v>3.7</v>
       </c>
       <c r="AR21">
         <v>4</v>
@@ -6180,28 +6180,28 @@
         <v>7.6</v>
       </c>
       <c r="AV21">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="AW21">
         <v>4</v>
       </c>
       <c r="AX21">
-        <v>8</v>
+        <v>7.6</v>
       </c>
       <c r="AY21">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AZ21">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BA21">
         <v>4</v>
       </c>
       <c r="BB21">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC21">
-        <v>12</v>
+        <v>3.5</v>
       </c>
       <c r="BD21">
         <v>3.85</v>
@@ -6299,7 +6299,7 @@
         <v>1.91</v>
       </c>
       <c r="G22">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="H22">
         <v>3.5</v>
@@ -6347,7 +6347,7 @@
         <v>1.28</v>
       </c>
       <c r="W22">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="X22">
         <v>1000</v>
@@ -6541,13 +6541,13 @@
         <v>1.97</v>
       </c>
       <c r="G23">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H23">
         <v>3.35</v>
       </c>
       <c r="I23">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J23">
         <v>3.95</v>
@@ -6783,10 +6783,10 @@
         <v>1.46</v>
       </c>
       <c r="G24">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="H24">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="I24">
         <v>8.199999999999999</v>
@@ -6795,7 +6795,7 @@
         <v>4.8</v>
       </c>
       <c r="K24">
-        <v>6.2</v>
+        <v>5.5</v>
       </c>
       <c r="L24">
         <v>1.01</v>
@@ -6810,13 +6810,13 @@
         <v>1.13</v>
       </c>
       <c r="P24">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="Q24">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="R24">
-        <v>1.61</v>
+        <v>1.48</v>
       </c>
       <c r="S24">
         <v>2.14</v>
@@ -6831,7 +6831,7 @@
         <v>1.14</v>
       </c>
       <c r="W24">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="X24">
         <v>38</v>
@@ -6936,7 +6936,7 @@
         <v>2.64</v>
       </c>
       <c r="BF24">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="BG24">
         <v>2.64</v>
@@ -6945,7 +6945,7 @@
         <v>5.8</v>
       </c>
       <c r="BI24">
-        <v>3.4</v>
+        <v>3.15</v>
       </c>
       <c r="BJ24">
         <v>13.5</v>
@@ -7037,7 +7037,7 @@
         <v>4.3</v>
       </c>
       <c r="K25">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="L25">
         <v>1.01</v>
@@ -7064,10 +7064,10 @@
         <v>2.4</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V25">
         <v>1.07</v>
@@ -7288,13 +7288,13 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O26">
         <v>1.28</v>
       </c>
       <c r="P26">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="Q26">
         <v>1.86</v>
@@ -7509,16 +7509,16 @@
         <v>1.04</v>
       </c>
       <c r="G27">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H27">
         <v>1.04</v>
       </c>
       <c r="I27">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J27">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K27">
         <v>950</v>
@@ -7539,7 +7539,7 @@
         <v>1.25</v>
       </c>
       <c r="Q27">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="R27">
         <v>1.25</v>
@@ -7548,16 +7548,16 @@
         <v>1.23</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V27">
         <v>1.02</v>
       </c>
       <c r="W27">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7796,7 +7796,7 @@
         <v>2.32</v>
       </c>
       <c r="V28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W28">
         <v>1.84</v>
@@ -7805,7 +7805,7 @@
         <v>19</v>
       </c>
       <c r="Y28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="Z28">
         <v>34</v>
@@ -7814,25 +7814,25 @@
         <v>80</v>
       </c>
       <c r="AB28">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AC28">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AD28">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AE28">
         <v>48</v>
       </c>
       <c r="AF28">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AG28">
-        <v>12.5</v>
+        <v>13.5</v>
       </c>
       <c r="AH28">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AI28">
         <v>55</v>
@@ -7841,7 +7841,7 @@
         <v>32</v>
       </c>
       <c r="AK28">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AL28">
         <v>38</v>
@@ -7850,7 +7850,7 @@
         <v>75</v>
       </c>
       <c r="AN28">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AO28">
         <v>38</v>
@@ -7865,7 +7865,7 @@
         <v>23</v>
       </c>
       <c r="AS28">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="AT28">
         <v>10</v>
@@ -7877,7 +7877,7 @@
         <v>13</v>
       </c>
       <c r="AW28">
-        <v>32</v>
+        <v>4.1</v>
       </c>
       <c r="AX28">
         <v>13</v>
@@ -7889,25 +7889,25 @@
         <v>14</v>
       </c>
       <c r="BA28">
-        <v>36</v>
+        <v>4.2</v>
       </c>
       <c r="BB28">
-        <v>4.7</v>
+        <v>3.95</v>
       </c>
       <c r="BC28">
         <v>18.5</v>
       </c>
       <c r="BD28">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="BE28">
-        <v>5.1</v>
+        <v>4.3</v>
       </c>
       <c r="BF28">
         <v>9.6</v>
       </c>
       <c r="BG28">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -7990,7 +7990,7 @@
         <v>235</v>
       </c>
       <c r="F29">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="G29">
         <v>3.25</v>
@@ -8498,7 +8498,7 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O31">
         <v>1.28</v>
@@ -8639,19 +8639,19 @@
         <v>1000</v>
       </c>
       <c r="BI31">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="BJ31">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BK31">
-        <v>1.64</v>
+        <v>1.43</v>
       </c>
       <c r="BL31">
         <v>1000</v>
       </c>
       <c r="BM31">
-        <v>1.87</v>
+        <v>1.61</v>
       </c>
       <c r="BN31">
         <v>7.8</v>
@@ -8660,16 +8660,16 @@
         <v>3.95</v>
       </c>
       <c r="BP31">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="BQ31">
-        <v>1.76</v>
+        <v>1.61</v>
       </c>
       <c r="BR31">
         <v>46</v>
       </c>
       <c r="BS31">
-        <v>1.8</v>
+        <v>1.56</v>
       </c>
       <c r="BT31">
         <v>8</v>
@@ -8678,22 +8678,22 @@
         <v>4.3</v>
       </c>
       <c r="BV31">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="BW31">
-        <v>1.77</v>
+        <v>1.61</v>
       </c>
       <c r="BX31">
         <v>48</v>
       </c>
       <c r="BY31">
-        <v>1.81</v>
+        <v>1.56</v>
       </c>
       <c r="BZ31">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA31">
-        <v>1.79</v>
+        <v>1.61</v>
       </c>
       <c r="CB31" t="s">
         <v>282</v>
@@ -8917,7 +8917,7 @@
         <v>7.4</v>
       </c>
       <c r="BU32">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BV32">
         <v>21</v>
@@ -9445,10 +9445,10 @@
         <v>3.45</v>
       </c>
       <c r="G35">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H35">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="I35">
         <v>2.1</v>
@@ -9484,10 +9484,10 @@
         <v>2.16</v>
       </c>
       <c r="T35">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="U35">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V35">
         <v>1.9</v>
@@ -9717,7 +9717,7 @@
         <v>2.42</v>
       </c>
       <c r="Q36">
-        <v>1.49</v>
+        <v>1.57</v>
       </c>
       <c r="R36">
         <v>1.5</v>
@@ -9726,10 +9726,10 @@
         <v>2.16</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V36">
         <v>1.32</v>
@@ -9738,49 +9738,49 @@
         <v>1.89</v>
       </c>
       <c r="X36">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y36">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="Z36">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AA36">
         <v>1000</v>
       </c>
       <c r="AB36">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC36">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD36">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AE36">
         <v>1000</v>
       </c>
       <c r="AF36">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG36">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AI36">
         <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK36">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AL36">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM36">
         <v>1000</v>
@@ -9792,49 +9792,49 @@
         <v>1000</v>
       </c>
       <c r="AP36">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
         <v>1.03</v>
       </c>
       <c r="AT36">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
         <v>1.03</v>
       </c>
       <c r="AX36">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
         <v>1.03</v>
       </c>
       <c r="BB36">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC36">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE36">
         <v>1.03</v>
@@ -10019,7 +10019,7 @@
         <v>38</v>
       </c>
       <c r="AK37">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AL37">
         <v>32</v>
@@ -10067,7 +10067,7 @@
         <v>12.5</v>
       </c>
       <c r="BA37">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BB37">
         <v>6.4</v>
@@ -10127,7 +10127,7 @@
         <v>8.6</v>
       </c>
       <c r="BU37">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="BV37">
         <v>28</v>
@@ -10413,16 +10413,16 @@
         <v>1.6</v>
       </c>
       <c r="G39">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="H39">
-        <v>1.04</v>
+        <v>3.05</v>
       </c>
       <c r="I39">
-        <v>110</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="J39">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="K39">
         <v>950</v>
@@ -10446,10 +10446,10 @@
         <v>1.69</v>
       </c>
       <c r="R39">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S39">
-        <v>2.2</v>
+        <v>2.68</v>
       </c>
       <c r="T39">
         <v>1.01</v>
@@ -10458,10 +10458,10 @@
         <v>1.01</v>
       </c>
       <c r="V39">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="W39">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="X39">
         <v>1000</v>
@@ -10676,7 +10676,7 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
         <v>1.14</v>
@@ -10685,19 +10685,19 @@
         <v>2.6</v>
       </c>
       <c r="Q40">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R40">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="S40">
         <v>2.02</v>
       </c>
       <c r="T40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U40">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V40">
         <v>1.47</v>
@@ -11136,7 +11136,7 @@
         <v>248</v>
       </c>
       <c r="F42">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G42">
         <v>3.2</v>
@@ -11160,7 +11160,7 @@
         <v>1.01</v>
       </c>
       <c r="N42">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="O42">
         <v>1.19</v>
@@ -11390,7 +11390,7 @@
         <v>3.15</v>
       </c>
       <c r="J43">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="K43">
         <v>4.3</v>
@@ -11399,19 +11399,19 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N43">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O43">
         <v>1.19</v>
       </c>
       <c r="P43">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="Q43">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R43">
         <v>1.54</v>
@@ -11420,10 +11420,10 @@
         <v>2.38</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V43">
         <v>1.46</v>
@@ -11653,7 +11653,7 @@
         <v>2.78</v>
       </c>
       <c r="Q44">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="R44">
         <v>1.71</v>
@@ -11865,19 +11865,19 @@
         <v>1.35</v>
       </c>
       <c r="G45">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="H45">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="I45">
         <v>12.5</v>
       </c>
       <c r="J45">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="K45">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11892,7 +11892,7 @@
         <v>1.26</v>
       </c>
       <c r="P45">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="Q45">
         <v>1.78</v>
@@ -11913,7 +11913,7 @@
         <v>1.08</v>
       </c>
       <c r="W45">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="X45">
         <v>1000</v>
@@ -12104,22 +12104,22 @@
         <v>252</v>
       </c>
       <c r="F46">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G46">
         <v>2.8</v>
       </c>
       <c r="H46">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="I46">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="J46">
         <v>3.85</v>
       </c>
       <c r="K46">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12131,31 +12131,31 @@
         <v>5.1</v>
       </c>
       <c r="O46">
-        <v>1.13</v>
+        <v>1.16</v>
       </c>
       <c r="P46">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="Q46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R46">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="S46">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="T46">
         <v>1.36</v>
       </c>
       <c r="U46">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V46">
         <v>1.55</v>
       </c>
       <c r="W46">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12358,7 +12358,7 @@
         <v>9.6</v>
       </c>
       <c r="J47">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="K47">
         <v>5.7</v>
@@ -12388,10 +12388,10 @@
         <v>2.12</v>
       </c>
       <c r="T47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U47">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V47">
         <v>1.12</v>
@@ -12597,10 +12597,10 @@
         <v>1.47</v>
       </c>
       <c r="I48">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="J48">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K48">
         <v>5.2</v>
@@ -12636,7 +12636,7 @@
         <v>1.94</v>
       </c>
       <c r="V48">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="W48">
         <v>1.14</v>
@@ -12702,7 +12702,7 @@
         <v>6.8</v>
       </c>
       <c r="AR48">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AS48">
         <v>10</v>
@@ -12711,22 +12711,22 @@
         <v>18.5</v>
       </c>
       <c r="AU48">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AV48">
         <v>7.4</v>
       </c>
       <c r="AW48">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AX48">
         <v>4.2</v>
       </c>
       <c r="AY48">
-        <v>3.95</v>
+        <v>20</v>
       </c>
       <c r="AZ48">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BA48">
         <v>4</v>
@@ -12836,10 +12836,10 @@
         <v>2.62</v>
       </c>
       <c r="H49">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I49">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J49">
         <v>3.2</v>
@@ -12851,22 +12851,22 @@
         <v>1.33</v>
       </c>
       <c r="M49">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N49">
         <v>3.4</v>
       </c>
       <c r="O49">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="P49">
         <v>1.84</v>
       </c>
       <c r="Q49">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="R49">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S49">
         <v>3.45</v>
@@ -12878,7 +12878,7 @@
         <v>2.08</v>
       </c>
       <c r="V49">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W49">
         <v>1.61</v>
@@ -13102,13 +13102,13 @@
         <v>1.24</v>
       </c>
       <c r="P50">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="Q50">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="R50">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="S50">
         <v>2.68</v>
@@ -13326,7 +13326,7 @@
         <v>3.3</v>
       </c>
       <c r="J51">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="K51">
         <v>3.9</v>
@@ -13365,7 +13365,7 @@
         <v>1.44</v>
       </c>
       <c r="W51">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="X51">
         <v>26</v>
@@ -13565,7 +13565,7 @@
         <v>5.1</v>
       </c>
       <c r="I52">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J52">
         <v>4.2</v>
@@ -13831,7 +13831,7 @@
         <v>1.97</v>
       </c>
       <c r="Q53">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="R53">
         <v>1.31</v>
@@ -14070,7 +14070,7 @@
         <v>1.25</v>
       </c>
       <c r="P54">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="Q54">
         <v>1.68</v>
@@ -14285,13 +14285,13 @@
         <v>2.74</v>
       </c>
       <c r="G55">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="H55">
         <v>2.06</v>
       </c>
       <c r="I55">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="J55">
         <v>2.96</v>
@@ -14306,7 +14306,7 @@
         <v>1.01</v>
       </c>
       <c r="N55">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O55">
         <v>1.01</v>
@@ -14324,16 +14324,16 @@
         <v>2.56</v>
       </c>
       <c r="T55">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U55">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V55">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="W55">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X55">
         <v>1000</v>
@@ -14566,16 +14566,16 @@
         <v>2.4</v>
       </c>
       <c r="T56">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U56">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V56">
         <v>1.06</v>
       </c>
       <c r="W56">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="X56">
         <v>1000</v>
@@ -14778,7 +14778,7 @@
         <v>1.56</v>
       </c>
       <c r="J57">
-        <v>3.75</v>
+        <v>4.6</v>
       </c>
       <c r="K57">
         <v>5.7</v>
@@ -15020,7 +15020,7 @@
         <v>5</v>
       </c>
       <c r="J58">
-        <v>3.6</v>
+        <v>3.25</v>
       </c>
       <c r="K58">
         <v>4.1</v>
@@ -15253,16 +15253,16 @@
         <v>1.02</v>
       </c>
       <c r="G59">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H59">
         <v>1.02</v>
       </c>
       <c r="I59">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J59">
-        <v>1.03</v>
+        <v>1.11</v>
       </c>
       <c r="K59">
         <v>950</v>
@@ -15280,7 +15280,7 @@
         <v>1.01</v>
       </c>
       <c r="P59">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="Q59">
         <v>1.27</v>
@@ -15292,10 +15292,10 @@
         <v>1.27</v>
       </c>
       <c r="T59">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U59">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V59">
         <v>1.01</v>
@@ -15534,10 +15534,10 @@
         <v>2.78</v>
       </c>
       <c r="T60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U60">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V60">
         <v>1.11</v>
@@ -15776,10 +15776,10 @@
         <v>2.64</v>
       </c>
       <c r="T61">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U61">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V61">
         <v>1.26</v>
@@ -15979,7 +15979,7 @@
         <v>2.68</v>
       </c>
       <c r="G62">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="H62">
         <v>2.58</v>
@@ -16944,10 +16944,10 @@
         <v>272</v>
       </c>
       <c r="F66">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G66">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="H66">
         <v>3.75</v>
@@ -16956,10 +16956,10 @@
         <v>4.7</v>
       </c>
       <c r="J66">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K66">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="L66">
         <v>1.39</v>
@@ -16968,10 +16968,10 @@
         <v>1.01</v>
       </c>
       <c r="N66">
-        <v>2.92</v>
+        <v>2.84</v>
       </c>
       <c r="O66">
-        <v>1.02</v>
+        <v>1.4</v>
       </c>
       <c r="P66">
         <v>1.64</v>
@@ -16986,10 +16986,10 @@
         <v>2.6</v>
       </c>
       <c r="T66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U66">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V66">
         <v>1.27</v>
@@ -17213,7 +17213,7 @@
         <v>2.92</v>
       </c>
       <c r="O67">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P67">
         <v>1.88</v>
@@ -17670,7 +17670,7 @@
         <v>275</v>
       </c>
       <c r="F69">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="G69">
         <v>1.28</v>
@@ -17679,7 +17679,7 @@
         <v>11.5</v>
       </c>
       <c r="I69">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="J69">
         <v>7.4</v>
@@ -17691,7 +17691,7 @@
         <v>1.01</v>
       </c>
       <c r="M69">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N69">
         <v>6.6</v>
@@ -17700,7 +17700,7 @@
         <v>1.15</v>
       </c>
       <c r="P69">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q69">
         <v>1.45</v>
@@ -17912,7 +17912,7 @@
         <v>276</v>
       </c>
       <c r="F70">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G70">
         <v>1.57</v>
@@ -17921,13 +17921,13 @@
         <v>7.6</v>
       </c>
       <c r="I70">
-        <v>170</v>
+        <v>990</v>
       </c>
       <c r="J70">
         <v>2.62</v>
       </c>
       <c r="K70">
-        <v>7.6</v>
+        <v>5.5</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -17954,10 +17954,10 @@
         <v>2.32</v>
       </c>
       <c r="T70">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U70">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V70">
         <v>1.04</v>
@@ -18175,25 +18175,25 @@
         <v>1.01</v>
       </c>
       <c r="M71">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N71">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="O71">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P71">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q71">
-        <v>1.67</v>
+        <v>1.77</v>
       </c>
       <c r="R71">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="S71">
-        <v>2.78</v>
+        <v>2.62</v>
       </c>
       <c r="T71">
         <v>1.56</v>
@@ -18208,7 +18208,7 @@
         <v>2.28</v>
       </c>
       <c r="X71">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y71">
         <v>21</v>
@@ -18220,19 +18220,19 @@
         <v>140</v>
       </c>
       <c r="AB71">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AC71">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD71">
         <v>21</v>
       </c>
       <c r="AE71">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AF71">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG71">
         <v>10.5</v>
@@ -18244,7 +18244,7 @@
         <v>75</v>
       </c>
       <c r="AJ71">
-        <v>970</v>
+        <v>18</v>
       </c>
       <c r="AK71">
         <v>18</v>
@@ -18271,7 +18271,7 @@
         <v>32</v>
       </c>
       <c r="AS71">
-        <v>8.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT71">
         <v>8.4</v>
@@ -18280,10 +18280,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AV71">
-        <v>17.5</v>
+        <v>16</v>
       </c>
       <c r="AW71">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX71">
         <v>9.800000000000001</v>
@@ -18292,10 +18292,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AZ71">
-        <v>16</v>
+        <v>6.4</v>
       </c>
       <c r="BA71">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BB71">
         <v>15.5</v>
@@ -18304,16 +18304,16 @@
         <v>14.5</v>
       </c>
       <c r="BD71">
-        <v>6.8</v>
+        <v>27</v>
       </c>
       <c r="BE71">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF71">
         <v>8</v>
       </c>
       <c r="BG71">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BH71">
         <v>1000</v>
@@ -18402,13 +18402,13 @@
         <v>3.35</v>
       </c>
       <c r="H72">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I72">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="J72">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K72">
         <v>3.6</v>
@@ -18432,10 +18432,10 @@
         <v>1.94</v>
       </c>
       <c r="R72">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S72">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="T72">
         <v>1.73</v>
@@ -18444,10 +18444,10 @@
         <v>2.18</v>
       </c>
       <c r="V72">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W72">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="X72">
         <v>970</v>
@@ -18456,7 +18456,7 @@
         <v>11.5</v>
       </c>
       <c r="Z72">
-        <v>970</v>
+        <v>19.5</v>
       </c>
       <c r="AA72">
         <v>36</v>
@@ -18513,7 +18513,7 @@
         <v>14.5</v>
       </c>
       <c r="AS72">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT72">
         <v>11</v>
@@ -18528,7 +18528,7 @@
         <v>19</v>
       </c>
       <c r="AX72">
-        <v>8.199999999999999</v>
+        <v>7.8</v>
       </c>
       <c r="AY72">
         <v>12</v>
@@ -18537,22 +18537,22 @@
         <v>14</v>
       </c>
       <c r="BA72">
-        <v>9.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BB72">
-        <v>10.5</v>
+        <v>9.6</v>
       </c>
       <c r="BC72">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD72">
         <v>9.4</v>
       </c>
-      <c r="BD72">
+      <c r="BE72">
         <v>10</v>
       </c>
-      <c r="BE72">
-        <v>11</v>
-      </c>
       <c r="BF72">
-        <v>9.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BG72">
         <v>16</v>
@@ -18579,7 +18579,7 @@
         <v>8.6</v>
       </c>
       <c r="BO72">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="BP72">
         <v>34</v>
@@ -18597,7 +18597,7 @@
         <v>7.4</v>
       </c>
       <c r="BU72">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="BV72">
         <v>25</v>
@@ -18638,7 +18638,7 @@
         <v>279</v>
       </c>
       <c r="F73">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="G73">
         <v>110</v>
@@ -18650,7 +18650,7 @@
         <v>110</v>
       </c>
       <c r="J73">
-        <v>1.12</v>
+        <v>3.95</v>
       </c>
       <c r="K73">
         <v>950</v>
@@ -18686,7 +18686,7 @@
         <v>1.01</v>
       </c>
       <c r="V73">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W73">
         <v>1.1</v>
@@ -18880,19 +18880,19 @@
         <v>280</v>
       </c>
       <c r="F74">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="G74">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="H74">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="I74">
-        <v>110</v>
+        <v>990</v>
       </c>
       <c r="J74">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="K74">
         <v>950</v>
@@ -18904,13 +18904,13 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="O74">
         <v>1.13</v>
       </c>
       <c r="P74">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="Q74">
         <v>1.12</v>
@@ -18922,10 +18922,10 @@
         <v>1.12</v>
       </c>
       <c r="T74">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="U74">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="V74">
         <v>1.02</v>
